--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="465">
   <si>
     <t>Component list</t>
   </si>
@@ -976,9 +976,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -1355,12 +1352,6 @@
   </si>
   <si>
     <t>RES SMD 22HM 1/10W 0603</t>
-  </si>
-  <si>
-    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, CF1, CF2</t>
-  </si>
-  <si>
-    <t>Quantity changed from 9 to 13. C15, C20 and C40 merged into this due to same value. C55 changed from 1uF to 0.1uF</t>
   </si>
   <si>
     <t>C5, C6, C14, C23, C24, C29, C34, C35</t>
@@ -1548,6 +1539,24 @@
         <scheme val="minor"/>
       </rPr>
       <t>R31</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantity changed from 13 to 15. C15, C20 and C40 merged into this due to same value. C55 changed from 1uF to 0.1uF. Cx1 and Cx2 added due to U8</t>
+  </si>
+  <si>
+    <r>
+      <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, CF1, CF2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cx1, Cx2</t>
     </r>
   </si>
 </sst>
@@ -2729,7 +2738,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R89"/>
+  <dimension ref="A1:AB89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
@@ -2778,7 +2787,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2802,7 +2811,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -2826,7 +2835,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -2929,7 +2938,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
@@ -2947,10 +2956,10 @@
         <v>226</v>
       </c>
       <c r="I9" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="J9" s="29" t="s">
         <v>336</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>337</v>
       </c>
       <c r="K9" s="30" t="s">
         <v>260</v>
@@ -2959,22 +2968,22 @@
         <v>307</v>
       </c>
       <c r="M9" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="N9" s="31" t="s">
         <v>338</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="O9" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="P9" s="31" t="s">
         <v>340</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="Q9" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="Q9" s="31" t="s">
-        <v>342</v>
-      </c>
       <c r="R9" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2984,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
@@ -3005,7 +3014,7 @@
         <v>314</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K10" s="38" t="s">
         <v>261</v>
@@ -3021,7 +3030,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P10" s="41">
         <v>0.25869999999999999</v>
@@ -3032,17 +3041,17 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B87" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D11" s="82" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="E11" s="83" t="s">
         <v>69</v>
@@ -3060,23 +3069,23 @@
         <v>314</v>
       </c>
       <c r="J11" s="82" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K11" s="83" t="s">
         <v>262</v>
       </c>
       <c r="L11" s="82">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M11" s="84">
         <f>L11*20</f>
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="N11" s="84">
         <v>300</v>
       </c>
       <c r="O11" s="85" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P11" s="84">
         <v>1.4E-3</v>
@@ -3086,7 +3095,7 @@
         <v>0.42</v>
       </c>
       <c r="R11" s="84" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3096,10 +3105,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>70</v>
@@ -3117,7 +3126,7 @@
         <v>314</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K12" s="38" t="s">
         <v>263</v>
@@ -3133,7 +3142,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
@@ -3151,10 +3160,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>71</v>
@@ -3172,7 +3181,7 @@
         <v>314</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K13" s="40" t="s">
         <v>264</v>
@@ -3188,7 +3197,7 @@
         <v>40</v>
       </c>
       <c r="O13" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
@@ -3206,10 +3215,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>72</v>
@@ -3227,7 +3236,7 @@
         <v>314</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K14" s="38" t="s">
         <v>265</v>
@@ -3243,7 +3252,7 @@
         <v>200</v>
       </c>
       <c r="O14" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
@@ -3261,10 +3270,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>73</v>
@@ -3282,7 +3291,7 @@
         <v>314</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K15" s="40" t="s">
         <v>266</v>
@@ -3298,7 +3307,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
@@ -3316,19 +3325,19 @@
         <v>7</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F16" s="37" t="s">
         <v>143</v>
       </c>
       <c r="G16" s="101" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H16" s="86" t="s">
         <v>231</v>
@@ -3337,7 +3346,7 @@
         <v>314</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K16" s="38" t="s">
         <v>267</v>
@@ -3353,7 +3362,7 @@
         <v>130</v>
       </c>
       <c r="O16" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P16" s="41">
         <v>3.32E-2</v>
@@ -3371,7 +3380,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>9</v>
@@ -3392,7 +3401,7 @@
         <v>314</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K17" s="40" t="s">
         <v>268</v>
@@ -3408,7 +3417,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
@@ -3426,10 +3435,10 @@
         <v>9</v>
       </c>
       <c r="C18" s="102" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D18" s="103" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E18" s="104" t="s">
         <v>75</v>
@@ -3444,10 +3453,10 @@
         <v>232</v>
       </c>
       <c r="I18" s="103" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J18" s="103" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K18" s="104" t="s">
         <v>269</v>
@@ -3463,7 +3472,7 @@
         <v>180</v>
       </c>
       <c r="O18" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P18" s="96">
         <v>3.09E-2</v>
@@ -3481,7 +3490,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D19" s="107" t="s">
         <v>10</v>
@@ -3499,10 +3508,10 @@
         <v>233</v>
       </c>
       <c r="I19" s="107" t="s">
+        <v>352</v>
+      </c>
+      <c r="J19" s="107" t="s">
         <v>353</v>
-      </c>
-      <c r="J19" s="107" t="s">
-        <v>354</v>
       </c>
       <c r="K19" s="108" t="s">
         <v>270</v>
@@ -3518,7 +3527,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P19" s="109">
         <v>5.3E-3</v>
@@ -3536,7 +3545,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="102" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D20" s="103" t="s">
         <v>11</v>
@@ -3557,7 +3566,7 @@
         <v>314</v>
       </c>
       <c r="J20" s="103" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K20" s="104" t="s">
         <v>261</v>
@@ -3573,7 +3582,7 @@
         <v>22</v>
       </c>
       <c r="O20" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P20" s="96">
         <v>0.22189999999999999</v>
@@ -3591,7 +3600,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D21" s="107" t="s">
         <v>12</v>
@@ -3612,7 +3621,7 @@
         <v>314</v>
       </c>
       <c r="J21" s="107" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K21" s="108" t="s">
         <v>271</v>
@@ -3628,7 +3637,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P21" s="109">
         <v>7.7000000000000002E-3</v>
@@ -3646,7 +3655,7 @@
         <v>13</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>13</v>
@@ -3667,7 +3676,7 @@
         <v>314</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K22" s="38" t="s">
         <v>264</v>
@@ -3683,7 +3692,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P22" s="41">
         <v>3.49E-2</v>
@@ -3701,10 +3710,10 @@
         <v>14</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>80</v>
@@ -3722,7 +3731,7 @@
         <v>314</v>
       </c>
       <c r="J23" s="39" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K23" s="40" t="s">
         <v>272</v>
@@ -3738,7 +3747,7 @@
         <v>40</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P23" s="42">
         <v>1.9199999999999998E-2</v>
@@ -3756,7 +3765,7 @@
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D24" s="37" t="s">
         <v>14</v>
@@ -3774,10 +3783,10 @@
         <v>235</v>
       </c>
       <c r="I24" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="J24" s="37" t="s">
         <v>360</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>361</v>
       </c>
       <c r="K24" s="38" t="s">
         <v>273</v>
@@ -3793,7 +3802,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P24" s="41">
         <v>5.1999999999999998E-3</v>
@@ -3811,7 +3820,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D25" s="39" t="s">
         <v>15</v>
@@ -3832,7 +3841,7 @@
         <v>314</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K25" s="40" t="s">
         <v>274</v>
@@ -3848,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P25" s="42">
         <v>3.2000000000000002E-3</v>
@@ -3866,19 +3875,19 @@
         <v>17</v>
       </c>
       <c r="C26" s="102" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D26" s="103" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="111" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F26" s="103" t="s">
         <v>143</v>
       </c>
       <c r="G26" s="111" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H26" s="112" t="s">
         <v>249</v>
@@ -3887,10 +3896,10 @@
         <v>314</v>
       </c>
       <c r="J26" s="103" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K26" s="111" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L26" s="103">
         <v>1</v>
@@ -3903,7 +3912,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P26" s="96">
         <v>3.3999999999999998E-3</v>
@@ -3921,10 +3930,10 @@
         <v>18</v>
       </c>
       <c r="C27" s="106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D27" s="107" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E27" s="108" t="s">
         <v>83</v>
@@ -3942,7 +3951,7 @@
         <v>314</v>
       </c>
       <c r="J27" s="107" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K27" s="108" t="s">
         <v>275</v>
@@ -3958,7 +3967,7 @@
         <v>30</v>
       </c>
       <c r="O27" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P27" s="109">
         <v>0.2525</v>
@@ -3976,7 +3985,7 @@
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D28" s="37" t="s">
         <v>17</v>
@@ -3997,7 +4006,7 @@
         <v>314</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K28" s="38" t="s">
         <v>276</v>
@@ -4013,7 +4022,7 @@
         <v>22</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P28" s="41">
         <v>0.89629999999999999</v>
@@ -4031,7 +4040,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D29" s="39" t="s">
         <v>18</v>
@@ -4052,7 +4061,7 @@
         <v>314</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K29" s="40" t="s">
         <v>277</v>
@@ -4068,7 +4077,7 @@
         <v>21</v>
       </c>
       <c r="O29" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P29" s="42">
         <v>0.47249999999999998</v>
@@ -4086,7 +4095,7 @@
         <v>21</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D30" s="37" t="s">
         <v>19</v>
@@ -4107,7 +4116,7 @@
         <v>314</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K30" s="38" t="s">
         <v>278</v>
@@ -4123,7 +4132,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P30" s="41">
         <v>3.0999999999999999E-3</v>
@@ -4141,7 +4150,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D31" s="107" t="s">
         <v>20</v>
@@ -4162,7 +4171,7 @@
         <v>314</v>
       </c>
       <c r="J31" s="107" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K31" s="108" t="s">
         <v>279</v>
@@ -4178,7 +4187,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P31" s="109">
         <v>5.4999999999999997E-3</v>
@@ -4196,7 +4205,7 @@
         <v>23</v>
       </c>
       <c r="C32" s="102" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D32" s="103" t="s">
         <v>21</v>
@@ -4217,7 +4226,7 @@
         <v>314</v>
       </c>
       <c r="J32" s="103" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K32" s="104" t="s">
         <v>314</v>
@@ -4233,7 +4242,7 @@
         <v>30</v>
       </c>
       <c r="O32" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P32" s="96">
         <v>4.87E-2</v>
@@ -4251,7 +4260,7 @@
         <v>24</v>
       </c>
       <c r="C33" s="106" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D33" s="107" t="s">
         <v>22</v>
@@ -4272,7 +4281,7 @@
         <v>314</v>
       </c>
       <c r="J33" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K33" s="108" t="s">
         <v>314</v>
@@ -4288,7 +4297,7 @@
         <v>30</v>
       </c>
       <c r="O33" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P33" s="109">
         <v>7.4300000000000005E-2</v>
@@ -4306,10 +4315,10 @@
         <v>25</v>
       </c>
       <c r="C34" s="102" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D34" s="103" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E34" s="104" t="s">
         <v>90</v>
@@ -4327,7 +4336,7 @@
         <v>281</v>
       </c>
       <c r="J34" s="103" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K34" s="104" t="s">
         <v>314</v>
@@ -4343,7 +4352,7 @@
         <v>60</v>
       </c>
       <c r="O34" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P34" s="96">
         <v>2.8899999999999999E-2</v>
@@ -4361,10 +4370,10 @@
         <v>26</v>
       </c>
       <c r="C35" s="89" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D35" s="90" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E35" s="91" t="s">
         <v>91</v>
@@ -4379,10 +4388,10 @@
         <v>239</v>
       </c>
       <c r="I35" s="90" t="s">
+        <v>370</v>
+      </c>
+      <c r="J35" s="90" t="s">
         <v>371</v>
-      </c>
-      <c r="J35" s="90" t="s">
-        <v>372</v>
       </c>
       <c r="K35" s="91" t="s">
         <v>314</v>
@@ -4398,7 +4407,7 @@
         <v>170</v>
       </c>
       <c r="O35" s="95" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P35" s="93">
         <v>0.12590000000000001</v>
@@ -4408,7 +4417,7 @@
         <v>21.403000000000002</v>
       </c>
       <c r="R35" s="84" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4418,7 +4427,7 @@
         <v>27</v>
       </c>
       <c r="C36" s="102" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D36" s="103" t="s">
         <v>23</v>
@@ -4436,10 +4445,10 @@
         <v>240</v>
       </c>
       <c r="I36" s="103" t="s">
+        <v>372</v>
+      </c>
+      <c r="J36" s="103" t="s">
         <v>373</v>
-      </c>
-      <c r="J36" s="103" t="s">
-        <v>374</v>
       </c>
       <c r="K36" s="104" t="s">
         <v>314</v>
@@ -4455,7 +4464,7 @@
         <v>30</v>
       </c>
       <c r="O36" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P36" s="96">
         <v>5.6000000000000001E-2</v>
@@ -4473,7 +4482,7 @@
         <v>28</v>
       </c>
       <c r="C37" s="106" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D37" s="107" t="s">
         <v>24</v>
@@ -4494,7 +4503,7 @@
         <v>314</v>
       </c>
       <c r="J37" s="107" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K37" s="108" t="s">
         <v>314</v>
@@ -4510,7 +4519,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P37" s="109">
         <v>2.9499999999999998E-2</v>
@@ -4528,7 +4537,7 @@
         <v>29</v>
       </c>
       <c r="C38" s="102" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D38" s="103" t="s">
         <v>25</v>
@@ -4546,10 +4555,10 @@
         <v>241</v>
       </c>
       <c r="I38" s="103" t="s">
+        <v>375</v>
+      </c>
+      <c r="J38" s="103" t="s">
         <v>376</v>
-      </c>
-      <c r="J38" s="103" t="s">
-        <v>377</v>
       </c>
       <c r="K38" s="104" t="s">
         <v>314</v>
@@ -4565,7 +4574,7 @@
         <v>21</v>
       </c>
       <c r="O38" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P38" s="96">
         <v>0.53559999999999997</v>
@@ -4583,7 +4592,7 @@
         <v>30</v>
       </c>
       <c r="C39" s="106" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D39" s="107" t="s">
         <v>26</v>
@@ -4601,10 +4610,10 @@
         <v>242</v>
       </c>
       <c r="I39" s="107" t="s">
+        <v>377</v>
+      </c>
+      <c r="J39" s="107" t="s">
         <v>378</v>
-      </c>
-      <c r="J39" s="107" t="s">
-        <v>379</v>
       </c>
       <c r="K39" s="108" t="s">
         <v>314</v>
@@ -4620,7 +4629,7 @@
         <v>42</v>
       </c>
       <c r="O39" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P39" s="109">
         <v>0.65639999999999998</v>
@@ -4638,7 +4647,7 @@
         <v>31</v>
       </c>
       <c r="C40" s="102" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D40" s="103" t="s">
         <v>27</v>
@@ -4675,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="O40" s="105" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P40" s="96">
         <v>1.2</v>
@@ -4693,7 +4702,7 @@
         <v>32</v>
       </c>
       <c r="C41" s="106" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D41" s="107" t="s">
         <v>28</v>
@@ -4714,7 +4723,7 @@
         <v>314</v>
       </c>
       <c r="J41" s="107" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K41" s="108" t="s">
         <v>314</v>
@@ -4730,7 +4739,7 @@
         <v>25</v>
       </c>
       <c r="O41" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P41" s="109">
         <v>9.2200000000000004E-2</v>
@@ -4748,7 +4757,7 @@
         <v>33</v>
       </c>
       <c r="C42" s="102" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D42" s="103" t="s">
         <v>29</v>
@@ -4769,7 +4778,7 @@
         <v>314</v>
       </c>
       <c r="J42" s="103" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K42" s="104" t="s">
         <v>282</v>
@@ -4785,7 +4794,7 @@
         <v>21</v>
       </c>
       <c r="O42" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P42" s="96">
         <v>0.45629999999999998</v>
@@ -4803,31 +4812,31 @@
         <v>34</v>
       </c>
       <c r="C43" s="106" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D43" s="107" t="s">
         <v>30</v>
       </c>
       <c r="E43" s="108" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F43" s="107" t="s">
         <v>308</v>
       </c>
       <c r="G43" s="108" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H43" s="107" t="s">
+        <v>436</v>
+      </c>
+      <c r="I43" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J43" s="107" t="s">
         <v>437</v>
       </c>
-      <c r="I43" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J43" s="107" t="s">
-        <v>438</v>
-      </c>
       <c r="K43" s="108" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L43" s="107">
         <v>1</v>
@@ -4840,7 +4849,7 @@
         <v>25</v>
       </c>
       <c r="O43" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P43" s="109">
         <v>0.1012</v>
@@ -4858,7 +4867,7 @@
         <v>35</v>
       </c>
       <c r="C44" s="102" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D44" s="103" t="s">
         <v>31</v>
@@ -4895,7 +4904,7 @@
         <v>30</v>
       </c>
       <c r="O44" s="105" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P44" s="96">
         <v>0.156</v>
@@ -4913,7 +4922,7 @@
         <v>36</v>
       </c>
       <c r="C45" s="106" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D45" s="107" t="s">
         <v>32</v>
@@ -4950,7 +4959,7 @@
         <v>30</v>
       </c>
       <c r="O45" s="110" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P45" s="109">
         <v>0.08</v>
@@ -4968,7 +4977,7 @@
         <v>37</v>
       </c>
       <c r="C46" s="102" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D46" s="103" t="s">
         <v>33</v>
@@ -5005,7 +5014,7 @@
         <v>50</v>
       </c>
       <c r="O46" s="105" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P46" s="96">
         <v>1.5</v>
@@ -5063,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="R47" s="66" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5073,7 +5082,7 @@
         <v>39</v>
       </c>
       <c r="C48" s="102" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D48" s="103" t="s">
         <v>35</v>
@@ -5110,7 +5119,7 @@
         <v>90</v>
       </c>
       <c r="O48" s="105" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P48" s="96">
         <v>0.13</v>
@@ -5128,10 +5137,10 @@
         <v>40</v>
       </c>
       <c r="C49" s="106" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D49" s="107" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E49" s="108" t="s">
         <v>104</v>
@@ -5146,10 +5155,10 @@
         <v>248</v>
       </c>
       <c r="I49" s="107" t="s">
+        <v>385</v>
+      </c>
+      <c r="J49" s="107" t="s">
         <v>386</v>
-      </c>
-      <c r="J49" s="107" t="s">
-        <v>387</v>
       </c>
       <c r="K49" s="108" t="s">
         <v>314</v>
@@ -5165,7 +5174,7 @@
         <v>85</v>
       </c>
       <c r="O49" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P49" s="109">
         <v>0.21740000000000001</v>
@@ -5183,7 +5192,7 @@
         <v>41</v>
       </c>
       <c r="C50" s="102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D50" s="103" t="s">
         <v>36</v>
@@ -5204,7 +5213,7 @@
         <v>314</v>
       </c>
       <c r="J50" s="103" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K50" s="104" t="s">
         <v>284</v>
@@ -5220,7 +5229,7 @@
         <v>100</v>
       </c>
       <c r="O50" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P50" s="96">
         <v>1E-3</v>
@@ -5238,7 +5247,7 @@
         <v>42</v>
       </c>
       <c r="C51" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D51" s="107" t="s">
         <v>37</v>
@@ -5259,7 +5268,7 @@
         <v>314</v>
       </c>
       <c r="J51" s="107" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K51" s="108" t="s">
         <v>285</v>
@@ -5275,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="O51" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P51" s="109">
         <v>1.4E-3</v>
@@ -5293,7 +5302,7 @@
         <v>43</v>
       </c>
       <c r="C52" s="102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D52" s="103" t="s">
         <v>38</v>
@@ -5314,7 +5323,7 @@
         <v>314</v>
       </c>
       <c r="J52" s="103" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K52" s="104" t="s">
         <v>286</v>
@@ -5330,7 +5339,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P52" s="96">
         <v>1.6000000000000001E-3</v>
@@ -5348,7 +5357,7 @@
         <v>44</v>
       </c>
       <c r="C53" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D53" s="107" t="s">
         <v>39</v>
@@ -5369,7 +5378,7 @@
         <v>314</v>
       </c>
       <c r="J53" s="107" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K53" s="108" t="s">
         <v>287</v>
@@ -5385,7 +5394,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P53" s="109">
         <v>1.4E-3</v>
@@ -5403,7 +5412,7 @@
         <v>45</v>
       </c>
       <c r="C54" s="102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D54" s="103" t="s">
         <v>40</v>
@@ -5424,7 +5433,7 @@
         <v>314</v>
       </c>
       <c r="J54" s="103" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K54" s="104" t="s">
         <v>288</v>
@@ -5440,7 +5449,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P54" s="96">
         <v>1.2999999999999999E-3</v>
@@ -5458,7 +5467,7 @@
         <v>46</v>
       </c>
       <c r="C55" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D55" s="107" t="s">
         <v>41</v>
@@ -5470,16 +5479,16 @@
         <v>167</v>
       </c>
       <c r="G55" s="108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H55" s="107" t="s">
         <v>250</v>
       </c>
       <c r="I55" s="107" t="s">
+        <v>392</v>
+      </c>
+      <c r="J55" s="107" t="s">
         <v>393</v>
-      </c>
-      <c r="J55" s="107" t="s">
-        <v>394</v>
       </c>
       <c r="K55" s="108" t="s">
         <v>289</v>
@@ -5495,7 +5504,7 @@
         <v>90</v>
       </c>
       <c r="O55" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P55" s="109">
         <v>6.4500000000000002E-2</v>
@@ -5513,19 +5522,19 @@
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F56" s="37" t="s">
         <v>166</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H56" s="37" t="s">
         <v>252</v>
@@ -5534,10 +5543,10 @@
         <v>314</v>
       </c>
       <c r="J56" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="K56" s="37" t="s">
         <v>427</v>
-      </c>
-      <c r="K56" s="37" t="s">
-        <v>428</v>
       </c>
       <c r="L56" s="37">
         <v>8</v>
@@ -5550,7 +5559,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="80" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P56" s="37">
         <v>1.1000000000000001E-3</v>
@@ -5568,7 +5577,7 @@
         <v>48</v>
       </c>
       <c r="C57" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D57" s="107" t="s">
         <v>42</v>
@@ -5605,7 +5614,7 @@
         <v>30</v>
       </c>
       <c r="O57" s="110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P57" s="109">
         <v>1.8589999999999999E-2</v>
@@ -5623,7 +5632,7 @@
         <v>49</v>
       </c>
       <c r="C58" s="102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D58" s="103" t="s">
         <v>43</v>
@@ -5644,7 +5653,7 @@
         <v>314</v>
       </c>
       <c r="J58" s="103" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K58" s="104" t="s">
         <v>292</v>
@@ -5660,7 +5669,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P58" s="96">
         <v>1.4E-3</v>
@@ -5678,7 +5687,7 @@
         <v>50</v>
       </c>
       <c r="C59" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D59" s="107" t="s">
         <v>44</v>
@@ -5715,7 +5724,7 @@
         <v>50</v>
       </c>
       <c r="O59" s="110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P59" s="109">
         <v>4.6699999999999997E-3</v>
@@ -5733,7 +5742,7 @@
         <v>51</v>
       </c>
       <c r="C60" s="102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D60" s="103" t="s">
         <v>45</v>
@@ -5754,7 +5763,7 @@
         <v>314</v>
       </c>
       <c r="J60" s="103" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K60" s="104" t="s">
         <v>294</v>
@@ -5770,7 +5779,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P60" s="96">
         <v>1.1999999999999999E-3</v>
@@ -5788,7 +5797,7 @@
         <v>52</v>
       </c>
       <c r="C61" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D61" s="107" t="s">
         <v>46</v>
@@ -5825,7 +5834,7 @@
         <v>50</v>
       </c>
       <c r="O61" s="110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P61" s="109">
         <v>1.11E-2</v>
@@ -5843,7 +5852,7 @@
         <v>53</v>
       </c>
       <c r="C62" s="102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D62" s="103" t="s">
         <v>47</v>
@@ -5864,7 +5873,7 @@
         <v>314</v>
       </c>
       <c r="J62" s="103" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K62" s="104" t="s">
         <v>296</v>
@@ -5880,7 +5889,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P62" s="96">
         <v>2.0999999999999999E-3</v>
@@ -5898,7 +5907,7 @@
         <v>54</v>
       </c>
       <c r="C63" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D63" s="107" t="s">
         <v>48</v>
@@ -5919,7 +5928,7 @@
         <v>314</v>
       </c>
       <c r="J63" s="107" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K63" s="108" t="s">
         <v>297</v>
@@ -5935,7 +5944,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P63" s="109">
         <v>1.6000000000000001E-3</v>
@@ -5953,7 +5962,7 @@
         <v>55</v>
       </c>
       <c r="C64" s="102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D64" s="103" t="s">
         <v>49</v>
@@ -5971,10 +5980,10 @@
         <v>229</v>
       </c>
       <c r="I64" s="103" t="s">
+        <v>399</v>
+      </c>
+      <c r="J64" s="103" t="s">
         <v>400</v>
-      </c>
-      <c r="J64" s="103" t="s">
-        <v>401</v>
       </c>
       <c r="K64" s="104" t="s">
         <v>298</v>
@@ -5990,7 +5999,7 @@
         <v>50</v>
       </c>
       <c r="O64" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P64" s="96">
         <v>6.8999999999999999E-3</v>
@@ -6001,17 +6010,17 @@
       </c>
       <c r="R64" s="96"/>
     </row>
-    <row r="65" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
       <c r="C65" s="106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D65" s="107" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E65" s="108" t="s">
         <v>120</v>
@@ -6029,7 +6038,7 @@
         <v>314</v>
       </c>
       <c r="J65" s="107" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K65" s="108" t="s">
         <v>299</v>
@@ -6045,7 +6054,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P65" s="109">
         <v>1.1000000000000001E-3</v>
@@ -6056,14 +6065,14 @@
       </c>
       <c r="R65" s="109"/>
     </row>
-    <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>50</v>
@@ -6084,7 +6093,7 @@
         <v>314</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K66" s="38" t="s">
         <v>300</v>
@@ -6100,7 +6109,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P66" s="41">
         <v>1.5E-3</v>
@@ -6111,17 +6120,17 @@
       </c>
       <c r="R66" s="41"/>
     </row>
-    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
       <c r="C67" s="59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D67" s="87" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E67" s="40" t="s">
         <v>111</v>
@@ -6137,7 +6146,7 @@
       </c>
       <c r="I67" s="39"/>
       <c r="J67" s="39" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K67" s="40" t="s">
         <v>290</v>
@@ -6153,7 +6162,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P67" s="42">
         <v>1.5E-3</v>
@@ -6164,14 +6173,14 @@
       </c>
       <c r="R67" s="77"/>
     </row>
-    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D68" s="37" t="s">
         <v>51</v>
@@ -6192,7 +6201,7 @@
         <v>314</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K68" s="38" t="s">
         <v>301</v>
@@ -6208,7 +6217,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P68" s="41">
         <v>1.5E-3</v>
@@ -6219,14 +6228,14 @@
       </c>
       <c r="R68" s="41"/>
     </row>
-    <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="C69" s="59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D69" s="39" t="s">
         <v>52</v>
@@ -6263,7 +6272,7 @@
         <v>25</v>
       </c>
       <c r="O69" s="64" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P69" s="42">
         <v>8.5400000000000004E-2</v>
@@ -6274,26 +6283,26 @@
       </c>
       <c r="R69" s="42"/>
     </row>
-    <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D70" s="37" t="s">
         <v>53</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F70" s="86" t="s">
         <v>166</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H70" s="37" t="s">
         <v>252</v>
@@ -6302,10 +6311,10 @@
         <v>314</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="L70" s="37">
         <v>1</v>
@@ -6318,7 +6327,7 @@
         <v>50</v>
       </c>
       <c r="O70" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P70" s="41">
         <v>3.8E-3</v>
@@ -6329,17 +6338,17 @@
       </c>
       <c r="R70" s="76"/>
     </row>
-    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
       <c r="C71" s="59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E71" s="40" t="s">
         <v>127</v>
@@ -6357,7 +6366,7 @@
         <v>314</v>
       </c>
       <c r="J71" s="39" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K71" s="40" t="s">
         <v>306</v>
@@ -6373,7 +6382,7 @@
         <v>200</v>
       </c>
       <c r="O71" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P71" s="42">
         <v>1.1999999999999999E-3</v>
@@ -6384,14 +6393,14 @@
       </c>
       <c r="R71" s="77"/>
     </row>
-    <row r="72" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D72" s="37" t="s">
         <v>54</v>
@@ -6403,7 +6412,7 @@
         <v>166</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H72" s="37" t="s">
         <v>252</v>
@@ -6412,7 +6421,7 @@
         <v>314</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K72" s="38" t="s">
         <v>303</v>
@@ -6428,7 +6437,7 @@
         <v>100</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P72" s="41">
         <v>1E-3</v>
@@ -6439,14 +6448,14 @@
       </c>
       <c r="R72" s="41"/>
     </row>
-    <row r="73" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C73" s="59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D73" s="39" t="s">
         <v>55</v>
@@ -6458,7 +6467,7 @@
         <v>166</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H73" s="39" t="s">
         <v>253</v>
@@ -6467,7 +6476,7 @@
         <v>314</v>
       </c>
       <c r="J73" s="39" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K73" s="40" t="s">
         <v>304</v>
@@ -6483,7 +6492,7 @@
         <v>50</v>
       </c>
       <c r="O73" s="64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P73" s="42">
         <v>4.3E-3</v>
@@ -6494,14 +6503,14 @@
       </c>
       <c r="R73" s="42"/>
     </row>
-    <row r="74" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
       <c r="C74" s="97" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D74" s="98" t="s">
         <v>56</v>
@@ -6522,7 +6531,7 @@
         <v>314</v>
       </c>
       <c r="J74" s="98" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K74" s="99" t="s">
         <v>305</v>
@@ -6538,7 +6547,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="100" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P74" s="66">
         <v>1.1999999999999999E-3</v>
@@ -6548,10 +6557,10 @@
         <v>0.12</v>
       </c>
       <c r="R74" s="66" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
         <f>ROW(B75) - ROW($B$9)</f>
@@ -6561,7 +6570,7 @@
         <v>169</v>
       </c>
       <c r="D75" s="98" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E75" s="99" t="s">
         <v>128</v>
@@ -6602,17 +6611,17 @@
         <v>0</v>
       </c>
       <c r="R75" s="66" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="C76" s="102" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D76" s="103" t="s">
         <v>57</v>
@@ -6656,15 +6665,40 @@
         <v>0</v>
       </c>
       <c r="R76" s="96"/>
-    </row>
-    <row r="77" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T76" t="s">
+        <v>57</v>
+      </c>
+      <c r="V76" t="s">
+        <v>314</v>
+      </c>
+      <c r="W76">
+        <v>1</v>
+      </c>
+      <c r="Y76" t="str">
+        <f>IF(T76=D76, "Match", "Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="Z76" t="str">
+        <f>IF(G76=U76, "Match", "Mismatch")</f>
+        <v>Mismatch</v>
+      </c>
+      <c r="AA76" t="str">
+        <f>IF(K76=V76, "Match", "Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="AB76" t="str">
+        <f>IF(W76=L76, "Match", "Mismatch")</f>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
       <c r="C77" s="106" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D77" s="107" t="s">
         <v>58</v>
@@ -6701,7 +6735,7 @@
         <v>21</v>
       </c>
       <c r="O77" s="110" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P77" s="109">
         <v>3.81</v>
@@ -6711,15 +6745,43 @@
         <v>80.010000000000005</v>
       </c>
       <c r="R77" s="109"/>
-    </row>
-    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T77" t="s">
+        <v>58</v>
+      </c>
+      <c r="U77">
+        <v>750314597</v>
+      </c>
+      <c r="V77" t="s">
+        <v>314</v>
+      </c>
+      <c r="W77">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="str">
+        <f t="shared" ref="Y77:Y87" si="69">IF(T77=D77, "Match", "Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="Z77" t="str">
+        <f t="shared" ref="Z77:Z87" si="70">IF(G77=U77, "Match", "Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="AA77" t="str">
+        <f t="shared" ref="AA77:AA87" si="71">IF(K77=V77, "Match", "Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="AB77" t="str">
+        <f t="shared" ref="AB77:AB87" si="72">IF(W77=L77, "Match", "Mismatch")</f>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C78" s="102" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D78" s="103" t="s">
         <v>59</v>
@@ -6756,25 +6818,53 @@
         <v>21</v>
       </c>
       <c r="O78" s="105" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P78" s="96">
         <v>2.48</v>
       </c>
       <c r="Q78" s="96">
-        <f t="shared" ref="Q78" si="69">N78*P78</f>
+        <f t="shared" ref="Q78" si="73">N78*P78</f>
         <v>52.08</v>
       </c>
       <c r="R78" s="96"/>
-    </row>
-    <row r="79" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T78" t="s">
+        <v>59</v>
+      </c>
+      <c r="U78" t="s">
+        <v>171</v>
+      </c>
+      <c r="V78" t="s">
+        <v>314</v>
+      </c>
+      <c r="W78">
+        <v>1</v>
+      </c>
+      <c r="Y78" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z78" t="str">
+        <f t="shared" si="70"/>
+        <v>Match</v>
+      </c>
+      <c r="AA78" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB78" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
       <c r="C79" s="106" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D79" s="107" t="s">
         <v>60</v>
@@ -6792,10 +6882,10 @@
         <v>257</v>
       </c>
       <c r="I79" s="107" t="s">
+        <v>410</v>
+      </c>
+      <c r="J79" s="107" t="s">
         <v>411</v>
-      </c>
-      <c r="J79" s="107" t="s">
-        <v>412</v>
       </c>
       <c r="K79" s="108" t="s">
         <v>314</v>
@@ -6811,25 +6901,53 @@
         <v>21</v>
       </c>
       <c r="O79" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P79" s="109">
         <v>1.3939999999999999</v>
       </c>
       <c r="Q79" s="109">
-        <f t="shared" ref="Q79" si="70">P79*N79</f>
+        <f t="shared" ref="Q79" si="74">P79*N79</f>
         <v>29.273999999999997</v>
       </c>
       <c r="R79" s="79"/>
-    </row>
-    <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T79" t="s">
+        <v>60</v>
+      </c>
+      <c r="U79" t="s">
+        <v>410</v>
+      </c>
+      <c r="V79" t="s">
+        <v>314</v>
+      </c>
+      <c r="W79">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z79" t="str">
+        <f t="shared" si="70"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="AA79" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB79" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C80" s="102" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D80" s="103" t="s">
         <v>61</v>
@@ -6847,10 +6965,10 @@
         <v>256</v>
       </c>
       <c r="I80" s="103" t="s">
+        <v>412</v>
+      </c>
+      <c r="J80" s="103" t="s">
         <v>413</v>
-      </c>
-      <c r="J80" s="103" t="s">
-        <v>414</v>
       </c>
       <c r="K80" s="104" t="s">
         <v>314</v>
@@ -6866,25 +6984,53 @@
         <v>21</v>
       </c>
       <c r="O80" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P80" s="96">
         <v>0.69430000000000003</v>
       </c>
       <c r="Q80" s="96">
-        <f t="shared" ref="Q80" si="71">N80*P80</f>
+        <f t="shared" ref="Q80" si="75">N80*P80</f>
         <v>14.580300000000001</v>
       </c>
       <c r="R80" s="78"/>
-    </row>
-    <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T80" t="s">
+        <v>61</v>
+      </c>
+      <c r="U80" t="s">
+        <v>412</v>
+      </c>
+      <c r="V80" t="s">
+        <v>314</v>
+      </c>
+      <c r="W80">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z80" t="str">
+        <f t="shared" si="70"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="AA80" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB80" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
       <c r="C81" s="106" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D81" s="107" t="s">
         <v>62</v>
@@ -6921,25 +7067,53 @@
         <v>21</v>
       </c>
       <c r="O81" s="110" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P81" s="109">
         <v>3.637</v>
       </c>
       <c r="Q81" s="109">
-        <f t="shared" ref="Q81" si="72">P81*N81</f>
+        <f t="shared" ref="Q81" si="76">P81*N81</f>
         <v>76.376999999999995</v>
       </c>
       <c r="R81" s="109"/>
-    </row>
-    <row r="82" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T81" t="s">
+        <v>62</v>
+      </c>
+      <c r="U81" t="s">
+        <v>174</v>
+      </c>
+      <c r="V81" t="s">
+        <v>314</v>
+      </c>
+      <c r="W81">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z81" t="str">
+        <f t="shared" si="70"/>
+        <v>Match</v>
+      </c>
+      <c r="AA81" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB81" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="C82" s="102" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D82" s="103" t="s">
         <v>63</v>
@@ -6960,7 +7134,7 @@
         <v>314</v>
       </c>
       <c r="J82" s="103" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K82" s="104" t="s">
         <v>314</v>
@@ -6976,25 +7150,53 @@
         <v>21</v>
       </c>
       <c r="O82" s="105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P82" s="96">
         <v>0.43280000000000002</v>
       </c>
       <c r="Q82" s="96">
-        <f t="shared" ref="Q82" si="73">N82*P82</f>
+        <f t="shared" ref="Q82" si="77">N82*P82</f>
         <v>9.0888000000000009</v>
       </c>
       <c r="R82" s="96"/>
-    </row>
-    <row r="83" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T82" t="s">
+        <v>63</v>
+      </c>
+      <c r="U82" t="s">
+        <v>223</v>
+      </c>
+      <c r="V82" t="s">
+        <v>314</v>
+      </c>
+      <c r="W82">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z82" t="str">
+        <f t="shared" si="70"/>
+        <v>Match</v>
+      </c>
+      <c r="AA82" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB82" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
       <c r="C83" s="71" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D83" s="72" t="s">
         <v>64</v>
@@ -7015,7 +7217,7 @@
         <v>314</v>
       </c>
       <c r="J83" s="72" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K83" s="73" t="s">
         <v>314</v>
@@ -7031,27 +7233,55 @@
         <v>21</v>
       </c>
       <c r="O83" s="75" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P83" s="74">
         <v>7.4638</v>
       </c>
       <c r="Q83" s="74">
-        <f t="shared" ref="Q83" si="74">P83*N83</f>
+        <f t="shared" ref="Q83" si="78">P83*N83</f>
         <v>156.7398</v>
       </c>
       <c r="R83" s="74" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>438</v>
+      </c>
+      <c r="T83" t="s">
+        <v>64</v>
+      </c>
+      <c r="U83" t="s">
+        <v>224</v>
+      </c>
+      <c r="V83" t="s">
+        <v>314</v>
+      </c>
+      <c r="W83">
+        <v>1</v>
+      </c>
+      <c r="Y83" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z83" t="str">
+        <f t="shared" si="70"/>
+        <v>Match</v>
+      </c>
+      <c r="AA83" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB83" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C84" s="102" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D84" s="103" t="s">
         <v>65</v>
@@ -7075,7 +7305,7 @@
         <v>314</v>
       </c>
       <c r="K84" s="114" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L84" s="103">
         <v>1</v>
@@ -7088,28 +7318,56 @@
         <v>21</v>
       </c>
       <c r="O84" s="105" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P84" s="96">
         <v>2.6459999999999999</v>
       </c>
       <c r="Q84" s="96">
-        <f t="shared" ref="Q84" si="75">N84*P84</f>
+        <f t="shared" ref="Q84" si="79">N84*P84</f>
         <v>55.565999999999995</v>
       </c>
       <c r="R84" s="96"/>
-    </row>
-    <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T84" t="s">
+        <v>65</v>
+      </c>
+      <c r="U84" t="s">
+        <v>225</v>
+      </c>
+      <c r="V84" t="s">
+        <v>314</v>
+      </c>
+      <c r="W84">
+        <v>1</v>
+      </c>
+      <c r="Y84" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z84" t="str">
+        <f t="shared" si="70"/>
+        <v>Match</v>
+      </c>
+      <c r="AA84" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB84" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
         <f>ROW(B85) - ROW($B$9)</f>
         <v>76</v>
       </c>
       <c r="C85" s="106" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D85" s="107" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E85" s="108" t="s">
         <v>138</v>
@@ -7124,10 +7382,10 @@
         <v>256</v>
       </c>
       <c r="I85" s="107" t="s">
+        <v>416</v>
+      </c>
+      <c r="J85" s="107" t="s">
         <v>417</v>
-      </c>
-      <c r="J85" s="107" t="s">
-        <v>418</v>
       </c>
       <c r="K85" s="108" t="s">
         <v>314</v>
@@ -7143,25 +7401,53 @@
         <v>42</v>
       </c>
       <c r="O85" s="110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P85" s="109">
         <v>2.2974000000000001</v>
       </c>
       <c r="Q85" s="109">
-        <f t="shared" ref="Q85" si="76">P85*N85</f>
+        <f t="shared" ref="Q85" si="80">P85*N85</f>
         <v>96.490800000000007</v>
       </c>
       <c r="R85" s="79"/>
-    </row>
-    <row r="86" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T85" t="s">
+        <v>454</v>
+      </c>
+      <c r="U85" t="s">
+        <v>416</v>
+      </c>
+      <c r="V85" t="s">
+        <v>314</v>
+      </c>
+      <c r="W85">
+        <v>2</v>
+      </c>
+      <c r="Y85" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z85" t="str">
+        <f t="shared" si="70"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="AA85" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB85" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
       <c r="C86" s="60" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D86" s="37" t="s">
         <v>66</v>
@@ -7182,7 +7468,7 @@
         <v>314</v>
       </c>
       <c r="J86" s="62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K86" s="38" t="s">
         <v>314</v>
@@ -7198,28 +7484,56 @@
         <v>21</v>
       </c>
       <c r="O86" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P86" s="41">
         <v>0.39140000000000003</v>
       </c>
       <c r="Q86" s="41">
-        <f t="shared" ref="Q86" si="77">P86*N86</f>
+        <f t="shared" ref="Q86" si="81">P86*N86</f>
         <v>8.2194000000000003</v>
       </c>
       <c r="R86" s="41"/>
-    </row>
-    <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T86" t="s">
+        <v>66</v>
+      </c>
+      <c r="U86" t="s">
+        <v>180</v>
+      </c>
+      <c r="V86" t="s">
+        <v>314</v>
+      </c>
+      <c r="W86">
+        <v>1</v>
+      </c>
+      <c r="Y86" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z86" t="str">
+        <f t="shared" si="70"/>
+        <v>Match</v>
+      </c>
+      <c r="AA86" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB86" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="C87" s="59" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E87" s="40" t="s">
         <v>139</v>
@@ -7234,7 +7548,7 @@
         <v>259</v>
       </c>
       <c r="I87" s="39" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J87" s="39" t="s">
         <v>314</v>
@@ -7253,18 +7567,46 @@
         <v>21</v>
       </c>
       <c r="O87" s="64" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P87" s="42">
         <v>3.532</v>
       </c>
       <c r="Q87" s="42">
-        <f t="shared" ref="Q87" si="78">N87*P87</f>
+        <f t="shared" ref="Q87" si="82">N87*P87</f>
         <v>74.171999999999997</v>
       </c>
       <c r="R87" s="79"/>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T87" t="s">
+        <v>455</v>
+      </c>
+      <c r="U87" t="s">
+        <v>418</v>
+      </c>
+      <c r="V87" t="s">
+        <v>314</v>
+      </c>
+      <c r="W87">
+        <v>1</v>
+      </c>
+      <c r="Y87" t="str">
+        <f t="shared" si="69"/>
+        <v>Match</v>
+      </c>
+      <c r="Z87" t="str">
+        <f t="shared" si="70"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="AA87" t="str">
+        <f t="shared" si="71"/>
+        <v>Match</v>
+      </c>
+      <c r="AB87" t="str">
+        <f t="shared" si="72"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="32"/>
       <c r="C88" s="51"/>
@@ -7282,7 +7624,7 @@
       <c r="M88" s="36"/>
       <c r="N88" s="36"/>
       <c r="O88" s="69" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P88" s="67"/>
       <c r="Q88" s="67">
@@ -7291,7 +7633,7 @@
       </c>
       <c r="R88" s="44"/>
     </row>
-    <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="24"/>
       <c r="C89" s="52"/>
@@ -7309,7 +7651,7 @@
       <c r="M89" s="9"/>
       <c r="N89" s="9"/>
       <c r="O89" s="70" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P89" s="68"/>
       <c r="Q89" s="68">

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="471">
   <si>
     <t>Component list</t>
   </si>
@@ -1558,6 +1558,24 @@
       </rPr>
       <t xml:space="preserve"> Cx1, Cx2</t>
     </r>
+  </si>
+  <si>
+    <t>LED Glass Pipe</t>
+  </si>
+  <si>
+    <t>LED Light Pipes PCB Mount</t>
+  </si>
+  <si>
+    <t>3mm .5 inch</t>
+  </si>
+  <si>
+    <t>VBL3D0500C</t>
+  </si>
+  <si>
+    <t>VCC</t>
+  </si>
+  <si>
+    <t>Mounting Holes required in design</t>
   </si>
 </sst>
 </file>
@@ -2064,7 +2082,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2376,9 +2394,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2738,7 +2753,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB89"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
@@ -2769,14 +2784,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
     </row>
     <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -2824,7 +2839,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="117"/>
+      <c r="R3" s="116"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -2848,7 +2863,7 @@
       <c r="O4" s="61"/>
       <c r="P4" s="61"/>
       <c r="Q4" s="61"/>
-      <c r="R4" s="118"/>
+      <c r="R4" s="117"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -2870,7 +2885,7 @@
       <c r="O5" s="61"/>
       <c r="P5" s="61"/>
       <c r="Q5" s="61"/>
-      <c r="R5" s="118"/>
+      <c r="R5" s="117"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -2890,7 +2905,7 @@
       <c r="O6" s="61"/>
       <c r="P6" s="61"/>
       <c r="Q6" s="61"/>
-      <c r="R6" s="118"/>
+      <c r="R6" s="117"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2910,7 +2925,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="118"/>
+      <c r="R7" s="117"/>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -2930,7 +2945,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="118"/>
+      <c r="R8" s="117"/>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -3044,7 +3059,7 @@
     <row r="11" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B87" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B88" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="81" t="s">
@@ -3135,7 +3150,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="41">
-        <f t="shared" ref="M12:M69" si="1">L12*20</f>
+        <f t="shared" ref="M12:M70" si="1">L12*20</f>
         <v>40</v>
       </c>
       <c r="N12" s="41">
@@ -4965,2700 +4980,2402 @@
         <v>0.08</v>
       </c>
       <c r="Q45" s="109">
-        <f t="shared" ref="Q45" si="34">P45*N45</f>
+        <f t="shared" ref="Q45:Q46" si="34">P45*N45</f>
         <v>2.4</v>
       </c>
       <c r="R45" s="109"/>
     </row>
     <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="113">
-        <f t="shared" si="0"/>
+      <c r="B46" s="53">
         <v>37</v>
       </c>
-      <c r="C46" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="D46" s="103" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" s="104" t="s">
-        <v>101</v>
-      </c>
-      <c r="F46" s="103" t="s">
-        <v>308</v>
-      </c>
-      <c r="G46" s="104" t="s">
-        <v>162</v>
-      </c>
-      <c r="H46" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="I46" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J46" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K46" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L46" s="103">
-        <v>2</v>
-      </c>
-      <c r="M46" s="96">
+      <c r="C46" s="106" t="s">
+        <v>465</v>
+      </c>
+      <c r="D46" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="E46" s="108" t="s">
+        <v>466</v>
+      </c>
+      <c r="F46" s="107" t="s">
+        <v>467</v>
+      </c>
+      <c r="G46" s="108" t="s">
+        <v>468</v>
+      </c>
+      <c r="H46" s="107" t="s">
+        <v>469</v>
+      </c>
+      <c r="I46" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J46" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K46" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L46" s="107">
+        <v>1</v>
+      </c>
+      <c r="M46" s="109">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N46" s="96">
-        <v>50</v>
-      </c>
-      <c r="O46" s="105" t="s">
+        <v>20</v>
+      </c>
+      <c r="N46" s="109">
+        <v>20</v>
+      </c>
+      <c r="O46" s="110" t="s">
         <v>379</v>
       </c>
-      <c r="P46" s="96">
-        <v>1.5</v>
-      </c>
-      <c r="Q46" s="96">
-        <f t="shared" ref="Q46" si="35">N46*P46</f>
-        <v>75</v>
-      </c>
-      <c r="R46" s="96"/>
+      <c r="P46" s="109">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="Q46" s="109">
+        <f t="shared" si="34"/>
+        <v>9.24</v>
+      </c>
+      <c r="R46" s="109" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
-        <f>ROW(B47) - ROW($B$9)</f>
+        <f t="shared" ref="B47:B88" si="35">ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="97" t="s">
-        <v>283</v>
-      </c>
-      <c r="D47" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="99" t="s">
-        <v>102</v>
-      </c>
-      <c r="F47" s="98" t="s">
-        <v>163</v>
-      </c>
-      <c r="G47" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="H47" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="I47" s="98"/>
-      <c r="J47" s="98"/>
-      <c r="K47" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="L47" s="98">
-        <v>4</v>
-      </c>
-      <c r="M47" s="66">
+      <c r="C47" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="D47" s="103" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G47" s="104" t="s">
+        <v>162</v>
+      </c>
+      <c r="H47" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="I47" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J47" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K47" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L47" s="103">
+        <v>2</v>
+      </c>
+      <c r="M47" s="96">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N47" s="66">
-        <f t="shared" ref="N47" si="36">M47+(M47*0.1)</f>
-        <v>88</v>
-      </c>
-      <c r="O47" s="66"/>
-      <c r="P47" s="66"/>
-      <c r="Q47" s="66">
-        <f t="shared" ref="Q47" si="37">P47*N47</f>
-        <v>0</v>
-      </c>
-      <c r="R47" s="66" t="s">
-        <v>384</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N47" s="96">
+        <v>50</v>
+      </c>
+      <c r="O47" s="105" t="s">
+        <v>379</v>
+      </c>
+      <c r="P47" s="96">
+        <v>1.5</v>
+      </c>
+      <c r="Q47" s="96">
+        <f t="shared" ref="Q47" si="36">N47*P47</f>
+        <v>75</v>
+      </c>
+      <c r="R47" s="96"/>
     </row>
     <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C48" s="102" t="s">
-        <v>321</v>
-      </c>
-      <c r="D48" s="103" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="104" t="s">
-        <v>103</v>
-      </c>
-      <c r="F48" s="103" t="s">
-        <v>164</v>
-      </c>
-      <c r="G48" s="104">
-        <v>61300211121</v>
-      </c>
-      <c r="H48" s="103" t="s">
-        <v>235</v>
-      </c>
-      <c r="I48" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J48" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K48" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L48" s="103">
+        <v>38</v>
+      </c>
+      <c r="C48" s="97" t="s">
+        <v>283</v>
+      </c>
+      <c r="D48" s="98" t="s">
+        <v>34</v>
+      </c>
+      <c r="E48" s="99" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="98" t="s">
+        <v>163</v>
+      </c>
+      <c r="G48" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H48" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I48" s="98"/>
+      <c r="J48" s="98"/>
+      <c r="K48" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L48" s="98">
         <v>4</v>
       </c>
-      <c r="M48" s="96">
+      <c r="M48" s="66">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N48" s="96">
-        <v>90</v>
-      </c>
-      <c r="O48" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="P48" s="96">
-        <v>0.13</v>
-      </c>
-      <c r="Q48" s="96">
-        <f t="shared" ref="Q48" si="38">N48*P48</f>
-        <v>11.700000000000001</v>
-      </c>
-      <c r="R48" s="96"/>
+      <c r="N48" s="66">
+        <f t="shared" ref="N48" si="37">M48+(M48*0.1)</f>
+        <v>88</v>
+      </c>
+      <c r="O48" s="66"/>
+      <c r="P48" s="66"/>
+      <c r="Q48" s="66">
+        <f t="shared" ref="Q48" si="38">P48*N48</f>
+        <v>0</v>
+      </c>
+      <c r="R48" s="66" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
-        <f>ROW(B49) - ROW($B$9)</f>
+        <f t="shared" ref="B49:B88" si="39">ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="106" t="s">
-        <v>323</v>
-      </c>
-      <c r="D49" s="107" t="s">
-        <v>439</v>
-      </c>
-      <c r="E49" s="108" t="s">
-        <v>104</v>
-      </c>
-      <c r="F49" s="107" t="s">
-        <v>165</v>
-      </c>
-      <c r="G49" s="108" t="s">
-        <v>200</v>
-      </c>
-      <c r="H49" s="107" t="s">
-        <v>248</v>
-      </c>
-      <c r="I49" s="107" t="s">
-        <v>385</v>
-      </c>
-      <c r="J49" s="107" t="s">
-        <v>386</v>
-      </c>
-      <c r="K49" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L49" s="107">
+      <c r="C49" s="102" t="s">
+        <v>321</v>
+      </c>
+      <c r="D49" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="F49" s="103" t="s">
+        <v>164</v>
+      </c>
+      <c r="G49" s="104">
+        <v>61300211121</v>
+      </c>
+      <c r="H49" s="103" t="s">
+        <v>235</v>
+      </c>
+      <c r="I49" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J49" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K49" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L49" s="103">
         <v>4</v>
       </c>
-      <c r="M49" s="109">
+      <c r="M49" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N49" s="109">
-        <v>85</v>
-      </c>
-      <c r="O49" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="P49" s="109">
-        <v>0.21740000000000001</v>
-      </c>
-      <c r="Q49" s="109">
-        <f t="shared" ref="Q49" si="39">P49*N49</f>
-        <v>18.478999999999999</v>
-      </c>
-      <c r="R49" s="109"/>
+      <c r="N49" s="96">
+        <v>90</v>
+      </c>
+      <c r="O49" s="105" t="s">
+        <v>379</v>
+      </c>
+      <c r="P49" s="96">
+        <v>0.13</v>
+      </c>
+      <c r="Q49" s="96">
+        <f t="shared" ref="Q49" si="40">N49*P49</f>
+        <v>11.700000000000001</v>
+      </c>
+      <c r="R49" s="96"/>
     </row>
     <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C50" s="102" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="D50" s="107" t="s">
+        <v>439</v>
+      </c>
+      <c r="E50" s="108" t="s">
+        <v>104</v>
+      </c>
+      <c r="F50" s="107" t="s">
+        <v>165</v>
+      </c>
+      <c r="G50" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="H50" s="107" t="s">
+        <v>248</v>
+      </c>
+      <c r="I50" s="107" t="s">
+        <v>385</v>
+      </c>
+      <c r="J50" s="107" t="s">
+        <v>386</v>
+      </c>
+      <c r="K50" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L50" s="107">
+        <v>4</v>
+      </c>
+      <c r="M50" s="109">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N50" s="109">
+        <v>85</v>
+      </c>
+      <c r="O50" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P50" s="109">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q50" s="109">
+        <f t="shared" ref="Q50" si="41">P50*N50</f>
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R50" s="109"/>
+    </row>
+    <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1"/>
+      <c r="B51" s="53">
+        <f t="shared" ref="B51:B88" si="42">ROW(B51) - ROW($B$9)</f>
+        <v>42</v>
+      </c>
+      <c r="C51" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D50" s="103" t="s">
+      <c r="D51" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="E50" s="104" t="s">
+      <c r="E51" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="F50" s="103" t="s">
+      <c r="F51" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G50" s="104" t="s">
+      <c r="G51" s="104" t="s">
         <v>201</v>
       </c>
-      <c r="H50" s="103" t="s">
+      <c r="H51" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I50" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J50" s="103" t="s">
+      <c r="I51" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J51" s="103" t="s">
         <v>387</v>
       </c>
-      <c r="K50" s="104" t="s">
+      <c r="K51" s="104" t="s">
         <v>284</v>
       </c>
-      <c r="L50" s="103">
+      <c r="L51" s="103">
         <v>2</v>
       </c>
-      <c r="M50" s="96">
+      <c r="M51" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N50" s="96">
+      <c r="N51" s="96">
         <v>100</v>
       </c>
-      <c r="O50" s="105" t="s">
+      <c r="O51" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P50" s="96">
+      <c r="P51" s="96">
         <v>1E-3</v>
       </c>
-      <c r="Q50" s="96">
-        <f t="shared" ref="Q50" si="40">N50*P50</f>
+      <c r="Q51" s="96">
+        <f t="shared" ref="Q51" si="43">N51*P51</f>
         <v>0.1</v>
       </c>
-      <c r="R50" s="96"/>
-    </row>
-    <row r="51" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1"/>
-      <c r="B51" s="53">
-        <f>ROW(B51) - ROW($B$9)</f>
-        <v>42</v>
-      </c>
-      <c r="C51" s="106" t="s">
+      <c r="R51" s="96"/>
+    </row>
+    <row r="52" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="1"/>
+      <c r="B52" s="53">
+        <v>40</v>
+      </c>
+      <c r="C52" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D51" s="107" t="s">
+      <c r="D52" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="E51" s="108" t="s">
+      <c r="E52" s="108" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="107" t="s">
+      <c r="F52" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="108" t="s">
+      <c r="G52" s="108" t="s">
         <v>202</v>
       </c>
-      <c r="H51" s="107" t="s">
+      <c r="H52" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I51" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J51" s="107" t="s">
+      <c r="I52" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J52" s="107" t="s">
         <v>388</v>
       </c>
-      <c r="K51" s="108" t="s">
+      <c r="K52" s="108" t="s">
         <v>285</v>
       </c>
-      <c r="L51" s="107">
+      <c r="L52" s="107">
         <v>1</v>
       </c>
-      <c r="M51" s="109">
+      <c r="M52" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N51" s="109">
+      <c r="N52" s="109">
         <v>100</v>
       </c>
-      <c r="O51" s="110" t="s">
+      <c r="O52" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P51" s="109">
+      <c r="P52" s="109">
         <v>1.4E-3</v>
       </c>
-      <c r="Q51" s="109">
-        <f t="shared" ref="Q51" si="41">P51*N51</f>
+      <c r="Q52" s="109">
+        <f t="shared" ref="Q52" si="44">P52*N52</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R51" s="109"/>
-    </row>
-    <row r="52" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1"/>
-      <c r="B52" s="53">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="C52" s="102" t="s">
+      <c r="R52" s="109"/>
+    </row>
+    <row r="53" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="1"/>
+      <c r="B53" s="53">
+        <f t="shared" ref="B53:B88" si="45">ROW(B53) - ROW($B$9)</f>
+        <v>44</v>
+      </c>
+      <c r="C53" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D52" s="103" t="s">
+      <c r="D53" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="E52" s="104" t="s">
+      <c r="E53" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="103" t="s">
+      <c r="F53" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="104" t="s">
+      <c r="G53" s="104" t="s">
         <v>203</v>
       </c>
-      <c r="H52" s="103" t="s">
+      <c r="H53" s="103" t="s">
         <v>249</v>
       </c>
-      <c r="I52" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J52" s="103" t="s">
+      <c r="I53" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J53" s="103" t="s">
         <v>389</v>
       </c>
-      <c r="K52" s="104" t="s">
+      <c r="K53" s="104" t="s">
         <v>286</v>
       </c>
-      <c r="L52" s="103">
+      <c r="L53" s="103">
         <v>1</v>
       </c>
-      <c r="M52" s="96">
+      <c r="M53" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N52" s="96">
+      <c r="N53" s="96">
         <v>100</v>
       </c>
-      <c r="O52" s="105" t="s">
+      <c r="O53" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P52" s="96">
+      <c r="P53" s="96">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q52" s="96">
-        <f t="shared" ref="Q52" si="42">N52*P52</f>
+      <c r="Q53" s="96">
+        <f t="shared" ref="Q53" si="46">N53*P53</f>
         <v>0.16</v>
       </c>
-      <c r="R52" s="96"/>
-    </row>
-    <row r="53" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1"/>
-      <c r="B53" s="53">
-        <f>ROW(B53) - ROW($B$9)</f>
-        <v>44</v>
-      </c>
-      <c r="C53" s="106" t="s">
-        <v>324</v>
-      </c>
-      <c r="D53" s="107" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="108" t="s">
-        <v>108</v>
-      </c>
-      <c r="F53" s="107" t="s">
-        <v>166</v>
-      </c>
-      <c r="G53" s="108" t="s">
-        <v>204</v>
-      </c>
-      <c r="H53" s="107" t="s">
-        <v>229</v>
-      </c>
-      <c r="I53" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J53" s="107" t="s">
-        <v>390</v>
-      </c>
-      <c r="K53" s="108" t="s">
-        <v>287</v>
-      </c>
-      <c r="L53" s="107">
-        <v>2</v>
-      </c>
-      <c r="M53" s="109">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N53" s="109">
-        <v>100</v>
-      </c>
-      <c r="O53" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="P53" s="109">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q53" s="109">
-        <f t="shared" ref="Q53" si="43">P53*N53</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R53" s="109"/>
+      <c r="R53" s="96"/>
     </row>
     <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="C54" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D54" s="103" t="s">
+      <c r="D54" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="E54" s="108" t="s">
+        <v>108</v>
+      </c>
+      <c r="F54" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" s="108" t="s">
+        <v>204</v>
+      </c>
+      <c r="H54" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="I54" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J54" s="107" t="s">
+        <v>390</v>
+      </c>
+      <c r="K54" s="108" t="s">
+        <v>287</v>
+      </c>
+      <c r="L54" s="107">
+        <v>2</v>
+      </c>
+      <c r="M54" s="109">
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="E54" s="104" t="s">
+      <c r="N54" s="109">
+        <v>100</v>
+      </c>
+      <c r="O54" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P54" s="109">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q54" s="109">
+        <f t="shared" ref="Q54" si="47">P54*N54</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R54" s="109"/>
+    </row>
+    <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="1"/>
+      <c r="B55" s="53">
+        <f t="shared" ref="B55:B88" si="48">ROW(B55) - ROW($B$9)</f>
+        <v>46</v>
+      </c>
+      <c r="C55" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D55" s="103" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="F54" s="103" t="s">
+      <c r="F55" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="104" t="s">
+      <c r="G55" s="104" t="s">
         <v>205</v>
       </c>
-      <c r="H54" s="103" t="s">
+      <c r="H55" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I54" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J54" s="103" t="s">
+      <c r="I55" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J55" s="103" t="s">
         <v>391</v>
       </c>
-      <c r="K54" s="104" t="s">
+      <c r="K55" s="104" t="s">
         <v>288</v>
       </c>
-      <c r="L54" s="103">
+      <c r="L55" s="103">
         <v>4</v>
       </c>
-      <c r="M54" s="96">
+      <c r="M55" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N54" s="96">
+      <c r="N55" s="96">
         <v>100</v>
       </c>
-      <c r="O54" s="105" t="s">
+      <c r="O55" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P54" s="96">
+      <c r="P55" s="96">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q54" s="96">
-        <f t="shared" ref="Q54" si="44">N54*P54</f>
+      <c r="Q55" s="96">
+        <f t="shared" ref="Q55" si="49">N55*P55</f>
         <v>0.13</v>
       </c>
-      <c r="R54" s="96"/>
-    </row>
-    <row r="55" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1"/>
-      <c r="B55" s="53">
-        <f>ROW(B55) - ROW($B$9)</f>
-        <v>46</v>
-      </c>
-      <c r="C55" s="106" t="s">
+      <c r="R55" s="96"/>
+    </row>
+    <row r="56" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="1"/>
+      <c r="B56" s="53">
+        <v>42</v>
+      </c>
+      <c r="C56" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D55" s="107" t="s">
+      <c r="D56" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="E55" s="108" t="s">
+      <c r="E56" s="108" t="s">
         <v>110</v>
       </c>
-      <c r="F55" s="107" t="s">
+      <c r="F56" s="107" t="s">
         <v>167</v>
       </c>
-      <c r="G55" s="108" t="s">
+      <c r="G56" s="108" t="s">
         <v>329</v>
       </c>
-      <c r="H55" s="107" t="s">
+      <c r="H56" s="107" t="s">
         <v>250</v>
       </c>
-      <c r="I55" s="107" t="s">
+      <c r="I56" s="107" t="s">
         <v>392</v>
       </c>
-      <c r="J55" s="107" t="s">
+      <c r="J56" s="107" t="s">
         <v>393</v>
       </c>
-      <c r="K55" s="108" t="s">
+      <c r="K56" s="108" t="s">
         <v>289</v>
       </c>
-      <c r="L55" s="107">
+      <c r="L56" s="107">
         <v>4</v>
       </c>
-      <c r="M55" s="109">
+      <c r="M56" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N55" s="109">
+      <c r="N56" s="109">
         <v>90</v>
       </c>
-      <c r="O55" s="110" t="s">
+      <c r="O56" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P55" s="109">
+      <c r="P56" s="109">
         <v>6.4500000000000002E-2</v>
       </c>
-      <c r="Q55" s="109">
-        <f t="shared" ref="Q55" si="45">P55*N55</f>
+      <c r="Q56" s="109">
+        <f t="shared" ref="Q56" si="50">P56*N56</f>
         <v>5.8049999999999997</v>
       </c>
-      <c r="R55" s="109"/>
-    </row>
-    <row r="56" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="1"/>
-      <c r="B56" s="53">
-        <f>ROW(B56) - ROW($B$9)</f>
-        <v>47</v>
-      </c>
-      <c r="C56" s="60" t="s">
-        <v>324</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>423</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>440</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>425</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>426</v>
-      </c>
-      <c r="K56" s="37" t="s">
-        <v>427</v>
-      </c>
-      <c r="L56" s="37">
-        <v>8</v>
-      </c>
-      <c r="M56" s="37">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N56" s="96">
-        <v>100</v>
-      </c>
-      <c r="O56" s="80" t="s">
-        <v>343</v>
-      </c>
-      <c r="P56" s="37">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q56" s="37">
-        <f t="shared" ref="Q56" si="46">N56*P56</f>
-        <v>0.11</v>
-      </c>
-      <c r="R56" s="76"/>
+      <c r="R56" s="109"/>
     </row>
     <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
-        <f>ROW(B57) - ROW($B$9)</f>
+        <f t="shared" ref="B57:B88" si="51">ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="106" t="s">
+      <c r="C57" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D57" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="E57" s="108" t="s">
-        <v>112</v>
-      </c>
-      <c r="F57" s="107" t="s">
+      <c r="D57" s="37" t="s">
+        <v>423</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="F57" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="108" t="s">
-        <v>207</v>
-      </c>
-      <c r="H57" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="I57" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J57" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K57" s="108" t="s">
-        <v>291</v>
-      </c>
-      <c r="L57" s="107">
-        <v>1</v>
-      </c>
-      <c r="M57" s="109">
+      <c r="G57" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>427</v>
+      </c>
+      <c r="L57" s="37">
+        <v>8</v>
+      </c>
+      <c r="M57" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N57" s="109">
-        <v>30</v>
-      </c>
-      <c r="O57" s="110" t="s">
-        <v>382</v>
-      </c>
-      <c r="P57" s="109">
-        <v>1.8589999999999999E-2</v>
-      </c>
-      <c r="Q57" s="109">
-        <f t="shared" ref="Q57" si="47">P57*N57</f>
-        <v>0.55769999999999997</v>
-      </c>
-      <c r="R57" s="109"/>
+        <v>160</v>
+      </c>
+      <c r="N57" s="96">
+        <v>100</v>
+      </c>
+      <c r="O57" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="P57" s="37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q57" s="37">
+        <f t="shared" ref="Q57" si="52">N57*P57</f>
+        <v>0.11</v>
+      </c>
+      <c r="R57" s="76"/>
     </row>
     <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="C58" s="102" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D58" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="E58" s="104" t="s">
-        <v>113</v>
-      </c>
-      <c r="F58" s="103" t="s">
+      <c r="D58" s="107" t="s">
+        <v>42</v>
+      </c>
+      <c r="E58" s="108" t="s">
+        <v>112</v>
+      </c>
+      <c r="F58" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="104" t="s">
-        <v>208</v>
-      </c>
-      <c r="H58" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I58" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J58" s="103" t="s">
-        <v>395</v>
-      </c>
-      <c r="K58" s="104" t="s">
-        <v>292</v>
-      </c>
-      <c r="L58" s="103">
+      <c r="G58" s="108" t="s">
+        <v>207</v>
+      </c>
+      <c r="H58" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I58" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J58" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K58" s="108" t="s">
+        <v>291</v>
+      </c>
+      <c r="L58" s="107">
         <v>1</v>
       </c>
-      <c r="M58" s="96">
+      <c r="M58" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N58" s="96">
-        <v>100</v>
-      </c>
-      <c r="O58" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P58" s="96">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q58" s="96">
-        <f t="shared" ref="Q58" si="48">N58*P58</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R58" s="96"/>
+      <c r="N58" s="109">
+        <v>30</v>
+      </c>
+      <c r="O58" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P58" s="109">
+        <v>1.8589999999999999E-2</v>
+      </c>
+      <c r="Q58" s="109">
+        <f t="shared" ref="Q58" si="53">P58*N58</f>
+        <v>0.55769999999999997</v>
+      </c>
+      <c r="R58" s="109"/>
     </row>
     <row r="59" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
-        <f>ROW(B59) - ROW($B$9)</f>
+        <f t="shared" ref="B59:B88" si="54">ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="106" t="s">
+      <c r="C59" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D59" s="107" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" s="108" t="s">
-        <v>114</v>
-      </c>
-      <c r="F59" s="107" t="s">
+      <c r="D59" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="F59" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G59" s="108" t="s">
-        <v>209</v>
-      </c>
-      <c r="H59" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="I59" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J59" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K59" s="108" t="s">
-        <v>293</v>
-      </c>
-      <c r="L59" s="107">
+      <c r="G59" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="H59" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I59" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" s="103" t="s">
+        <v>395</v>
+      </c>
+      <c r="K59" s="104" t="s">
+        <v>292</v>
+      </c>
+      <c r="L59" s="103">
         <v>1</v>
       </c>
-      <c r="M59" s="109">
+      <c r="M59" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N59" s="109">
-        <v>50</v>
-      </c>
-      <c r="O59" s="110" t="s">
-        <v>382</v>
-      </c>
-      <c r="P59" s="109">
-        <v>4.6699999999999997E-3</v>
-      </c>
-      <c r="Q59" s="109">
-        <f t="shared" ref="Q59" si="49">P59*N59</f>
-        <v>0.23349999999999999</v>
-      </c>
-      <c r="R59" s="109"/>
+      <c r="N59" s="96">
+        <v>100</v>
+      </c>
+      <c r="O59" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P59" s="96">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q59" s="96">
+        <f t="shared" ref="Q59" si="55">N59*P59</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R59" s="96"/>
     </row>
     <row r="60" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="C60" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D60" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="E60" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="F60" s="103" t="s">
+      <c r="D60" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="108" t="s">
+        <v>114</v>
+      </c>
+      <c r="F60" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G60" s="104" t="s">
-        <v>210</v>
-      </c>
-      <c r="H60" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I60" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J60" s="103" t="s">
-        <v>396</v>
-      </c>
-      <c r="K60" s="104" t="s">
-        <v>294</v>
-      </c>
-      <c r="L60" s="103">
+      <c r="G60" s="108" t="s">
+        <v>209</v>
+      </c>
+      <c r="H60" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I60" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J60" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K60" s="108" t="s">
+        <v>293</v>
+      </c>
+      <c r="L60" s="107">
         <v>1</v>
       </c>
-      <c r="M60" s="96">
+      <c r="M60" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="96">
-        <v>100</v>
-      </c>
-      <c r="O60" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P60" s="96">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q60" s="96">
-        <f t="shared" ref="Q60" si="50">N60*P60</f>
-        <v>0.12</v>
-      </c>
-      <c r="R60" s="96"/>
+      <c r="N60" s="109">
+        <v>50</v>
+      </c>
+      <c r="O60" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P60" s="109">
+        <v>4.6699999999999997E-3</v>
+      </c>
+      <c r="Q60" s="109">
+        <f t="shared" ref="Q60" si="56">P60*N60</f>
+        <v>0.23349999999999999</v>
+      </c>
+      <c r="R60" s="109"/>
     </row>
     <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f>ROW(B61) - ROW($B$9)</f>
+        <f t="shared" ref="B61:B88" si="57">ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="106" t="s">
+      <c r="C61" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D61" s="107" t="s">
-        <v>46</v>
-      </c>
-      <c r="E61" s="108" t="s">
-        <v>116</v>
-      </c>
-      <c r="F61" s="107" t="s">
+      <c r="D61" s="103" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="F61" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G61" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="H61" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="I61" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J61" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K61" s="108" t="s">
-        <v>295</v>
-      </c>
-      <c r="L61" s="107">
+      <c r="G61" s="104" t="s">
+        <v>210</v>
+      </c>
+      <c r="H61" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I61" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J61" s="103" t="s">
+        <v>396</v>
+      </c>
+      <c r="K61" s="104" t="s">
+        <v>294</v>
+      </c>
+      <c r="L61" s="103">
         <v>1</v>
       </c>
-      <c r="M61" s="109">
+      <c r="M61" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="109">
-        <v>50</v>
-      </c>
-      <c r="O61" s="110" t="s">
-        <v>382</v>
-      </c>
-      <c r="P61" s="109">
-        <v>1.11E-2</v>
-      </c>
-      <c r="Q61" s="109">
-        <f t="shared" ref="Q61" si="51">P61*N61</f>
-        <v>0.55500000000000005</v>
-      </c>
-      <c r="R61" s="109"/>
+      <c r="N61" s="96">
+        <v>100</v>
+      </c>
+      <c r="O61" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P61" s="96">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q61" s="96">
+        <f t="shared" ref="Q61" si="58">N61*P61</f>
+        <v>0.12</v>
+      </c>
+      <c r="R61" s="96"/>
     </row>
     <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="C62" s="102" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D62" s="103" t="s">
-        <v>47</v>
-      </c>
-      <c r="E62" s="104" t="s">
-        <v>117</v>
-      </c>
-      <c r="F62" s="103" t="s">
+      <c r="D62" s="107" t="s">
+        <v>46</v>
+      </c>
+      <c r="E62" s="108" t="s">
+        <v>116</v>
+      </c>
+      <c r="F62" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G62" s="104" t="s">
-        <v>212</v>
-      </c>
-      <c r="H62" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I62" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="103" t="s">
-        <v>397</v>
-      </c>
-      <c r="K62" s="104" t="s">
-        <v>296</v>
-      </c>
-      <c r="L62" s="103">
+      <c r="G62" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="H62" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I62" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K62" s="108" t="s">
+        <v>295</v>
+      </c>
+      <c r="L62" s="107">
         <v>1</v>
       </c>
-      <c r="M62" s="96">
+      <c r="M62" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N62" s="96">
-        <v>100</v>
-      </c>
-      <c r="O62" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P62" s="96">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q62" s="96">
-        <f t="shared" ref="Q62" si="52">N62*P62</f>
-        <v>0.21</v>
-      </c>
-      <c r="R62" s="96"/>
+      <c r="N62" s="109">
+        <v>50</v>
+      </c>
+      <c r="O62" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P62" s="109">
+        <v>1.11E-2</v>
+      </c>
+      <c r="Q62" s="109">
+        <f t="shared" ref="Q62" si="59">P62*N62</f>
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="R62" s="109"/>
     </row>
     <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
-        <f>ROW(B63) - ROW($B$9)</f>
+        <f t="shared" ref="B63:B88" si="60">ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="106" t="s">
+      <c r="C63" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D63" s="107" t="s">
-        <v>48</v>
-      </c>
-      <c r="E63" s="108" t="s">
-        <v>118</v>
-      </c>
-      <c r="F63" s="107" t="s">
+      <c r="D63" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="F63" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G63" s="108" t="s">
-        <v>213</v>
-      </c>
-      <c r="H63" s="107" t="s">
+      <c r="G63" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="H63" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I63" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J63" s="107" t="s">
-        <v>398</v>
-      </c>
-      <c r="K63" s="108" t="s">
-        <v>297</v>
-      </c>
-      <c r="L63" s="107">
+      <c r="I63" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="103" t="s">
+        <v>397</v>
+      </c>
+      <c r="K63" s="104" t="s">
+        <v>296</v>
+      </c>
+      <c r="L63" s="103">
         <v>1</v>
       </c>
-      <c r="M63" s="109">
+      <c r="M63" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N63" s="109">
+      <c r="N63" s="96">
         <v>100</v>
       </c>
-      <c r="O63" s="110" t="s">
+      <c r="O63" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P63" s="109">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="Q63" s="109">
-        <f t="shared" ref="Q63" si="53">P63*N63</f>
-        <v>0.16</v>
-      </c>
-      <c r="R63" s="109"/>
+      <c r="P63" s="96">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="Q63" s="96">
+        <f t="shared" ref="Q63" si="61">N63*P63</f>
+        <v>0.21</v>
+      </c>
+      <c r="R63" s="96"/>
     </row>
     <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="C64" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D64" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="E64" s="104" t="s">
-        <v>119</v>
-      </c>
-      <c r="F64" s="103" t="s">
+      <c r="D64" s="107" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="F64" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G64" s="104" t="s">
-        <v>214</v>
-      </c>
-      <c r="H64" s="103" t="s">
+      <c r="G64" s="108" t="s">
+        <v>213</v>
+      </c>
+      <c r="H64" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I64" s="103" t="s">
-        <v>399</v>
-      </c>
-      <c r="J64" s="103" t="s">
-        <v>400</v>
-      </c>
-      <c r="K64" s="104" t="s">
-        <v>298</v>
-      </c>
-      <c r="L64" s="103">
+      <c r="I64" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J64" s="107" t="s">
+        <v>398</v>
+      </c>
+      <c r="K64" s="108" t="s">
+        <v>297</v>
+      </c>
+      <c r="L64" s="107">
         <v>1</v>
       </c>
-      <c r="M64" s="96">
+      <c r="M64" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N64" s="96">
-        <v>50</v>
-      </c>
-      <c r="O64" s="105" t="s">
+      <c r="N64" s="109">
+        <v>100</v>
+      </c>
+      <c r="O64" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P64" s="96">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="Q64" s="96">
-        <f t="shared" ref="Q64" si="54">N64*P64</f>
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="R64" s="96"/>
-    </row>
-    <row r="65" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P64" s="109">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q64" s="109">
+        <f t="shared" ref="Q64" si="62">P64*N64</f>
+        <v>0.16</v>
+      </c>
+      <c r="R64" s="109"/>
+    </row>
+    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
-        <f>ROW(B65) - ROW($B$9)</f>
+        <f t="shared" ref="B65:B88" si="63">ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="106" t="s">
+      <c r="C65" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D65" s="107" t="s">
+      <c r="D65" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="E65" s="104" t="s">
+        <v>119</v>
+      </c>
+      <c r="F65" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G65" s="104" t="s">
+        <v>214</v>
+      </c>
+      <c r="H65" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I65" s="103" t="s">
+        <v>399</v>
+      </c>
+      <c r="J65" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="K65" s="104" t="s">
+        <v>298</v>
+      </c>
+      <c r="L65" s="103">
+        <v>1</v>
+      </c>
+      <c r="M65" s="96">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N65" s="96">
+        <v>50</v>
+      </c>
+      <c r="O65" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P65" s="96">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="Q65" s="96">
+        <f t="shared" ref="Q65" si="64">N65*P65</f>
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="R65" s="96"/>
+    </row>
+    <row r="66" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="1"/>
+      <c r="B66" s="53">
+        <v>47</v>
+      </c>
+      <c r="C66" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D66" s="107" t="s">
         <v>462</v>
       </c>
-      <c r="E65" s="108" t="s">
+      <c r="E66" s="108" t="s">
         <v>120</v>
       </c>
-      <c r="F65" s="107" t="s">
+      <c r="F66" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G65" s="108" t="s">
+      <c r="G66" s="108" t="s">
         <v>215</v>
       </c>
-      <c r="H65" s="107" t="s">
+      <c r="H66" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I65" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J65" s="107" t="s">
+      <c r="I66" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J66" s="107" t="s">
         <v>401</v>
       </c>
-      <c r="K65" s="108" t="s">
+      <c r="K66" s="108" t="s">
         <v>299</v>
       </c>
-      <c r="L65" s="107">
+      <c r="L66" s="107">
         <v>2</v>
       </c>
-      <c r="M65" s="109">
+      <c r="M66" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N65" s="109">
+      <c r="N66" s="109">
         <v>100</v>
       </c>
-      <c r="O65" s="110" t="s">
+      <c r="O66" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P65" s="109">
+      <c r="P66" s="109">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q65" s="109">
-        <f t="shared" ref="Q65" si="55">P65*N65</f>
+      <c r="Q66" s="109">
+        <f t="shared" ref="Q66" si="65">P66*N66</f>
         <v>0.11</v>
       </c>
-      <c r="R65" s="109"/>
-    </row>
-    <row r="66" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1"/>
-      <c r="B66" s="53">
-        <f>ROW(B66) - ROW($B$9)</f>
-        <v>57</v>
-      </c>
-      <c r="C66" s="60" t="s">
+      <c r="R66" s="109"/>
+    </row>
+    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="1"/>
+      <c r="B67" s="53">
+        <f t="shared" ref="B67:B88" si="66">ROW(B67) - ROW($B$9)</f>
+        <v>58</v>
+      </c>
+      <c r="C67" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D66" s="37" t="s">
+      <c r="D67" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="38" t="s">
+      <c r="E67" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="F66" s="37" t="s">
+      <c r="F67" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G66" s="38" t="s">
+      <c r="G67" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="H66" s="37" t="s">
+      <c r="H67" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="I66" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J66" s="37" t="s">
+      <c r="I67" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J67" s="37" t="s">
         <v>402</v>
       </c>
-      <c r="K66" s="38" t="s">
+      <c r="K67" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="L66" s="37">
+      <c r="L67" s="37">
         <v>2</v>
       </c>
-      <c r="M66" s="41">
+      <c r="M67" s="41">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N66" s="41">
+      <c r="N67" s="41">
         <v>100</v>
       </c>
-      <c r="O66" s="63" t="s">
+      <c r="O67" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="P66" s="41">
+      <c r="P67" s="41">
         <v>1.5E-3</v>
       </c>
-      <c r="Q66" s="41">
-        <f t="shared" ref="Q66" si="56">P66*N66</f>
+      <c r="Q67" s="41">
+        <f t="shared" ref="Q67" si="67">P67*N67</f>
         <v>0.15</v>
       </c>
-      <c r="R66" s="41"/>
-    </row>
-    <row r="67" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="1"/>
-      <c r="B67" s="53">
-        <f>ROW(B67) - ROW($B$9)</f>
-        <v>58</v>
-      </c>
-      <c r="C67" s="59" t="s">
-        <v>324</v>
-      </c>
-      <c r="D67" s="87" t="s">
-        <v>424</v>
-      </c>
-      <c r="E67" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="F67" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="G67" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="H67" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="K67" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="L67" s="39">
-        <v>1</v>
-      </c>
-      <c r="M67" s="42">
-        <f>L67*20</f>
-        <v>20</v>
-      </c>
-      <c r="N67" s="42">
-        <v>100</v>
-      </c>
-      <c r="O67" s="64" t="s">
-        <v>343</v>
-      </c>
-      <c r="P67" s="42">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q67" s="42">
-        <f>N67*P67</f>
-        <v>0.15</v>
-      </c>
-      <c r="R67" s="77"/>
-    </row>
-    <row r="68" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R67" s="41"/>
+    </row>
+    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
-        <f>ROW(B68) - ROW($B$9)</f>
-        <v>59</v>
-      </c>
-      <c r="C68" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D68" s="37" t="s">
+      <c r="D68" s="87" t="s">
+        <v>424</v>
+      </c>
+      <c r="E68" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="F68" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G68" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="H68" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="I68" s="39"/>
+      <c r="J68" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="K68" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="L68" s="39">
+        <v>1</v>
+      </c>
+      <c r="M68" s="42">
+        <f>L68*20</f>
+        <v>20</v>
+      </c>
+      <c r="N68" s="42">
+        <v>100</v>
+      </c>
+      <c r="O68" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P68" s="42">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q68" s="42">
+        <f>N68*P68</f>
+        <v>0.15</v>
+      </c>
+      <c r="R68" s="77"/>
+    </row>
+    <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="1"/>
+      <c r="B69" s="53">
+        <f t="shared" ref="B69:B88" si="68">ROW(B69) - ROW($B$9)</f>
+        <v>60</v>
+      </c>
+      <c r="C69" s="60" t="s">
+        <v>324</v>
+      </c>
+      <c r="D69" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="38" t="s">
+      <c r="E69" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="F68" s="37" t="s">
+      <c r="F69" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G68" s="38" t="s">
+      <c r="G69" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="H68" s="37" t="s">
+      <c r="H69" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="I68" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J68" s="37" t="s">
+      <c r="I69" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J69" s="37" t="s">
         <v>403</v>
       </c>
-      <c r="K68" s="38" t="s">
+      <c r="K69" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="L68" s="37">
+      <c r="L69" s="37">
         <v>2</v>
       </c>
-      <c r="M68" s="41">
+      <c r="M69" s="41">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N68" s="41">
+      <c r="N69" s="41">
         <v>100</v>
       </c>
-      <c r="O68" s="63" t="s">
+      <c r="O69" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="P68" s="41">
+      <c r="P69" s="41">
         <v>1.5E-3</v>
       </c>
-      <c r="Q68" s="41">
-        <f t="shared" ref="Q68" si="57">P68*N68</f>
+      <c r="Q69" s="41">
+        <f t="shared" ref="Q69" si="69">P69*N69</f>
         <v>0.15</v>
       </c>
-      <c r="R68" s="41"/>
-    </row>
-    <row r="69" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="1"/>
-      <c r="B69" s="53">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="C69" s="59" t="s">
+      <c r="R69" s="41"/>
+    </row>
+    <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="1"/>
+      <c r="B70" s="53">
+        <v>49</v>
+      </c>
+      <c r="C70" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D69" s="39" t="s">
+      <c r="D70" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E69" s="40" t="s">
+      <c r="E70" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="F69" s="39" t="s">
+      <c r="F70" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="G69" s="40" t="s">
+      <c r="G70" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="H69" s="39" t="s">
+      <c r="H70" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="I69" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J69" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K69" s="40" t="s">
+      <c r="I70" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J70" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K70" s="40" t="s">
         <v>302</v>
       </c>
-      <c r="L69" s="39">
+      <c r="L70" s="39">
         <v>1</v>
       </c>
-      <c r="M69" s="42">
+      <c r="M70" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N69" s="42">
+      <c r="N70" s="42">
         <v>25</v>
       </c>
-      <c r="O69" s="64" t="s">
+      <c r="O70" s="64" t="s">
         <v>404</v>
       </c>
-      <c r="P69" s="42">
+      <c r="P70" s="42">
         <v>8.5400000000000004E-2</v>
       </c>
-      <c r="Q69" s="42">
-        <f t="shared" ref="Q69" si="58">N69*P69</f>
+      <c r="Q70" s="42">
+        <f t="shared" ref="Q70" si="70">N70*P70</f>
         <v>2.1350000000000002</v>
       </c>
-      <c r="R69" s="42"/>
-    </row>
-    <row r="70" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1"/>
-      <c r="B70" s="53">
-        <f>ROW(B70) - ROW($B$9)</f>
-        <v>61</v>
-      </c>
-      <c r="C70" s="60" t="s">
-        <v>324</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E70" s="38" t="s">
-        <v>434</v>
-      </c>
-      <c r="F70" s="86" t="s">
-        <v>166</v>
-      </c>
-      <c r="G70" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="H70" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="I70" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J70" s="37" t="s">
-        <v>435</v>
-      </c>
-      <c r="K70" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="L70" s="37">
-        <v>1</v>
-      </c>
-      <c r="M70" s="41">
-        <f t="shared" ref="M70:M87" si="59">L70*20</f>
-        <v>20</v>
-      </c>
-      <c r="N70" s="41">
-        <v>50</v>
-      </c>
-      <c r="O70" s="63" t="s">
-        <v>343</v>
-      </c>
-      <c r="P70" s="41">
-        <v>3.8E-3</v>
-      </c>
-      <c r="Q70" s="41">
-        <f t="shared" ref="Q70" si="60">P70*N70</f>
-        <v>0.19</v>
-      </c>
-      <c r="R70" s="76"/>
-    </row>
-    <row r="71" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R70" s="42"/>
+    </row>
+    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f>ROW(B71) - ROW($B$9)</f>
+        <f t="shared" ref="B71:B88" si="71">ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="59" t="s">
+      <c r="C71" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D71" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="E71" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="F71" s="39" t="s">
+      <c r="D71" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E71" s="38" t="s">
+        <v>434</v>
+      </c>
+      <c r="F71" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G71" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="H71" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="I71" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J71" s="39" t="s">
-        <v>408</v>
-      </c>
-      <c r="K71" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="L71" s="39">
-        <v>6</v>
-      </c>
-      <c r="M71" s="42">
-        <f>L71*20</f>
-        <v>120</v>
-      </c>
-      <c r="N71" s="42">
-        <v>200</v>
-      </c>
-      <c r="O71" s="64" t="s">
+      <c r="G71" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="K71" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="L71" s="37">
+        <v>1</v>
+      </c>
+      <c r="M71" s="41">
+        <f t="shared" ref="M71:M88" si="72">L71*20</f>
+        <v>20</v>
+      </c>
+      <c r="N71" s="41">
+        <v>50</v>
+      </c>
+      <c r="O71" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="P71" s="42">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q71" s="42">
-        <f t="shared" ref="Q71" si="61">N71*P71</f>
-        <v>0.24</v>
-      </c>
-      <c r="R71" s="77"/>
-    </row>
-    <row r="72" spans="1:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P71" s="41">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q71" s="41">
+        <f t="shared" ref="Q71" si="73">P71*N71</f>
+        <v>0.19</v>
+      </c>
+      <c r="R71" s="76"/>
+    </row>
+    <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
-        <f>ROW(B72) - ROW($B$9)</f>
-        <v>63</v>
-      </c>
-      <c r="C72" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C72" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D72" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="F72" s="37" t="s">
+      <c r="D72" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="E72" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="F72" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="G72" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J72" s="37" t="s">
-        <v>405</v>
-      </c>
-      <c r="K72" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="L72" s="37">
-        <v>1</v>
-      </c>
-      <c r="M72" s="41">
-        <f t="shared" si="59"/>
-        <v>20</v>
-      </c>
-      <c r="N72" s="41">
-        <v>100</v>
-      </c>
-      <c r="O72" s="63" t="s">
+      <c r="G72" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="H72" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="I72" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J72" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="K72" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="L72" s="39">
+        <v>6</v>
+      </c>
+      <c r="M72" s="42">
+        <f>L72*20</f>
+        <v>120</v>
+      </c>
+      <c r="N72" s="42">
+        <v>200</v>
+      </c>
+      <c r="O72" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="P72" s="41">
-        <v>1E-3</v>
-      </c>
-      <c r="Q72" s="41">
-        <f t="shared" ref="Q72" si="62">P72*N72</f>
-        <v>0.1</v>
-      </c>
-      <c r="R72" s="41"/>
-    </row>
-    <row r="73" spans="1:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P72" s="42">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q72" s="42">
+        <f t="shared" ref="Q72" si="74">N72*P72</f>
+        <v>0.24</v>
+      </c>
+      <c r="R72" s="77"/>
+    </row>
+    <row r="73" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B73:B88" si="75">ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
-      <c r="C73" s="59" t="s">
+      <c r="C73" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D73" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="E73" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="F73" s="39" t="s">
+      <c r="D73" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F73" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G73" s="40" t="s">
-        <v>331</v>
-      </c>
-      <c r="H73" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="I73" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J73" s="39" t="s">
-        <v>406</v>
-      </c>
-      <c r="K73" s="40" t="s">
-        <v>304</v>
-      </c>
-      <c r="L73" s="39">
+      <c r="G73" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="H73" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="I73" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J73" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="K73" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="L73" s="37">
         <v>1</v>
       </c>
-      <c r="M73" s="42">
-        <f t="shared" si="59"/>
+      <c r="M73" s="41">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N73" s="42">
-        <v>50</v>
-      </c>
-      <c r="O73" s="64" t="s">
+      <c r="N73" s="41">
+        <v>100</v>
+      </c>
+      <c r="O73" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="P73" s="42">
-        <v>4.3E-3</v>
-      </c>
-      <c r="Q73" s="42">
-        <f t="shared" ref="Q73" si="63">N73*P73</f>
-        <v>0.215</v>
-      </c>
-      <c r="R73" s="42"/>
-    </row>
-    <row r="74" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P73" s="41">
+        <v>1E-3</v>
+      </c>
+      <c r="Q73" s="41">
+        <f t="shared" ref="Q73" si="76">P73*N73</f>
+        <v>0.1</v>
+      </c>
+      <c r="R73" s="41"/>
+    </row>
+    <row r="74" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
-        <f>ROW(B74) - ROW($B$9)</f>
-        <v>65</v>
-      </c>
-      <c r="C74" s="97" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D74" s="98" t="s">
-        <v>56</v>
-      </c>
-      <c r="E74" s="99" t="s">
-        <v>126</v>
-      </c>
-      <c r="F74" s="98" t="s">
-        <v>168</v>
-      </c>
-      <c r="G74" s="99" t="s">
-        <v>219</v>
-      </c>
-      <c r="H74" s="98" t="s">
-        <v>229</v>
-      </c>
-      <c r="I74" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="J74" s="98" t="s">
-        <v>407</v>
-      </c>
-      <c r="K74" s="99" t="s">
-        <v>305</v>
-      </c>
-      <c r="L74" s="98">
-        <v>4</v>
-      </c>
-      <c r="M74" s="66">
-        <f t="shared" si="59"/>
-        <v>80</v>
-      </c>
-      <c r="N74" s="66">
-        <v>100</v>
-      </c>
-      <c r="O74" s="100" t="s">
+      <c r="D74" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E74" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="F74" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G74" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="H74" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="I74" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J74" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="K74" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="L74" s="39">
+        <v>1</v>
+      </c>
+      <c r="M74" s="42">
+        <f t="shared" si="72"/>
+        <v>20</v>
+      </c>
+      <c r="N74" s="42">
+        <v>50</v>
+      </c>
+      <c r="O74" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="P74" s="66">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q74" s="66">
-        <f t="shared" ref="Q74" si="64">P74*N74</f>
-        <v>0.12</v>
-      </c>
-      <c r="R74" s="66" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P74" s="42">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q74" s="42">
+        <f t="shared" ref="Q74" si="77">N74*P74</f>
+        <v>0.215</v>
+      </c>
+      <c r="R74" s="42"/>
+    </row>
+    <row r="75" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
-        <f>ROW(B75) - ROW($B$9)</f>
+        <f t="shared" ref="B75:B88" si="78">ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
       <c r="C75" s="97" t="s">
-        <v>169</v>
+        <v>324</v>
       </c>
       <c r="D75" s="98" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="E75" s="99" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F75" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G75" s="99" t="s">
-        <v>314</v>
+        <v>219</v>
       </c>
       <c r="H75" s="98" t="s">
-        <v>314</v>
+        <v>229</v>
       </c>
       <c r="I75" s="98" t="s">
         <v>314</v>
       </c>
       <c r="J75" s="98" t="s">
-        <v>314</v>
+        <v>407</v>
       </c>
       <c r="K75" s="99" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L75" s="98">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M75" s="66">
-        <f t="shared" si="59"/>
-        <v>300</v>
+        <f t="shared" si="72"/>
+        <v>80</v>
       </c>
       <c r="N75" s="66">
-        <f t="shared" ref="N75:N76" si="65">M75+(M75*0.1)</f>
-        <v>330</v>
-      </c>
-      <c r="O75" s="66"/>
-      <c r="P75" s="66"/>
+        <v>100</v>
+      </c>
+      <c r="O75" s="100" t="s">
+        <v>343</v>
+      </c>
+      <c r="P75" s="66">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q75" s="66">
-        <f t="shared" ref="Q75" si="66">P75*N75</f>
-        <v>0</v>
+        <f t="shared" ref="Q75" si="79">P75*N75</f>
+        <v>0.12</v>
       </c>
       <c r="R75" s="66" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="76" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-      <c r="C76" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="D76" s="103" t="s">
-        <v>57</v>
-      </c>
-      <c r="E76" s="104" t="s">
-        <v>129</v>
-      </c>
-      <c r="F76" s="103" t="s">
-        <v>170</v>
-      </c>
-      <c r="G76" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="H76" s="103" t="s">
-        <v>254</v>
-      </c>
-      <c r="I76" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J76" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K76" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L76" s="103">
-        <v>1</v>
-      </c>
-      <c r="M76" s="96">
-        <f t="shared" si="59"/>
-        <v>20</v>
-      </c>
-      <c r="N76" s="96">
-        <f t="shared" si="65"/>
-        <v>22</v>
-      </c>
-      <c r="O76" s="96"/>
-      <c r="P76" s="96"/>
-      <c r="Q76" s="96">
-        <f t="shared" ref="Q76" si="67">N76*P76</f>
+        <v>52</v>
+      </c>
+      <c r="C76" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" s="98" t="s">
+        <v>453</v>
+      </c>
+      <c r="E76" s="99" t="s">
+        <v>128</v>
+      </c>
+      <c r="F76" s="98" t="s">
+        <v>169</v>
+      </c>
+      <c r="G76" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H76" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I76" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="J76" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="K76" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L76" s="98">
+        <v>15</v>
+      </c>
+      <c r="M76" s="66">
+        <f t="shared" si="72"/>
+        <v>300</v>
+      </c>
+      <c r="N76" s="66">
+        <f t="shared" ref="N76:N77" si="80">M76+(M76*0.1)</f>
+        <v>330</v>
+      </c>
+      <c r="O76" s="66"/>
+      <c r="P76" s="66"/>
+      <c r="Q76" s="66">
+        <f t="shared" ref="Q76" si="81">P76*N76</f>
         <v>0</v>
       </c>
-      <c r="R76" s="96"/>
-      <c r="T76" t="s">
-        <v>57</v>
-      </c>
-      <c r="V76" t="s">
-        <v>314</v>
-      </c>
-      <c r="W76">
-        <v>1</v>
-      </c>
-      <c r="Y76" t="str">
-        <f>IF(T76=D76, "Match", "Mismatch")</f>
-        <v>Match</v>
-      </c>
-      <c r="Z76" t="str">
-        <f>IF(G76=U76, "Match", "Mismatch")</f>
-        <v>Mismatch</v>
-      </c>
-      <c r="AA76" t="str">
-        <f>IF(K76=V76, "Match", "Mismatch")</f>
-        <v>Match</v>
-      </c>
-      <c r="AB76" t="str">
-        <f>IF(W76=L76, "Match", "Mismatch")</f>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="77" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R76" s="66" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f>ROW(B77) - ROW($B$9)</f>
+        <f t="shared" ref="B77:B88" si="82">ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="106" t="s">
-        <v>327</v>
-      </c>
-      <c r="D77" s="107" t="s">
-        <v>58</v>
-      </c>
-      <c r="E77" s="108" t="s">
-        <v>130</v>
-      </c>
-      <c r="F77" s="107" t="s">
-        <v>308</v>
-      </c>
-      <c r="G77" s="108">
-        <v>750314597</v>
-      </c>
-      <c r="H77" s="107" t="s">
-        <v>255</v>
-      </c>
-      <c r="I77" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J77" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K77" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L77" s="107">
+      <c r="C77" s="102" t="s">
+        <v>326</v>
+      </c>
+      <c r="D77" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="E77" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" s="103" t="s">
+        <v>170</v>
+      </c>
+      <c r="G77" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="H77" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="I77" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L77" s="103">
         <v>1</v>
       </c>
-      <c r="M77" s="109">
-        <f t="shared" si="59"/>
+      <c r="M77" s="96">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N77" s="109">
-        <v>21</v>
-      </c>
-      <c r="O77" s="110" t="s">
-        <v>379</v>
-      </c>
-      <c r="P77" s="109">
-        <v>3.81</v>
-      </c>
-      <c r="Q77" s="109">
-        <f t="shared" ref="Q77" si="68">P77*N77</f>
-        <v>80.010000000000005</v>
-      </c>
-      <c r="R77" s="109"/>
-      <c r="T77" t="s">
-        <v>58</v>
-      </c>
-      <c r="U77">
-        <v>750314597</v>
-      </c>
-      <c r="V77" t="s">
-        <v>314</v>
-      </c>
-      <c r="W77">
-        <v>1</v>
-      </c>
-      <c r="Y77" t="str">
-        <f t="shared" ref="Y77:Y87" si="69">IF(T77=D77, "Match", "Mismatch")</f>
-        <v>Match</v>
-      </c>
-      <c r="Z77" t="str">
-        <f t="shared" ref="Z77:Z87" si="70">IF(G77=U77, "Match", "Mismatch")</f>
-        <v>Match</v>
-      </c>
-      <c r="AA77" t="str">
-        <f t="shared" ref="AA77:AA87" si="71">IF(K77=V77, "Match", "Mismatch")</f>
-        <v>Match</v>
-      </c>
-      <c r="AB77" t="str">
-        <f t="shared" ref="AB77:AB87" si="72">IF(W77=L77, "Match", "Mismatch")</f>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N77" s="96">
+        <f t="shared" si="80"/>
+        <v>22</v>
+      </c>
+      <c r="O77" s="96"/>
+      <c r="P77" s="96"/>
+      <c r="Q77" s="96">
+        <f t="shared" ref="Q77" si="83">N77*P77</f>
+        <v>0</v>
+      </c>
+      <c r="R77" s="96"/>
+    </row>
+    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="C78" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="D78" s="103" t="s">
-        <v>59</v>
-      </c>
-      <c r="E78" s="104" t="s">
-        <v>131</v>
-      </c>
-      <c r="F78" s="103" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="D78" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="E78" s="108" t="s">
+        <v>130</v>
+      </c>
+      <c r="F78" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G78" s="104" t="s">
-        <v>171</v>
-      </c>
-      <c r="H78" s="103" t="s">
-        <v>256</v>
-      </c>
-      <c r="I78" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J78" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K78" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L78" s="103">
+      <c r="G78" s="108">
+        <v>750314597</v>
+      </c>
+      <c r="H78" s="107" t="s">
+        <v>255</v>
+      </c>
+      <c r="I78" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L78" s="107">
         <v>1</v>
       </c>
-      <c r="M78" s="96">
-        <f t="shared" si="59"/>
+      <c r="M78" s="109">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N78" s="96">
+      <c r="N78" s="109">
         <v>21</v>
       </c>
-      <c r="O78" s="105" t="s">
-        <v>409</v>
-      </c>
-      <c r="P78" s="96">
-        <v>2.48</v>
-      </c>
-      <c r="Q78" s="96">
-        <f t="shared" ref="Q78" si="73">N78*P78</f>
-        <v>52.08</v>
-      </c>
-      <c r="R78" s="96"/>
-      <c r="T78" t="s">
-        <v>59</v>
-      </c>
-      <c r="U78" t="s">
-        <v>171</v>
-      </c>
-      <c r="V78" t="s">
-        <v>314</v>
-      </c>
-      <c r="W78">
-        <v>1</v>
-      </c>
-      <c r="Y78" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z78" t="str">
-        <f t="shared" si="70"/>
-        <v>Match</v>
-      </c>
-      <c r="AA78" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB78" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="79" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O78" s="110" t="s">
+        <v>379</v>
+      </c>
+      <c r="P78" s="109">
+        <v>3.81</v>
+      </c>
+      <c r="Q78" s="109">
+        <f t="shared" ref="Q78" si="84">P78*N78</f>
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R78" s="109"/>
+    </row>
+    <row r="79" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
-        <f>ROW(B79) - ROW($B$9)</f>
+        <f t="shared" ref="B79:B88" si="85">ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="106" t="s">
+      <c r="C79" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D79" s="107" t="s">
-        <v>60</v>
-      </c>
-      <c r="E79" s="108" t="s">
-        <v>132</v>
-      </c>
-      <c r="F79" s="107" t="s">
-        <v>172</v>
-      </c>
-      <c r="G79" s="108" t="s">
-        <v>221</v>
-      </c>
-      <c r="H79" s="107" t="s">
-        <v>257</v>
-      </c>
-      <c r="I79" s="107" t="s">
-        <v>410</v>
-      </c>
-      <c r="J79" s="107" t="s">
-        <v>411</v>
-      </c>
-      <c r="K79" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L79" s="107">
+      <c r="D79" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="E79" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="F79" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G79" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H79" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I79" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J79" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K79" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L79" s="103">
         <v>1</v>
       </c>
-      <c r="M79" s="109">
-        <f t="shared" si="59"/>
+      <c r="M79" s="96">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N79" s="109">
+      <c r="N79" s="96">
         <v>21</v>
       </c>
-      <c r="O79" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="P79" s="109">
-        <v>1.3939999999999999</v>
-      </c>
-      <c r="Q79" s="109">
-        <f t="shared" ref="Q79" si="74">P79*N79</f>
-        <v>29.273999999999997</v>
-      </c>
-      <c r="R79" s="79"/>
-      <c r="T79" t="s">
-        <v>60</v>
-      </c>
-      <c r="U79" t="s">
-        <v>410</v>
-      </c>
-      <c r="V79" t="s">
-        <v>314</v>
-      </c>
-      <c r="W79">
-        <v>1</v>
-      </c>
-      <c r="Y79" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z79" t="str">
-        <f t="shared" si="70"/>
-        <v>Mismatch</v>
-      </c>
-      <c r="AA79" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB79" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="80" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O79" s="105" t="s">
+        <v>409</v>
+      </c>
+      <c r="P79" s="96">
+        <v>2.48</v>
+      </c>
+      <c r="Q79" s="96">
+        <f t="shared" ref="Q79" si="86">N79*P79</f>
+        <v>52.08</v>
+      </c>
+      <c r="R79" s="96"/>
+    </row>
+    <row r="80" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
-        <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-      <c r="C80" s="102" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="D80" s="103" t="s">
-        <v>61</v>
-      </c>
-      <c r="E80" s="104" t="s">
-        <v>133</v>
-      </c>
-      <c r="F80" s="103" t="s">
-        <v>173</v>
-      </c>
-      <c r="G80" s="104" t="s">
-        <v>222</v>
-      </c>
-      <c r="H80" s="103" t="s">
-        <v>256</v>
-      </c>
-      <c r="I80" s="103" t="s">
-        <v>412</v>
-      </c>
-      <c r="J80" s="103" t="s">
-        <v>413</v>
-      </c>
-      <c r="K80" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L80" s="103">
+      <c r="D80" s="107" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="F80" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="G80" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="H80" s="107" t="s">
+        <v>257</v>
+      </c>
+      <c r="I80" s="107" t="s">
+        <v>410</v>
+      </c>
+      <c r="J80" s="107" t="s">
+        <v>411</v>
+      </c>
+      <c r="K80" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L80" s="107">
         <v>1</v>
       </c>
-      <c r="M80" s="96">
-        <f t="shared" si="59"/>
+      <c r="M80" s="109">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N80" s="96">
+      <c r="N80" s="109">
         <v>21</v>
       </c>
-      <c r="O80" s="105" t="s">
+      <c r="O80" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P80" s="96">
-        <v>0.69430000000000003</v>
-      </c>
-      <c r="Q80" s="96">
-        <f t="shared" ref="Q80" si="75">N80*P80</f>
-        <v>14.580300000000001</v>
-      </c>
-      <c r="R80" s="78"/>
-      <c r="T80" t="s">
-        <v>61</v>
-      </c>
-      <c r="U80" t="s">
-        <v>412</v>
-      </c>
-      <c r="V80" t="s">
-        <v>314</v>
-      </c>
-      <c r="W80">
-        <v>1</v>
-      </c>
-      <c r="Y80" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z80" t="str">
-        <f t="shared" si="70"/>
-        <v>Mismatch</v>
-      </c>
-      <c r="AA80" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB80" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P80" s="109">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="Q80" s="109">
+        <f t="shared" ref="Q80" si="87">P80*N80</f>
+        <v>29.273999999999997</v>
+      </c>
+      <c r="R80" s="79"/>
+    </row>
+    <row r="81" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f>ROW(B81) - ROW($B$9)</f>
+        <f t="shared" ref="B81:B88" si="88">ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="106" t="s">
+      <c r="C81" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D81" s="107" t="s">
-        <v>62</v>
-      </c>
-      <c r="E81" s="108" t="s">
-        <v>134</v>
-      </c>
-      <c r="F81" s="107" t="s">
-        <v>310</v>
-      </c>
-      <c r="G81" s="108" t="s">
-        <v>174</v>
-      </c>
-      <c r="H81" s="107" t="s">
+      <c r="D81" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="E81" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="F81" s="103" t="s">
+        <v>173</v>
+      </c>
+      <c r="G81" s="104" t="s">
+        <v>222</v>
+      </c>
+      <c r="H81" s="103" t="s">
         <v>256</v>
       </c>
-      <c r="I81" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J81" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K81" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L81" s="107">
+      <c r="I81" s="103" t="s">
+        <v>412</v>
+      </c>
+      <c r="J81" s="103" t="s">
+        <v>413</v>
+      </c>
+      <c r="K81" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L81" s="103">
         <v>1</v>
       </c>
-      <c r="M81" s="109">
-        <f t="shared" si="59"/>
+      <c r="M81" s="96">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N81" s="109">
+      <c r="N81" s="96">
         <v>21</v>
       </c>
-      <c r="O81" s="110" t="s">
-        <v>409</v>
-      </c>
-      <c r="P81" s="109">
-        <v>3.637</v>
-      </c>
-      <c r="Q81" s="109">
-        <f t="shared" ref="Q81" si="76">P81*N81</f>
-        <v>76.376999999999995</v>
-      </c>
-      <c r="R81" s="109"/>
-      <c r="T81" t="s">
-        <v>62</v>
-      </c>
-      <c r="U81" t="s">
-        <v>174</v>
-      </c>
-      <c r="V81" t="s">
-        <v>314</v>
-      </c>
-      <c r="W81">
-        <v>1</v>
-      </c>
-      <c r="Y81" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z81" t="str">
-        <f t="shared" si="70"/>
-        <v>Match</v>
-      </c>
-      <c r="AA81" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB81" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O81" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P81" s="96">
+        <v>0.69430000000000003</v>
+      </c>
+      <c r="Q81" s="96">
+        <f t="shared" ref="Q81" si="89">N81*P81</f>
+        <v>14.580300000000001</v>
+      </c>
+      <c r="R81" s="78"/>
+    </row>
+    <row r="82" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
-        <f t="shared" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="C82" s="102" t="s">
+        <v>55</v>
+      </c>
+      <c r="C82" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="D82" s="103" t="s">
-        <v>63</v>
-      </c>
-      <c r="E82" s="104" t="s">
-        <v>135</v>
-      </c>
-      <c r="F82" s="103" t="s">
-        <v>175</v>
-      </c>
-      <c r="G82" s="104" t="s">
-        <v>223</v>
-      </c>
-      <c r="H82" s="103" t="s">
+      <c r="D82" s="107" t="s">
+        <v>62</v>
+      </c>
+      <c r="E82" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="F82" s="107" t="s">
+        <v>310</v>
+      </c>
+      <c r="G82" s="108" t="s">
+        <v>174</v>
+      </c>
+      <c r="H82" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="I82" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J82" s="103" t="s">
-        <v>414</v>
-      </c>
-      <c r="K82" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L82" s="103">
+      <c r="I82" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J82" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K82" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L82" s="107">
         <v>1</v>
       </c>
-      <c r="M82" s="96">
-        <f t="shared" si="59"/>
+      <c r="M82" s="109">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N82" s="96">
+      <c r="N82" s="109">
         <v>21</v>
       </c>
-      <c r="O82" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P82" s="96">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q82" s="96">
-        <f t="shared" ref="Q82" si="77">N82*P82</f>
-        <v>9.0888000000000009</v>
-      </c>
-      <c r="R82" s="96"/>
-      <c r="T82" t="s">
-        <v>63</v>
-      </c>
-      <c r="U82" t="s">
-        <v>223</v>
-      </c>
-      <c r="V82" t="s">
-        <v>314</v>
-      </c>
-      <c r="W82">
-        <v>1</v>
-      </c>
-      <c r="Y82" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z82" t="str">
-        <f t="shared" si="70"/>
-        <v>Match</v>
-      </c>
-      <c r="AA82" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB82" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O82" s="110" t="s">
+        <v>409</v>
+      </c>
+      <c r="P82" s="109">
+        <v>3.637</v>
+      </c>
+      <c r="Q82" s="109">
+        <f t="shared" ref="Q82" si="90">P82*N82</f>
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R82" s="109"/>
+    </row>
+    <row r="83" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
-        <f>ROW(B83) - ROW($B$9)</f>
+        <f t="shared" ref="B83:B88" si="91">ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="71" t="s">
+      <c r="C83" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D83" s="72" t="s">
-        <v>64</v>
-      </c>
-      <c r="E83" s="73" t="s">
-        <v>136</v>
-      </c>
-      <c r="F83" s="72" t="s">
-        <v>176</v>
-      </c>
-      <c r="G83" s="73" t="s">
-        <v>224</v>
-      </c>
-      <c r="H83" s="72" t="s">
-        <v>258</v>
-      </c>
-      <c r="I83" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="J83" s="72" t="s">
-        <v>415</v>
-      </c>
-      <c r="K83" s="73" t="s">
-        <v>314</v>
-      </c>
-      <c r="L83" s="72">
+      <c r="D83" s="103" t="s">
+        <v>63</v>
+      </c>
+      <c r="E83" s="104" t="s">
+        <v>135</v>
+      </c>
+      <c r="F83" s="103" t="s">
+        <v>175</v>
+      </c>
+      <c r="G83" s="104" t="s">
+        <v>223</v>
+      </c>
+      <c r="H83" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I83" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J83" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="K83" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L83" s="103">
         <v>1</v>
       </c>
-      <c r="M83" s="74">
-        <f t="shared" si="59"/>
+      <c r="M83" s="96">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N83" s="74">
+      <c r="N83" s="96">
         <v>21</v>
       </c>
-      <c r="O83" s="75" t="s">
+      <c r="O83" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P83" s="74">
-        <v>7.4638</v>
-      </c>
-      <c r="Q83" s="74">
-        <f t="shared" ref="Q83" si="78">P83*N83</f>
-        <v>156.7398</v>
-      </c>
-      <c r="R83" s="74" t="s">
-        <v>438</v>
-      </c>
-      <c r="T83" t="s">
-        <v>64</v>
-      </c>
-      <c r="U83" t="s">
-        <v>224</v>
-      </c>
-      <c r="V83" t="s">
-        <v>314</v>
-      </c>
-      <c r="W83">
-        <v>1</v>
-      </c>
-      <c r="Y83" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z83" t="str">
-        <f t="shared" si="70"/>
-        <v>Match</v>
-      </c>
-      <c r="AA83" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB83" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P83" s="96">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="Q83" s="96">
+        <f t="shared" ref="Q83" si="92">N83*P83</f>
+        <v>9.0888000000000009</v>
+      </c>
+      <c r="R83" s="96"/>
+    </row>
+    <row r="84" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="C84" s="102" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" s="71" t="s">
         <v>328</v>
       </c>
-      <c r="D84" s="103" t="s">
-        <v>65</v>
-      </c>
-      <c r="E84" s="104" t="s">
-        <v>137</v>
-      </c>
-      <c r="F84" s="103" t="s">
-        <v>177</v>
-      </c>
-      <c r="G84" s="104" t="s">
-        <v>225</v>
-      </c>
-      <c r="H84" s="103" t="s">
-        <v>259</v>
-      </c>
-      <c r="I84" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J84" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K84" s="114" t="s">
-        <v>314</v>
-      </c>
-      <c r="L84" s="103">
+      <c r="D84" s="72" t="s">
+        <v>64</v>
+      </c>
+      <c r="E84" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="F84" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="G84" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="H84" s="72" t="s">
+        <v>258</v>
+      </c>
+      <c r="I84" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" s="72" t="s">
+        <v>415</v>
+      </c>
+      <c r="K84" s="73" t="s">
+        <v>314</v>
+      </c>
+      <c r="L84" s="72">
         <v>1</v>
       </c>
-      <c r="M84" s="96">
-        <f t="shared" si="59"/>
+      <c r="M84" s="74">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N84" s="96">
+      <c r="N84" s="74">
         <v>21</v>
       </c>
-      <c r="O84" s="105" t="s">
-        <v>409</v>
-      </c>
-      <c r="P84" s="96">
-        <v>2.6459999999999999</v>
-      </c>
-      <c r="Q84" s="96">
-        <f t="shared" ref="Q84" si="79">N84*P84</f>
-        <v>55.565999999999995</v>
-      </c>
-      <c r="R84" s="96"/>
-      <c r="T84" t="s">
-        <v>65</v>
-      </c>
-      <c r="U84" t="s">
-        <v>225</v>
-      </c>
-      <c r="V84" t="s">
-        <v>314</v>
-      </c>
-      <c r="W84">
-        <v>1</v>
-      </c>
-      <c r="Y84" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z84" t="str">
-        <f t="shared" si="70"/>
-        <v>Match</v>
-      </c>
-      <c r="AA84" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB84" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O84" s="75" t="s">
+        <v>343</v>
+      </c>
+      <c r="P84" s="74">
+        <v>7.4638</v>
+      </c>
+      <c r="Q84" s="74">
+        <f t="shared" ref="Q84" si="93">P84*N84</f>
+        <v>156.7398</v>
+      </c>
+      <c r="R84" s="74" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
-        <f>ROW(B85) - ROW($B$9)</f>
+        <f t="shared" ref="B85:B88" si="94">ROW(B85) - ROW($B$9)</f>
         <v>76</v>
       </c>
-      <c r="C85" s="106" t="s">
+      <c r="C85" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D85" s="107" t="s">
-        <v>454</v>
-      </c>
-      <c r="E85" s="108" t="s">
-        <v>138</v>
-      </c>
-      <c r="F85" s="107" t="s">
-        <v>311</v>
-      </c>
-      <c r="G85" s="108" t="s">
-        <v>178</v>
-      </c>
-      <c r="H85" s="107" t="s">
-        <v>256</v>
-      </c>
-      <c r="I85" s="107" t="s">
-        <v>416</v>
-      </c>
-      <c r="J85" s="107" t="s">
-        <v>417</v>
-      </c>
-      <c r="K85" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L85" s="115">
-        <v>2</v>
-      </c>
-      <c r="M85" s="109">
-        <f t="shared" si="59"/>
-        <v>40</v>
-      </c>
-      <c r="N85" s="109">
-        <v>42</v>
-      </c>
-      <c r="O85" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="P85" s="109">
-        <v>2.2974000000000001</v>
-      </c>
-      <c r="Q85" s="109">
-        <f t="shared" ref="Q85" si="80">P85*N85</f>
-        <v>96.490800000000007</v>
-      </c>
-      <c r="R85" s="79"/>
-      <c r="T85" t="s">
-        <v>454</v>
-      </c>
-      <c r="U85" t="s">
-        <v>416</v>
-      </c>
-      <c r="V85" t="s">
-        <v>314</v>
-      </c>
-      <c r="W85">
-        <v>2</v>
-      </c>
-      <c r="Y85" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z85" t="str">
-        <f t="shared" si="70"/>
-        <v>Mismatch</v>
-      </c>
-      <c r="AA85" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB85" t="str">
+      <c r="D85" s="103" t="s">
+        <v>65</v>
+      </c>
+      <c r="E85" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="F85" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="G85" s="104" t="s">
+        <v>225</v>
+      </c>
+      <c r="H85" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="I85" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J85" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K85" s="113" t="s">
+        <v>314</v>
+      </c>
+      <c r="L85" s="103">
+        <v>1</v>
+      </c>
+      <c r="M85" s="96">
         <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="N85" s="96">
+        <v>21</v>
+      </c>
+      <c r="O85" s="105" t="s">
+        <v>409</v>
+      </c>
+      <c r="P85" s="96">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="Q85" s="96">
+        <f t="shared" ref="Q85" si="95">N85*P85</f>
+        <v>55.565999999999995</v>
+      </c>
+      <c r="R85" s="96"/>
+    </row>
+    <row r="86" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
-        <f>ROW(B86) - ROW($B$9)</f>
-        <v>77</v>
-      </c>
-      <c r="C86" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="D86" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G86" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="H86" s="37" t="s">
+      <c r="D86" s="107" t="s">
+        <v>454</v>
+      </c>
+      <c r="E86" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="F86" s="107" t="s">
+        <v>311</v>
+      </c>
+      <c r="G86" s="108" t="s">
+        <v>178</v>
+      </c>
+      <c r="H86" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="I86" s="62" t="s">
-        <v>314</v>
-      </c>
-      <c r="J86" s="62" t="s">
-        <v>420</v>
-      </c>
-      <c r="K86" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L86" s="37">
-        <v>1</v>
-      </c>
-      <c r="M86" s="41">
-        <f>L86*20</f>
-        <v>20</v>
-      </c>
-      <c r="N86" s="41">
-        <v>21</v>
-      </c>
-      <c r="O86" s="63" t="s">
+      <c r="I86" s="107" t="s">
+        <v>416</v>
+      </c>
+      <c r="J86" s="107" t="s">
+        <v>417</v>
+      </c>
+      <c r="K86" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L86" s="114">
+        <v>2</v>
+      </c>
+      <c r="M86" s="109">
+        <f t="shared" si="72"/>
+        <v>40</v>
+      </c>
+      <c r="N86" s="109">
+        <v>42</v>
+      </c>
+      <c r="O86" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P86" s="41">
-        <v>0.39140000000000003</v>
-      </c>
-      <c r="Q86" s="41">
-        <f t="shared" ref="Q86" si="81">P86*N86</f>
-        <v>8.2194000000000003</v>
-      </c>
-      <c r="R86" s="41"/>
-      <c r="T86" t="s">
-        <v>66</v>
-      </c>
-      <c r="U86" t="s">
-        <v>180</v>
-      </c>
-      <c r="V86" t="s">
-        <v>314</v>
-      </c>
-      <c r="W86">
-        <v>1</v>
-      </c>
-      <c r="Y86" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z86" t="str">
-        <f t="shared" si="70"/>
-        <v>Match</v>
-      </c>
-      <c r="AA86" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB86" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P86" s="109">
+        <v>2.2974000000000001</v>
+      </c>
+      <c r="Q86" s="109">
+        <f t="shared" ref="Q86" si="96">P86*N86</f>
+        <v>96.490800000000007</v>
+      </c>
+      <c r="R86" s="79"/>
+    </row>
+    <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B87:B88" si="97">ROW(B87) - ROW($B$9)</f>
         <v>78</v>
       </c>
-      <c r="C87" s="59" t="s">
+      <c r="C87" s="60" t="s">
         <v>328</v>
       </c>
-      <c r="D87" s="39" t="s">
+      <c r="D87" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E87" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F87" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="G87" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="H87" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="I87" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="J87" s="62" t="s">
+        <v>420</v>
+      </c>
+      <c r="K87" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L87" s="37">
+        <v>1</v>
+      </c>
+      <c r="M87" s="41">
+        <f>L87*20</f>
+        <v>20</v>
+      </c>
+      <c r="N87" s="41">
+        <v>21</v>
+      </c>
+      <c r="O87" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P87" s="41">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="Q87" s="41">
+        <f t="shared" ref="Q87" si="98">P87*N87</f>
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R87" s="41"/>
+    </row>
+    <row r="88" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="1"/>
+      <c r="B88" s="53">
+        <v>58</v>
+      </c>
+      <c r="C88" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="D88" s="39" t="s">
         <v>455</v>
       </c>
-      <c r="E87" s="40" t="s">
+      <c r="E88" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="F87" s="39" t="s">
+      <c r="F88" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G87" s="40" t="s">
+      <c r="G88" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="H87" s="39" t="s">
+      <c r="H88" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="I87" s="39" t="s">
+      <c r="I88" s="39" t="s">
         <v>418</v>
       </c>
-      <c r="J87" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K87" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L87" s="39">
+      <c r="J88" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K88" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L88" s="39">
         <v>1</v>
       </c>
-      <c r="M87" s="42">
-        <f t="shared" si="59"/>
+      <c r="M88" s="42">
+        <f t="shared" si="72"/>
         <v>20</v>
       </c>
-      <c r="N87" s="42">
+      <c r="N88" s="42">
         <v>21</v>
       </c>
-      <c r="O87" s="64" t="s">
+      <c r="O88" s="64" t="s">
         <v>419</v>
       </c>
-      <c r="P87" s="42">
+      <c r="P88" s="42">
         <v>3.532</v>
       </c>
-      <c r="Q87" s="42">
-        <f t="shared" ref="Q87" si="82">N87*P87</f>
+      <c r="Q88" s="42">
+        <f t="shared" ref="Q88" si="99">N88*P88</f>
         <v>74.171999999999997</v>
       </c>
-      <c r="R87" s="79"/>
-      <c r="T87" t="s">
-        <v>455</v>
-      </c>
-      <c r="U87" t="s">
-        <v>418</v>
-      </c>
-      <c r="V87" t="s">
-        <v>314</v>
-      </c>
-      <c r="W87">
-        <v>1</v>
-      </c>
-      <c r="Y87" t="str">
-        <f t="shared" si="69"/>
-        <v>Match</v>
-      </c>
-      <c r="Z87" t="str">
-        <f t="shared" si="70"/>
-        <v>Mismatch</v>
-      </c>
-      <c r="AA87" t="str">
-        <f t="shared" si="71"/>
-        <v>Match</v>
-      </c>
-      <c r="AB87" t="str">
-        <f t="shared" si="72"/>
-        <v>Match</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="33" t="s">
+      <c r="R88" s="79"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A89" s="1"/>
+      <c r="B89" s="32"/>
+      <c r="C89" s="51"/>
+      <c r="D89" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E88" s="34"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="36"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
-      <c r="J88" s="35"/>
-      <c r="K88" s="36"/>
-      <c r="L88" s="36"/>
-      <c r="M88" s="36"/>
-      <c r="N88" s="36"/>
-      <c r="O88" s="69" t="s">
+      <c r="E89" s="34"/>
+      <c r="F89" s="35"/>
+      <c r="G89" s="36"/>
+      <c r="H89" s="35"/>
+      <c r="I89" s="35"/>
+      <c r="J89" s="35"/>
+      <c r="K89" s="36"/>
+      <c r="L89" s="36"/>
+      <c r="M89" s="36"/>
+      <c r="N89" s="36"/>
+      <c r="O89" s="69" t="s">
         <v>421</v>
       </c>
-      <c r="P88" s="67"/>
-      <c r="Q88" s="67">
-        <f>SUM(Q10:Q87)</f>
-        <v>960.72630000000004</v>
-      </c>
-      <c r="R88" s="44"/>
-    </row>
-    <row r="89" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="1"/>
-      <c r="B89" s="24"/>
-      <c r="C89" s="52"/>
-      <c r="D89" s="8" t="s">
+      <c r="P89" s="67"/>
+      <c r="Q89" s="67">
+        <f>SUM(Q10:Q88)</f>
+        <v>969.96630000000005</v>
+      </c>
+      <c r="R89" s="44"/>
+    </row>
+    <row r="90" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="1"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="52"/>
+      <c r="D90" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9"/>
-      <c r="L89" s="9"/>
-      <c r="M89" s="9"/>
-      <c r="N89" s="9"/>
-      <c r="O89" s="70" t="s">
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="9"/>
+      <c r="M90" s="9"/>
+      <c r="N90" s="9"/>
+      <c r="O90" s="70" t="s">
         <v>422</v>
       </c>
-      <c r="P89" s="68"/>
-      <c r="Q89" s="68">
-        <f>Q88/20</f>
-        <v>48.036315000000002</v>
-      </c>
-      <c r="R89" s="45"/>
+      <c r="P90" s="68"/>
+      <c r="Q90" s="68">
+        <f>Q89/20</f>
+        <v>48.498315000000005</v>
+      </c>
+      <c r="R90" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7702,47 +7419,48 @@
     <hyperlink ref="O43" r:id="rId34"/>
     <hyperlink ref="O44" r:id="rId35"/>
     <hyperlink ref="O45" r:id="rId36"/>
-    <hyperlink ref="O46" r:id="rId37"/>
-    <hyperlink ref="O48" r:id="rId38"/>
-    <hyperlink ref="O49" r:id="rId39"/>
-    <hyperlink ref="O50" r:id="rId40"/>
-    <hyperlink ref="O51" r:id="rId41"/>
-    <hyperlink ref="O52" r:id="rId42"/>
-    <hyperlink ref="O53" r:id="rId43"/>
-    <hyperlink ref="O54" r:id="rId44"/>
-    <hyperlink ref="O55" r:id="rId45"/>
-    <hyperlink ref="O67" r:id="rId46"/>
-    <hyperlink ref="O57" r:id="rId47"/>
-    <hyperlink ref="O58" r:id="rId48"/>
-    <hyperlink ref="O59" r:id="rId49"/>
-    <hyperlink ref="O60" r:id="rId50"/>
-    <hyperlink ref="O61" r:id="rId51"/>
-    <hyperlink ref="O62" r:id="rId52"/>
-    <hyperlink ref="O63" r:id="rId53"/>
-    <hyperlink ref="O64" r:id="rId54"/>
-    <hyperlink ref="O65" r:id="rId55"/>
-    <hyperlink ref="O66" r:id="rId56"/>
-    <hyperlink ref="O68" r:id="rId57"/>
-    <hyperlink ref="O69" r:id="rId58"/>
-    <hyperlink ref="O70" r:id="rId59"/>
-    <hyperlink ref="O73" r:id="rId60"/>
-    <hyperlink ref="O74" r:id="rId61"/>
-    <hyperlink ref="O71" r:id="rId62"/>
-    <hyperlink ref="O77" r:id="rId63"/>
-    <hyperlink ref="O78" r:id="rId64"/>
-    <hyperlink ref="O79" r:id="rId65"/>
-    <hyperlink ref="O80" r:id="rId66"/>
-    <hyperlink ref="O81" r:id="rId67"/>
-    <hyperlink ref="O82" r:id="rId68"/>
-    <hyperlink ref="O83" r:id="rId69"/>
-    <hyperlink ref="O84" r:id="rId70"/>
-    <hyperlink ref="O85" r:id="rId71"/>
-    <hyperlink ref="O87" r:id="rId72"/>
-    <hyperlink ref="O86" r:id="rId73"/>
-    <hyperlink ref="O56" r:id="rId74"/>
+    <hyperlink ref="O47" r:id="rId37"/>
+    <hyperlink ref="O49" r:id="rId38"/>
+    <hyperlink ref="O50" r:id="rId39"/>
+    <hyperlink ref="O51" r:id="rId40"/>
+    <hyperlink ref="O52" r:id="rId41"/>
+    <hyperlink ref="O53" r:id="rId42"/>
+    <hyperlink ref="O54" r:id="rId43"/>
+    <hyperlink ref="O55" r:id="rId44"/>
+    <hyperlink ref="O56" r:id="rId45"/>
+    <hyperlink ref="O68" r:id="rId46"/>
+    <hyperlink ref="O58" r:id="rId47"/>
+    <hyperlink ref="O59" r:id="rId48"/>
+    <hyperlink ref="O60" r:id="rId49"/>
+    <hyperlink ref="O61" r:id="rId50"/>
+    <hyperlink ref="O62" r:id="rId51"/>
+    <hyperlink ref="O63" r:id="rId52"/>
+    <hyperlink ref="O64" r:id="rId53"/>
+    <hyperlink ref="O65" r:id="rId54"/>
+    <hyperlink ref="O66" r:id="rId55"/>
+    <hyperlink ref="O67" r:id="rId56"/>
+    <hyperlink ref="O69" r:id="rId57"/>
+    <hyperlink ref="O70" r:id="rId58"/>
+    <hyperlink ref="O71" r:id="rId59"/>
+    <hyperlink ref="O74" r:id="rId60"/>
+    <hyperlink ref="O75" r:id="rId61"/>
+    <hyperlink ref="O72" r:id="rId62"/>
+    <hyperlink ref="O78" r:id="rId63"/>
+    <hyperlink ref="O79" r:id="rId64"/>
+    <hyperlink ref="O80" r:id="rId65"/>
+    <hyperlink ref="O81" r:id="rId66"/>
+    <hyperlink ref="O82" r:id="rId67"/>
+    <hyperlink ref="O83" r:id="rId68"/>
+    <hyperlink ref="O84" r:id="rId69"/>
+    <hyperlink ref="O85" r:id="rId70"/>
+    <hyperlink ref="O86" r:id="rId71"/>
+    <hyperlink ref="O88" r:id="rId72"/>
+    <hyperlink ref="O87" r:id="rId73"/>
+    <hyperlink ref="O57" r:id="rId74"/>
+    <hyperlink ref="O46" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
-  <drawing r:id="rId76"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
+  <drawing r:id="rId77"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -5,16 +5,16 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11496" windowHeight="7596"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11490" windowHeight="7590"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="470">
   <si>
     <t>Component list</t>
   </si>
@@ -1563,25 +1563,22 @@
     <t>LED Glass Pipe</t>
   </si>
   <si>
-    <t>LED Light Pipes PCB Mount</t>
-  </si>
-  <si>
-    <t>3mm .5 inch</t>
-  </si>
-  <si>
-    <t>VBL3D0500C</t>
-  </si>
-  <si>
-    <t>VCC</t>
-  </si>
-  <si>
     <t>Mounting Holes required in design</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LIGHT PIPE VERT 0.500" RND FACE</t>
+  </si>
+  <si>
+    <t>VLP-500-R</t>
+  </si>
+  <si>
+    <t>Bivar Inc.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -2455,7 +2452,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2754,26 +2751,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R90"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.109375" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.44140625" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2793,7 +2790,7 @@
       <c r="Q1" s="115"/>
       <c r="R1" s="115"/>
     </row>
-    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -2817,7 +2814,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="43"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -2841,7 +2838,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="116"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -2865,7 +2862,7 @@
       <c r="Q4" s="61"/>
       <c r="R4" s="117"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -2887,7 +2884,7 @@
       <c r="Q5" s="61"/>
       <c r="R5" s="117"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -2907,7 +2904,7 @@
       <c r="Q6" s="61"/>
       <c r="R6" s="117"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -2927,7 +2924,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="117"/>
     </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -2947,7 +2944,7 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="117"/>
     </row>
-    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -3001,7 +2998,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -3056,10 +3053,10 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B88" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B44" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="81" t="s">
@@ -3113,7 +3110,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -3168,7 +3165,7 @@
       </c>
       <c r="R12" s="76"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
@@ -3223,7 +3220,7 @@
       </c>
       <c r="R13" s="77"/>
     </row>
-    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -3278,7 +3275,7 @@
       </c>
       <c r="R14" s="76"/>
     </row>
-    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
@@ -3333,7 +3330,7 @@
       </c>
       <c r="R15" s="77"/>
     </row>
-    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -3388,7 +3385,7 @@
       </c>
       <c r="R16" s="76"/>
     </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
@@ -3443,7 +3440,7 @@
       </c>
       <c r="R17" s="42"/>
     </row>
-    <row r="18" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f t="shared" si="0"/>
@@ -3498,7 +3495,7 @@
       </c>
       <c r="R18" s="96"/>
     </row>
-    <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f>ROW(B19) - ROW($B$9)</f>
@@ -3553,7 +3550,7 @@
       </c>
       <c r="R19" s="109"/>
     </row>
-    <row r="20" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f t="shared" si="0"/>
@@ -3608,7 +3605,7 @@
       </c>
       <c r="R20" s="96"/>
     </row>
-    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f>ROW(B21) - ROW($B$9)</f>
@@ -3663,7 +3660,7 @@
       </c>
       <c r="R21" s="109"/>
     </row>
-    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
@@ -3718,7 +3715,7 @@
       </c>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f t="shared" si="0"/>
@@ -3773,7 +3770,7 @@
       </c>
       <c r="R23" s="77"/>
     </row>
-    <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f>ROW(B24) - ROW($B$9)</f>
@@ -3828,7 +3825,7 @@
       </c>
       <c r="R24" s="41"/>
     </row>
-    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f t="shared" si="0"/>
@@ -3883,7 +3880,7 @@
       </c>
       <c r="R25" s="42"/>
     </row>
-    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
@@ -3938,7 +3935,7 @@
       </c>
       <c r="R26" s="76"/>
     </row>
-    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -3993,7 +3990,7 @@
       </c>
       <c r="R27" s="79"/>
     </row>
-    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f>ROW(B28) - ROW($B$9)</f>
@@ -4048,7 +4045,7 @@
       </c>
       <c r="R28" s="41"/>
     </row>
-    <row r="29" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f t="shared" si="0"/>
@@ -4103,7 +4100,7 @@
       </c>
       <c r="R29" s="42"/>
     </row>
-    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -4158,7 +4155,7 @@
       </c>
       <c r="R30" s="41"/>
     </row>
-    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -4213,7 +4210,7 @@
       </c>
       <c r="R31" s="109"/>
     </row>
-    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f t="shared" si="0"/>
@@ -4268,7 +4265,7 @@
       </c>
       <c r="R32" s="96"/>
     </row>
-    <row r="33" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -4323,7 +4320,7 @@
       </c>
       <c r="R33" s="109"/>
     </row>
-    <row r="34" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
@@ -4378,7 +4375,7 @@
       </c>
       <c r="R34" s="78"/>
     </row>
-    <row r="35" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -4435,7 +4432,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
@@ -4490,7 +4487,7 @@
       </c>
       <c r="R36" s="96"/>
     </row>
-    <row r="37" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -4545,7 +4542,7 @@
       </c>
       <c r="R37" s="109"/>
     </row>
-    <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
@@ -4600,7 +4597,7 @@
       </c>
       <c r="R38" s="78"/>
     </row>
-    <row r="39" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -4655,7 +4652,7 @@
       </c>
       <c r="R39" s="79"/>
     </row>
-    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
@@ -4710,7 +4707,7 @@
       </c>
       <c r="R40" s="96"/>
     </row>
-    <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
@@ -4765,7 +4762,7 @@
       </c>
       <c r="R41" s="109"/>
     </row>
-    <row r="42" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f t="shared" si="0"/>
@@ -4820,7 +4817,7 @@
       </c>
       <c r="R42" s="96"/>
     </row>
-    <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="53">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -4875,7 +4872,7 @@
       </c>
       <c r="R43" s="77"/>
     </row>
-    <row r="44" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f t="shared" si="0"/>
@@ -4930,7 +4927,7 @@
       </c>
       <c r="R44" s="96"/>
     </row>
-    <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -4985,7 +4982,7 @@
       </c>
       <c r="R45" s="109"/>
     </row>
-    <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <v>37</v>
@@ -4997,10 +4994,10 @@
         <v>314</v>
       </c>
       <c r="E46" s="108" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F46" s="107" t="s">
-        <v>467</v>
+        <v>308</v>
       </c>
       <c r="G46" s="108" t="s">
         <v>468</v>
@@ -5028,23 +5025,23 @@
         <v>20</v>
       </c>
       <c r="O46" s="110" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="P46" s="109">
-        <v>0.46200000000000002</v>
+        <v>0.435</v>
       </c>
       <c r="Q46" s="109">
         <f t="shared" si="34"/>
-        <v>9.24</v>
-      </c>
-      <c r="R46" s="109" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R46" s="79" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
-        <f t="shared" ref="B47:B88" si="35">ROW(B47) - ROW($B$9)</f>
+        <f t="shared" ref="B47" si="35">ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
       <c r="C47" s="102" t="s">
@@ -5096,7 +5093,7 @@
       </c>
       <c r="R47" s="96"/>
     </row>
-    <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
         <v>38</v>
@@ -5145,10 +5142,10 @@
         <v>384</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
-        <f t="shared" ref="B49:B88" si="39">ROW(B49) - ROW($B$9)</f>
+        <f t="shared" ref="B49" si="39">ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
       <c r="C49" s="102" t="s">
@@ -5200,7 +5197,7 @@
       </c>
       <c r="R49" s="96"/>
     </row>
-    <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
         <v>39</v>
@@ -5254,10 +5251,10 @@
       </c>
       <c r="R50" s="109"/>
     </row>
-    <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="53">
-        <f t="shared" ref="B51:B88" si="42">ROW(B51) - ROW($B$9)</f>
+        <f t="shared" ref="B51" si="42">ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
       <c r="C51" s="102" t="s">
@@ -5309,7 +5306,7 @@
       </c>
       <c r="R51" s="96"/>
     </row>
-    <row r="52" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <v>40</v>
@@ -5363,10 +5360,10 @@
       </c>
       <c r="R52" s="109"/>
     </row>
-    <row r="53" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
-        <f t="shared" ref="B53:B88" si="45">ROW(B53) - ROW($B$9)</f>
+        <f t="shared" ref="B53" si="45">ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
       <c r="C53" s="102" t="s">
@@ -5418,7 +5415,7 @@
       </c>
       <c r="R53" s="96"/>
     </row>
-    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <v>41</v>
@@ -5472,10 +5469,10 @@
       </c>
       <c r="R54" s="109"/>
     </row>
-    <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
-        <f t="shared" ref="B55:B88" si="48">ROW(B55) - ROW($B$9)</f>
+        <f t="shared" ref="B55" si="48">ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
       <c r="C55" s="102" t="s">
@@ -5527,7 +5524,7 @@
       </c>
       <c r="R55" s="96"/>
     </row>
-    <row r="56" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
         <v>42</v>
@@ -5581,10 +5578,10 @@
       </c>
       <c r="R56" s="109"/>
     </row>
-    <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
-        <f t="shared" ref="B57:B88" si="51">ROW(B57) - ROW($B$9)</f>
+        <f t="shared" ref="B57" si="51">ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
       <c r="C57" s="60" t="s">
@@ -5636,7 +5633,7 @@
       </c>
       <c r="R57" s="76"/>
     </row>
-    <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
         <v>43</v>
@@ -5690,10 +5687,10 @@
       </c>
       <c r="R58" s="109"/>
     </row>
-    <row r="59" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
-        <f t="shared" ref="B59:B88" si="54">ROW(B59) - ROW($B$9)</f>
+        <f t="shared" ref="B59" si="54">ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
       <c r="C59" s="102" t="s">
@@ -5745,7 +5742,7 @@
       </c>
       <c r="R59" s="96"/>
     </row>
-    <row r="60" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
         <v>44</v>
@@ -5799,10 +5796,10 @@
       </c>
       <c r="R60" s="109"/>
     </row>
-    <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f t="shared" ref="B61:B88" si="57">ROW(B61) - ROW($B$9)</f>
+        <f t="shared" ref="B61" si="57">ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
       <c r="C61" s="102" t="s">
@@ -5854,7 +5851,7 @@
       </c>
       <c r="R61" s="96"/>
     </row>
-    <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
         <v>45</v>
@@ -5908,10 +5905,10 @@
       </c>
       <c r="R62" s="109"/>
     </row>
-    <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
-        <f t="shared" ref="B63:B88" si="60">ROW(B63) - ROW($B$9)</f>
+        <f t="shared" ref="B63" si="60">ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
       <c r="C63" s="102" t="s">
@@ -5963,7 +5960,7 @@
       </c>
       <c r="R63" s="96"/>
     </row>
-    <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
         <v>46</v>
@@ -6017,10 +6014,10 @@
       </c>
       <c r="R64" s="109"/>
     </row>
-    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
-        <f t="shared" ref="B65:B88" si="63">ROW(B65) - ROW($B$9)</f>
+        <f t="shared" ref="B65" si="63">ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
       <c r="C65" s="102" t="s">
@@ -6072,7 +6069,7 @@
       </c>
       <c r="R65" s="96"/>
     </row>
-    <row r="66" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
         <v>47</v>
@@ -6126,10 +6123,10 @@
       </c>
       <c r="R66" s="109"/>
     </row>
-    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
-        <f t="shared" ref="B67:B88" si="66">ROW(B67) - ROW($B$9)</f>
+        <f t="shared" ref="B67" si="66">ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
       <c r="C67" s="60" t="s">
@@ -6181,7 +6178,7 @@
       </c>
       <c r="R67" s="41"/>
     </row>
-    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
         <v>48</v>
@@ -6233,10 +6230,10 @@
       </c>
       <c r="R68" s="77"/>
     </row>
-    <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
-        <f t="shared" ref="B69:B88" si="68">ROW(B69) - ROW($B$9)</f>
+        <f t="shared" ref="B69" si="68">ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
       <c r="C69" s="60" t="s">
@@ -6288,7 +6285,7 @@
       </c>
       <c r="R69" s="41"/>
     </row>
-    <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
         <v>49</v>
@@ -6342,10 +6339,10 @@
       </c>
       <c r="R70" s="42"/>
     </row>
-    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f t="shared" ref="B71:B88" si="71">ROW(B71) - ROW($B$9)</f>
+        <f t="shared" ref="B71" si="71">ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
       <c r="C71" s="60" t="s">
@@ -6397,7 +6394,7 @@
       </c>
       <c r="R71" s="76"/>
     </row>
-    <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
         <v>50</v>
@@ -6451,10 +6448,10 @@
       </c>
       <c r="R72" s="77"/>
     </row>
-    <row r="73" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
-        <f t="shared" ref="B73:B88" si="75">ROW(B73) - ROW($B$9)</f>
+        <f t="shared" ref="B73" si="75">ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
       <c r="C73" s="60" t="s">
@@ -6506,7 +6503,7 @@
       </c>
       <c r="R73" s="41"/>
     </row>
-    <row r="74" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
         <v>51</v>
@@ -6560,10 +6557,10 @@
       </c>
       <c r="R74" s="42"/>
     </row>
-    <row r="75" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
-        <f t="shared" ref="B75:B88" si="78">ROW(B75) - ROW($B$9)</f>
+        <f t="shared" ref="B75" si="78">ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
       <c r="C75" s="97" t="s">
@@ -6617,7 +6614,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
         <v>52</v>
@@ -6670,10 +6667,10 @@
         <v>384</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f t="shared" ref="B77:B88" si="82">ROW(B77) - ROW($B$9)</f>
+        <f t="shared" ref="B77" si="82">ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
       <c r="C77" s="102" t="s">
@@ -6722,7 +6719,7 @@
       </c>
       <c r="R77" s="96"/>
     </row>
-    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
         <v>53</v>
@@ -6776,10 +6773,10 @@
       </c>
       <c r="R78" s="109"/>
     </row>
-    <row r="79" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
-        <f t="shared" ref="B79:B88" si="85">ROW(B79) - ROW($B$9)</f>
+        <f t="shared" ref="B79" si="85">ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
       <c r="C79" s="102" t="s">
@@ -6831,7 +6828,7 @@
       </c>
       <c r="R79" s="96"/>
     </row>
-    <row r="80" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
         <v>54</v>
@@ -6885,10 +6882,10 @@
       </c>
       <c r="R80" s="79"/>
     </row>
-    <row r="81" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f t="shared" ref="B81:B88" si="88">ROW(B81) - ROW($B$9)</f>
+        <f t="shared" ref="B81" si="88">ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
       <c r="C81" s="102" t="s">
@@ -6940,7 +6937,7 @@
       </c>
       <c r="R81" s="78"/>
     </row>
-    <row r="82" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
         <v>55</v>
@@ -6994,10 +6991,10 @@
       </c>
       <c r="R82" s="109"/>
     </row>
-    <row r="83" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
-        <f t="shared" ref="B83:B88" si="91">ROW(B83) - ROW($B$9)</f>
+        <f t="shared" ref="B83" si="91">ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
       <c r="C83" s="102" t="s">
@@ -7049,7 +7046,7 @@
       </c>
       <c r="R83" s="96"/>
     </row>
-    <row r="84" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
         <v>56</v>
@@ -7105,10 +7102,10 @@
         <v>438</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
-        <f t="shared" ref="B85:B88" si="94">ROW(B85) - ROW($B$9)</f>
+        <f t="shared" ref="B85" si="94">ROW(B85) - ROW($B$9)</f>
         <v>76</v>
       </c>
       <c r="C85" s="102" t="s">
@@ -7160,7 +7157,7 @@
       </c>
       <c r="R85" s="96"/>
     </row>
-    <row r="86" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
         <v>57</v>
@@ -7214,10 +7211,10 @@
       </c>
       <c r="R86" s="79"/>
     </row>
-    <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
-        <f t="shared" ref="B87:B88" si="97">ROW(B87) - ROW($B$9)</f>
+        <f t="shared" ref="B87" si="97">ROW(B87) - ROW($B$9)</f>
         <v>78</v>
       </c>
       <c r="C87" s="60" t="s">
@@ -7269,7 +7266,7 @@
       </c>
       <c r="R87" s="41"/>
     </row>
-    <row r="88" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
         <v>58</v>
@@ -7323,7 +7320,7 @@
       </c>
       <c r="R88" s="79"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="32"/>
       <c r="C89" s="51"/>
@@ -7346,11 +7343,11 @@
       <c r="P89" s="67"/>
       <c r="Q89" s="67">
         <f>SUM(Q10:Q88)</f>
-        <v>969.96630000000005</v>
+        <v>969.42630000000008</v>
       </c>
       <c r="R89" s="44"/>
     </row>
-    <row r="90" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="24"/>
       <c r="C90" s="52"/>
@@ -7373,7 +7370,7 @@
       <c r="P90" s="68"/>
       <c r="Q90" s="68">
         <f>Q89/20</f>
-        <v>48.498315000000005</v>
+        <v>48.471315000000004</v>
       </c>
       <c r="R90" s="45"/>
     </row>

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B3974B-7077-4EFB-AACA-BB30D08EB492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11490" windowHeight="7590"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="474">
   <si>
     <t>Component list</t>
   </si>
@@ -1574,11 +1575,23 @@
   <si>
     <t>Bivar Inc.</t>
   </si>
+  <si>
+    <t>Heat Sink</t>
+  </si>
+  <si>
+    <t>C4651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XSD </t>
+  </si>
+  <si>
+    <t>18*6*14 Heat Sinks ROHS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -2452,7 +2465,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2748,9 +2761,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -4985,6 +4998,7 @@
     <row r="46" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
+        <f t="shared" ref="B46:B89" si="35">ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
       <c r="C46" s="106" t="s">
@@ -5041,7 +5055,7 @@
     <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
-        <f t="shared" ref="B47" si="35">ROW(B47) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>38</v>
       </c>
       <c r="C47" s="102" t="s">
@@ -5096,7 +5110,8 @@
     <row r="48" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
-        <v>38</v>
+        <f t="shared" si="35"/>
+        <v>39</v>
       </c>
       <c r="C48" s="97" t="s">
         <v>283</v>
@@ -5145,7 +5160,7 @@
     <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
-        <f t="shared" ref="B49" si="39">ROW(B49) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>40</v>
       </c>
       <c r="C49" s="102" t="s">
@@ -5192,7 +5207,7 @@
         <v>0.13</v>
       </c>
       <c r="Q49" s="96">
-        <f t="shared" ref="Q49" si="40">N49*P49</f>
+        <f t="shared" ref="Q49" si="39">N49*P49</f>
         <v>11.700000000000001</v>
       </c>
       <c r="R49" s="96"/>
@@ -5200,7 +5215,8 @@
     <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
-        <v>39</v>
+        <f t="shared" si="35"/>
+        <v>41</v>
       </c>
       <c r="C50" s="106" t="s">
         <v>323</v>
@@ -5246,7 +5262,7 @@
         <v>0.21740000000000001</v>
       </c>
       <c r="Q50" s="109">
-        <f t="shared" ref="Q50" si="41">P50*N50</f>
+        <f t="shared" ref="Q50" si="40">P50*N50</f>
         <v>18.478999999999999</v>
       </c>
       <c r="R50" s="109"/>
@@ -5254,7 +5270,7 @@
     <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="53">
-        <f t="shared" ref="B51" si="42">ROW(B51) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>42</v>
       </c>
       <c r="C51" s="102" t="s">
@@ -5301,7 +5317,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q51" s="96">
-        <f t="shared" ref="Q51" si="43">N51*P51</f>
+        <f t="shared" ref="Q51" si="41">N51*P51</f>
         <v>0.1</v>
       </c>
       <c r="R51" s="96"/>
@@ -5309,7 +5325,8 @@
     <row r="52" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
-        <v>40</v>
+        <f t="shared" si="35"/>
+        <v>43</v>
       </c>
       <c r="C52" s="106" t="s">
         <v>324</v>
@@ -5355,7 +5372,7 @@
         <v>1.4E-3</v>
       </c>
       <c r="Q52" s="109">
-        <f t="shared" ref="Q52" si="44">P52*N52</f>
+        <f t="shared" ref="Q52" si="42">P52*N52</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R52" s="109"/>
@@ -5363,7 +5380,7 @@
     <row r="53" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
-        <f t="shared" ref="B53" si="45">ROW(B53) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>44</v>
       </c>
       <c r="C53" s="102" t="s">
@@ -5410,7 +5427,7 @@
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q53" s="96">
-        <f t="shared" ref="Q53" si="46">N53*P53</f>
+        <f t="shared" ref="Q53" si="43">N53*P53</f>
         <v>0.16</v>
       </c>
       <c r="R53" s="96"/>
@@ -5418,7 +5435,8 @@
     <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
-        <v>41</v>
+        <f t="shared" si="35"/>
+        <v>45</v>
       </c>
       <c r="C54" s="106" t="s">
         <v>324</v>
@@ -5464,7 +5482,7 @@
         <v>1.4E-3</v>
       </c>
       <c r="Q54" s="109">
-        <f t="shared" ref="Q54" si="47">P54*N54</f>
+        <f t="shared" ref="Q54" si="44">P54*N54</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R54" s="109"/>
@@ -5472,7 +5490,7 @@
     <row r="55" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
-        <f t="shared" ref="B55" si="48">ROW(B55) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>46</v>
       </c>
       <c r="C55" s="102" t="s">
@@ -5519,7 +5537,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q55" s="96">
-        <f t="shared" ref="Q55" si="49">N55*P55</f>
+        <f t="shared" ref="Q55" si="45">N55*P55</f>
         <v>0.13</v>
       </c>
       <c r="R55" s="96"/>
@@ -5527,7 +5545,8 @@
     <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
-        <v>42</v>
+        <f t="shared" si="35"/>
+        <v>47</v>
       </c>
       <c r="C56" s="106" t="s">
         <v>324</v>
@@ -5573,7 +5592,7 @@
         <v>6.4500000000000002E-2</v>
       </c>
       <c r="Q56" s="109">
-        <f t="shared" ref="Q56" si="50">P56*N56</f>
+        <f t="shared" ref="Q56" si="46">P56*N56</f>
         <v>5.8049999999999997</v>
       </c>
       <c r="R56" s="109"/>
@@ -5581,7 +5600,7 @@
     <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
-        <f t="shared" ref="B57" si="51">ROW(B57) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>48</v>
       </c>
       <c r="C57" s="60" t="s">
@@ -5628,7 +5647,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q57" s="37">
-        <f t="shared" ref="Q57" si="52">N57*P57</f>
+        <f t="shared" ref="Q57" si="47">N57*P57</f>
         <v>0.11</v>
       </c>
       <c r="R57" s="76"/>
@@ -5636,7 +5655,8 @@
     <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
-        <v>43</v>
+        <f t="shared" si="35"/>
+        <v>49</v>
       </c>
       <c r="C58" s="106" t="s">
         <v>324</v>
@@ -5682,7 +5702,7 @@
         <v>1.8589999999999999E-2</v>
       </c>
       <c r="Q58" s="109">
-        <f t="shared" ref="Q58" si="53">P58*N58</f>
+        <f t="shared" ref="Q58" si="48">P58*N58</f>
         <v>0.55769999999999997</v>
       </c>
       <c r="R58" s="109"/>
@@ -5690,7 +5710,7 @@
     <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
-        <f t="shared" ref="B59" si="54">ROW(B59) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>50</v>
       </c>
       <c r="C59" s="102" t="s">
@@ -5737,7 +5757,7 @@
         <v>1.4E-3</v>
       </c>
       <c r="Q59" s="96">
-        <f t="shared" ref="Q59" si="55">N59*P59</f>
+        <f t="shared" ref="Q59" si="49">N59*P59</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R59" s="96"/>
@@ -5745,7 +5765,8 @@
     <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
-        <v>44</v>
+        <f t="shared" si="35"/>
+        <v>51</v>
       </c>
       <c r="C60" s="106" t="s">
         <v>324</v>
@@ -5791,7 +5812,7 @@
         <v>4.6699999999999997E-3</v>
       </c>
       <c r="Q60" s="109">
-        <f t="shared" ref="Q60" si="56">P60*N60</f>
+        <f t="shared" ref="Q60" si="50">P60*N60</f>
         <v>0.23349999999999999</v>
       </c>
       <c r="R60" s="109"/>
@@ -5799,7 +5820,7 @@
     <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f t="shared" ref="B61" si="57">ROW(B61) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>52</v>
       </c>
       <c r="C61" s="102" t="s">
@@ -5846,7 +5867,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q61" s="96">
-        <f t="shared" ref="Q61" si="58">N61*P61</f>
+        <f t="shared" ref="Q61" si="51">N61*P61</f>
         <v>0.12</v>
       </c>
       <c r="R61" s="96"/>
@@ -5854,7 +5875,8 @@
     <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
-        <v>45</v>
+        <f t="shared" si="35"/>
+        <v>53</v>
       </c>
       <c r="C62" s="106" t="s">
         <v>324</v>
@@ -5900,7 +5922,7 @@
         <v>1.11E-2</v>
       </c>
       <c r="Q62" s="109">
-        <f t="shared" ref="Q62" si="59">P62*N62</f>
+        <f t="shared" ref="Q62" si="52">P62*N62</f>
         <v>0.55500000000000005</v>
       </c>
       <c r="R62" s="109"/>
@@ -5908,7 +5930,7 @@
     <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
-        <f t="shared" ref="B63" si="60">ROW(B63) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>54</v>
       </c>
       <c r="C63" s="102" t="s">
@@ -5955,7 +5977,7 @@
         <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q63" s="96">
-        <f t="shared" ref="Q63" si="61">N63*P63</f>
+        <f t="shared" ref="Q63" si="53">N63*P63</f>
         <v>0.21</v>
       </c>
       <c r="R63" s="96"/>
@@ -5963,7 +5985,8 @@
     <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
-        <v>46</v>
+        <f t="shared" si="35"/>
+        <v>55</v>
       </c>
       <c r="C64" s="106" t="s">
         <v>324</v>
@@ -6009,7 +6032,7 @@
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q64" s="109">
-        <f t="shared" ref="Q64" si="62">P64*N64</f>
+        <f t="shared" ref="Q64" si="54">P64*N64</f>
         <v>0.16</v>
       </c>
       <c r="R64" s="109"/>
@@ -6017,7 +6040,7 @@
     <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
-        <f t="shared" ref="B65" si="63">ROW(B65) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>56</v>
       </c>
       <c r="C65" s="102" t="s">
@@ -6064,7 +6087,7 @@
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q65" s="96">
-        <f t="shared" ref="Q65" si="64">N65*P65</f>
+        <f t="shared" ref="Q65" si="55">N65*P65</f>
         <v>0.34499999999999997</v>
       </c>
       <c r="R65" s="96"/>
@@ -6072,7 +6095,8 @@
     <row r="66" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
-        <v>47</v>
+        <f t="shared" si="35"/>
+        <v>57</v>
       </c>
       <c r="C66" s="106" t="s">
         <v>324</v>
@@ -6118,7 +6142,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q66" s="109">
-        <f t="shared" ref="Q66" si="65">P66*N66</f>
+        <f t="shared" ref="Q66" si="56">P66*N66</f>
         <v>0.11</v>
       </c>
       <c r="R66" s="109"/>
@@ -6126,7 +6150,7 @@
     <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
-        <f t="shared" ref="B67" si="66">ROW(B67) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>58</v>
       </c>
       <c r="C67" s="60" t="s">
@@ -6173,7 +6197,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="Q67" s="41">
-        <f t="shared" ref="Q67" si="67">P67*N67</f>
+        <f t="shared" ref="Q67" si="57">P67*N67</f>
         <v>0.15</v>
       </c>
       <c r="R67" s="41"/>
@@ -6181,7 +6205,8 @@
     <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
-        <v>48</v>
+        <f t="shared" si="35"/>
+        <v>59</v>
       </c>
       <c r="C68" s="59" t="s">
         <v>324</v>
@@ -6233,7 +6258,7 @@
     <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
-        <f t="shared" ref="B69" si="68">ROW(B69) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>60</v>
       </c>
       <c r="C69" s="60" t="s">
@@ -6280,7 +6305,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="Q69" s="41">
-        <f t="shared" ref="Q69" si="69">P69*N69</f>
+        <f t="shared" ref="Q69" si="58">P69*N69</f>
         <v>0.15</v>
       </c>
       <c r="R69" s="41"/>
@@ -6288,7 +6313,8 @@
     <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
-        <v>49</v>
+        <f t="shared" si="35"/>
+        <v>61</v>
       </c>
       <c r="C70" s="59" t="s">
         <v>324</v>
@@ -6334,7 +6360,7 @@
         <v>8.5400000000000004E-2</v>
       </c>
       <c r="Q70" s="42">
-        <f t="shared" ref="Q70" si="70">N70*P70</f>
+        <f t="shared" ref="Q70" si="59">N70*P70</f>
         <v>2.1350000000000002</v>
       </c>
       <c r="R70" s="42"/>
@@ -6342,7 +6368,7 @@
     <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f t="shared" ref="B71" si="71">ROW(B71) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>62</v>
       </c>
       <c r="C71" s="60" t="s">
@@ -6376,7 +6402,7 @@
         <v>1</v>
       </c>
       <c r="M71" s="41">
-        <f t="shared" ref="M71:M88" si="72">L71*20</f>
+        <f t="shared" ref="M71:M89" si="60">L71*20</f>
         <v>20</v>
       </c>
       <c r="N71" s="41">
@@ -6389,7 +6415,7 @@
         <v>3.8E-3</v>
       </c>
       <c r="Q71" s="41">
-        <f t="shared" ref="Q71" si="73">P71*N71</f>
+        <f t="shared" ref="Q71" si="61">P71*N71</f>
         <v>0.19</v>
       </c>
       <c r="R71" s="76"/>
@@ -6397,7 +6423,8 @@
     <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
-        <v>50</v>
+        <f t="shared" si="35"/>
+        <v>63</v>
       </c>
       <c r="C72" s="59" t="s">
         <v>324</v>
@@ -6443,7 +6470,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q72" s="42">
-        <f t="shared" ref="Q72" si="74">N72*P72</f>
+        <f t="shared" ref="Q72" si="62">N72*P72</f>
         <v>0.24</v>
       </c>
       <c r="R72" s="77"/>
@@ -6451,7 +6478,7 @@
     <row r="73" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
-        <f t="shared" ref="B73" si="75">ROW(B73) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>64</v>
       </c>
       <c r="C73" s="60" t="s">
@@ -6485,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="M73" s="41">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N73" s="41">
@@ -6498,7 +6525,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q73" s="41">
-        <f t="shared" ref="Q73" si="76">P73*N73</f>
+        <f t="shared" ref="Q73" si="63">P73*N73</f>
         <v>0.1</v>
       </c>
       <c r="R73" s="41"/>
@@ -6506,7 +6533,8 @@
     <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
-        <v>51</v>
+        <f t="shared" si="35"/>
+        <v>65</v>
       </c>
       <c r="C74" s="59" t="s">
         <v>324</v>
@@ -6539,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="42">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N74" s="42">
@@ -6552,7 +6580,7 @@
         <v>4.3E-3</v>
       </c>
       <c r="Q74" s="42">
-        <f t="shared" ref="Q74" si="77">N74*P74</f>
+        <f t="shared" ref="Q74" si="64">N74*P74</f>
         <v>0.215</v>
       </c>
       <c r="R74" s="42"/>
@@ -6560,7 +6588,7 @@
     <row r="75" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
-        <f t="shared" ref="B75" si="78">ROW(B75) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>66</v>
       </c>
       <c r="C75" s="97" t="s">
@@ -6594,7 +6622,7 @@
         <v>4</v>
       </c>
       <c r="M75" s="66">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>80</v>
       </c>
       <c r="N75" s="66">
@@ -6607,7 +6635,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q75" s="66">
-        <f t="shared" ref="Q75" si="79">P75*N75</f>
+        <f t="shared" ref="Q75" si="65">P75*N75</f>
         <v>0.12</v>
       </c>
       <c r="R75" s="66" t="s">
@@ -6617,7 +6645,8 @@
     <row r="76" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
-        <v>52</v>
+        <f t="shared" si="35"/>
+        <v>67</v>
       </c>
       <c r="C76" s="97" t="s">
         <v>169</v>
@@ -6650,17 +6679,17 @@
         <v>15</v>
       </c>
       <c r="M76" s="66">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>300</v>
       </c>
       <c r="N76" s="66">
-        <f t="shared" ref="N76:N77" si="80">M76+(M76*0.1)</f>
+        <f t="shared" ref="N76:N77" si="66">M76+(M76*0.1)</f>
         <v>330</v>
       </c>
       <c r="O76" s="66"/>
       <c r="P76" s="66"/>
       <c r="Q76" s="66">
-        <f t="shared" ref="Q76" si="81">P76*N76</f>
+        <f t="shared" ref="Q76" si="67">P76*N76</f>
         <v>0</v>
       </c>
       <c r="R76" s="66" t="s">
@@ -6670,7 +6699,7 @@
     <row r="77" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f t="shared" ref="B77" si="82">ROW(B77) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>68</v>
       </c>
       <c r="C77" s="102" t="s">
@@ -6704,17 +6733,17 @@
         <v>1</v>
       </c>
       <c r="M77" s="96">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N77" s="96">
-        <f t="shared" si="80"/>
+        <f t="shared" si="66"/>
         <v>22</v>
       </c>
       <c r="O77" s="96"/>
       <c r="P77" s="96"/>
       <c r="Q77" s="96">
-        <f t="shared" ref="Q77" si="83">N77*P77</f>
+        <f t="shared" ref="Q77" si="68">N77*P77</f>
         <v>0</v>
       </c>
       <c r="R77" s="96"/>
@@ -6722,7 +6751,8 @@
     <row r="78" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
-        <v>53</v>
+        <f t="shared" si="35"/>
+        <v>69</v>
       </c>
       <c r="C78" s="106" t="s">
         <v>327</v>
@@ -6755,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="109">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N78" s="109">
@@ -6768,7 +6798,7 @@
         <v>3.81</v>
       </c>
       <c r="Q78" s="109">
-        <f t="shared" ref="Q78" si="84">P78*N78</f>
+        <f t="shared" ref="Q78" si="69">P78*N78</f>
         <v>80.010000000000005</v>
       </c>
       <c r="R78" s="109"/>
@@ -6776,7 +6806,7 @@
     <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
-        <f t="shared" ref="B79" si="85">ROW(B79) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>70</v>
       </c>
       <c r="C79" s="102" t="s">
@@ -6810,7 +6840,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="96">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N79" s="96">
@@ -6823,7 +6853,7 @@
         <v>2.48</v>
       </c>
       <c r="Q79" s="96">
-        <f t="shared" ref="Q79" si="86">N79*P79</f>
+        <f t="shared" ref="Q79" si="70">N79*P79</f>
         <v>52.08</v>
       </c>
       <c r="R79" s="96"/>
@@ -6831,7 +6861,8 @@
     <row r="80" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
-        <v>54</v>
+        <f t="shared" si="35"/>
+        <v>71</v>
       </c>
       <c r="C80" s="106" t="s">
         <v>328</v>
@@ -6864,7 +6895,7 @@
         <v>1</v>
       </c>
       <c r="M80" s="109">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N80" s="109">
@@ -6877,7 +6908,7 @@
         <v>1.3939999999999999</v>
       </c>
       <c r="Q80" s="109">
-        <f t="shared" ref="Q80" si="87">P80*N80</f>
+        <f t="shared" ref="Q80" si="71">P80*N80</f>
         <v>29.273999999999997</v>
       </c>
       <c r="R80" s="79"/>
@@ -6885,7 +6916,7 @@
     <row r="81" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f t="shared" ref="B81" si="88">ROW(B81) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>72</v>
       </c>
       <c r="C81" s="102" t="s">
@@ -6919,7 +6950,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="96">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N81" s="96">
@@ -6932,7 +6963,7 @@
         <v>0.69430000000000003</v>
       </c>
       <c r="Q81" s="96">
-        <f t="shared" ref="Q81" si="89">N81*P81</f>
+        <f t="shared" ref="Q81" si="72">N81*P81</f>
         <v>14.580300000000001</v>
       </c>
       <c r="R81" s="78"/>
@@ -6940,7 +6971,8 @@
     <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
-        <v>55</v>
+        <f t="shared" si="35"/>
+        <v>73</v>
       </c>
       <c r="C82" s="106" t="s">
         <v>328</v>
@@ -6973,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="109">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N82" s="109">
@@ -6986,7 +7018,7 @@
         <v>3.637</v>
       </c>
       <c r="Q82" s="109">
-        <f t="shared" ref="Q82" si="90">P82*N82</f>
+        <f t="shared" ref="Q82" si="73">P82*N82</f>
         <v>76.376999999999995</v>
       </c>
       <c r="R82" s="109"/>
@@ -6994,7 +7026,7 @@
     <row r="83" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
-        <f t="shared" ref="B83" si="91">ROW(B83) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>74</v>
       </c>
       <c r="C83" s="102" t="s">
@@ -7028,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="96">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N83" s="96">
@@ -7041,7 +7073,7 @@
         <v>0.43280000000000002</v>
       </c>
       <c r="Q83" s="96">
-        <f t="shared" ref="Q83" si="92">N83*P83</f>
+        <f t="shared" ref="Q83" si="74">N83*P83</f>
         <v>9.0888000000000009</v>
       </c>
       <c r="R83" s="96"/>
@@ -7049,7 +7081,8 @@
     <row r="84" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
-        <v>56</v>
+        <f t="shared" si="35"/>
+        <v>75</v>
       </c>
       <c r="C84" s="71" t="s">
         <v>328</v>
@@ -7082,7 +7115,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="74">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N84" s="74">
@@ -7095,7 +7128,7 @@
         <v>7.4638</v>
       </c>
       <c r="Q84" s="74">
-        <f t="shared" ref="Q84" si="93">P84*N84</f>
+        <f t="shared" ref="Q84" si="75">P84*N84</f>
         <v>156.7398</v>
       </c>
       <c r="R84" s="74" t="s">
@@ -7105,7 +7138,7 @@
     <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
-        <f t="shared" ref="B85" si="94">ROW(B85) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>76</v>
       </c>
       <c r="C85" s="102" t="s">
@@ -7139,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="96">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N85" s="96">
@@ -7152,7 +7185,7 @@
         <v>2.6459999999999999</v>
       </c>
       <c r="Q85" s="96">
-        <f t="shared" ref="Q85" si="95">N85*P85</f>
+        <f t="shared" ref="Q85" si="76">N85*P85</f>
         <v>55.565999999999995</v>
       </c>
       <c r="R85" s="96"/>
@@ -7160,7 +7193,8 @@
     <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
-        <v>57</v>
+        <f t="shared" si="35"/>
+        <v>77</v>
       </c>
       <c r="C86" s="106" t="s">
         <v>328</v>
@@ -7193,7 +7227,7 @@
         <v>2</v>
       </c>
       <c r="M86" s="109">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>40</v>
       </c>
       <c r="N86" s="109">
@@ -7206,7 +7240,7 @@
         <v>2.2974000000000001</v>
       </c>
       <c r="Q86" s="109">
-        <f t="shared" ref="Q86" si="96">P86*N86</f>
+        <f t="shared" ref="Q86" si="77">P86*N86</f>
         <v>96.490800000000007</v>
       </c>
       <c r="R86" s="79"/>
@@ -7214,7 +7248,7 @@
     <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
-        <f t="shared" ref="B87" si="97">ROW(B87) - ROW($B$9)</f>
+        <f t="shared" si="35"/>
         <v>78</v>
       </c>
       <c r="C87" s="60" t="s">
@@ -7261,7 +7295,7 @@
         <v>0.39140000000000003</v>
       </c>
       <c r="Q87" s="41">
-        <f t="shared" ref="Q87" si="98">P87*N87</f>
+        <f t="shared" ref="Q87" si="78">P87*N87</f>
         <v>8.2194000000000003</v>
       </c>
       <c r="R87" s="41"/>
@@ -7269,7 +7303,8 @@
     <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
-        <v>58</v>
+        <f t="shared" si="35"/>
+        <v>79</v>
       </c>
       <c r="C88" s="59" t="s">
         <v>328</v>
@@ -7302,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="42">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N88" s="42">
@@ -7315,64 +7350,117 @@
         <v>3.532</v>
       </c>
       <c r="Q88" s="42">
-        <f t="shared" ref="Q88" si="99">N88*P88</f>
+        <f t="shared" ref="Q88:Q89" si="79">N88*P88</f>
         <v>74.171999999999997</v>
       </c>
       <c r="R88" s="79"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
-      <c r="B89" s="32"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="33" t="s">
+      <c r="B89" s="53">
+        <f t="shared" si="35"/>
+        <v>80</v>
+      </c>
+      <c r="C89" s="59" t="s">
+        <v>470</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="E89" s="40" t="s">
+        <v>473</v>
+      </c>
+      <c r="F89" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="G89" s="40" t="s">
+        <v>471</v>
+      </c>
+      <c r="H89" s="39" t="s">
+        <v>472</v>
+      </c>
+      <c r="I89" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J89" s="39" t="s">
+        <v>471</v>
+      </c>
+      <c r="K89" s="40"/>
+      <c r="L89" s="39">
+        <v>1</v>
+      </c>
+      <c r="M89" s="42">
+        <f t="shared" si="60"/>
+        <v>20</v>
+      </c>
+      <c r="N89" s="42">
+        <v>25</v>
+      </c>
+      <c r="O89" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P89" s="42">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="Q89" s="42">
+        <f t="shared" si="79"/>
+        <v>2.2250000000000001</v>
+      </c>
+      <c r="R89" s="79"/>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="B90" s="32"/>
+      <c r="C90" s="51"/>
+      <c r="D90" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="34"/>
-      <c r="F89" s="35"/>
-      <c r="G89" s="36"/>
-      <c r="H89" s="35"/>
-      <c r="I89" s="35"/>
-      <c r="J89" s="35"/>
-      <c r="K89" s="36"/>
-      <c r="L89" s="36"/>
-      <c r="M89" s="36"/>
-      <c r="N89" s="36"/>
-      <c r="O89" s="69" t="s">
+      <c r="E90" s="34"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="36"/>
+      <c r="H90" s="35"/>
+      <c r="I90" s="35"/>
+      <c r="J90" s="35"/>
+      <c r="K90" s="36"/>
+      <c r="L90" s="36"/>
+      <c r="M90" s="36"/>
+      <c r="N90" s="36"/>
+      <c r="O90" s="69" t="s">
         <v>421</v>
       </c>
-      <c r="P89" s="67"/>
-      <c r="Q89" s="67">
+      <c r="P90" s="67"/>
+      <c r="Q90" s="67">
         <f>SUM(Q10:Q88)</f>
         <v>969.42630000000008</v>
       </c>
-      <c r="R89" s="44"/>
-    </row>
-    <row r="90" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1"/>
-      <c r="B90" s="24"/>
-      <c r="C90" s="52"/>
-      <c r="D90" s="8" t="s">
+      <c r="R90" s="44"/>
+    </row>
+    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="B91" s="24"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="9"/>
-      <c r="K90" s="9"/>
-      <c r="L90" s="9"/>
-      <c r="M90" s="9"/>
-      <c r="N90" s="9"/>
-      <c r="O90" s="70" t="s">
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+      <c r="N91" s="9"/>
+      <c r="O91" s="70" t="s">
         <v>422</v>
       </c>
-      <c r="P90" s="68"/>
-      <c r="Q90" s="68">
-        <f>Q89/20</f>
+      <c r="P91" s="68"/>
+      <c r="Q91" s="68">
+        <f>Q90/20</f>
         <v>48.471315000000004</v>
       </c>
-      <c r="R90" s="45"/>
+      <c r="R91" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7380,84 +7468,85 @@
     <mergeCell ref="R3:R8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
-    <hyperlink ref="O12" r:id="rId3"/>
-    <hyperlink ref="O13" r:id="rId4"/>
-    <hyperlink ref="O14" r:id="rId5"/>
-    <hyperlink ref="O15" r:id="rId6"/>
-    <hyperlink ref="O16" r:id="rId7"/>
-    <hyperlink ref="O17" r:id="rId8"/>
-    <hyperlink ref="O18" r:id="rId9"/>
-    <hyperlink ref="O19" r:id="rId10"/>
-    <hyperlink ref="O20" r:id="rId11"/>
-    <hyperlink ref="O21" r:id="rId12"/>
-    <hyperlink ref="O22" r:id="rId13"/>
-    <hyperlink ref="O23" r:id="rId14"/>
-    <hyperlink ref="O24" r:id="rId15"/>
-    <hyperlink ref="O25" r:id="rId16"/>
-    <hyperlink ref="O26" r:id="rId17"/>
-    <hyperlink ref="O27" r:id="rId18"/>
-    <hyperlink ref="O28" r:id="rId19"/>
-    <hyperlink ref="O29" r:id="rId20"/>
-    <hyperlink ref="O30" r:id="rId21"/>
-    <hyperlink ref="O31" r:id="rId22"/>
-    <hyperlink ref="O32" r:id="rId23"/>
-    <hyperlink ref="O33" r:id="rId24"/>
-    <hyperlink ref="O34" r:id="rId25"/>
-    <hyperlink ref="O35" r:id="rId26"/>
-    <hyperlink ref="O36" r:id="rId27"/>
-    <hyperlink ref="O37" r:id="rId28"/>
-    <hyperlink ref="O38" r:id="rId29"/>
-    <hyperlink ref="O39" r:id="rId30"/>
-    <hyperlink ref="O40" r:id="rId31"/>
-    <hyperlink ref="O41" r:id="rId32"/>
-    <hyperlink ref="O42" r:id="rId33"/>
-    <hyperlink ref="O43" r:id="rId34"/>
-    <hyperlink ref="O44" r:id="rId35"/>
-    <hyperlink ref="O45" r:id="rId36"/>
-    <hyperlink ref="O47" r:id="rId37"/>
-    <hyperlink ref="O49" r:id="rId38"/>
-    <hyperlink ref="O50" r:id="rId39"/>
-    <hyperlink ref="O51" r:id="rId40"/>
-    <hyperlink ref="O52" r:id="rId41"/>
-    <hyperlink ref="O53" r:id="rId42"/>
-    <hyperlink ref="O54" r:id="rId43"/>
-    <hyperlink ref="O55" r:id="rId44"/>
-    <hyperlink ref="O56" r:id="rId45"/>
-    <hyperlink ref="O68" r:id="rId46"/>
-    <hyperlink ref="O58" r:id="rId47"/>
-    <hyperlink ref="O59" r:id="rId48"/>
-    <hyperlink ref="O60" r:id="rId49"/>
-    <hyperlink ref="O61" r:id="rId50"/>
-    <hyperlink ref="O62" r:id="rId51"/>
-    <hyperlink ref="O63" r:id="rId52"/>
-    <hyperlink ref="O64" r:id="rId53"/>
-    <hyperlink ref="O65" r:id="rId54"/>
-    <hyperlink ref="O66" r:id="rId55"/>
-    <hyperlink ref="O67" r:id="rId56"/>
-    <hyperlink ref="O69" r:id="rId57"/>
-    <hyperlink ref="O70" r:id="rId58"/>
-    <hyperlink ref="O71" r:id="rId59"/>
-    <hyperlink ref="O74" r:id="rId60"/>
-    <hyperlink ref="O75" r:id="rId61"/>
-    <hyperlink ref="O72" r:id="rId62"/>
-    <hyperlink ref="O78" r:id="rId63"/>
-    <hyperlink ref="O79" r:id="rId64"/>
-    <hyperlink ref="O80" r:id="rId65"/>
-    <hyperlink ref="O81" r:id="rId66"/>
-    <hyperlink ref="O82" r:id="rId67"/>
-    <hyperlink ref="O83" r:id="rId68"/>
-    <hyperlink ref="O84" r:id="rId69"/>
-    <hyperlink ref="O85" r:id="rId70"/>
-    <hyperlink ref="O86" r:id="rId71"/>
-    <hyperlink ref="O88" r:id="rId72"/>
-    <hyperlink ref="O87" r:id="rId73"/>
-    <hyperlink ref="O57" r:id="rId74"/>
-    <hyperlink ref="O46" r:id="rId75"/>
+    <hyperlink ref="O10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="O11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="O12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="O13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="O14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="O16" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="O17" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O18" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O19" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O20" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O21" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O22" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O23" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="O24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O25" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O26" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O27" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O28" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O29" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O30" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O31" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O32" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O33" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O34" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O35" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O36" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O37" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O38" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O39" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O40" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O41" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O42" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O43" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="O44" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O45" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O47" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O49" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O50" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O51" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O52" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O53" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O54" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O55" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O56" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O68" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O58" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O59" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O60" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O61" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O62" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O63" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O64" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O65" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O66" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O67" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O69" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O70" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O71" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O74" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O75" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O72" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O78" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O79" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O80" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="O81" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O82" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O83" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="O84" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O85" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O86" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O88" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O87" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O57" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O46" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O89" r:id="rId76" xr:uid="{94AF4969-113D-4C22-911F-093FC1147D5D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
-  <drawing r:id="rId77"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId77"/>
+  <drawing r:id="rId78"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B3974B-7077-4EFB-AACA-BB30D08EB492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="479">
   <si>
     <t>Component list</t>
   </si>
@@ -1587,11 +1586,26 @@
   <si>
     <t>18*6*14 Heat Sinks ROHS</t>
   </si>
+  <si>
+    <t>J11</t>
+  </si>
+  <si>
+    <t>X6521WVS-2x04H-C60D74</t>
+  </si>
+  <si>
+    <t>Gold 250V 3A Brick nogging Square Pins 2.5mm 260℃ 6mm -40℃~+105℃ 2 8 2.54mm Black Brass 2.54mm 2x4P SMD,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>XKB Connectivity</t>
+  </si>
+  <si>
+    <t>C780053</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -2092,7 +2106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2420,6 +2434,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2465,7 +2485,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2761,9 +2781,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:U92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -3069,7 +3089,7 @@
     <row r="11" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B44" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B45" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="81" t="s">
@@ -3160,7 +3180,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="41">
-        <f t="shared" ref="M12:M70" si="1">L12*20</f>
+        <f t="shared" ref="M12:M71" si="1">L12*20</f>
         <v>40</v>
       </c>
       <c r="N12" s="41">
@@ -4278,7 +4298,7 @@
       </c>
       <c r="R32" s="96"/>
     </row>
-    <row r="33" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -4333,7 +4353,7 @@
       </c>
       <c r="R33" s="109"/>
     </row>
-    <row r="34" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
@@ -4388,7 +4408,7 @@
       </c>
       <c r="R34" s="78"/>
     </row>
-    <row r="35" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -4444,8 +4464,9 @@
       <c r="R35" s="84" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U35" s="119"/>
+    </row>
+    <row r="36" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
@@ -4500,7 +4521,7 @@
       </c>
       <c r="R36" s="96"/>
     </row>
-    <row r="37" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -4555,7 +4576,7 @@
       </c>
       <c r="R37" s="109"/>
     </row>
-    <row r="38" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
@@ -4610,7 +4631,7 @@
       </c>
       <c r="R38" s="78"/>
     </row>
-    <row r="39" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -4665,7 +4686,7 @@
       </c>
       <c r="R39" s="79"/>
     </row>
-    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
@@ -4720,7 +4741,7 @@
       </c>
       <c r="R40" s="96"/>
     </row>
-    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
@@ -4775,249 +4796,246 @@
       </c>
       <c r="R41" s="109"/>
     </row>
-    <row r="42" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="53">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="102" t="s">
-        <v>318</v>
-      </c>
-      <c r="D42" s="103" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="104" t="s">
-        <v>98</v>
-      </c>
-      <c r="F42" s="103" t="s">
+      <c r="B42" s="53"/>
+      <c r="C42" s="106" t="s">
+        <v>321</v>
+      </c>
+      <c r="D42" s="107" t="s">
+        <v>474</v>
+      </c>
+      <c r="E42" s="108" t="s">
+        <v>476</v>
+      </c>
+      <c r="F42" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G42" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="H42" s="103" t="s">
-        <v>233</v>
-      </c>
-      <c r="I42" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J42" s="103" t="s">
-        <v>381</v>
-      </c>
-      <c r="K42" s="104" t="s">
-        <v>282</v>
-      </c>
-      <c r="L42" s="103">
+      <c r="G42" s="108" t="s">
+        <v>475</v>
+      </c>
+      <c r="H42" s="107" t="s">
+        <v>477</v>
+      </c>
+      <c r="I42" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J42" s="107" t="s">
+        <v>478</v>
+      </c>
+      <c r="K42" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L42" s="107">
         <v>1</v>
       </c>
-      <c r="M42" s="96">
+      <c r="M42" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N42" s="96">
-        <v>21</v>
-      </c>
-      <c r="O42" s="105" t="s">
+      <c r="N42" s="109">
+        <v>25</v>
+      </c>
+      <c r="O42" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P42" s="96">
-        <v>0.45629999999999998</v>
-      </c>
-      <c r="Q42" s="96">
-        <f t="shared" ref="Q42" si="31">N42*P42</f>
-        <v>9.5823</v>
-      </c>
-      <c r="R42" s="96"/>
-    </row>
-    <row r="43" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P42" s="109">
+        <v>0.21210000000000001</v>
+      </c>
+      <c r="Q42" s="109">
+        <f>P42*N42</f>
+        <v>5.3025000000000002</v>
+      </c>
+      <c r="R42" s="109"/>
+    </row>
+    <row r="43" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="53">
-        <f>ROW(B43) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="106" t="s">
+      <c r="C43" s="102" t="s">
         <v>318</v>
       </c>
-      <c r="D43" s="107" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="108" t="s">
-        <v>448</v>
-      </c>
-      <c r="F43" s="107" t="s">
+      <c r="D43" s="103" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="104" t="s">
+        <v>98</v>
+      </c>
+      <c r="F43" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G43" s="108" t="s">
-        <v>447</v>
-      </c>
-      <c r="H43" s="107" t="s">
-        <v>436</v>
-      </c>
-      <c r="I43" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J43" s="107" t="s">
-        <v>437</v>
-      </c>
-      <c r="K43" s="108" t="s">
-        <v>446</v>
-      </c>
-      <c r="L43" s="107">
+      <c r="G43" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="H43" s="103" t="s">
+        <v>233</v>
+      </c>
+      <c r="I43" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J43" s="103" t="s">
+        <v>381</v>
+      </c>
+      <c r="K43" s="104" t="s">
+        <v>282</v>
+      </c>
+      <c r="L43" s="103">
         <v>1</v>
       </c>
-      <c r="M43" s="109">
+      <c r="M43" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N43" s="109">
-        <v>25</v>
-      </c>
-      <c r="O43" s="110" t="s">
+      <c r="N43" s="96">
+        <v>21</v>
+      </c>
+      <c r="O43" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P43" s="109">
-        <v>0.1012</v>
-      </c>
-      <c r="Q43" s="109">
-        <f t="shared" ref="Q43" si="32">P43*N43</f>
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="R43" s="77"/>
-    </row>
-    <row r="44" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P43" s="96">
+        <v>0.45629999999999998</v>
+      </c>
+      <c r="Q43" s="96">
+        <f t="shared" ref="Q43" si="31">N43*P43</f>
+        <v>9.5823</v>
+      </c>
+      <c r="R43" s="96"/>
+    </row>
+    <row r="44" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="102" t="s">
-        <v>322</v>
-      </c>
-      <c r="D44" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="104" t="s">
-        <v>99</v>
-      </c>
-      <c r="F44" s="103" t="s">
+      <c r="C44" s="106" t="s">
+        <v>318</v>
+      </c>
+      <c r="D44" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="108" t="s">
+        <v>448</v>
+      </c>
+      <c r="F44" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G44" s="104" t="s">
-        <v>160</v>
-      </c>
-      <c r="H44" s="103" t="s">
-        <v>245</v>
-      </c>
-      <c r="I44" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J44" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K44" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L44" s="103">
+      <c r="G44" s="108" t="s">
+        <v>447</v>
+      </c>
+      <c r="H44" s="107" t="s">
+        <v>436</v>
+      </c>
+      <c r="I44" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J44" s="107" t="s">
+        <v>437</v>
+      </c>
+      <c r="K44" s="108" t="s">
+        <v>446</v>
+      </c>
+      <c r="L44" s="107">
         <v>1</v>
       </c>
-      <c r="M44" s="96">
+      <c r="M44" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N44" s="96">
-        <v>30</v>
-      </c>
-      <c r="O44" s="105" t="s">
-        <v>382</v>
-      </c>
-      <c r="P44" s="96">
-        <v>0.156</v>
-      </c>
-      <c r="Q44" s="96">
-        <f t="shared" ref="Q44" si="33">N44*P44</f>
-        <v>4.68</v>
-      </c>
-      <c r="R44" s="96"/>
-    </row>
-    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N44" s="109">
+        <v>25</v>
+      </c>
+      <c r="O44" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P44" s="109">
+        <v>0.1012</v>
+      </c>
+      <c r="Q44" s="109">
+        <f t="shared" ref="Q44" si="32">P44*N44</f>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="R44" s="77"/>
+    </row>
+    <row r="45" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
-        <f>ROW(B45) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="106" t="s">
+      <c r="C45" s="102" t="s">
         <v>322</v>
       </c>
-      <c r="D45" s="107" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" s="108" t="s">
-        <v>100</v>
-      </c>
-      <c r="F45" s="107" t="s">
-        <v>161</v>
-      </c>
-      <c r="G45" s="108" t="s">
-        <v>199</v>
-      </c>
-      <c r="H45" s="107" t="s">
-        <v>246</v>
-      </c>
-      <c r="I45" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J45" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K45" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L45" s="107">
+      <c r="D45" s="103" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="104" t="s">
+        <v>99</v>
+      </c>
+      <c r="F45" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G45" s="104" t="s">
+        <v>160</v>
+      </c>
+      <c r="H45" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="I45" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J45" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K45" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L45" s="103">
         <v>1</v>
       </c>
-      <c r="M45" s="109">
+      <c r="M45" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N45" s="109">
+      <c r="N45" s="96">
         <v>30</v>
       </c>
-      <c r="O45" s="110" t="s">
-        <v>383</v>
-      </c>
-      <c r="P45" s="109">
-        <v>0.08</v>
-      </c>
-      <c r="Q45" s="109">
-        <f t="shared" ref="Q45:Q46" si="34">P45*N45</f>
-        <v>2.4</v>
-      </c>
-      <c r="R45" s="109"/>
-    </row>
-    <row r="46" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O45" s="105" t="s">
+        <v>382</v>
+      </c>
+      <c r="P45" s="96">
+        <v>0.156</v>
+      </c>
+      <c r="Q45" s="96">
+        <f t="shared" ref="Q45" si="33">N45*P45</f>
+        <v>4.68</v>
+      </c>
+      <c r="R45" s="96"/>
+    </row>
+    <row r="46" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
-        <f t="shared" ref="B46:B89" si="35">ROW(B46) - ROW($B$9)</f>
+        <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
       <c r="C46" s="106" t="s">
-        <v>465</v>
+        <v>322</v>
       </c>
       <c r="D46" s="107" t="s">
-        <v>314</v>
+        <v>32</v>
       </c>
       <c r="E46" s="108" t="s">
-        <v>467</v>
+        <v>100</v>
       </c>
       <c r="F46" s="107" t="s">
-        <v>308</v>
+        <v>161</v>
       </c>
       <c r="G46" s="108" t="s">
-        <v>468</v>
+        <v>199</v>
       </c>
       <c r="H46" s="107" t="s">
-        <v>469</v>
+        <v>246</v>
       </c>
       <c r="I46" s="107" t="s">
         <v>314</v>
@@ -5036,126 +5054,131 @@
         <v>20</v>
       </c>
       <c r="N46" s="109">
+        <v>30</v>
+      </c>
+      <c r="O46" s="110" t="s">
+        <v>383</v>
+      </c>
+      <c r="P46" s="109">
+        <v>0.08</v>
+      </c>
+      <c r="Q46" s="109">
+        <f t="shared" ref="Q46:Q47" si="34">P46*N46</f>
+        <v>2.4</v>
+      </c>
+      <c r="R46" s="109"/>
+    </row>
+    <row r="47" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="53">
+        <f t="shared" ref="B47:B90" si="35">ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="106" t="s">
+        <v>465</v>
+      </c>
+      <c r="D47" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="E47" s="108" t="s">
+        <v>467</v>
+      </c>
+      <c r="F47" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="G47" s="108" t="s">
+        <v>468</v>
+      </c>
+      <c r="H47" s="107" t="s">
+        <v>469</v>
+      </c>
+      <c r="I47" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J47" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K47" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L47" s="107">
+        <v>1</v>
+      </c>
+      <c r="M47" s="109">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="O46" s="110" t="s">
+      <c r="N47" s="109">
+        <v>20</v>
+      </c>
+      <c r="O47" s="110" t="s">
         <v>419</v>
       </c>
-      <c r="P46" s="109">
+      <c r="P47" s="109">
         <v>0.435</v>
       </c>
-      <c r="Q46" s="109">
+      <c r="Q47" s="109">
         <f t="shared" si="34"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="R46" s="79" t="s">
+      <c r="R47" s="79" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1"/>
-      <c r="B47" s="53">
-        <f t="shared" si="35"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="D47" s="103" t="s">
-        <v>33</v>
-      </c>
-      <c r="E47" s="104" t="s">
-        <v>101</v>
-      </c>
-      <c r="F47" s="103" t="s">
-        <v>308</v>
-      </c>
-      <c r="G47" s="104" t="s">
-        <v>162</v>
-      </c>
-      <c r="H47" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="I47" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J47" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K47" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L47" s="103">
-        <v>2</v>
-      </c>
-      <c r="M47" s="96">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N47" s="96">
-        <v>50</v>
-      </c>
-      <c r="O47" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="P47" s="96">
-        <v>1.5</v>
-      </c>
-      <c r="Q47" s="96">
-        <f t="shared" ref="Q47" si="36">N47*P47</f>
-        <v>75</v>
-      </c>
-      <c r="R47" s="96"/>
-    </row>
-    <row r="48" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
         <f t="shared" si="35"/>
         <v>39</v>
       </c>
-      <c r="C48" s="97" t="s">
-        <v>283</v>
-      </c>
-      <c r="D48" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="E48" s="99" t="s">
-        <v>102</v>
-      </c>
-      <c r="F48" s="98" t="s">
-        <v>163</v>
-      </c>
-      <c r="G48" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="H48" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="I48" s="98"/>
-      <c r="J48" s="98"/>
-      <c r="K48" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="L48" s="98">
-        <v>4</v>
-      </c>
-      <c r="M48" s="66">
+      <c r="C48" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="D48" s="103" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G48" s="104" t="s">
+        <v>162</v>
+      </c>
+      <c r="H48" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="I48" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J48" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K48" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L48" s="103">
+        <v>2</v>
+      </c>
+      <c r="M48" s="96">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N48" s="66">
-        <f t="shared" ref="N48" si="37">M48+(M48*0.1)</f>
-        <v>88</v>
-      </c>
-      <c r="O48" s="66"/>
-      <c r="P48" s="66"/>
-      <c r="Q48" s="66">
-        <f t="shared" ref="Q48" si="38">P48*N48</f>
-        <v>0</v>
-      </c>
-      <c r="R48" s="66" t="s">
-        <v>384</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N48" s="96">
+        <v>50</v>
+      </c>
+      <c r="O48" s="105" t="s">
+        <v>379</v>
+      </c>
+      <c r="P48" s="96">
+        <v>1.5</v>
+      </c>
+      <c r="Q48" s="96">
+        <f t="shared" ref="Q48" si="36">N48*P48</f>
+        <v>75</v>
+      </c>
+      <c r="R48" s="96"/>
     </row>
     <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
@@ -5163,54 +5186,49 @@
         <f t="shared" si="35"/>
         <v>40</v>
       </c>
-      <c r="C49" s="102" t="s">
-        <v>321</v>
-      </c>
-      <c r="D49" s="103" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="104" t="s">
-        <v>103</v>
-      </c>
-      <c r="F49" s="103" t="s">
-        <v>164</v>
-      </c>
-      <c r="G49" s="104">
-        <v>61300211121</v>
-      </c>
-      <c r="H49" s="103" t="s">
-        <v>235</v>
-      </c>
-      <c r="I49" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J49" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K49" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L49" s="103">
+      <c r="C49" s="97" t="s">
+        <v>283</v>
+      </c>
+      <c r="D49" s="98" t="s">
+        <v>34</v>
+      </c>
+      <c r="E49" s="99" t="s">
+        <v>102</v>
+      </c>
+      <c r="F49" s="98" t="s">
+        <v>163</v>
+      </c>
+      <c r="G49" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H49" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I49" s="98"/>
+      <c r="J49" s="98"/>
+      <c r="K49" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L49" s="98">
         <v>4</v>
       </c>
-      <c r="M49" s="96">
+      <c r="M49" s="66">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N49" s="96">
-        <v>90</v>
-      </c>
-      <c r="O49" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="P49" s="96">
-        <v>0.13</v>
-      </c>
-      <c r="Q49" s="96">
-        <f t="shared" ref="Q49" si="39">N49*P49</f>
-        <v>11.700000000000001</v>
-      </c>
-      <c r="R49" s="96"/>
+      <c r="N49" s="66">
+        <f t="shared" ref="N49" si="37">M49+(M49*0.1)</f>
+        <v>88</v>
+      </c>
+      <c r="O49" s="66"/>
+      <c r="P49" s="66"/>
+      <c r="Q49" s="66">
+        <f t="shared" ref="Q49" si="38">P49*N49</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="66" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
@@ -5218,54 +5236,54 @@
         <f t="shared" si="35"/>
         <v>41</v>
       </c>
-      <c r="C50" s="106" t="s">
-        <v>323</v>
-      </c>
-      <c r="D50" s="107" t="s">
-        <v>439</v>
-      </c>
-      <c r="E50" s="108" t="s">
-        <v>104</v>
-      </c>
-      <c r="F50" s="107" t="s">
-        <v>165</v>
-      </c>
-      <c r="G50" s="108" t="s">
-        <v>200</v>
-      </c>
-      <c r="H50" s="107" t="s">
-        <v>248</v>
-      </c>
-      <c r="I50" s="107" t="s">
-        <v>385</v>
-      </c>
-      <c r="J50" s="107" t="s">
-        <v>386</v>
-      </c>
-      <c r="K50" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L50" s="107">
+      <c r="C50" s="102" t="s">
+        <v>321</v>
+      </c>
+      <c r="D50" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="F50" s="103" t="s">
+        <v>164</v>
+      </c>
+      <c r="G50" s="104">
+        <v>61300211121</v>
+      </c>
+      <c r="H50" s="103" t="s">
+        <v>235</v>
+      </c>
+      <c r="I50" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J50" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K50" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L50" s="103">
         <v>4</v>
       </c>
-      <c r="M50" s="109">
+      <c r="M50" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N50" s="109">
-        <v>85</v>
-      </c>
-      <c r="O50" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="P50" s="109">
-        <v>0.21740000000000001</v>
-      </c>
-      <c r="Q50" s="109">
-        <f t="shared" ref="Q50" si="40">P50*N50</f>
-        <v>18.478999999999999</v>
-      </c>
-      <c r="R50" s="109"/>
+      <c r="N50" s="96">
+        <v>90</v>
+      </c>
+      <c r="O50" s="105" t="s">
+        <v>379</v>
+      </c>
+      <c r="P50" s="96">
+        <v>0.13</v>
+      </c>
+      <c r="Q50" s="96">
+        <f t="shared" ref="Q50" si="39">N50*P50</f>
+        <v>11.700000000000001</v>
+      </c>
+      <c r="R50" s="96"/>
     </row>
     <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -5273,219 +5291,219 @@
         <f t="shared" si="35"/>
         <v>42</v>
       </c>
-      <c r="C51" s="102" t="s">
-        <v>324</v>
-      </c>
-      <c r="D51" s="103" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51" s="104" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" s="103" t="s">
-        <v>166</v>
-      </c>
-      <c r="G51" s="104" t="s">
-        <v>201</v>
-      </c>
-      <c r="H51" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I51" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J51" s="103" t="s">
-        <v>387</v>
-      </c>
-      <c r="K51" s="104" t="s">
-        <v>284</v>
-      </c>
-      <c r="L51" s="103">
-        <v>2</v>
-      </c>
-      <c r="M51" s="96">
+      <c r="C51" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="D51" s="107" t="s">
+        <v>439</v>
+      </c>
+      <c r="E51" s="108" t="s">
+        <v>104</v>
+      </c>
+      <c r="F51" s="107" t="s">
+        <v>165</v>
+      </c>
+      <c r="G51" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="H51" s="107" t="s">
+        <v>248</v>
+      </c>
+      <c r="I51" s="107" t="s">
+        <v>385</v>
+      </c>
+      <c r="J51" s="107" t="s">
+        <v>386</v>
+      </c>
+      <c r="K51" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L51" s="107">
+        <v>4</v>
+      </c>
+      <c r="M51" s="109">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N51" s="96">
-        <v>100</v>
-      </c>
-      <c r="O51" s="105" t="s">
+        <v>80</v>
+      </c>
+      <c r="N51" s="109">
+        <v>85</v>
+      </c>
+      <c r="O51" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P51" s="96">
-        <v>1E-3</v>
-      </c>
-      <c r="Q51" s="96">
-        <f t="shared" ref="Q51" si="41">N51*P51</f>
-        <v>0.1</v>
-      </c>
-      <c r="R51" s="96"/>
-    </row>
-    <row r="52" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P51" s="109">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q51" s="109">
+        <f t="shared" ref="Q51" si="40">P51*N51</f>
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R51" s="109"/>
+    </row>
+    <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <f t="shared" si="35"/>
         <v>43</v>
       </c>
-      <c r="C52" s="106" t="s">
+      <c r="C52" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D52" s="107" t="s">
-        <v>37</v>
-      </c>
-      <c r="E52" s="108" t="s">
-        <v>106</v>
-      </c>
-      <c r="F52" s="107" t="s">
+      <c r="D52" s="103" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="104" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="108" t="s">
-        <v>202</v>
-      </c>
-      <c r="H52" s="107" t="s">
+      <c r="G52" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="H52" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I52" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J52" s="107" t="s">
-        <v>388</v>
-      </c>
-      <c r="K52" s="108" t="s">
-        <v>285</v>
-      </c>
-      <c r="L52" s="107">
-        <v>1</v>
-      </c>
-      <c r="M52" s="109">
+      <c r="I52" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J52" s="103" t="s">
+        <v>387</v>
+      </c>
+      <c r="K52" s="104" t="s">
+        <v>284</v>
+      </c>
+      <c r="L52" s="103">
+        <v>2</v>
+      </c>
+      <c r="M52" s="96">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N52" s="109">
+        <v>40</v>
+      </c>
+      <c r="N52" s="96">
         <v>100</v>
       </c>
-      <c r="O52" s="110" t="s">
+      <c r="O52" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P52" s="109">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q52" s="109">
-        <f t="shared" ref="Q52" si="42">P52*N52</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R52" s="109"/>
-    </row>
-    <row r="53" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P52" s="96">
+        <v>1E-3</v>
+      </c>
+      <c r="Q52" s="96">
+        <f t="shared" ref="Q52" si="41">N52*P52</f>
+        <v>0.1</v>
+      </c>
+      <c r="R52" s="96"/>
+    </row>
+    <row r="53" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
         <f t="shared" si="35"/>
         <v>44</v>
       </c>
-      <c r="C53" s="102" t="s">
+      <c r="C53" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D53" s="103" t="s">
-        <v>38</v>
-      </c>
-      <c r="E53" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="F53" s="103" t="s">
+      <c r="D53" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" s="108" t="s">
+        <v>106</v>
+      </c>
+      <c r="F53" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="104" t="s">
-        <v>203</v>
-      </c>
-      <c r="H53" s="103" t="s">
-        <v>249</v>
-      </c>
-      <c r="I53" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J53" s="103" t="s">
-        <v>389</v>
-      </c>
-      <c r="K53" s="104" t="s">
-        <v>286</v>
-      </c>
-      <c r="L53" s="103">
+      <c r="G53" s="108" t="s">
+        <v>202</v>
+      </c>
+      <c r="H53" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="I53" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J53" s="107" t="s">
+        <v>388</v>
+      </c>
+      <c r="K53" s="108" t="s">
+        <v>285</v>
+      </c>
+      <c r="L53" s="107">
         <v>1</v>
       </c>
-      <c r="M53" s="96">
+      <c r="M53" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N53" s="96">
+      <c r="N53" s="109">
         <v>100</v>
       </c>
-      <c r="O53" s="105" t="s">
+      <c r="O53" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P53" s="96">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="Q53" s="96">
-        <f t="shared" ref="Q53" si="43">N53*P53</f>
-        <v>0.16</v>
-      </c>
-      <c r="R53" s="96"/>
-    </row>
-    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P53" s="109">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q53" s="109">
+        <f t="shared" ref="Q53" si="42">P53*N53</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R53" s="109"/>
+    </row>
+    <row r="54" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <f t="shared" si="35"/>
         <v>45</v>
       </c>
-      <c r="C54" s="106" t="s">
+      <c r="C54" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D54" s="107" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="108" t="s">
-        <v>108</v>
-      </c>
-      <c r="F54" s="107" t="s">
+      <c r="D54" s="103" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="104" t="s">
+        <v>107</v>
+      </c>
+      <c r="F54" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="108" t="s">
-        <v>204</v>
-      </c>
-      <c r="H54" s="107" t="s">
-        <v>229</v>
-      </c>
-      <c r="I54" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J54" s="107" t="s">
-        <v>390</v>
-      </c>
-      <c r="K54" s="108" t="s">
-        <v>287</v>
-      </c>
-      <c r="L54" s="107">
-        <v>2</v>
-      </c>
-      <c r="M54" s="109">
+      <c r="G54" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="H54" s="103" t="s">
+        <v>249</v>
+      </c>
+      <c r="I54" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J54" s="103" t="s">
+        <v>389</v>
+      </c>
+      <c r="K54" s="104" t="s">
+        <v>286</v>
+      </c>
+      <c r="L54" s="103">
+        <v>1</v>
+      </c>
+      <c r="M54" s="96">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N54" s="109">
+        <v>20</v>
+      </c>
+      <c r="N54" s="96">
         <v>100</v>
       </c>
-      <c r="O54" s="110" t="s">
+      <c r="O54" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P54" s="109">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q54" s="109">
-        <f t="shared" ref="Q54" si="44">P54*N54</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R54" s="109"/>
+      <c r="P54" s="96">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q54" s="96">
+        <f t="shared" ref="Q54" si="43">N54*P54</f>
+        <v>0.16</v>
+      </c>
+      <c r="R54" s="96"/>
     </row>
     <row r="55" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
@@ -5493,164 +5511,164 @@
         <f t="shared" si="35"/>
         <v>46</v>
       </c>
-      <c r="C55" s="102" t="s">
+      <c r="C55" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D55" s="103" t="s">
+      <c r="D55" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="108" t="s">
+        <v>108</v>
+      </c>
+      <c r="F55" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" s="108" t="s">
+        <v>204</v>
+      </c>
+      <c r="H55" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="I55" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J55" s="107" t="s">
+        <v>390</v>
+      </c>
+      <c r="K55" s="108" t="s">
+        <v>287</v>
+      </c>
+      <c r="L55" s="107">
+        <v>2</v>
+      </c>
+      <c r="M55" s="109">
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="E55" s="104" t="s">
-        <v>109</v>
-      </c>
-      <c r="F55" s="103" t="s">
-        <v>166</v>
-      </c>
-      <c r="G55" s="104" t="s">
-        <v>205</v>
-      </c>
-      <c r="H55" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I55" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J55" s="103" t="s">
-        <v>391</v>
-      </c>
-      <c r="K55" s="104" t="s">
-        <v>288</v>
-      </c>
-      <c r="L55" s="103">
-        <v>4</v>
-      </c>
-      <c r="M55" s="96">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N55" s="96">
+      <c r="N55" s="109">
         <v>100</v>
       </c>
-      <c r="O55" s="105" t="s">
+      <c r="O55" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P55" s="96">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q55" s="96">
-        <f t="shared" ref="Q55" si="45">N55*P55</f>
-        <v>0.13</v>
-      </c>
-      <c r="R55" s="96"/>
-    </row>
-    <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P55" s="109">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q55" s="109">
+        <f t="shared" ref="Q55" si="44">P55*N55</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R55" s="109"/>
+    </row>
+    <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
         <f t="shared" si="35"/>
         <v>47</v>
       </c>
-      <c r="C56" s="106" t="s">
+      <c r="C56" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D56" s="107" t="s">
-        <v>41</v>
-      </c>
-      <c r="E56" s="108" t="s">
-        <v>110</v>
-      </c>
-      <c r="F56" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="G56" s="108" t="s">
-        <v>329</v>
-      </c>
-      <c r="H56" s="107" t="s">
-        <v>250</v>
-      </c>
-      <c r="I56" s="107" t="s">
-        <v>392</v>
-      </c>
-      <c r="J56" s="107" t="s">
-        <v>393</v>
-      </c>
-      <c r="K56" s="108" t="s">
-        <v>289</v>
-      </c>
-      <c r="L56" s="107">
+      <c r="D56" s="103" t="s">
+        <v>40</v>
+      </c>
+      <c r="E56" s="104" t="s">
+        <v>109</v>
+      </c>
+      <c r="F56" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G56" s="104" t="s">
+        <v>205</v>
+      </c>
+      <c r="H56" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I56" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J56" s="103" t="s">
+        <v>391</v>
+      </c>
+      <c r="K56" s="104" t="s">
+        <v>288</v>
+      </c>
+      <c r="L56" s="103">
         <v>4</v>
       </c>
-      <c r="M56" s="109">
+      <c r="M56" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N56" s="109">
-        <v>90</v>
-      </c>
-      <c r="O56" s="110" t="s">
+      <c r="N56" s="96">
+        <v>100</v>
+      </c>
+      <c r="O56" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P56" s="109">
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="Q56" s="109">
-        <f t="shared" ref="Q56" si="46">P56*N56</f>
-        <v>5.8049999999999997</v>
-      </c>
-      <c r="R56" s="109"/>
-    </row>
-    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P56" s="96">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q56" s="96">
+        <f t="shared" ref="Q56" si="45">N56*P56</f>
+        <v>0.13</v>
+      </c>
+      <c r="R56" s="96"/>
+    </row>
+    <row r="57" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f t="shared" si="35"/>
         <v>48</v>
       </c>
-      <c r="C57" s="60" t="s">
+      <c r="C57" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D57" s="37" t="s">
-        <v>423</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>440</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="G57" s="37" t="s">
-        <v>425</v>
-      </c>
-      <c r="H57" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="I57" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J57" s="37" t="s">
-        <v>426</v>
-      </c>
-      <c r="K57" s="37" t="s">
-        <v>427</v>
-      </c>
-      <c r="L57" s="37">
-        <v>8</v>
-      </c>
-      <c r="M57" s="37">
+      <c r="D57" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="108" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" s="107" t="s">
+        <v>167</v>
+      </c>
+      <c r="G57" s="108" t="s">
+        <v>329</v>
+      </c>
+      <c r="H57" s="107" t="s">
+        <v>250</v>
+      </c>
+      <c r="I57" s="107" t="s">
+        <v>392</v>
+      </c>
+      <c r="J57" s="107" t="s">
+        <v>393</v>
+      </c>
+      <c r="K57" s="108" t="s">
+        <v>289</v>
+      </c>
+      <c r="L57" s="107">
+        <v>4</v>
+      </c>
+      <c r="M57" s="109">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N57" s="96">
-        <v>100</v>
-      </c>
-      <c r="O57" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="N57" s="109">
+        <v>90</v>
+      </c>
+      <c r="O57" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P57" s="37">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q57" s="37">
-        <f t="shared" ref="Q57" si="47">N57*P57</f>
-        <v>0.11</v>
-      </c>
-      <c r="R57" s="76"/>
+      <c r="P57" s="109">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="Q57" s="109">
+        <f t="shared" ref="Q57" si="46">P57*N57</f>
+        <v>5.8049999999999997</v>
+      </c>
+      <c r="R57" s="109"/>
     </row>
     <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
@@ -5658,54 +5676,54 @@
         <f t="shared" si="35"/>
         <v>49</v>
       </c>
-      <c r="C58" s="106" t="s">
+      <c r="C58" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D58" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="E58" s="108" t="s">
-        <v>112</v>
-      </c>
-      <c r="F58" s="107" t="s">
+      <c r="D58" s="37" t="s">
+        <v>423</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="F58" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="108" t="s">
-        <v>207</v>
-      </c>
-      <c r="H58" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="I58" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J58" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K58" s="108" t="s">
-        <v>291</v>
-      </c>
-      <c r="L58" s="107">
-        <v>1</v>
-      </c>
-      <c r="M58" s="109">
+      <c r="G58" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="H58" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="I58" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J58" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="K58" s="37" t="s">
+        <v>427</v>
+      </c>
+      <c r="L58" s="37">
+        <v>8</v>
+      </c>
+      <c r="M58" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N58" s="109">
-        <v>30</v>
-      </c>
-      <c r="O58" s="110" t="s">
-        <v>382</v>
-      </c>
-      <c r="P58" s="109">
-        <v>1.8589999999999999E-2</v>
-      </c>
-      <c r="Q58" s="109">
-        <f t="shared" ref="Q58" si="48">P58*N58</f>
-        <v>0.55769999999999997</v>
-      </c>
-      <c r="R58" s="109"/>
+        <v>160</v>
+      </c>
+      <c r="N58" s="96">
+        <v>100</v>
+      </c>
+      <c r="O58" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="P58" s="37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q58" s="37">
+        <f t="shared" ref="Q58" si="47">N58*P58</f>
+        <v>0.11</v>
+      </c>
+      <c r="R58" s="76"/>
     </row>
     <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
@@ -5713,54 +5731,54 @@
         <f t="shared" si="35"/>
         <v>50</v>
       </c>
-      <c r="C59" s="102" t="s">
+      <c r="C59" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D59" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="E59" s="104" t="s">
-        <v>113</v>
-      </c>
-      <c r="F59" s="103" t="s">
+      <c r="D59" s="107" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" s="108" t="s">
+        <v>112</v>
+      </c>
+      <c r="F59" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G59" s="104" t="s">
-        <v>208</v>
-      </c>
-      <c r="H59" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I59" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J59" s="103" t="s">
-        <v>395</v>
-      </c>
-      <c r="K59" s="104" t="s">
-        <v>292</v>
-      </c>
-      <c r="L59" s="103">
+      <c r="G59" s="108" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I59" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K59" s="108" t="s">
+        <v>291</v>
+      </c>
+      <c r="L59" s="107">
         <v>1</v>
       </c>
-      <c r="M59" s="96">
+      <c r="M59" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N59" s="96">
-        <v>100</v>
-      </c>
-      <c r="O59" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P59" s="96">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q59" s="96">
-        <f t="shared" ref="Q59" si="49">N59*P59</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R59" s="96"/>
+      <c r="N59" s="109">
+        <v>30</v>
+      </c>
+      <c r="O59" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P59" s="109">
+        <v>1.8589999999999999E-2</v>
+      </c>
+      <c r="Q59" s="109">
+        <f t="shared" ref="Q59" si="48">P59*N59</f>
+        <v>0.55769999999999997</v>
+      </c>
+      <c r="R59" s="109"/>
     </row>
     <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
@@ -5768,54 +5786,54 @@
         <f t="shared" si="35"/>
         <v>51</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D60" s="107" t="s">
-        <v>44</v>
-      </c>
-      <c r="E60" s="108" t="s">
-        <v>114</v>
-      </c>
-      <c r="F60" s="107" t="s">
+      <c r="D60" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="F60" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G60" s="108" t="s">
-        <v>209</v>
-      </c>
-      <c r="H60" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="I60" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J60" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K60" s="108" t="s">
-        <v>293</v>
-      </c>
-      <c r="L60" s="107">
+      <c r="G60" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="H60" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I60" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J60" s="103" t="s">
+        <v>395</v>
+      </c>
+      <c r="K60" s="104" t="s">
+        <v>292</v>
+      </c>
+      <c r="L60" s="103">
         <v>1</v>
       </c>
-      <c r="M60" s="109">
+      <c r="M60" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="109">
-        <v>50</v>
-      </c>
-      <c r="O60" s="110" t="s">
-        <v>382</v>
-      </c>
-      <c r="P60" s="109">
-        <v>4.6699999999999997E-3</v>
-      </c>
-      <c r="Q60" s="109">
-        <f t="shared" ref="Q60" si="50">P60*N60</f>
-        <v>0.23349999999999999</v>
-      </c>
-      <c r="R60" s="109"/>
+      <c r="N60" s="96">
+        <v>100</v>
+      </c>
+      <c r="O60" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P60" s="96">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q60" s="96">
+        <f t="shared" ref="Q60" si="49">N60*P60</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R60" s="96"/>
     </row>
     <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
@@ -5823,54 +5841,54 @@
         <f t="shared" si="35"/>
         <v>52</v>
       </c>
-      <c r="C61" s="102" t="s">
+      <c r="C61" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D61" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="F61" s="103" t="s">
+      <c r="D61" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" s="108" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G61" s="104" t="s">
-        <v>210</v>
-      </c>
-      <c r="H61" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I61" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J61" s="103" t="s">
-        <v>396</v>
-      </c>
-      <c r="K61" s="104" t="s">
-        <v>294</v>
-      </c>
-      <c r="L61" s="103">
+      <c r="G61" s="108" t="s">
+        <v>209</v>
+      </c>
+      <c r="H61" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I61" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J61" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K61" s="108" t="s">
+        <v>293</v>
+      </c>
+      <c r="L61" s="107">
         <v>1</v>
       </c>
-      <c r="M61" s="96">
+      <c r="M61" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="96">
-        <v>100</v>
-      </c>
-      <c r="O61" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P61" s="96">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q61" s="96">
-        <f t="shared" ref="Q61" si="51">N61*P61</f>
-        <v>0.12</v>
-      </c>
-      <c r="R61" s="96"/>
+      <c r="N61" s="109">
+        <v>50</v>
+      </c>
+      <c r="O61" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P61" s="109">
+        <v>4.6699999999999997E-3</v>
+      </c>
+      <c r="Q61" s="109">
+        <f t="shared" ref="Q61" si="50">P61*N61</f>
+        <v>0.23349999999999999</v>
+      </c>
+      <c r="R61" s="109"/>
     </row>
     <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
@@ -5878,54 +5896,54 @@
         <f t="shared" si="35"/>
         <v>53</v>
       </c>
-      <c r="C62" s="106" t="s">
+      <c r="C62" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D62" s="107" t="s">
-        <v>46</v>
-      </c>
-      <c r="E62" s="108" t="s">
-        <v>116</v>
-      </c>
-      <c r="F62" s="107" t="s">
+      <c r="D62" s="103" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="F62" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G62" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="H62" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="I62" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K62" s="108" t="s">
-        <v>295</v>
-      </c>
-      <c r="L62" s="107">
+      <c r="G62" s="104" t="s">
+        <v>210</v>
+      </c>
+      <c r="H62" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I62" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="103" t="s">
+        <v>396</v>
+      </c>
+      <c r="K62" s="104" t="s">
+        <v>294</v>
+      </c>
+      <c r="L62" s="103">
         <v>1</v>
       </c>
-      <c r="M62" s="109">
+      <c r="M62" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N62" s="109">
-        <v>50</v>
-      </c>
-      <c r="O62" s="110" t="s">
-        <v>382</v>
-      </c>
-      <c r="P62" s="109">
-        <v>1.11E-2</v>
-      </c>
-      <c r="Q62" s="109">
-        <f t="shared" ref="Q62" si="52">P62*N62</f>
-        <v>0.55500000000000005</v>
-      </c>
-      <c r="R62" s="109"/>
+      <c r="N62" s="96">
+        <v>100</v>
+      </c>
+      <c r="O62" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P62" s="96">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q62" s="96">
+        <f t="shared" ref="Q62" si="51">N62*P62</f>
+        <v>0.12</v>
+      </c>
+      <c r="R62" s="96"/>
     </row>
     <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
@@ -5933,54 +5951,54 @@
         <f t="shared" si="35"/>
         <v>54</v>
       </c>
-      <c r="C63" s="102" t="s">
+      <c r="C63" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D63" s="103" t="s">
-        <v>47</v>
-      </c>
-      <c r="E63" s="104" t="s">
-        <v>117</v>
-      </c>
-      <c r="F63" s="103" t="s">
+      <c r="D63" s="107" t="s">
+        <v>46</v>
+      </c>
+      <c r="E63" s="108" t="s">
+        <v>116</v>
+      </c>
+      <c r="F63" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G63" s="104" t="s">
-        <v>212</v>
-      </c>
-      <c r="H63" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="I63" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J63" s="103" t="s">
-        <v>397</v>
-      </c>
-      <c r="K63" s="104" t="s">
-        <v>296</v>
-      </c>
-      <c r="L63" s="103">
+      <c r="G63" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="H63" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I63" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K63" s="108" t="s">
+        <v>295</v>
+      </c>
+      <c r="L63" s="107">
         <v>1</v>
       </c>
-      <c r="M63" s="96">
+      <c r="M63" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N63" s="96">
-        <v>100</v>
-      </c>
-      <c r="O63" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P63" s="96">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q63" s="96">
-        <f t="shared" ref="Q63" si="53">N63*P63</f>
-        <v>0.21</v>
-      </c>
-      <c r="R63" s="96"/>
+      <c r="N63" s="109">
+        <v>50</v>
+      </c>
+      <c r="O63" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P63" s="109">
+        <v>1.11E-2</v>
+      </c>
+      <c r="Q63" s="109">
+        <f t="shared" ref="Q63" si="52">P63*N63</f>
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="R63" s="109"/>
     </row>
     <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
@@ -5988,54 +6006,54 @@
         <f t="shared" si="35"/>
         <v>55</v>
       </c>
-      <c r="C64" s="106" t="s">
+      <c r="C64" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D64" s="107" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" s="108" t="s">
-        <v>118</v>
-      </c>
-      <c r="F64" s="107" t="s">
+      <c r="D64" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="F64" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G64" s="108" t="s">
-        <v>213</v>
-      </c>
-      <c r="H64" s="107" t="s">
+      <c r="G64" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="H64" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I64" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J64" s="107" t="s">
-        <v>398</v>
-      </c>
-      <c r="K64" s="108" t="s">
-        <v>297</v>
-      </c>
-      <c r="L64" s="107">
+      <c r="I64" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J64" s="103" t="s">
+        <v>397</v>
+      </c>
+      <c r="K64" s="104" t="s">
+        <v>296</v>
+      </c>
+      <c r="L64" s="103">
         <v>1</v>
       </c>
-      <c r="M64" s="109">
+      <c r="M64" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N64" s="109">
+      <c r="N64" s="96">
         <v>100</v>
       </c>
-      <c r="O64" s="110" t="s">
+      <c r="O64" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P64" s="109">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="Q64" s="109">
-        <f t="shared" ref="Q64" si="54">P64*N64</f>
-        <v>0.16</v>
-      </c>
-      <c r="R64" s="109"/>
+      <c r="P64" s="96">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="Q64" s="96">
+        <f t="shared" ref="Q64" si="53">N64*P64</f>
+        <v>0.21</v>
+      </c>
+      <c r="R64" s="96"/>
     </row>
     <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
@@ -6043,164 +6061,164 @@
         <f t="shared" si="35"/>
         <v>56</v>
       </c>
-      <c r="C65" s="102" t="s">
+      <c r="C65" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D65" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="E65" s="104" t="s">
-        <v>119</v>
-      </c>
-      <c r="F65" s="103" t="s">
+      <c r="D65" s="107" t="s">
+        <v>48</v>
+      </c>
+      <c r="E65" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="F65" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G65" s="104" t="s">
-        <v>214</v>
-      </c>
-      <c r="H65" s="103" t="s">
+      <c r="G65" s="108" t="s">
+        <v>213</v>
+      </c>
+      <c r="H65" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I65" s="103" t="s">
-        <v>399</v>
-      </c>
-      <c r="J65" s="103" t="s">
-        <v>400</v>
-      </c>
-      <c r="K65" s="104" t="s">
-        <v>298</v>
-      </c>
-      <c r="L65" s="103">
+      <c r="I65" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J65" s="107" t="s">
+        <v>398</v>
+      </c>
+      <c r="K65" s="108" t="s">
+        <v>297</v>
+      </c>
+      <c r="L65" s="107">
         <v>1</v>
       </c>
-      <c r="M65" s="96">
+      <c r="M65" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N65" s="96">
-        <v>50</v>
-      </c>
-      <c r="O65" s="105" t="s">
+      <c r="N65" s="109">
+        <v>100</v>
+      </c>
+      <c r="O65" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P65" s="96">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="Q65" s="96">
-        <f t="shared" ref="Q65" si="55">N65*P65</f>
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="R65" s="96"/>
-    </row>
-    <row r="66" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P65" s="109">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q65" s="109">
+        <f t="shared" ref="Q65" si="54">P65*N65</f>
+        <v>0.16</v>
+      </c>
+      <c r="R65" s="109"/>
+    </row>
+    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
         <f t="shared" si="35"/>
         <v>57</v>
       </c>
-      <c r="C66" s="106" t="s">
+      <c r="C66" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="D66" s="107" t="s">
-        <v>462</v>
-      </c>
-      <c r="E66" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="F66" s="107" t="s">
+      <c r="D66" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="E66" s="104" t="s">
+        <v>119</v>
+      </c>
+      <c r="F66" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G66" s="108" t="s">
-        <v>215</v>
-      </c>
-      <c r="H66" s="107" t="s">
+      <c r="G66" s="104" t="s">
+        <v>214</v>
+      </c>
+      <c r="H66" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I66" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J66" s="107" t="s">
-        <v>401</v>
-      </c>
-      <c r="K66" s="108" t="s">
-        <v>299</v>
-      </c>
-      <c r="L66" s="107">
-        <v>2</v>
-      </c>
-      <c r="M66" s="109">
+      <c r="I66" s="103" t="s">
+        <v>399</v>
+      </c>
+      <c r="J66" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="K66" s="104" t="s">
+        <v>298</v>
+      </c>
+      <c r="L66" s="103">
+        <v>1</v>
+      </c>
+      <c r="M66" s="96">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N66" s="109">
-        <v>100</v>
-      </c>
-      <c r="O66" s="110" t="s">
+        <v>20</v>
+      </c>
+      <c r="N66" s="96">
+        <v>50</v>
+      </c>
+      <c r="O66" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P66" s="109">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q66" s="109">
-        <f t="shared" ref="Q66" si="56">P66*N66</f>
-        <v>0.11</v>
-      </c>
-      <c r="R66" s="109"/>
-    </row>
-    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P66" s="96">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="Q66" s="96">
+        <f t="shared" ref="Q66" si="55">N66*P66</f>
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="R66" s="96"/>
+    </row>
+    <row r="67" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
         <f t="shared" si="35"/>
         <v>58</v>
       </c>
-      <c r="C67" s="60" t="s">
+      <c r="C67" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D67" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="F67" s="37" t="s">
+      <c r="D67" s="107" t="s">
+        <v>462</v>
+      </c>
+      <c r="E67" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="F67" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G67" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="H67" s="37" t="s">
+      <c r="G67" s="108" t="s">
+        <v>215</v>
+      </c>
+      <c r="H67" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I67" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J67" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="K67" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="L67" s="37">
+      <c r="I67" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J67" s="107" t="s">
+        <v>401</v>
+      </c>
+      <c r="K67" s="108" t="s">
+        <v>299</v>
+      </c>
+      <c r="L67" s="107">
         <v>2</v>
       </c>
-      <c r="M67" s="41">
+      <c r="M67" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N67" s="41">
+      <c r="N67" s="109">
         <v>100</v>
       </c>
-      <c r="O67" s="63" t="s">
+      <c r="O67" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P67" s="41">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q67" s="41">
-        <f t="shared" ref="Q67" si="57">P67*N67</f>
-        <v>0.15</v>
-      </c>
-      <c r="R67" s="41"/>
+      <c r="P67" s="109">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q67" s="109">
+        <f t="shared" ref="Q67" si="56">P67*N67</f>
+        <v>0.11</v>
+      </c>
+      <c r="R67" s="109"/>
     </row>
     <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -6208,52 +6226,54 @@
         <f t="shared" si="35"/>
         <v>59</v>
       </c>
-      <c r="C68" s="59" t="s">
+      <c r="C68" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D68" s="87" t="s">
-        <v>424</v>
-      </c>
-      <c r="E68" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="F68" s="39" t="s">
+      <c r="D68" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E68" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="F68" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G68" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="H68" s="39" t="s">
+      <c r="G68" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H68" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="K68" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="L68" s="39">
-        <v>1</v>
-      </c>
-      <c r="M68" s="42">
-        <f>L68*20</f>
-        <v>20</v>
-      </c>
-      <c r="N68" s="42">
+      <c r="I68" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J68" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="L68" s="37">
+        <v>2</v>
+      </c>
+      <c r="M68" s="41">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N68" s="41">
         <v>100</v>
       </c>
-      <c r="O68" s="64" t="s">
+      <c r="O68" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="P68" s="42">
+      <c r="P68" s="41">
         <v>1.5E-3</v>
       </c>
-      <c r="Q68" s="42">
-        <f>N68*P68</f>
+      <c r="Q68" s="41">
+        <f t="shared" ref="Q68" si="57">P68*N68</f>
         <v>0.15</v>
       </c>
-      <c r="R68" s="77"/>
+      <c r="R68" s="41"/>
     </row>
     <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -6261,54 +6281,52 @@
         <f t="shared" si="35"/>
         <v>60</v>
       </c>
-      <c r="C69" s="60" t="s">
+      <c r="C69" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D69" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="F69" s="37" t="s">
+      <c r="D69" s="87" t="s">
+        <v>424</v>
+      </c>
+      <c r="E69" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="F69" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="G69" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="H69" s="37" t="s">
+      <c r="G69" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="H69" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="I69" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J69" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="K69" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="L69" s="37">
-        <v>2</v>
-      </c>
-      <c r="M69" s="41">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N69" s="41">
+      <c r="I69" s="39"/>
+      <c r="J69" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="L69" s="39">
+        <v>1</v>
+      </c>
+      <c r="M69" s="42">
+        <f>L69*20</f>
+        <v>20</v>
+      </c>
+      <c r="N69" s="42">
         <v>100</v>
       </c>
-      <c r="O69" s="63" t="s">
+      <c r="O69" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="P69" s="41">
+      <c r="P69" s="42">
         <v>1.5E-3</v>
       </c>
-      <c r="Q69" s="41">
-        <f t="shared" ref="Q69" si="58">P69*N69</f>
+      <c r="Q69" s="42">
+        <f>N69*P69</f>
         <v>0.15</v>
       </c>
-      <c r="R69" s="41"/>
+      <c r="R69" s="77"/>
     </row>
     <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
@@ -6316,54 +6334,54 @@
         <f t="shared" si="35"/>
         <v>61</v>
       </c>
-      <c r="C70" s="59" t="s">
+      <c r="C70" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D70" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E70" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="F70" s="39" t="s">
+      <c r="D70" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="F70" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G70" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="H70" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="I70" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J70" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K70" s="40" t="s">
-        <v>302</v>
-      </c>
-      <c r="L70" s="39">
-        <v>1</v>
-      </c>
-      <c r="M70" s="42">
+      <c r="G70" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="I70" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J70" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="K70" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="L70" s="37">
+        <v>2</v>
+      </c>
+      <c r="M70" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N70" s="42">
-        <v>25</v>
-      </c>
-      <c r="O70" s="64" t="s">
-        <v>404</v>
-      </c>
-      <c r="P70" s="42">
-        <v>8.5400000000000004E-2</v>
-      </c>
-      <c r="Q70" s="42">
-        <f t="shared" ref="Q70" si="59">N70*P70</f>
-        <v>2.1350000000000002</v>
-      </c>
-      <c r="R70" s="42"/>
+        <v>40</v>
+      </c>
+      <c r="N70" s="41">
+        <v>100</v>
+      </c>
+      <c r="O70" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P70" s="41">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q70" s="41">
+        <f t="shared" ref="Q70" si="58">P70*N70</f>
+        <v>0.15</v>
+      </c>
+      <c r="R70" s="41"/>
     </row>
     <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
@@ -6371,54 +6389,54 @@
         <f t="shared" si="35"/>
         <v>62</v>
       </c>
-      <c r="C71" s="60" t="s">
+      <c r="C71" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D71" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E71" s="38" t="s">
-        <v>434</v>
-      </c>
-      <c r="F71" s="86" t="s">
+      <c r="D71" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F71" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="G71" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="H71" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J71" s="37" t="s">
-        <v>435</v>
-      </c>
-      <c r="K71" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="L71" s="37">
+      <c r="G71" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="H71" s="39" t="s">
+        <v>251</v>
+      </c>
+      <c r="I71" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J71" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K71" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="L71" s="39">
         <v>1</v>
       </c>
-      <c r="M71" s="41">
-        <f t="shared" ref="M71:M89" si="60">L71*20</f>
+      <c r="M71" s="42">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N71" s="41">
-        <v>50</v>
-      </c>
-      <c r="O71" s="63" t="s">
-        <v>343</v>
-      </c>
-      <c r="P71" s="41">
-        <v>3.8E-3</v>
-      </c>
-      <c r="Q71" s="41">
-        <f t="shared" ref="Q71" si="61">P71*N71</f>
-        <v>0.19</v>
-      </c>
-      <c r="R71" s="76"/>
+      <c r="N71" s="42">
+        <v>25</v>
+      </c>
+      <c r="O71" s="64" t="s">
+        <v>404</v>
+      </c>
+      <c r="P71" s="42">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="Q71" s="42">
+        <f t="shared" ref="Q71" si="59">N71*P71</f>
+        <v>2.1350000000000002</v>
+      </c>
+      <c r="R71" s="42"/>
     </row>
     <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
@@ -6426,109 +6444,109 @@
         <f t="shared" si="35"/>
         <v>63</v>
       </c>
-      <c r="C72" s="59" t="s">
+      <c r="C72" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D72" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="E72" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="F72" s="39" t="s">
+      <c r="D72" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E72" s="38" t="s">
+        <v>434</v>
+      </c>
+      <c r="F72" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G72" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="H72" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="I72" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J72" s="39" t="s">
-        <v>408</v>
-      </c>
-      <c r="K72" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="L72" s="39">
-        <v>6</v>
-      </c>
-      <c r="M72" s="42">
-        <f>L72*20</f>
-        <v>120</v>
-      </c>
-      <c r="N72" s="42">
-        <v>200</v>
-      </c>
-      <c r="O72" s="64" t="s">
+      <c r="G72" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="H72" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="I72" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J72" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="L72" s="37">
+        <v>1</v>
+      </c>
+      <c r="M72" s="41">
+        <f t="shared" ref="M72:M90" si="60">L72*20</f>
+        <v>20</v>
+      </c>
+      <c r="N72" s="41">
+        <v>50</v>
+      </c>
+      <c r="O72" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="P72" s="42">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q72" s="42">
-        <f t="shared" ref="Q72" si="62">N72*P72</f>
-        <v>0.24</v>
-      </c>
-      <c r="R72" s="77"/>
-    </row>
-    <row r="73" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P72" s="41">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q72" s="41">
+        <f t="shared" ref="Q72" si="61">P72*N72</f>
+        <v>0.19</v>
+      </c>
+      <c r="R72" s="76"/>
+    </row>
+    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
         <f t="shared" si="35"/>
         <v>64</v>
       </c>
-      <c r="C73" s="60" t="s">
+      <c r="C73" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D73" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="F73" s="37" t="s">
+      <c r="D73" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="E73" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="F73" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="G73" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J73" s="37" t="s">
-        <v>405</v>
-      </c>
-      <c r="K73" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="L73" s="37">
-        <v>1</v>
-      </c>
-      <c r="M73" s="41">
-        <f t="shared" si="60"/>
-        <v>20</v>
-      </c>
-      <c r="N73" s="41">
-        <v>100</v>
-      </c>
-      <c r="O73" s="63" t="s">
+      <c r="G73" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="H73" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="I73" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J73" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="K73" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="L73" s="39">
+        <v>6</v>
+      </c>
+      <c r="M73" s="42">
+        <f>L73*20</f>
+        <v>120</v>
+      </c>
+      <c r="N73" s="42">
+        <v>200</v>
+      </c>
+      <c r="O73" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="P73" s="41">
-        <v>1E-3</v>
-      </c>
-      <c r="Q73" s="41">
-        <f t="shared" ref="Q73" si="63">P73*N73</f>
-        <v>0.1</v>
-      </c>
-      <c r="R73" s="41"/>
+      <c r="P73" s="42">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q73" s="42">
+        <f t="shared" ref="Q73" si="62">N73*P73</f>
+        <v>0.24</v>
+      </c>
+      <c r="R73" s="77"/>
     </row>
     <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -6536,327 +6554,327 @@
         <f t="shared" si="35"/>
         <v>65</v>
       </c>
-      <c r="C74" s="59" t="s">
+      <c r="C74" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D74" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="E74" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="F74" s="39" t="s">
+      <c r="D74" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F74" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G74" s="40" t="s">
-        <v>331</v>
-      </c>
-      <c r="H74" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="I74" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J74" s="39" t="s">
-        <v>406</v>
-      </c>
-      <c r="K74" s="40" t="s">
-        <v>304</v>
-      </c>
-      <c r="L74" s="39">
+      <c r="G74" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="H74" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="I74" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J74" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="L74" s="37">
         <v>1</v>
       </c>
-      <c r="M74" s="42">
+      <c r="M74" s="41">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N74" s="42">
-        <v>50</v>
-      </c>
-      <c r="O74" s="64" t="s">
+      <c r="N74" s="41">
+        <v>100</v>
+      </c>
+      <c r="O74" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="P74" s="42">
-        <v>4.3E-3</v>
-      </c>
-      <c r="Q74" s="42">
-        <f t="shared" ref="Q74" si="64">N74*P74</f>
-        <v>0.215</v>
-      </c>
-      <c r="R74" s="42"/>
-    </row>
-    <row r="75" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P74" s="41">
+        <v>1E-3</v>
+      </c>
+      <c r="Q74" s="41">
+        <f t="shared" ref="Q74" si="63">P74*N74</f>
+        <v>0.1</v>
+      </c>
+      <c r="R74" s="41"/>
+    </row>
+    <row r="75" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
         <f t="shared" si="35"/>
         <v>66</v>
       </c>
-      <c r="C75" s="97" t="s">
+      <c r="C75" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D75" s="98" t="s">
-        <v>56</v>
-      </c>
-      <c r="E75" s="99" t="s">
-        <v>126</v>
-      </c>
-      <c r="F75" s="98" t="s">
-        <v>168</v>
-      </c>
-      <c r="G75" s="99" t="s">
-        <v>219</v>
-      </c>
-      <c r="H75" s="98" t="s">
-        <v>229</v>
-      </c>
-      <c r="I75" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="J75" s="98" t="s">
-        <v>407</v>
-      </c>
-      <c r="K75" s="99" t="s">
-        <v>305</v>
-      </c>
-      <c r="L75" s="98">
-        <v>4</v>
-      </c>
-      <c r="M75" s="66">
+      <c r="D75" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E75" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="F75" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G75" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="H75" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="I75" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J75" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="K75" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="L75" s="39">
+        <v>1</v>
+      </c>
+      <c r="M75" s="42">
         <f t="shared" si="60"/>
-        <v>80</v>
-      </c>
-      <c r="N75" s="66">
-        <v>100</v>
-      </c>
-      <c r="O75" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="N75" s="42">
+        <v>50</v>
+      </c>
+      <c r="O75" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="P75" s="66">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q75" s="66">
-        <f t="shared" ref="Q75" si="65">P75*N75</f>
-        <v>0.12</v>
-      </c>
-      <c r="R75" s="66" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P75" s="42">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q75" s="42">
+        <f t="shared" ref="Q75" si="64">N75*P75</f>
+        <v>0.215</v>
+      </c>
+      <c r="R75" s="42"/>
+    </row>
+    <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
         <f t="shared" si="35"/>
         <v>67</v>
       </c>
       <c r="C76" s="97" t="s">
-        <v>169</v>
+        <v>324</v>
       </c>
       <c r="D76" s="98" t="s">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="E76" s="99" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F76" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G76" s="99" t="s">
-        <v>314</v>
+        <v>219</v>
       </c>
       <c r="H76" s="98" t="s">
-        <v>314</v>
+        <v>229</v>
       </c>
       <c r="I76" s="98" t="s">
         <v>314</v>
       </c>
       <c r="J76" s="98" t="s">
-        <v>314</v>
+        <v>407</v>
       </c>
       <c r="K76" s="99" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L76" s="98">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M76" s="66">
         <f t="shared" si="60"/>
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="N76" s="66">
-        <f t="shared" ref="N76:N77" si="66">M76+(M76*0.1)</f>
-        <v>330</v>
-      </c>
-      <c r="O76" s="66"/>
-      <c r="P76" s="66"/>
+        <v>100</v>
+      </c>
+      <c r="O76" s="100" t="s">
+        <v>343</v>
+      </c>
+      <c r="P76" s="66">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q76" s="66">
-        <f t="shared" ref="Q76" si="67">P76*N76</f>
-        <v>0</v>
+        <f t="shared" ref="Q76" si="65">P76*N76</f>
+        <v>0.12</v>
       </c>
       <c r="R76" s="66" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
         <f t="shared" si="35"/>
         <v>68</v>
       </c>
-      <c r="C77" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="D77" s="103" t="s">
-        <v>57</v>
-      </c>
-      <c r="E77" s="104" t="s">
-        <v>129</v>
-      </c>
-      <c r="F77" s="103" t="s">
-        <v>170</v>
-      </c>
-      <c r="G77" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="H77" s="103" t="s">
-        <v>254</v>
-      </c>
-      <c r="I77" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J77" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K77" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L77" s="103">
-        <v>1</v>
-      </c>
-      <c r="M77" s="96">
+      <c r="C77" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="D77" s="98" t="s">
+        <v>453</v>
+      </c>
+      <c r="E77" s="99" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" s="98" t="s">
+        <v>169</v>
+      </c>
+      <c r="G77" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L77" s="98">
+        <v>15</v>
+      </c>
+      <c r="M77" s="66">
         <f t="shared" si="60"/>
-        <v>20</v>
-      </c>
-      <c r="N77" s="96">
-        <f t="shared" si="66"/>
-        <v>22</v>
-      </c>
-      <c r="O77" s="96"/>
-      <c r="P77" s="96"/>
-      <c r="Q77" s="96">
-        <f t="shared" ref="Q77" si="68">N77*P77</f>
+        <v>300</v>
+      </c>
+      <c r="N77" s="66">
+        <f t="shared" ref="N77:N78" si="66">M77+(M77*0.1)</f>
+        <v>330</v>
+      </c>
+      <c r="O77" s="66"/>
+      <c r="P77" s="66"/>
+      <c r="Q77" s="66">
+        <f t="shared" ref="Q77" si="67">P77*N77</f>
         <v>0</v>
       </c>
-      <c r="R77" s="96"/>
-    </row>
-    <row r="78" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R77" s="66" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
         <f t="shared" si="35"/>
         <v>69</v>
       </c>
-      <c r="C78" s="106" t="s">
-        <v>327</v>
-      </c>
-      <c r="D78" s="107" t="s">
-        <v>58</v>
-      </c>
-      <c r="E78" s="108" t="s">
-        <v>130</v>
-      </c>
-      <c r="F78" s="107" t="s">
-        <v>308</v>
-      </c>
-      <c r="G78" s="108">
-        <v>750314597</v>
-      </c>
-      <c r="H78" s="107" t="s">
-        <v>255</v>
-      </c>
-      <c r="I78" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J78" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K78" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L78" s="107">
+      <c r="C78" s="102" t="s">
+        <v>326</v>
+      </c>
+      <c r="D78" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="E78" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="F78" s="103" t="s">
+        <v>170</v>
+      </c>
+      <c r="G78" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="H78" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="I78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L78" s="103">
         <v>1</v>
       </c>
-      <c r="M78" s="109">
+      <c r="M78" s="96">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N78" s="109">
-        <v>21</v>
-      </c>
-      <c r="O78" s="110" t="s">
-        <v>379</v>
-      </c>
-      <c r="P78" s="109">
-        <v>3.81</v>
-      </c>
-      <c r="Q78" s="109">
-        <f t="shared" ref="Q78" si="69">P78*N78</f>
-        <v>80.010000000000005</v>
-      </c>
-      <c r="R78" s="109"/>
-    </row>
-    <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N78" s="96">
+        <f t="shared" si="66"/>
+        <v>22</v>
+      </c>
+      <c r="O78" s="96"/>
+      <c r="P78" s="96"/>
+      <c r="Q78" s="96">
+        <f t="shared" ref="Q78" si="68">N78*P78</f>
+        <v>0</v>
+      </c>
+      <c r="R78" s="96"/>
+    </row>
+    <row r="79" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
         <f t="shared" si="35"/>
         <v>70</v>
       </c>
-      <c r="C79" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="D79" s="103" t="s">
-        <v>59</v>
-      </c>
-      <c r="E79" s="104" t="s">
-        <v>131</v>
-      </c>
-      <c r="F79" s="103" t="s">
+      <c r="C79" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="D79" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" s="108" t="s">
+        <v>130</v>
+      </c>
+      <c r="F79" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G79" s="104" t="s">
-        <v>171</v>
-      </c>
-      <c r="H79" s="103" t="s">
-        <v>256</v>
-      </c>
-      <c r="I79" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J79" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K79" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L79" s="103">
+      <c r="G79" s="108">
+        <v>750314597</v>
+      </c>
+      <c r="H79" s="107" t="s">
+        <v>255</v>
+      </c>
+      <c r="I79" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J79" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K79" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L79" s="107">
         <v>1</v>
       </c>
-      <c r="M79" s="96">
+      <c r="M79" s="109">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N79" s="96">
+      <c r="N79" s="109">
         <v>21</v>
       </c>
-      <c r="O79" s="105" t="s">
-        <v>409</v>
-      </c>
-      <c r="P79" s="96">
-        <v>2.48</v>
-      </c>
-      <c r="Q79" s="96">
-        <f t="shared" ref="Q79" si="70">N79*P79</f>
-        <v>52.08</v>
-      </c>
-      <c r="R79" s="96"/>
+      <c r="O79" s="110" t="s">
+        <v>379</v>
+      </c>
+      <c r="P79" s="109">
+        <v>3.81</v>
+      </c>
+      <c r="Q79" s="109">
+        <f t="shared" ref="Q79" si="69">P79*N79</f>
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R79" s="109"/>
     </row>
     <row r="80" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
@@ -6864,528 +6882,531 @@
         <f t="shared" si="35"/>
         <v>71</v>
       </c>
-      <c r="C80" s="106" t="s">
+      <c r="C80" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D80" s="107" t="s">
-        <v>60</v>
-      </c>
-      <c r="E80" s="108" t="s">
-        <v>132</v>
-      </c>
-      <c r="F80" s="107" t="s">
-        <v>172</v>
-      </c>
-      <c r="G80" s="108" t="s">
-        <v>221</v>
-      </c>
-      <c r="H80" s="107" t="s">
-        <v>257</v>
-      </c>
-      <c r="I80" s="107" t="s">
-        <v>410</v>
-      </c>
-      <c r="J80" s="107" t="s">
-        <v>411</v>
-      </c>
-      <c r="K80" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L80" s="107">
+      <c r="D80" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="E80" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="F80" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G80" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H80" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I80" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J80" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K80" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L80" s="103">
         <v>1</v>
       </c>
-      <c r="M80" s="109">
+      <c r="M80" s="96">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N80" s="109">
+      <c r="N80" s="96">
         <v>21</v>
       </c>
-      <c r="O80" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="P80" s="109">
-        <v>1.3939999999999999</v>
-      </c>
-      <c r="Q80" s="109">
-        <f t="shared" ref="Q80" si="71">P80*N80</f>
-        <v>29.273999999999997</v>
-      </c>
-      <c r="R80" s="79"/>
-    </row>
-    <row r="81" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O80" s="105" t="s">
+        <v>409</v>
+      </c>
+      <c r="P80" s="96">
+        <v>2.48</v>
+      </c>
+      <c r="Q80" s="96">
+        <f t="shared" ref="Q80" si="70">N80*P80</f>
+        <v>52.08</v>
+      </c>
+      <c r="R80" s="96"/>
+    </row>
+    <row r="81" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
         <f t="shared" si="35"/>
         <v>72</v>
       </c>
-      <c r="C81" s="102" t="s">
+      <c r="C81" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="D81" s="103" t="s">
-        <v>61</v>
-      </c>
-      <c r="E81" s="104" t="s">
-        <v>133</v>
-      </c>
-      <c r="F81" s="103" t="s">
-        <v>173</v>
-      </c>
-      <c r="G81" s="104" t="s">
-        <v>222</v>
-      </c>
-      <c r="H81" s="103" t="s">
-        <v>256</v>
-      </c>
-      <c r="I81" s="103" t="s">
-        <v>412</v>
-      </c>
-      <c r="J81" s="103" t="s">
-        <v>413</v>
-      </c>
-      <c r="K81" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L81" s="103">
+      <c r="D81" s="107" t="s">
+        <v>60</v>
+      </c>
+      <c r="E81" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="F81" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="G81" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="H81" s="107" t="s">
+        <v>257</v>
+      </c>
+      <c r="I81" s="107" t="s">
+        <v>410</v>
+      </c>
+      <c r="J81" s="107" t="s">
+        <v>411</v>
+      </c>
+      <c r="K81" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L81" s="107">
         <v>1</v>
       </c>
-      <c r="M81" s="96">
+      <c r="M81" s="109">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N81" s="96">
+      <c r="N81" s="109">
         <v>21</v>
       </c>
-      <c r="O81" s="105" t="s">
+      <c r="O81" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P81" s="96">
-        <v>0.69430000000000003</v>
-      </c>
-      <c r="Q81" s="96">
-        <f t="shared" ref="Q81" si="72">N81*P81</f>
-        <v>14.580300000000001</v>
-      </c>
-      <c r="R81" s="78"/>
-    </row>
-    <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P81" s="109">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="Q81" s="109">
+        <f t="shared" ref="Q81" si="71">P81*N81</f>
+        <v>29.273999999999997</v>
+      </c>
+      <c r="R81" s="79"/>
+    </row>
+    <row r="82" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
         <f t="shared" si="35"/>
         <v>73</v>
       </c>
-      <c r="C82" s="106" t="s">
+      <c r="C82" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D82" s="107" t="s">
-        <v>62</v>
-      </c>
-      <c r="E82" s="108" t="s">
-        <v>134</v>
-      </c>
-      <c r="F82" s="107" t="s">
-        <v>310</v>
-      </c>
-      <c r="G82" s="108" t="s">
-        <v>174</v>
-      </c>
-      <c r="H82" s="107" t="s">
+      <c r="D82" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="E82" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="F82" s="103" t="s">
+        <v>173</v>
+      </c>
+      <c r="G82" s="104" t="s">
+        <v>222</v>
+      </c>
+      <c r="H82" s="103" t="s">
         <v>256</v>
       </c>
-      <c r="I82" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J82" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K82" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L82" s="107">
+      <c r="I82" s="103" t="s">
+        <v>412</v>
+      </c>
+      <c r="J82" s="103" t="s">
+        <v>413</v>
+      </c>
+      <c r="K82" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L82" s="103">
         <v>1</v>
       </c>
-      <c r="M82" s="109">
+      <c r="M82" s="96">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N82" s="109">
+      <c r="N82" s="96">
         <v>21</v>
       </c>
-      <c r="O82" s="110" t="s">
-        <v>409</v>
-      </c>
-      <c r="P82" s="109">
-        <v>3.637</v>
-      </c>
-      <c r="Q82" s="109">
-        <f t="shared" ref="Q82" si="73">P82*N82</f>
-        <v>76.376999999999995</v>
-      </c>
-      <c r="R82" s="109"/>
-    </row>
-    <row r="83" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O82" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P82" s="96">
+        <v>0.69430000000000003</v>
+      </c>
+      <c r="Q82" s="96">
+        <f t="shared" ref="Q82" si="72">N82*P82</f>
+        <v>14.580300000000001</v>
+      </c>
+      <c r="R82" s="78"/>
+    </row>
+    <row r="83" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
         <f t="shared" si="35"/>
         <v>74</v>
       </c>
-      <c r="C83" s="102" t="s">
+      <c r="C83" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="D83" s="103" t="s">
-        <v>63</v>
-      </c>
-      <c r="E83" s="104" t="s">
-        <v>135</v>
-      </c>
-      <c r="F83" s="103" t="s">
-        <v>175</v>
-      </c>
-      <c r="G83" s="104" t="s">
-        <v>223</v>
-      </c>
-      <c r="H83" s="103" t="s">
+      <c r="D83" s="107" t="s">
+        <v>62</v>
+      </c>
+      <c r="E83" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="F83" s="107" t="s">
+        <v>310</v>
+      </c>
+      <c r="G83" s="108" t="s">
+        <v>174</v>
+      </c>
+      <c r="H83" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="I83" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J83" s="103" t="s">
-        <v>414</v>
-      </c>
-      <c r="K83" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L83" s="103">
+      <c r="I83" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J83" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K83" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L83" s="107">
         <v>1</v>
       </c>
-      <c r="M83" s="96">
+      <c r="M83" s="109">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N83" s="96">
+      <c r="N83" s="109">
         <v>21</v>
       </c>
-      <c r="O83" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="P83" s="96">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q83" s="96">
-        <f t="shared" ref="Q83" si="74">N83*P83</f>
-        <v>9.0888000000000009</v>
-      </c>
-      <c r="R83" s="96"/>
-    </row>
-    <row r="84" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O83" s="110" t="s">
+        <v>409</v>
+      </c>
+      <c r="P83" s="109">
+        <v>3.637</v>
+      </c>
+      <c r="Q83" s="109">
+        <f t="shared" ref="Q83" si="73">P83*N83</f>
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R83" s="109"/>
+    </row>
+    <row r="84" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
         <f t="shared" si="35"/>
         <v>75</v>
       </c>
-      <c r="C84" s="71" t="s">
+      <c r="C84" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D84" s="72" t="s">
-        <v>64</v>
-      </c>
-      <c r="E84" s="73" t="s">
-        <v>136</v>
-      </c>
-      <c r="F84" s="72" t="s">
-        <v>176</v>
-      </c>
-      <c r="G84" s="73" t="s">
-        <v>224</v>
-      </c>
-      <c r="H84" s="72" t="s">
-        <v>258</v>
-      </c>
-      <c r="I84" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="J84" s="72" t="s">
-        <v>415</v>
-      </c>
-      <c r="K84" s="73" t="s">
-        <v>314</v>
-      </c>
-      <c r="L84" s="72">
+      <c r="D84" s="103" t="s">
+        <v>63</v>
+      </c>
+      <c r="E84" s="104" t="s">
+        <v>135</v>
+      </c>
+      <c r="F84" s="103" t="s">
+        <v>175</v>
+      </c>
+      <c r="G84" s="104" t="s">
+        <v>223</v>
+      </c>
+      <c r="H84" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I84" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="K84" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L84" s="103">
         <v>1</v>
       </c>
-      <c r="M84" s="74">
+      <c r="M84" s="96">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N84" s="74">
+      <c r="N84" s="96">
         <v>21</v>
       </c>
-      <c r="O84" s="75" t="s">
+      <c r="O84" s="105" t="s">
         <v>343</v>
       </c>
-      <c r="P84" s="74">
-        <v>7.4638</v>
-      </c>
-      <c r="Q84" s="74">
-        <f t="shared" ref="Q84" si="75">P84*N84</f>
-        <v>156.7398</v>
-      </c>
-      <c r="R84" s="74" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P84" s="96">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="Q84" s="96">
+        <f t="shared" ref="Q84" si="74">N84*P84</f>
+        <v>9.0888000000000009</v>
+      </c>
+      <c r="R84" s="96"/>
+    </row>
+    <row r="85" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
         <f t="shared" si="35"/>
         <v>76</v>
       </c>
-      <c r="C85" s="102" t="s">
+      <c r="C85" s="71" t="s">
         <v>328</v>
       </c>
-      <c r="D85" s="103" t="s">
-        <v>65</v>
-      </c>
-      <c r="E85" s="104" t="s">
-        <v>137</v>
-      </c>
-      <c r="F85" s="103" t="s">
-        <v>177</v>
-      </c>
-      <c r="G85" s="104" t="s">
-        <v>225</v>
-      </c>
-      <c r="H85" s="103" t="s">
-        <v>259</v>
-      </c>
-      <c r="I85" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J85" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K85" s="113" t="s">
-        <v>314</v>
-      </c>
-      <c r="L85" s="103">
+      <c r="D85" s="72" t="s">
+        <v>64</v>
+      </c>
+      <c r="E85" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="F85" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="G85" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="H85" s="72" t="s">
+        <v>258</v>
+      </c>
+      <c r="I85" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="J85" s="72" t="s">
+        <v>415</v>
+      </c>
+      <c r="K85" s="73" t="s">
+        <v>314</v>
+      </c>
+      <c r="L85" s="72">
         <v>1</v>
       </c>
-      <c r="M85" s="96">
+      <c r="M85" s="74">
         <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="N85" s="96">
+      <c r="N85" s="74">
         <v>21</v>
       </c>
-      <c r="O85" s="105" t="s">
-        <v>409</v>
-      </c>
-      <c r="P85" s="96">
-        <v>2.6459999999999999</v>
-      </c>
-      <c r="Q85" s="96">
-        <f t="shared" ref="Q85" si="76">N85*P85</f>
-        <v>55.565999999999995</v>
-      </c>
-      <c r="R85" s="96"/>
-    </row>
-    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O85" s="75" t="s">
+        <v>343</v>
+      </c>
+      <c r="P85" s="74">
+        <v>7.4638</v>
+      </c>
+      <c r="Q85" s="74">
+        <f t="shared" ref="Q85" si="75">P85*N85</f>
+        <v>156.7398</v>
+      </c>
+      <c r="R85" s="74" t="s">
+        <v>438</v>
+      </c>
+      <c r="U85" s="118"/>
+    </row>
+    <row r="86" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
         <f t="shared" si="35"/>
         <v>77</v>
       </c>
-      <c r="C86" s="106" t="s">
+      <c r="C86" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="D86" s="107" t="s">
-        <v>454</v>
-      </c>
-      <c r="E86" s="108" t="s">
-        <v>138</v>
-      </c>
-      <c r="F86" s="107" t="s">
-        <v>311</v>
-      </c>
-      <c r="G86" s="108" t="s">
-        <v>178</v>
-      </c>
-      <c r="H86" s="107" t="s">
-        <v>256</v>
-      </c>
-      <c r="I86" s="107" t="s">
-        <v>416</v>
-      </c>
-      <c r="J86" s="107" t="s">
-        <v>417</v>
-      </c>
-      <c r="K86" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L86" s="114">
-        <v>2</v>
-      </c>
-      <c r="M86" s="109">
+      <c r="D86" s="103" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="F86" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="G86" s="104" t="s">
+        <v>225</v>
+      </c>
+      <c r="H86" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="I86" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J86" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K86" s="113" t="s">
+        <v>314</v>
+      </c>
+      <c r="L86" s="103">
+        <v>1</v>
+      </c>
+      <c r="M86" s="96">
         <f t="shared" si="60"/>
-        <v>40</v>
-      </c>
-      <c r="N86" s="109">
-        <v>42</v>
-      </c>
-      <c r="O86" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="P86" s="109">
-        <v>2.2974000000000001</v>
-      </c>
-      <c r="Q86" s="109">
-        <f t="shared" ref="Q86" si="77">P86*N86</f>
-        <v>96.490800000000007</v>
-      </c>
-      <c r="R86" s="79"/>
-    </row>
-    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="N86" s="96">
+        <v>21</v>
+      </c>
+      <c r="O86" s="105" t="s">
+        <v>409</v>
+      </c>
+      <c r="P86" s="96">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="Q86" s="96">
+        <f t="shared" ref="Q86" si="76">N86*P86</f>
+        <v>55.565999999999995</v>
+      </c>
+      <c r="R86" s="96"/>
+    </row>
+    <row r="87" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
         <f t="shared" si="35"/>
         <v>78</v>
       </c>
-      <c r="C87" s="60" t="s">
+      <c r="C87" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="D87" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="E87" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G87" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="H87" s="37" t="s">
+      <c r="D87" s="107" t="s">
+        <v>454</v>
+      </c>
+      <c r="E87" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="F87" s="107" t="s">
+        <v>311</v>
+      </c>
+      <c r="G87" s="108" t="s">
+        <v>178</v>
+      </c>
+      <c r="H87" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="I87" s="62" t="s">
-        <v>314</v>
-      </c>
-      <c r="J87" s="62" t="s">
-        <v>420</v>
-      </c>
-      <c r="K87" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L87" s="37">
-        <v>1</v>
-      </c>
-      <c r="M87" s="41">
-        <f>L87*20</f>
-        <v>20</v>
-      </c>
-      <c r="N87" s="41">
-        <v>21</v>
-      </c>
-      <c r="O87" s="63" t="s">
+      <c r="I87" s="107" t="s">
+        <v>416</v>
+      </c>
+      <c r="J87" s="107" t="s">
+        <v>417</v>
+      </c>
+      <c r="K87" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L87" s="114">
+        <v>2</v>
+      </c>
+      <c r="M87" s="109">
+        <f t="shared" si="60"/>
+        <v>40</v>
+      </c>
+      <c r="N87" s="109">
+        <v>42</v>
+      </c>
+      <c r="O87" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="P87" s="41">
-        <v>0.39140000000000003</v>
-      </c>
-      <c r="Q87" s="41">
-        <f t="shared" ref="Q87" si="78">P87*N87</f>
-        <v>8.2194000000000003</v>
-      </c>
-      <c r="R87" s="41"/>
-    </row>
-    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P87" s="109">
+        <v>2.2974000000000001</v>
+      </c>
+      <c r="Q87" s="109">
+        <f t="shared" ref="Q87" si="77">P87*N87</f>
+        <v>96.490800000000007</v>
+      </c>
+      <c r="R87" s="79"/>
+    </row>
+    <row r="88" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
         <f t="shared" si="35"/>
         <v>79</v>
       </c>
-      <c r="C88" s="59" t="s">
+      <c r="C88" s="60" t="s">
         <v>328</v>
       </c>
-      <c r="D88" s="39" t="s">
-        <v>455</v>
-      </c>
-      <c r="E88" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="F88" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="G88" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="H88" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="I88" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="J88" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K88" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L88" s="39">
+      <c r="D88" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E88" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F88" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="G88" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="H88" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="I88" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="J88" s="62" t="s">
+        <v>420</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L88" s="37">
         <v>1</v>
       </c>
-      <c r="M88" s="42">
-        <f t="shared" si="60"/>
+      <c r="M88" s="41">
+        <f>L88*20</f>
         <v>20</v>
       </c>
-      <c r="N88" s="42">
+      <c r="N88" s="41">
         <v>21</v>
       </c>
-      <c r="O88" s="64" t="s">
-        <v>419</v>
-      </c>
-      <c r="P88" s="42">
-        <v>3.532</v>
-      </c>
-      <c r="Q88" s="42">
-        <f t="shared" ref="Q88:Q89" si="79">N88*P88</f>
-        <v>74.171999999999997</v>
-      </c>
-      <c r="R88" s="79"/>
-    </row>
-    <row r="89" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O88" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P88" s="41">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="Q88" s="41">
+        <f t="shared" ref="Q88" si="78">P88*N88</f>
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R88" s="41"/>
+    </row>
+    <row r="89" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="53">
         <f t="shared" si="35"/>
         <v>80</v>
       </c>
       <c r="C89" s="59" t="s">
-        <v>470</v>
+        <v>328</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>314</v>
+        <v>455</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>473</v>
+        <v>139</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G89" s="40" t="s">
-        <v>471</v>
+        <v>179</v>
       </c>
       <c r="H89" s="39" t="s">
-        <v>472</v>
+        <v>259</v>
       </c>
       <c r="I89" s="39" t="s">
-        <v>314</v>
+        <v>418</v>
       </c>
       <c r="J89" s="39" t="s">
-        <v>471</v>
-      </c>
-      <c r="K89" s="40"/>
+        <v>314</v>
+      </c>
+      <c r="K89" s="40" t="s">
+        <v>314</v>
+      </c>
       <c r="L89" s="39">
         <v>1</v>
       </c>
@@ -7394,73 +7415,126 @@
         <v>20</v>
       </c>
       <c r="N89" s="42">
+        <v>21</v>
+      </c>
+      <c r="O89" s="64" t="s">
+        <v>419</v>
+      </c>
+      <c r="P89" s="42">
+        <v>3.532</v>
+      </c>
+      <c r="Q89" s="42">
+        <f t="shared" ref="Q89:Q90" si="79">N89*P89</f>
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R89" s="79"/>
+    </row>
+    <row r="90" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="B90" s="53">
+        <f t="shared" si="35"/>
+        <v>81</v>
+      </c>
+      <c r="C90" s="59" t="s">
+        <v>470</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="E90" s="40" t="s">
+        <v>473</v>
+      </c>
+      <c r="F90" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="G90" s="40" t="s">
+        <v>471</v>
+      </c>
+      <c r="H90" s="39" t="s">
+        <v>472</v>
+      </c>
+      <c r="I90" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J90" s="39" t="s">
+        <v>471</v>
+      </c>
+      <c r="K90" s="40"/>
+      <c r="L90" s="39">
+        <v>1</v>
+      </c>
+      <c r="M90" s="42">
+        <f t="shared" si="60"/>
+        <v>20</v>
+      </c>
+      <c r="N90" s="42">
         <v>25</v>
       </c>
-      <c r="O89" s="64" t="s">
+      <c r="O90" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="P89" s="42">
+      <c r="P90" s="42">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="Q89" s="42">
+      <c r="Q90" s="42">
         <f t="shared" si="79"/>
         <v>2.2250000000000001</v>
       </c>
-      <c r="R89" s="79"/>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="B90" s="32"/>
-      <c r="C90" s="51"/>
-      <c r="D90" s="33" t="s">
+      <c r="R90" s="79"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="51"/>
+      <c r="D91" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E90" s="34"/>
-      <c r="F90" s="35"/>
-      <c r="G90" s="36"/>
-      <c r="H90" s="35"/>
-      <c r="I90" s="35"/>
-      <c r="J90" s="35"/>
-      <c r="K90" s="36"/>
-      <c r="L90" s="36"/>
-      <c r="M90" s="36"/>
-      <c r="N90" s="36"/>
-      <c r="O90" s="69" t="s">
+      <c r="E91" s="34"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="36"/>
+      <c r="H91" s="35"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
+      <c r="K91" s="36"/>
+      <c r="L91" s="36"/>
+      <c r="M91" s="36"/>
+      <c r="N91" s="36"/>
+      <c r="O91" s="69" t="s">
         <v>421</v>
       </c>
-      <c r="P90" s="67"/>
-      <c r="Q90" s="67">
-        <f>SUM(Q10:Q88)</f>
-        <v>969.42630000000008</v>
-      </c>
-      <c r="R90" s="44"/>
-    </row>
-    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="B91" s="24"/>
-      <c r="C91" s="52"/>
-      <c r="D91" s="8" t="s">
+      <c r="P91" s="67"/>
+      <c r="Q91" s="67">
+        <f>SUM(Q10:Q90)</f>
+        <v>976.95380000000011</v>
+      </c>
+      <c r="R91" s="44"/>
+    </row>
+    <row r="92" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="B92" s="24"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="9"/>
-      <c r="K91" s="9"/>
-      <c r="L91" s="9"/>
-      <c r="M91" s="9"/>
-      <c r="N91" s="9"/>
-      <c r="O91" s="70" t="s">
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="9"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="70" t="s">
         <v>422</v>
       </c>
-      <c r="P91" s="68"/>
-      <c r="Q91" s="68">
-        <f>Q90/20</f>
-        <v>48.471315000000004</v>
-      </c>
-      <c r="R91" s="45"/>
+      <c r="P92" s="68"/>
+      <c r="Q92" s="68">
+        <f>Q91/20</f>
+        <v>48.847690000000007</v>
+      </c>
+      <c r="R92" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7468,85 +7542,86 @@
     <mergeCell ref="R3:R8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="O16" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="O17" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="O18" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="O19" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="O20" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="O21" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="O22" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O23" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="O24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="O25" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="O26" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="O27" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="O28" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="O29" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="O30" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="O31" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="O32" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="O33" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="O34" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="O35" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="O36" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="O37" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="O38" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="O39" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="O40" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="O41" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="O42" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="O43" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="O44" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="O45" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="O47" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="O49" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="O50" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="O51" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="O52" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="O53" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="O54" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="O55" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="O56" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="O68" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="O58" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="O59" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="O60" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="O61" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="O62" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="O63" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="O64" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="O65" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="O66" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="O67" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="O69" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="O70" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="O71" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="O74" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="O75" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="O72" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="O78" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="O79" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="O80" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="O81" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="O82" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="O83" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="O84" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="O85" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="O86" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="O88" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="O87" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="O57" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="O46" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="O89" r:id="rId76" xr:uid="{94AF4969-113D-4C22-911F-093FC1147D5D}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O15" r:id="rId6"/>
+    <hyperlink ref="O16" r:id="rId7"/>
+    <hyperlink ref="O17" r:id="rId8"/>
+    <hyperlink ref="O18" r:id="rId9"/>
+    <hyperlink ref="O19" r:id="rId10"/>
+    <hyperlink ref="O20" r:id="rId11"/>
+    <hyperlink ref="O21" r:id="rId12"/>
+    <hyperlink ref="O22" r:id="rId13"/>
+    <hyperlink ref="O23" r:id="rId14"/>
+    <hyperlink ref="O24" r:id="rId15"/>
+    <hyperlink ref="O25" r:id="rId16"/>
+    <hyperlink ref="O26" r:id="rId17"/>
+    <hyperlink ref="O27" r:id="rId18"/>
+    <hyperlink ref="O28" r:id="rId19"/>
+    <hyperlink ref="O29" r:id="rId20"/>
+    <hyperlink ref="O30" r:id="rId21"/>
+    <hyperlink ref="O31" r:id="rId22"/>
+    <hyperlink ref="O32" r:id="rId23"/>
+    <hyperlink ref="O33" r:id="rId24"/>
+    <hyperlink ref="O34" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O36" r:id="rId27"/>
+    <hyperlink ref="O37" r:id="rId28"/>
+    <hyperlink ref="O38" r:id="rId29"/>
+    <hyperlink ref="O39" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId31"/>
+    <hyperlink ref="O41" r:id="rId32"/>
+    <hyperlink ref="O43" r:id="rId33"/>
+    <hyperlink ref="O44" r:id="rId34"/>
+    <hyperlink ref="O45" r:id="rId35"/>
+    <hyperlink ref="O46" r:id="rId36"/>
+    <hyperlink ref="O48" r:id="rId37"/>
+    <hyperlink ref="O50" r:id="rId38"/>
+    <hyperlink ref="O51" r:id="rId39"/>
+    <hyperlink ref="O52" r:id="rId40"/>
+    <hyperlink ref="O53" r:id="rId41"/>
+    <hyperlink ref="O54" r:id="rId42"/>
+    <hyperlink ref="O55" r:id="rId43"/>
+    <hyperlink ref="O56" r:id="rId44"/>
+    <hyperlink ref="O57" r:id="rId45"/>
+    <hyperlink ref="O69" r:id="rId46"/>
+    <hyperlink ref="O59" r:id="rId47"/>
+    <hyperlink ref="O60" r:id="rId48"/>
+    <hyperlink ref="O61" r:id="rId49"/>
+    <hyperlink ref="O62" r:id="rId50"/>
+    <hyperlink ref="O63" r:id="rId51"/>
+    <hyperlink ref="O64" r:id="rId52"/>
+    <hyperlink ref="O65" r:id="rId53"/>
+    <hyperlink ref="O66" r:id="rId54"/>
+    <hyperlink ref="O67" r:id="rId55"/>
+    <hyperlink ref="O68" r:id="rId56"/>
+    <hyperlink ref="O70" r:id="rId57"/>
+    <hyperlink ref="O71" r:id="rId58"/>
+    <hyperlink ref="O72" r:id="rId59"/>
+    <hyperlink ref="O75" r:id="rId60"/>
+    <hyperlink ref="O76" r:id="rId61"/>
+    <hyperlink ref="O73" r:id="rId62"/>
+    <hyperlink ref="O79" r:id="rId63"/>
+    <hyperlink ref="O80" r:id="rId64"/>
+    <hyperlink ref="O81" r:id="rId65"/>
+    <hyperlink ref="O82" r:id="rId66"/>
+    <hyperlink ref="O83" r:id="rId67"/>
+    <hyperlink ref="O84" r:id="rId68"/>
+    <hyperlink ref="O85" r:id="rId69"/>
+    <hyperlink ref="O86" r:id="rId70"/>
+    <hyperlink ref="O87" r:id="rId71"/>
+    <hyperlink ref="O89" r:id="rId72"/>
+    <hyperlink ref="O88" r:id="rId73"/>
+    <hyperlink ref="O58" r:id="rId74"/>
+    <hyperlink ref="O47" r:id="rId75"/>
+    <hyperlink ref="O90" r:id="rId76"/>
+    <hyperlink ref="O42" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId77"/>
-  <drawing r:id="rId78"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId78"/>
+  <drawing r:id="rId79"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="479">
   <si>
     <t>Component list</t>
   </si>
@@ -256,6 +256,12 @@
     <t>CAP CER 0.082UF 50V X7R 0603</t>
   </si>
   <si>
+    <t>Cap Ceramic 0.22uF 100V X7R 10% SMD 0805 125°C Embossed T/R</t>
+  </si>
+  <si>
+    <t>0603 .022uF 100volts X7R 10% T=0.8mm</t>
+  </si>
+  <si>
     <t>220uF ±20% 63V 10mm 14.5mm 1.2A 100kHz 10000hrs 105℃ -55℃~+105℃ SMD,10x14.5mm Aluminum Electrolytic Capacitors - SMD RoHS</t>
   </si>
   <si>
@@ -268,6 +274,9 @@
     <t>CAP CER 4.7UF 25V X5R 0603</t>
   </si>
   <si>
+    <t>CAP CER 1000PF 100V X7R 0402</t>
+  </si>
+  <si>
     <t>CAP CER 2200PF 50V X7R 0603</t>
   </si>
   <si>
@@ -292,12 +301,24 @@
     <t>500μA@100V 100V Single 600mV@1A 1A SMA Schottky Barrier Diodes (SBD) ROHS</t>
   </si>
   <si>
+    <t>40V 500mV@2A 2A SMA(DO-214AC) Schottky Barrier Diodes (SBD) ROHS</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 30V 1A SOD123W</t>
+  </si>
+  <si>
+    <t>FUSE BOARD MNT 15A 125VAC 32VDC</t>
+  </si>
+  <si>
     <t>Ferrite Beads Multi-Layer 120Ohm 25% 100MHz 2A 45mOhm DCR 0603 Automotive T/R</t>
   </si>
   <si>
     <t>Receptacle USB - Type C 24 - SMD USB Connectors ROHS</t>
   </si>
   <si>
+    <t>Conn RJ-25 F 6 POS 2.54mm Solder ST Thru-Hole 4 Terminal 1 Port Tray Cat 3</t>
+  </si>
+  <si>
     <t>CONN HEADER SMD 26POS 1.27MM</t>
   </si>
   <si>
@@ -322,6 +343,9 @@
     <t>CONN HEADER VERT 2POS 2.54MM</t>
   </si>
   <si>
+    <t>MOSFET N-CH 80V 74A 8TDSON</t>
+  </si>
+  <si>
     <t>RES SMD 5.1K OHM 5% 1/10W 0603</t>
   </si>
   <si>
@@ -337,6 +361,9 @@
     <t>RES SMD 47OHM 0.1W 0603</t>
   </si>
   <si>
+    <t>0.033Ω ±1% 2W ±1800ppm/°C 2512 Low Resistors &amp; Current Sense Resistors - Surface Mount RoHS</t>
+  </si>
+  <si>
     <t>RES SMD 150OHM 1/10W 0603</t>
   </si>
   <si>
@@ -361,6 +388,9 @@
     <t>RES SMD 105K OHM 1% 1/10W 0603</t>
   </si>
   <si>
+    <t>RES SMD 127K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
     <t>Res Thick Film 0603 100K Ohm 5% 1/10W 100ppm/C Molded SMD SMD Paper T/R</t>
   </si>
   <si>
@@ -397,6 +427,12 @@
     <t>IC REG BUCK FLYBCK ADJ 12WSON</t>
   </si>
   <si>
+    <t>IC REG LINEAR 3.3V 1A 6UDFN</t>
+  </si>
+  <si>
+    <t>3.5V to 36V, 3A Synchronous Step-Down Voltage Converter 16-HTSSOP -40 to 125</t>
+  </si>
+  <si>
     <t>IC REG CHARGE PUMP 5V 140MA 6SON</t>
   </si>
   <si>
@@ -409,6 +445,12 @@
     <t>IC OPAMP GP 1.7MHZ RRO SOT23-6</t>
   </si>
   <si>
+    <t>DGTL ISO 3000VRMS 4CH 16SSOP</t>
+  </si>
+  <si>
+    <t>DGTL ISO 600VRMS 6CH GP 16SOIC</t>
+  </si>
+  <si>
     <t>IC BUS BUFFER TRI-ST QD 14TSSOP</t>
   </si>
   <si>
@@ -445,9 +487,21 @@
     <t>SMA</t>
   </si>
   <si>
+    <t>SOD-123W</t>
+  </si>
+  <si>
+    <t>0685H9150-01</t>
+  </si>
+  <si>
     <t>MPZ1608S121ATDH5</t>
   </si>
   <si>
+    <t>MC-318</t>
+  </si>
+  <si>
+    <t>5520425-2</t>
+  </si>
+  <si>
     <t>M55-7012642R</t>
   </si>
   <si>
@@ -472,6 +526,9 @@
     <t>HDR1X2</t>
   </si>
   <si>
+    <t>8-PowerTDFN</t>
+  </si>
+  <si>
     <t>Res0603</t>
   </si>
   <si>
@@ -490,6 +547,12 @@
     <t>LM5160ADNTR</t>
   </si>
   <si>
+    <t>6-UDFN (3x3)</t>
+  </si>
+  <si>
+    <t>HTSSOP-16</t>
+  </si>
+  <si>
     <t>TPS60150DRVR</t>
   </si>
   <si>
@@ -502,6 +565,12 @@
     <t>SOT-23-6</t>
   </si>
   <si>
+    <t>ISO7741QDBQQ1</t>
+  </si>
+  <si>
+    <t>MAX14850ASE+</t>
+  </si>
+  <si>
     <t>SN74LVTH125PWR</t>
   </si>
   <si>
@@ -526,6 +595,12 @@
     <t>CC0603KRX7R9BB823</t>
   </si>
   <si>
+    <t>08051C224K4T2A</t>
+  </si>
+  <si>
+    <t>CGA3E2X7R2A223K080AA</t>
+  </si>
+  <si>
     <t>CL05B104KB54PNC</t>
   </si>
   <si>
@@ -550,9 +625,15 @@
     <t>CL10B102KC8NNNC</t>
   </si>
   <si>
+    <t>PMEG3010ER,115</t>
+  </si>
+  <si>
     <t>XZVG68W-2</t>
   </si>
   <si>
+    <t>BSC072N08NS5ATMA1</t>
+  </si>
+  <si>
     <t>RC0603JR-075K1L</t>
   </si>
   <si>
@@ -592,6 +673,9 @@
     <t>RC0603FR-07105KL</t>
   </si>
   <si>
+    <t>RT0603FRE07127KL</t>
+  </si>
+  <si>
     <t>RC0603JR-07100KL</t>
   </si>
   <si>
@@ -610,6 +694,12 @@
     <t>RC0603FR-0710KL</t>
   </si>
   <si>
+    <t>NCP708MU330TAG</t>
+  </si>
+  <si>
+    <t>LM43603PWPR</t>
+  </si>
+  <si>
     <t>MC34063ADR</t>
   </si>
   <si>
@@ -661,6 +751,9 @@
     <t>Nexperia</t>
   </si>
   <si>
+    <t>Bel</t>
+  </si>
+  <si>
     <t>SOFNG</t>
   </si>
   <si>
@@ -682,9 +775,15 @@
     <t>SparkFun</t>
   </si>
   <si>
+    <t>Infineon</t>
+  </si>
+  <si>
     <t>FH</t>
   </si>
   <si>
+    <t>Ever Ohms Tech</t>
+  </si>
+  <si>
     <t>Panasonic</t>
   </si>
   <si>
@@ -703,6 +802,9 @@
     <t>Texas Instruments</t>
   </si>
   <si>
+    <t>ON Semiconductor</t>
+  </si>
+  <si>
     <t>Trinamic</t>
   </si>
   <si>
@@ -862,6 +964,9 @@
     <t>6-SON</t>
   </si>
   <si>
+    <t>16-SSOP</t>
+  </si>
+  <si>
     <t>16-SOIC</t>
   </si>
   <si>
@@ -913,6 +1018,9 @@
     <t>IC</t>
   </si>
   <si>
+    <t>CRH2512FR033E04Z</t>
+  </si>
+  <si>
     <t>0603WAF1201T5E</t>
   </si>
   <si>
@@ -928,57 +1036,270 @@
     <t>Bill of Materials for Project (Smart Motors)</t>
   </si>
   <si>
+    <t>Alternate Part Number</t>
+  </si>
+  <si>
+    <t>LCSC Part Number</t>
+  </si>
+  <si>
     <t>Quantity (20 Boards)</t>
   </si>
   <si>
+    <t>MOQ (20 Boards)</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Unit Cost (20 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (20 Boards)</t>
+  </si>
+  <si>
+    <t>C116211</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>C1591</t>
+  </si>
+  <si>
+    <t>C327025</t>
+  </si>
+  <si>
+    <t>C386109</t>
+  </si>
+  <si>
+    <t>C86017</t>
+  </si>
+  <si>
+    <t>C14664</t>
+  </si>
+  <si>
+    <t>C107100</t>
+  </si>
+  <si>
+    <t>C513710</t>
+  </si>
+  <si>
     <t>CC0805KKX7R0BB224</t>
   </si>
   <si>
     <t>TCC0603X7R223K101CT</t>
   </si>
   <si>
+    <t>C376821</t>
+  </si>
+  <si>
+    <t>C487391</t>
+  </si>
+  <si>
+    <t>C307331</t>
+  </si>
+  <si>
     <t>C16, C18, C19, C21, C26, C27, C28, C31</t>
   </si>
   <si>
+    <t>C92847</t>
+  </si>
+  <si>
+    <t>C69335</t>
+  </si>
+  <si>
     <t>CC0402KRX7R0BB102</t>
   </si>
   <si>
+    <t>C527013</t>
+  </si>
+  <si>
+    <t>C107082</t>
+  </si>
+  <si>
+    <t>C403725</t>
+  </si>
+  <si>
+    <t>C7230</t>
+  </si>
+  <si>
+    <t>C191227</t>
+  </si>
+  <si>
+    <t>C107092</t>
+  </si>
+  <si>
+    <t>C153291</t>
+  </si>
+  <si>
+    <t>C146335</t>
+  </si>
+  <si>
+    <t>C698870</t>
+  </si>
+  <si>
+    <t>C842786</t>
+  </si>
+  <si>
     <t>PMEG3010EP,115</t>
   </si>
   <si>
+    <t>C552865</t>
+  </si>
+  <si>
     <t>12D2150E</t>
   </si>
   <si>
+    <t>C182976</t>
+  </si>
+  <si>
+    <t>C307770</t>
+  </si>
+  <si>
     <t>MC-318FB</t>
   </si>
   <si>
+    <t>C2977724</t>
+  </si>
+  <si>
     <t>5520425-3</t>
   </si>
   <si>
+    <t>C305971</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>C144395</t>
+  </si>
+  <si>
+    <t>C93225</t>
+  </si>
+  <si>
+    <t>Chipmall</t>
+  </si>
+  <si>
+    <t>NACSemi</t>
+  </si>
+  <si>
     <t>DO NOT MOUNT</t>
   </si>
   <si>
     <t>AO4882-MS</t>
   </si>
   <si>
+    <t>C2847038</t>
+  </si>
+  <si>
+    <t>C14677</t>
+  </si>
+  <si>
+    <t>C114616</t>
+  </si>
+  <si>
+    <t>C322001</t>
+  </si>
+  <si>
+    <t>C100044</t>
+  </si>
+  <si>
+    <t>C114623</t>
+  </si>
+  <si>
     <t>LR2512-22R033F4</t>
   </si>
   <si>
+    <t>C2681032</t>
+  </si>
+  <si>
+    <t>C114608</t>
+  </si>
+  <si>
+    <t>C137801</t>
+  </si>
+  <si>
+    <t>C137798</t>
+  </si>
+  <si>
+    <t>C227561</t>
+  </si>
+  <si>
+    <t>C141685</t>
+  </si>
+  <si>
     <t>ARG03FTC1273</t>
   </si>
   <si>
+    <t>C217715</t>
+  </si>
+  <si>
+    <t>C100048</t>
+  </si>
+  <si>
+    <t>C114628</t>
+  </si>
+  <si>
+    <t>C105576</t>
+  </si>
+  <si>
+    <t>TME</t>
+  </si>
+  <si>
+    <t>C22765</t>
+  </si>
+  <si>
+    <t>C103893</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>C98220</t>
+  </si>
+  <si>
+    <t>Winsource</t>
+  </si>
+  <si>
     <t>TLV75733PDBVR</t>
   </si>
   <si>
+    <t>C485517</t>
+  </si>
+  <si>
     <t>BD9876AEFJ-E2</t>
   </si>
   <si>
+    <t>C79958</t>
+  </si>
+  <si>
+    <t>C100023</t>
+  </si>
+  <si>
+    <t>C516354</t>
+  </si>
+  <si>
     <t>ISO7221ADR</t>
   </si>
   <si>
+    <t>C28037</t>
+  </si>
+  <si>
     <t>ISO6761FDWR</t>
   </si>
   <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>C7042</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>PER BOARD COST</t>
+  </si>
+  <si>
     <t>R14, R15, R16, R17, R18, R19, R20, R26</t>
   </si>
   <si>
@@ -988,6 +1309,9 @@
     <t>0603WAF220JT5E</t>
   </si>
   <si>
+    <t>C23345</t>
+  </si>
+  <si>
     <t>22R</t>
   </si>
   <si>
@@ -1000,13 +1324,25 @@
     <t>CAP CER 6.8nF 50V X7R 0603</t>
   </si>
   <si>
+    <t>C1631</t>
+  </si>
+  <si>
     <t>GRM188R6YA106MA73D</t>
   </si>
   <si>
+    <t>C194427</t>
+  </si>
+  <si>
     <t>RES SMD 110K OHM 0.5% 1/10W 0603</t>
   </si>
   <si>
+    <t>C423090</t>
+  </si>
+  <si>
     <t>DMBJ</t>
+  </si>
+  <si>
+    <t>C2849490</t>
   </si>
   <si>
     <t>Will be provided by Robotshop for prototyping</t>
@@ -1263,73 +1599,7 @@
     <t>XKB Connectivity</t>
   </si>
   <si>
-    <t>100V 220nF X7R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
-  </si>
-  <si>
-    <t>CCTC</t>
-  </si>
-  <si>
-    <t>100V 22nF X7R ±10% 0603 Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
-  </si>
-  <si>
-    <t>100V 1nF X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
-  </si>
-  <si>
-    <t>FUXINSEMI</t>
-  </si>
-  <si>
-    <t>SMA(DO-214AC)</t>
-  </si>
-  <si>
-    <t>500uA@40V 40V Single 550mV@2A 2A SMA(DO-214AC) (SBD)</t>
-  </si>
-  <si>
-    <t>SOD-128</t>
-  </si>
-  <si>
-    <t>30V 360mV@1A 1A SOD-128</t>
-  </si>
-  <si>
-    <t>Shenzen</t>
-  </si>
-  <si>
-    <t>FastBlow 150A SMD Fuse 15A 1206</t>
-  </si>
-  <si>
-    <t>RJReceptacle No 1 cat3 Without LED Plugin Ethernet Connectors/Modular</t>
-  </si>
-  <si>
-    <t>MSKSEMI</t>
-  </si>
-  <si>
-    <t>SOP-8</t>
-  </si>
-  <si>
-    <t>40V 6A 25mΩ@10V,6A 1.9W 1.6V@250uA 76pF@15V 2 N-Channel</t>
-  </si>
-  <si>
-    <t>2W 33mΩ Surface Mount 81.65A ±25ppm/℃ ±1% 2512</t>
-  </si>
-  <si>
-    <t>Viking Tech</t>
-  </si>
-  <si>
-    <t>100mW Thin Film Resistor 75V ±1% -55℃~+155℃ 127kΩ 0603</t>
-  </si>
-  <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
-    <t>1A 475mV@(1A) Fixed 3.3V~3.3V Positive 1 5.5V</t>
-  </si>
-  <si>
-    <t>NO Step-down type 1 Step-down 1V~29.4V 7V~42V 3A 300kHz</t>
-  </si>
-  <si>
-    <t>2 Unidirectional 2500Vrms 1Mbps</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GENERAL PURPOSE, 50-MBPS, SIX-CH</t>
+    <t>C780053</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1609,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1470,6 +1740,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
@@ -1486,6 +1764,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
@@ -1496,6 +1782,15 @@
       <b/>
       <strike/>
       <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1559,7 +1854,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1793,11 +2088,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1961,9 +2270,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1976,16 +2306,22 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2000,10 +2336,16 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2015,25 +2357,34 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2045,6 +2396,9 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2057,17 +2411,29 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2075,17 +2441,9 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2111,13 +2469,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -2127,7 +2485,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2425,7 +2783,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:U92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2435,13 +2793,17 @@
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" customWidth="1"/>
+    <col min="9" max="10" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2450,12 +2812,18 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+    </row>
+    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -2464,16 +2832,22 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="43"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="43"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -2482,16 +2856,22 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="101"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="116"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -2500,16 +2880,22 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="102"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="117"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -2522,10 +2908,16 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="102"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="117"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -2536,10 +2928,16 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="102"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="117"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -2551,9 +2949,15 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="102"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="117"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -2565,15 +2969,21 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="102"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="117"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
@@ -2582,35 +2992,53 @@
         <v>67</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="I9" s="30" t="s">
         <v>226</v>
       </c>
+      <c r="I9" s="29" t="s">
+        <v>335</v>
+      </c>
       <c r="J9" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="M9" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="O9" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q9" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="R9" s="31" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
@@ -2619,252 +3047,385 @@
         <v>68</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="I10" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="J10" s="37">
+      <c r="I10" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="K10" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="L10" s="37">
         <v>1</v>
       </c>
-      <c r="K10" s="41">
-        <f>J10*20</f>
+      <c r="M10" s="41">
+        <f>L10*20</f>
         <v>20</v>
       </c>
-      <c r="L10" s="41"/>
-    </row>
-    <row r="11" spans="1:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="41">
+        <v>22</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P10" s="41">
+        <v>0.25869999999999999</v>
+      </c>
+      <c r="Q10" s="41">
+        <f>P10*N10</f>
+        <v>5.6913999999999998</v>
+      </c>
+      <c r="R10" s="41"/>
+    </row>
+    <row r="11" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B45" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>352</v>
-      </c>
-      <c r="E11" s="73" t="s">
+      <c r="C11" s="81" t="s">
+        <v>316</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>464</v>
+      </c>
+      <c r="E11" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="72" t="s">
-        <v>129</v>
-      </c>
-      <c r="G11" s="73" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="72" t="s">
-        <v>198</v>
-      </c>
-      <c r="I11" s="73" t="s">
+      <c r="F11" s="82" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="82" t="s">
         <v>228</v>
       </c>
-      <c r="J11" s="72">
+      <c r="I11" s="82" t="s">
+        <v>314</v>
+      </c>
+      <c r="J11" s="82" t="s">
+        <v>344</v>
+      </c>
+      <c r="K11" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="L11" s="82">
         <v>15</v>
       </c>
-      <c r="K11" s="74">
-        <f>J11*20</f>
+      <c r="M11" s="84">
+        <f>L11*20</f>
         <v>300</v>
       </c>
-      <c r="L11" s="74" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N11" s="84">
+        <v>300</v>
+      </c>
+      <c r="O11" s="85" t="s">
+        <v>343</v>
+      </c>
+      <c r="P11" s="84">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q11" s="84">
+        <f>N11*P11</f>
+        <v>0.42</v>
+      </c>
+      <c r="R11" s="84" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>348</v>
+        <v>460</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>70</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="I12" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="J12" s="75">
+      <c r="I12" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="K12" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="L12" s="86">
         <v>2</v>
       </c>
-      <c r="K12" s="41">
-        <f t="shared" ref="K12:K71" si="1">J12*20</f>
+      <c r="M12" s="41">
+        <f t="shared" ref="M12:M71" si="1">L12*20</f>
         <v>40</v>
       </c>
-      <c r="L12" s="67"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="41">
+        <v>100</v>
+      </c>
+      <c r="O12" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P12" s="41">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q12" s="41">
+        <f t="shared" ref="Q12" si="2">P12*N12</f>
+        <v>0.13</v>
+      </c>
+      <c r="R12" s="76"/>
+    </row>
+    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>321</v>
+        <v>429</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>71</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="I13" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="J13" s="76">
+      <c r="I13" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="K13" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="L13" s="87">
         <v>1</v>
       </c>
-      <c r="K13" s="42">
+      <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L13" s="68"/>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="88">
+        <v>40</v>
+      </c>
+      <c r="O13" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P13" s="42">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="Q13" s="42">
+        <f t="shared" ref="Q13" si="3">N13*P13</f>
+        <v>1.4359999999999999</v>
+      </c>
+      <c r="R13" s="77"/>
+    </row>
+    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
       <c r="C14" s="60" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>329</v>
+        <v>441</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>72</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="I14" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="J14" s="37">
+      <c r="I14" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="K14" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="L14" s="37">
         <v>8</v>
       </c>
-      <c r="K14" s="41">
+      <c r="M14" s="41">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="L14" s="67"/>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="41">
+        <v>200</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P14" s="41">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="Q14" s="41">
+        <f>P14*N14</f>
+        <v>8.18</v>
+      </c>
+      <c r="R14" s="76"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>347</v>
+        <v>459</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>73</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="I15" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="J15" s="76">
+        <v>229</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J15" s="39" t="s">
+        <v>348</v>
+      </c>
+      <c r="K15" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="L15" s="87">
         <v>3</v>
       </c>
-      <c r="K15" s="42">
+      <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="L15" s="68"/>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N15" s="88">
+        <v>100</v>
+      </c>
+      <c r="O15" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P15" s="42">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="Q15" s="42">
+        <f t="shared" ref="Q15" si="4">N15*P15</f>
+        <v>0.59</v>
+      </c>
+      <c r="R15" s="77"/>
+    </row>
+    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="86" t="s">
-        <v>323</v>
-      </c>
-      <c r="H16" s="75" t="s">
-        <v>201</v>
-      </c>
-      <c r="I16" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="J16" s="37">
+        <v>143</v>
+      </c>
+      <c r="G16" s="101" t="s">
+        <v>432</v>
+      </c>
+      <c r="H16" s="86" t="s">
+        <v>231</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>433</v>
+      </c>
+      <c r="K16" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="L16" s="37">
         <v>6</v>
       </c>
-      <c r="K16" s="41">
+      <c r="M16" s="41">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="L16" s="67"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="41">
+        <v>130</v>
+      </c>
+      <c r="O16" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P16" s="41">
+        <v>3.32E-2</v>
+      </c>
+      <c r="Q16" s="41">
+        <f t="shared" ref="Q16" si="5">P16*N16</f>
+        <v>4.3159999999999998</v>
+      </c>
+      <c r="R16" s="76"/>
+    </row>
+    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>9</v>
@@ -2873,2664 +3434,4055 @@
         <v>74</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="I17" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="J17" s="39">
+        <v>229</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>349</v>
+      </c>
+      <c r="K17" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="L17" s="39">
         <v>1</v>
       </c>
-      <c r="K17" s="42">
+      <c r="M17" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L17" s="42"/>
-    </row>
-    <row r="18" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="42">
+        <v>50</v>
+      </c>
+      <c r="O17" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P17" s="42">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="Q17" s="42">
+        <f t="shared" ref="Q17" si="6">N17*P17</f>
+        <v>0.49500000000000005</v>
+      </c>
+      <c r="R17" s="42"/>
+    </row>
+    <row r="18" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="87" t="s">
-        <v>281</v>
-      </c>
-      <c r="D18" s="88" t="s">
-        <v>302</v>
-      </c>
-      <c r="E18" s="89" t="s">
-        <v>366</v>
-      </c>
-      <c r="F18" s="88" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" s="88" t="s">
-        <v>300</v>
-      </c>
-      <c r="H18" s="88" t="s">
-        <v>199</v>
-      </c>
-      <c r="I18" s="89" t="s">
-        <v>235</v>
-      </c>
-      <c r="J18" s="88">
+      <c r="C18" s="102" t="s">
+        <v>316</v>
+      </c>
+      <c r="D18" s="103" t="s">
+        <v>356</v>
+      </c>
+      <c r="E18" s="104" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="103" t="s">
+        <v>145</v>
+      </c>
+      <c r="G18" s="104" t="s">
+        <v>188</v>
+      </c>
+      <c r="H18" s="103" t="s">
+        <v>232</v>
+      </c>
+      <c r="I18" s="103" t="s">
+        <v>351</v>
+      </c>
+      <c r="J18" s="103" t="s">
+        <v>350</v>
+      </c>
+      <c r="K18" s="104" t="s">
+        <v>269</v>
+      </c>
+      <c r="L18" s="103">
         <v>8</v>
       </c>
-      <c r="K18" s="82">
+      <c r="M18" s="96">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="L18" s="82"/>
-    </row>
-    <row r="19" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N18" s="96">
+        <v>180</v>
+      </c>
+      <c r="O18" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P18" s="96">
+        <v>3.09E-2</v>
+      </c>
+      <c r="Q18" s="96">
+        <f t="shared" ref="Q18" si="7">N18*P18</f>
+        <v>5.5620000000000003</v>
+      </c>
+      <c r="R18" s="96"/>
+    </row>
+    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="90" t="s">
-        <v>281</v>
-      </c>
-      <c r="D19" s="91" t="s">
+      <c r="C19" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="D19" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="92" t="s">
-        <v>368</v>
-      </c>
-      <c r="F19" s="91" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="91" t="s">
-        <v>301</v>
-      </c>
-      <c r="H19" s="91" t="s">
-        <v>367</v>
-      </c>
-      <c r="I19" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="J19" s="91">
+      <c r="E19" s="108" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="107" t="s">
+        <v>143</v>
+      </c>
+      <c r="G19" s="108" t="s">
+        <v>189</v>
+      </c>
+      <c r="H19" s="107" t="s">
+        <v>233</v>
+      </c>
+      <c r="I19" s="107" t="s">
+        <v>352</v>
+      </c>
+      <c r="J19" s="107" t="s">
+        <v>353</v>
+      </c>
+      <c r="K19" s="108" t="s">
+        <v>270</v>
+      </c>
+      <c r="L19" s="107">
         <v>1</v>
       </c>
-      <c r="K19" s="93">
+      <c r="M19" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L19" s="93"/>
-    </row>
-    <row r="20" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N19" s="109">
+        <v>50</v>
+      </c>
+      <c r="O19" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P19" s="109">
+        <v>5.3E-3</v>
+      </c>
+      <c r="Q19" s="109">
+        <f t="shared" ref="Q19" si="8">P19*N19</f>
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="R19" s="109"/>
+    </row>
+    <row r="20" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="87" t="s">
-        <v>281</v>
-      </c>
-      <c r="D20" s="88" t="s">
+      <c r="C20" s="102" t="s">
+        <v>316</v>
+      </c>
+      <c r="D20" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="89" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G20" s="88" t="s">
-        <v>132</v>
-      </c>
-      <c r="H20" s="88" t="s">
-        <v>204</v>
-      </c>
-      <c r="I20" s="89" t="s">
-        <v>227</v>
-      </c>
-      <c r="J20" s="88">
+      <c r="E20" s="104" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G20" s="103" t="s">
+        <v>146</v>
+      </c>
+      <c r="H20" s="103" t="s">
+        <v>234</v>
+      </c>
+      <c r="I20" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J20" s="103" t="s">
+        <v>354</v>
+      </c>
+      <c r="K20" s="104" t="s">
+        <v>261</v>
+      </c>
+      <c r="L20" s="103">
         <v>1</v>
       </c>
-      <c r="K20" s="82">
+      <c r="M20" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L20" s="82"/>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="96">
+        <v>22</v>
+      </c>
+      <c r="O20" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P20" s="96">
+        <v>0.22189999999999999</v>
+      </c>
+      <c r="Q20" s="96">
+        <f t="shared" ref="Q20" si="9">N20*P20</f>
+        <v>4.8818000000000001</v>
+      </c>
+      <c r="R20" s="96"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="90" t="s">
-        <v>281</v>
-      </c>
-      <c r="D21" s="91" t="s">
+      <c r="C21" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="D21" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="92" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="91" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="92" t="s">
-        <v>165</v>
-      </c>
-      <c r="H21" s="91" t="s">
-        <v>198</v>
-      </c>
-      <c r="I21" s="92" t="s">
-        <v>237</v>
-      </c>
-      <c r="J21" s="91">
+      <c r="E21" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="107" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="108" t="s">
+        <v>190</v>
+      </c>
+      <c r="H21" s="107" t="s">
+        <v>228</v>
+      </c>
+      <c r="I21" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J21" s="107" t="s">
+        <v>355</v>
+      </c>
+      <c r="K21" s="108" t="s">
+        <v>271</v>
+      </c>
+      <c r="L21" s="107">
         <v>2</v>
       </c>
-      <c r="K21" s="93">
+      <c r="M21" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L21" s="93"/>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N21" s="109">
+        <v>50</v>
+      </c>
+      <c r="O21" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P21" s="109">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="Q21" s="109">
+        <f t="shared" ref="Q21" si="10">P21*N21</f>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="R21" s="109"/>
+    </row>
+    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="I22" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="J22" s="37">
+      <c r="I22" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="K22" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="L22" s="37">
         <v>1</v>
       </c>
-      <c r="K22" s="41">
+      <c r="M22" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L22" s="41"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N22" s="41">
+        <v>40</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P22" s="41">
+        <v>3.49E-2</v>
+      </c>
+      <c r="Q22" s="41">
+        <f t="shared" ref="Q22" si="11">P22*N22</f>
+        <v>1.3959999999999999</v>
+      </c>
+      <c r="R22" s="41"/>
+    </row>
+    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>320</v>
+        <v>428</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="J23" s="39">
+        <v>228</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J23" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="L23" s="39">
         <v>1</v>
       </c>
-      <c r="K23" s="42">
+      <c r="M23" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L23" s="68"/>
-    </row>
-    <row r="24" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N23" s="42">
+        <v>40</v>
+      </c>
+      <c r="O23" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P23" s="42">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="Q23" s="42">
+        <f t="shared" ref="Q23" si="12">N23*P23</f>
+        <v>0.7679999999999999</v>
+      </c>
+      <c r="R23" s="77"/>
+    </row>
+    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D24" s="37" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>369</v>
+        <v>81</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>303</v>
+        <v>144</v>
+      </c>
+      <c r="G24" s="65">
+        <v>885012205080</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="J24" s="37">
+        <v>235</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="K24" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="L24" s="37">
         <v>1</v>
       </c>
-      <c r="K24" s="41">
+      <c r="M24" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L24" s="41"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N24" s="41">
+        <v>50</v>
+      </c>
+      <c r="O24" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P24" s="41">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="Q24" s="41">
+        <f t="shared" ref="Q24" si="13">P24*N24</f>
+        <v>0.26</v>
+      </c>
+      <c r="R24" s="41"/>
+    </row>
+    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D25" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="H25" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="I25" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="J25" s="39">
+        <v>229</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J25" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="K25" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="L25" s="39">
         <v>1</v>
       </c>
-      <c r="K25" s="42">
+      <c r="M25" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L25" s="42"/>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N25" s="42">
+        <v>100</v>
+      </c>
+      <c r="O25" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P25" s="42">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="Q25" s="42">
+        <f t="shared" ref="Q25" si="14">N25*P25</f>
+        <v>0.32</v>
+      </c>
+      <c r="R25" s="42"/>
+    </row>
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="87" t="s">
-        <v>281</v>
-      </c>
-      <c r="D26" s="88" t="s">
+      <c r="C26" s="102" t="s">
+        <v>316</v>
+      </c>
+      <c r="D26" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="94" t="s">
-        <v>322</v>
-      </c>
-      <c r="F26" s="88" t="s">
-        <v>129</v>
-      </c>
-      <c r="G26" s="94" t="s">
-        <v>344</v>
-      </c>
-      <c r="H26" s="95" t="s">
-        <v>217</v>
-      </c>
-      <c r="I26" s="94" t="s">
-        <v>331</v>
-      </c>
-      <c r="J26" s="88">
+      <c r="E26" s="111" t="s">
+        <v>430</v>
+      </c>
+      <c r="F26" s="103" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="111" t="s">
+        <v>456</v>
+      </c>
+      <c r="H26" s="112" t="s">
+        <v>249</v>
+      </c>
+      <c r="I26" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J26" s="103" t="s">
+        <v>431</v>
+      </c>
+      <c r="K26" s="111" t="s">
+        <v>443</v>
+      </c>
+      <c r="L26" s="103">
         <v>1</v>
       </c>
-      <c r="K26" s="82">
+      <c r="M26" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L26" s="67"/>
-    </row>
-    <row r="27" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N26" s="96">
+        <v>100</v>
+      </c>
+      <c r="O26" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P26" s="96">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="Q26" s="96">
+        <f t="shared" ref="Q26" si="15">N26*P26</f>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R26" s="76"/>
+    </row>
+    <row r="27" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="90" t="s">
-        <v>281</v>
-      </c>
-      <c r="D27" s="91" t="s">
-        <v>330</v>
-      </c>
-      <c r="E27" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="91" t="s">
-        <v>133</v>
-      </c>
-      <c r="G27" s="92" t="s">
-        <v>169</v>
-      </c>
-      <c r="H27" s="91" t="s">
-        <v>201</v>
-      </c>
-      <c r="I27" s="92" t="s">
-        <v>241</v>
-      </c>
-      <c r="J27" s="91">
+      <c r="C27" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="D27" s="107" t="s">
+        <v>442</v>
+      </c>
+      <c r="E27" s="108" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="G27" s="108" t="s">
+        <v>194</v>
+      </c>
+      <c r="H27" s="107" t="s">
+        <v>231</v>
+      </c>
+      <c r="I27" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J27" s="107" t="s">
+        <v>362</v>
+      </c>
+      <c r="K27" s="108" t="s">
+        <v>275</v>
+      </c>
+      <c r="L27" s="107">
         <v>1</v>
       </c>
-      <c r="K27" s="93">
+      <c r="M27" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L27" s="70"/>
-    </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N27" s="109">
+        <v>30</v>
+      </c>
+      <c r="O27" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P27" s="109">
+        <v>0.2525</v>
+      </c>
+      <c r="Q27" s="109">
+        <f t="shared" ref="Q27" si="16">P27*N27</f>
+        <v>7.5750000000000002</v>
+      </c>
+      <c r="R27" s="79"/>
+    </row>
+    <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D28" s="37" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="I28" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="J28" s="37">
+        <v>232</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>276</v>
+      </c>
+      <c r="L28" s="37">
         <v>1</v>
       </c>
-      <c r="K28" s="41">
+      <c r="M28" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L28" s="41"/>
-    </row>
-    <row r="29" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N28" s="41">
+        <v>22</v>
+      </c>
+      <c r="O28" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P28" s="41">
+        <v>0.89629999999999999</v>
+      </c>
+      <c r="Q28" s="41">
+        <f t="shared" ref="Q28" si="17">P28*N28</f>
+        <v>19.718599999999999</v>
+      </c>
+      <c r="R28" s="41"/>
+    </row>
+    <row r="29" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C29" s="59" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D29" s="39" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="G29" s="39" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="H29" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="I29" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="J29" s="39">
+        <v>236</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J29" s="39" t="s">
+        <v>364</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="L29" s="39">
         <v>1</v>
       </c>
-      <c r="K29" s="42">
+      <c r="M29" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L29" s="42"/>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="42">
+        <v>21</v>
+      </c>
+      <c r="O29" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P29" s="42">
+        <v>0.47249999999999998</v>
+      </c>
+      <c r="Q29" s="42">
+        <f t="shared" ref="Q29" si="18">N29*P29</f>
+        <v>9.9224999999999994</v>
+      </c>
+      <c r="R29" s="42"/>
+    </row>
+    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="D30" s="37" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="I30" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="J30" s="37">
+        <v>229</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="L30" s="37">
         <v>1</v>
       </c>
-      <c r="K30" s="41">
+      <c r="M30" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L30" s="41"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="41">
+        <v>100</v>
+      </c>
+      <c r="O30" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P30" s="41">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="Q30" s="41">
+        <f t="shared" ref="Q30" si="19">P30*N30</f>
+        <v>0.31</v>
+      </c>
+      <c r="R30" s="41"/>
+    </row>
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="90" t="s">
-        <v>281</v>
-      </c>
-      <c r="D31" s="91" t="s">
+      <c r="C31" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="D31" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="92" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="91" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" s="92" t="s">
-        <v>172</v>
-      </c>
-      <c r="H31" s="91" t="s">
-        <v>198</v>
-      </c>
-      <c r="I31" s="92" t="s">
-        <v>245</v>
-      </c>
-      <c r="J31" s="91">
+      <c r="E31" s="108" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="107" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="108" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31" s="107" t="s">
+        <v>228</v>
+      </c>
+      <c r="I31" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J31" s="107" t="s">
+        <v>366</v>
+      </c>
+      <c r="K31" s="108" t="s">
+        <v>279</v>
+      </c>
+      <c r="L31" s="107">
         <v>4</v>
       </c>
-      <c r="K31" s="93">
+      <c r="M31" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L31" s="93"/>
-    </row>
-    <row r="32" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N31" s="109">
+        <v>100</v>
+      </c>
+      <c r="O31" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P31" s="109">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="Q31" s="109">
+        <f t="shared" ref="Q31" si="20">P31*N31</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="R31" s="109"/>
+    </row>
+    <row r="32" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="87" t="s">
-        <v>282</v>
-      </c>
-      <c r="D32" s="88" t="s">
+      <c r="C32" s="102" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="89" t="s">
-        <v>85</v>
-      </c>
-      <c r="F32" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G32" s="89" t="s">
-        <v>136</v>
-      </c>
-      <c r="H32" s="88" t="s">
-        <v>207</v>
-      </c>
-      <c r="I32" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J32" s="88">
+      <c r="E32" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G32" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="103" t="s">
+        <v>237</v>
+      </c>
+      <c r="I32" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J32" s="103" t="s">
+        <v>367</v>
+      </c>
+      <c r="K32" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L32" s="103">
         <v>1</v>
       </c>
-      <c r="K32" s="82">
+      <c r="M32" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L32" s="82"/>
-    </row>
-    <row r="33" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N32" s="96">
+        <v>30</v>
+      </c>
+      <c r="O32" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P32" s="96">
+        <v>4.87E-2</v>
+      </c>
+      <c r="Q32" s="96">
+        <f t="shared" ref="Q32" si="21">N32*P32</f>
+        <v>1.4610000000000001</v>
+      </c>
+      <c r="R32" s="96"/>
+    </row>
+    <row r="33" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="90" t="s">
-        <v>282</v>
-      </c>
-      <c r="D33" s="91" t="s">
+      <c r="C33" s="106" t="s">
+        <v>317</v>
+      </c>
+      <c r="D33" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="92" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="91" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" s="92" t="s">
-        <v>246</v>
-      </c>
-      <c r="H33" s="91" t="s">
-        <v>208</v>
-      </c>
-      <c r="I33" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J33" s="91">
+      <c r="E33" s="108" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="107" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" s="108" t="s">
+        <v>280</v>
+      </c>
+      <c r="H33" s="107" t="s">
+        <v>238</v>
+      </c>
+      <c r="I33" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J33" s="107" t="s">
+        <v>368</v>
+      </c>
+      <c r="K33" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L33" s="107">
         <v>1</v>
       </c>
-      <c r="K33" s="93">
+      <c r="M33" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L33" s="93"/>
-    </row>
-    <row r="34" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N33" s="109">
+        <v>30</v>
+      </c>
+      <c r="O33" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P33" s="109">
+        <v>7.4300000000000005E-2</v>
+      </c>
+      <c r="Q33" s="109">
+        <f t="shared" ref="Q33" si="22">P33*N33</f>
+        <v>2.2290000000000001</v>
+      </c>
+      <c r="R33" s="109"/>
+    </row>
+    <row r="34" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="87" t="s">
-        <v>282</v>
-      </c>
-      <c r="D34" s="88" t="s">
-        <v>349</v>
-      </c>
-      <c r="E34" s="89" t="s">
-        <v>372</v>
-      </c>
-      <c r="F34" s="88" t="s">
-        <v>371</v>
-      </c>
-      <c r="G34" s="88" t="s">
-        <v>247</v>
-      </c>
-      <c r="H34" s="88" t="s">
-        <v>370</v>
-      </c>
-      <c r="I34" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J34" s="88">
+      <c r="C34" s="102" t="s">
+        <v>317</v>
+      </c>
+      <c r="D34" s="103" t="s">
+        <v>461</v>
+      </c>
+      <c r="E34" s="104" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="103" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" s="104" t="s">
+        <v>281</v>
+      </c>
+      <c r="H34" s="103" t="s">
+        <v>238</v>
+      </c>
+      <c r="I34" s="103" t="s">
+        <v>281</v>
+      </c>
+      <c r="J34" s="103" t="s">
+        <v>369</v>
+      </c>
+      <c r="K34" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L34" s="103">
         <v>2</v>
       </c>
-      <c r="K34" s="82">
+      <c r="M34" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L34" s="69"/>
-    </row>
-    <row r="35" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N34" s="96">
+        <v>60</v>
+      </c>
+      <c r="O34" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P34" s="96">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="Q34" s="96">
+        <f t="shared" ref="Q34" si="23">N34*P34</f>
+        <v>1.734</v>
+      </c>
+      <c r="R34" s="78"/>
+    </row>
+    <row r="35" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="77" t="s">
-        <v>282</v>
-      </c>
-      <c r="D35" s="78" t="s">
-        <v>332</v>
-      </c>
-      <c r="E35" s="79" t="s">
-        <v>374</v>
-      </c>
-      <c r="F35" s="78" t="s">
-        <v>373</v>
-      </c>
-      <c r="G35" s="79" t="s">
-        <v>304</v>
-      </c>
-      <c r="H35" s="78" t="s">
-        <v>209</v>
-      </c>
-      <c r="I35" s="79" t="s">
-        <v>279</v>
-      </c>
-      <c r="J35" s="80">
+      <c r="C35" s="89" t="s">
+        <v>317</v>
+      </c>
+      <c r="D35" s="90" t="s">
+        <v>444</v>
+      </c>
+      <c r="E35" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="90" t="s">
+        <v>152</v>
+      </c>
+      <c r="G35" s="91" t="s">
+        <v>198</v>
+      </c>
+      <c r="H35" s="90" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" s="90" t="s">
+        <v>370</v>
+      </c>
+      <c r="J35" s="90" t="s">
+        <v>371</v>
+      </c>
+      <c r="K35" s="91" t="s">
+        <v>314</v>
+      </c>
+      <c r="L35" s="92">
         <v>8</v>
       </c>
-      <c r="K35" s="81">
+      <c r="M35" s="93">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="L35" s="74" t="s">
-        <v>333</v>
-      </c>
-      <c r="O35" s="99"/>
-    </row>
-    <row r="36" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N35" s="94">
+        <v>170</v>
+      </c>
+      <c r="O35" s="95" t="s">
+        <v>343</v>
+      </c>
+      <c r="P35" s="93">
+        <v>0.12590000000000001</v>
+      </c>
+      <c r="Q35" s="93">
+        <f t="shared" ref="Q35" si="24">P35*N35</f>
+        <v>21.403000000000002</v>
+      </c>
+      <c r="R35" s="84" t="s">
+        <v>445</v>
+      </c>
+      <c r="U35" s="119"/>
+    </row>
+    <row r="36" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="87" t="s">
-        <v>284</v>
-      </c>
-      <c r="D36" s="88" t="s">
+      <c r="C36" s="102" t="s">
+        <v>319</v>
+      </c>
+      <c r="D36" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="89" t="s">
-        <v>376</v>
-      </c>
-      <c r="F36" s="88">
-        <v>1206</v>
-      </c>
-      <c r="G36" s="88" t="s">
-        <v>305</v>
-      </c>
-      <c r="H36" s="88" t="s">
-        <v>375</v>
-      </c>
-      <c r="I36" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J36" s="88">
+      <c r="E36" s="104" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G36" s="104" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="I36" s="103" t="s">
+        <v>372</v>
+      </c>
+      <c r="J36" s="103" t="s">
+        <v>373</v>
+      </c>
+      <c r="K36" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L36" s="103">
         <v>1</v>
       </c>
-      <c r="K36" s="82">
+      <c r="M36" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L36" s="82"/>
-    </row>
-    <row r="37" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N36" s="96">
+        <v>30</v>
+      </c>
+      <c r="O36" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P36" s="96">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="Q36" s="96">
+        <f t="shared" ref="Q36" si="25">N36*P36</f>
+        <v>1.68</v>
+      </c>
+      <c r="R36" s="96"/>
+    </row>
+    <row r="37" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="90" t="s">
-        <v>283</v>
-      </c>
-      <c r="D37" s="91" t="s">
+      <c r="C37" s="106" t="s">
+        <v>318</v>
+      </c>
+      <c r="D37" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="92" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="91" t="s">
-        <v>275</v>
-      </c>
-      <c r="G37" s="92" t="s">
-        <v>138</v>
-      </c>
-      <c r="H37" s="91" t="s">
-        <v>203</v>
-      </c>
-      <c r="I37" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J37" s="91">
+      <c r="E37" s="108" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="107" t="s">
+        <v>309</v>
+      </c>
+      <c r="G37" s="108" t="s">
+        <v>154</v>
+      </c>
+      <c r="H37" s="107" t="s">
+        <v>233</v>
+      </c>
+      <c r="I37" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J37" s="107" t="s">
+        <v>374</v>
+      </c>
+      <c r="K37" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L37" s="107">
         <v>4</v>
       </c>
-      <c r="K37" s="93">
+      <c r="M37" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L37" s="93"/>
-    </row>
-    <row r="38" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N37" s="109">
+        <v>100</v>
+      </c>
+      <c r="O37" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P37" s="109">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="Q37" s="109">
+        <f t="shared" ref="Q37" si="26">P37*N37</f>
+        <v>2.9499999999999997</v>
+      </c>
+      <c r="R37" s="109"/>
+    </row>
+    <row r="38" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="D38" s="88" t="s">
+      <c r="C38" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="D38" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="89" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G38" s="89" t="s">
-        <v>306</v>
-      </c>
-      <c r="H38" s="88" t="s">
-        <v>210</v>
-      </c>
-      <c r="I38" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J38" s="88">
+      <c r="E38" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G38" s="104" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="103" t="s">
+        <v>241</v>
+      </c>
+      <c r="I38" s="103" t="s">
+        <v>375</v>
+      </c>
+      <c r="J38" s="103" t="s">
+        <v>376</v>
+      </c>
+      <c r="K38" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L38" s="103">
         <v>1</v>
       </c>
-      <c r="K38" s="82">
+      <c r="M38" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L38" s="69"/>
-    </row>
-    <row r="39" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N38" s="96">
+        <v>21</v>
+      </c>
+      <c r="O38" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P38" s="96">
+        <v>0.53559999999999997</v>
+      </c>
+      <c r="Q38" s="96">
+        <f t="shared" ref="Q38" si="27">N38*P38</f>
+        <v>11.247599999999998</v>
+      </c>
+      <c r="R38" s="78"/>
+    </row>
+    <row r="39" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="90" t="s">
-        <v>285</v>
-      </c>
-      <c r="D39" s="91" t="s">
+      <c r="C39" s="106" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="92" t="s">
+      <c r="E39" s="108" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="G39" s="108" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" s="107" t="s">
+        <v>242</v>
+      </c>
+      <c r="I39" s="107" t="s">
         <v>377</v>
       </c>
-      <c r="F39" s="91" t="s">
-        <v>274</v>
-      </c>
-      <c r="G39" s="92" t="s">
-        <v>307</v>
-      </c>
-      <c r="H39" s="91" t="s">
-        <v>211</v>
-      </c>
-      <c r="I39" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J39" s="91">
+      <c r="J39" s="107" t="s">
+        <v>378</v>
+      </c>
+      <c r="K39" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L39" s="107">
         <v>2</v>
       </c>
-      <c r="K39" s="93">
+      <c r="M39" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L39" s="70"/>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N39" s="109">
+        <v>42</v>
+      </c>
+      <c r="O39" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P39" s="109">
+        <v>0.65639999999999998</v>
+      </c>
+      <c r="Q39" s="109">
+        <f t="shared" ref="Q39" si="28">P39*N39</f>
+        <v>27.5688</v>
+      </c>
+      <c r="R39" s="79"/>
+    </row>
+    <row r="40" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="87" t="s">
-        <v>286</v>
-      </c>
-      <c r="D40" s="88" t="s">
+      <c r="C40" s="102" t="s">
+        <v>321</v>
+      </c>
+      <c r="D40" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G40" s="89" t="s">
-        <v>139</v>
-      </c>
-      <c r="H40" s="88" t="s">
-        <v>212</v>
-      </c>
-      <c r="I40" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J40" s="88">
+      <c r="E40" s="104" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G40" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="H40" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="I40" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J40" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K40" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L40" s="103">
         <v>1</v>
       </c>
-      <c r="K40" s="82">
+      <c r="M40" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L40" s="82"/>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N40" s="96">
+        <v>21</v>
+      </c>
+      <c r="O40" s="105" t="s">
+        <v>379</v>
+      </c>
+      <c r="P40" s="96">
+        <v>1.2</v>
+      </c>
+      <c r="Q40" s="96">
+        <f t="shared" ref="Q40" si="29">N40*P40</f>
+        <v>25.2</v>
+      </c>
+      <c r="R40" s="96"/>
+    </row>
+    <row r="41" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="90" t="s">
-        <v>286</v>
-      </c>
-      <c r="D41" s="91" t="s">
+      <c r="C41" s="106" t="s">
+        <v>321</v>
+      </c>
+      <c r="D41" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="F41" s="91" t="s">
-        <v>274</v>
-      </c>
-      <c r="G41" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="H41" s="91" t="s">
-        <v>213</v>
-      </c>
-      <c r="I41" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J41" s="91">
+      <c r="E41" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="G41" s="108" t="s">
+        <v>158</v>
+      </c>
+      <c r="H41" s="107" t="s">
+        <v>244</v>
+      </c>
+      <c r="I41" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J41" s="107" t="s">
+        <v>380</v>
+      </c>
+      <c r="K41" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L41" s="107">
         <v>1</v>
       </c>
-      <c r="K41" s="93">
+      <c r="M41" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L41" s="93"/>
-    </row>
-    <row r="42" spans="1:15" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N41" s="109">
+        <v>25</v>
+      </c>
+      <c r="O41" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P41" s="109">
+        <v>9.2200000000000004E-2</v>
+      </c>
+      <c r="Q41" s="109">
+        <f t="shared" ref="Q41" si="30">P41*N41</f>
+        <v>2.3050000000000002</v>
+      </c>
+      <c r="R41" s="109"/>
+    </row>
+    <row r="42" spans="1:21" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="53"/>
-      <c r="C42" s="90" t="s">
-        <v>286</v>
-      </c>
-      <c r="D42" s="91" t="s">
-        <v>362</v>
-      </c>
-      <c r="E42" s="92" t="s">
-        <v>364</v>
-      </c>
-      <c r="F42" s="91" t="s">
-        <v>274</v>
-      </c>
-      <c r="G42" s="92" t="s">
-        <v>363</v>
-      </c>
-      <c r="H42" s="91" t="s">
-        <v>365</v>
-      </c>
-      <c r="I42" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J42" s="91">
+      <c r="C42" s="106" t="s">
+        <v>321</v>
+      </c>
+      <c r="D42" s="107" t="s">
+        <v>474</v>
+      </c>
+      <c r="E42" s="108" t="s">
+        <v>476</v>
+      </c>
+      <c r="F42" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="G42" s="108" t="s">
+        <v>475</v>
+      </c>
+      <c r="H42" s="107" t="s">
+        <v>477</v>
+      </c>
+      <c r="I42" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J42" s="107" t="s">
+        <v>478</v>
+      </c>
+      <c r="K42" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L42" s="107">
         <v>1</v>
       </c>
-      <c r="K42" s="93">
+      <c r="M42" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L42" s="93"/>
-    </row>
-    <row r="43" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N42" s="109">
+        <v>25</v>
+      </c>
+      <c r="O42" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P42" s="109">
+        <v>0.21210000000000001</v>
+      </c>
+      <c r="Q42" s="109">
+        <f>P42*N42</f>
+        <v>5.3025000000000002</v>
+      </c>
+      <c r="R42" s="109"/>
+    </row>
+    <row r="43" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="53">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="87" t="s">
-        <v>283</v>
-      </c>
-      <c r="D43" s="88" t="s">
+      <c r="C43" s="102" t="s">
+        <v>318</v>
+      </c>
+      <c r="D43" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="F43" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G43" s="89" t="s">
-        <v>141</v>
-      </c>
-      <c r="H43" s="88" t="s">
-        <v>203</v>
-      </c>
-      <c r="I43" s="89" t="s">
-        <v>248</v>
-      </c>
-      <c r="J43" s="88">
+      <c r="E43" s="104" t="s">
+        <v>98</v>
+      </c>
+      <c r="F43" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G43" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="H43" s="103" t="s">
+        <v>233</v>
+      </c>
+      <c r="I43" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J43" s="103" t="s">
+        <v>381</v>
+      </c>
+      <c r="K43" s="104" t="s">
+        <v>282</v>
+      </c>
+      <c r="L43" s="103">
         <v>1</v>
       </c>
-      <c r="K43" s="82">
+      <c r="M43" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L43" s="82"/>
-    </row>
-    <row r="44" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N43" s="96">
+        <v>21</v>
+      </c>
+      <c r="O43" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P43" s="96">
+        <v>0.45629999999999998</v>
+      </c>
+      <c r="Q43" s="96">
+        <f t="shared" ref="Q43" si="31">N43*P43</f>
+        <v>9.5823</v>
+      </c>
+      <c r="R43" s="96"/>
+    </row>
+    <row r="44" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="90" t="s">
-        <v>283</v>
-      </c>
-      <c r="D44" s="91" t="s">
+      <c r="C44" s="106" t="s">
+        <v>318</v>
+      </c>
+      <c r="D44" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="92" t="s">
-        <v>336</v>
-      </c>
-      <c r="F44" s="91" t="s">
-        <v>274</v>
-      </c>
-      <c r="G44" s="92" t="s">
-        <v>335</v>
-      </c>
-      <c r="H44" s="91" t="s">
-        <v>325</v>
-      </c>
-      <c r="I44" s="92" t="s">
-        <v>334</v>
-      </c>
-      <c r="J44" s="91">
+      <c r="E44" s="108" t="s">
+        <v>448</v>
+      </c>
+      <c r="F44" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="G44" s="108" t="s">
+        <v>447</v>
+      </c>
+      <c r="H44" s="107" t="s">
+        <v>436</v>
+      </c>
+      <c r="I44" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J44" s="107" t="s">
+        <v>437</v>
+      </c>
+      <c r="K44" s="108" t="s">
+        <v>446</v>
+      </c>
+      <c r="L44" s="107">
         <v>1</v>
       </c>
-      <c r="K44" s="93">
+      <c r="M44" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L44" s="68"/>
-    </row>
-    <row r="45" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N44" s="109">
+        <v>25</v>
+      </c>
+      <c r="O44" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P44" s="109">
+        <v>0.1012</v>
+      </c>
+      <c r="Q44" s="109">
+        <f t="shared" ref="Q44" si="32">P44*N44</f>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="R44" s="77"/>
+    </row>
+    <row r="45" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="87" t="s">
-        <v>287</v>
-      </c>
-      <c r="D45" s="88" t="s">
+      <c r="C45" s="102" t="s">
+        <v>322</v>
+      </c>
+      <c r="D45" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G45" s="89" t="s">
-        <v>142</v>
-      </c>
-      <c r="H45" s="88" t="s">
-        <v>214</v>
-      </c>
-      <c r="I45" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J45" s="88">
+      <c r="E45" s="104" t="s">
+        <v>99</v>
+      </c>
+      <c r="F45" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G45" s="104" t="s">
+        <v>160</v>
+      </c>
+      <c r="H45" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="I45" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J45" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K45" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L45" s="103">
         <v>1</v>
       </c>
-      <c r="K45" s="82">
+      <c r="M45" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L45" s="82"/>
-    </row>
-    <row r="46" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N45" s="96">
+        <v>30</v>
+      </c>
+      <c r="O45" s="105" t="s">
+        <v>382</v>
+      </c>
+      <c r="P45" s="96">
+        <v>0.156</v>
+      </c>
+      <c r="Q45" s="96">
+        <f t="shared" ref="Q45" si="33">N45*P45</f>
+        <v>4.68</v>
+      </c>
+      <c r="R45" s="96"/>
+    </row>
+    <row r="46" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="90" t="s">
-        <v>287</v>
-      </c>
-      <c r="D46" s="91" t="s">
+      <c r="C46" s="106" t="s">
+        <v>322</v>
+      </c>
+      <c r="D46" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="E46" s="92" t="s">
-        <v>93</v>
-      </c>
-      <c r="F46" s="91" t="s">
-        <v>143</v>
-      </c>
-      <c r="G46" s="92" t="s">
-        <v>173</v>
-      </c>
-      <c r="H46" s="91" t="s">
-        <v>215</v>
-      </c>
-      <c r="I46" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J46" s="91">
+      <c r="E46" s="108" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="G46" s="108" t="s">
+        <v>199</v>
+      </c>
+      <c r="H46" s="107" t="s">
+        <v>246</v>
+      </c>
+      <c r="I46" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J46" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K46" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L46" s="107">
         <v>1</v>
       </c>
-      <c r="K46" s="93">
+      <c r="M46" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L46" s="93"/>
-    </row>
-    <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N46" s="109">
+        <v>30</v>
+      </c>
+      <c r="O46" s="110" t="s">
+        <v>383</v>
+      </c>
+      <c r="P46" s="109">
+        <v>0.08</v>
+      </c>
+      <c r="Q46" s="109">
+        <f t="shared" ref="Q46:Q47" si="34">P46*N46</f>
+        <v>2.4</v>
+      </c>
+      <c r="R46" s="109"/>
+    </row>
+    <row r="47" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
-        <f t="shared" ref="B47:B90" si="2">ROW(B47) - ROW($B$9)</f>
+        <f t="shared" ref="B47:B90" si="35">ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="90" t="s">
-        <v>353</v>
-      </c>
-      <c r="D47" s="91" t="s">
-        <v>279</v>
-      </c>
-      <c r="E47" s="92" t="s">
-        <v>355</v>
-      </c>
-      <c r="F47" s="91" t="s">
-        <v>274</v>
-      </c>
-      <c r="G47" s="92" t="s">
-        <v>356</v>
-      </c>
-      <c r="H47" s="91" t="s">
-        <v>357</v>
-      </c>
-      <c r="I47" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J47" s="91">
+      <c r="C47" s="106" t="s">
+        <v>465</v>
+      </c>
+      <c r="D47" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="E47" s="108" t="s">
+        <v>467</v>
+      </c>
+      <c r="F47" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="G47" s="108" t="s">
+        <v>468</v>
+      </c>
+      <c r="H47" s="107" t="s">
+        <v>469</v>
+      </c>
+      <c r="I47" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J47" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K47" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L47" s="107">
         <v>1</v>
       </c>
-      <c r="K47" s="93">
+      <c r="M47" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L47" s="70" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N47" s="109">
+        <v>20</v>
+      </c>
+      <c r="O47" s="110" t="s">
+        <v>419</v>
+      </c>
+      <c r="P47" s="109">
+        <v>0.435</v>
+      </c>
+      <c r="Q47" s="109">
+        <f t="shared" si="34"/>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R47" s="79" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>39</v>
       </c>
-      <c r="C48" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="D48" s="88" t="s">
+      <c r="C48" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="D48" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="E48" s="89" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G48" s="89" t="s">
-        <v>144</v>
-      </c>
-      <c r="H48" s="88" t="s">
-        <v>216</v>
-      </c>
-      <c r="I48" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J48" s="88">
+      <c r="E48" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G48" s="104" t="s">
+        <v>162</v>
+      </c>
+      <c r="H48" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="I48" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J48" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K48" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L48" s="103">
         <v>2</v>
       </c>
-      <c r="K48" s="82">
+      <c r="M48" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L48" s="82"/>
-    </row>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N48" s="96">
+        <v>50</v>
+      </c>
+      <c r="O48" s="105" t="s">
+        <v>379</v>
+      </c>
+      <c r="P48" s="96">
+        <v>1.5</v>
+      </c>
+      <c r="Q48" s="96">
+        <f t="shared" ref="Q48" si="36">N48*P48</f>
+        <v>75</v>
+      </c>
+      <c r="R48" s="96"/>
+    </row>
+    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>40</v>
       </c>
-      <c r="C49" s="83" t="s">
-        <v>249</v>
-      </c>
-      <c r="D49" s="84" t="s">
+      <c r="C49" s="97" t="s">
+        <v>283</v>
+      </c>
+      <c r="D49" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="E49" s="85" t="s">
-        <v>95</v>
-      </c>
-      <c r="F49" s="84" t="s">
-        <v>145</v>
-      </c>
-      <c r="G49" s="85" t="s">
-        <v>279</v>
-      </c>
-      <c r="H49" s="84" t="s">
-        <v>279</v>
-      </c>
-      <c r="I49" s="85" t="s">
-        <v>279</v>
-      </c>
-      <c r="J49" s="84">
+      <c r="E49" s="99" t="s">
+        <v>102</v>
+      </c>
+      <c r="F49" s="98" t="s">
+        <v>163</v>
+      </c>
+      <c r="G49" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H49" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I49" s="98"/>
+      <c r="J49" s="98"/>
+      <c r="K49" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L49" s="98">
         <v>4</v>
       </c>
-      <c r="K49" s="62">
+      <c r="M49" s="66">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L49" s="62" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N49" s="66">
+        <f t="shared" ref="N49" si="37">M49+(M49*0.1)</f>
+        <v>88</v>
+      </c>
+      <c r="O49" s="66"/>
+      <c r="P49" s="66"/>
+      <c r="Q49" s="66">
+        <f t="shared" ref="Q49" si="38">P49*N49</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="66" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>41</v>
       </c>
-      <c r="C50" s="87" t="s">
-        <v>286</v>
-      </c>
-      <c r="D50" s="88" t="s">
+      <c r="C50" s="102" t="s">
+        <v>321</v>
+      </c>
+      <c r="D50" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="89" t="s">
-        <v>96</v>
-      </c>
-      <c r="F50" s="88" t="s">
-        <v>146</v>
-      </c>
-      <c r="G50" s="89">
+      <c r="E50" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="F50" s="103" t="s">
+        <v>164</v>
+      </c>
+      <c r="G50" s="104">
         <v>61300211121</v>
       </c>
-      <c r="H50" s="88" t="s">
-        <v>205</v>
-      </c>
-      <c r="I50" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J50" s="88">
+      <c r="H50" s="103" t="s">
+        <v>235</v>
+      </c>
+      <c r="I50" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J50" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K50" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L50" s="103">
         <v>4</v>
       </c>
-      <c r="K50" s="82">
+      <c r="M50" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L50" s="82"/>
-    </row>
-    <row r="51" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N50" s="96">
+        <v>90</v>
+      </c>
+      <c r="O50" s="105" t="s">
+        <v>379</v>
+      </c>
+      <c r="P50" s="96">
+        <v>0.13</v>
+      </c>
+      <c r="Q50" s="96">
+        <f t="shared" ref="Q50" si="39">N50*P50</f>
+        <v>11.700000000000001</v>
+      </c>
+      <c r="R50" s="96"/>
+    </row>
+    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>42</v>
       </c>
-      <c r="C51" s="90" t="s">
-        <v>288</v>
-      </c>
-      <c r="D51" s="91" t="s">
-        <v>327</v>
-      </c>
-      <c r="E51" s="92" t="s">
-        <v>380</v>
-      </c>
-      <c r="F51" s="91" t="s">
-        <v>379</v>
-      </c>
-      <c r="G51" s="91" t="s">
-        <v>309</v>
-      </c>
-      <c r="H51" s="91" t="s">
-        <v>378</v>
-      </c>
-      <c r="I51" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J51" s="91">
+      <c r="C51" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="D51" s="107" t="s">
+        <v>439</v>
+      </c>
+      <c r="E51" s="108" t="s">
+        <v>104</v>
+      </c>
+      <c r="F51" s="107" t="s">
+        <v>165</v>
+      </c>
+      <c r="G51" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="H51" s="107" t="s">
+        <v>248</v>
+      </c>
+      <c r="I51" s="107" t="s">
+        <v>385</v>
+      </c>
+      <c r="J51" s="107" t="s">
+        <v>386</v>
+      </c>
+      <c r="K51" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L51" s="107">
         <v>4</v>
       </c>
-      <c r="K51" s="93">
+      <c r="M51" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L51" s="93"/>
-    </row>
-    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N51" s="109">
+        <v>85</v>
+      </c>
+      <c r="O51" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P51" s="109">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q51" s="109">
+        <f t="shared" ref="Q51" si="40">P51*N51</f>
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R51" s="109"/>
+    </row>
+    <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>43</v>
       </c>
-      <c r="C52" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="D52" s="88" t="s">
+      <c r="C52" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D52" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="E52" s="89" t="s">
-        <v>97</v>
-      </c>
-      <c r="F52" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="G52" s="89" t="s">
-        <v>174</v>
-      </c>
-      <c r="H52" s="88" t="s">
-        <v>199</v>
-      </c>
-      <c r="I52" s="89" t="s">
-        <v>250</v>
-      </c>
-      <c r="J52" s="88">
+      <c r="E52" s="104" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G52" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="H52" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I52" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J52" s="103" t="s">
+        <v>387</v>
+      </c>
+      <c r="K52" s="104" t="s">
+        <v>284</v>
+      </c>
+      <c r="L52" s="103">
         <v>2</v>
       </c>
-      <c r="K52" s="82">
+      <c r="M52" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L52" s="82"/>
-    </row>
-    <row r="53" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N52" s="96">
+        <v>100</v>
+      </c>
+      <c r="O52" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P52" s="96">
+        <v>1E-3</v>
+      </c>
+      <c r="Q52" s="96">
+        <f t="shared" ref="Q52" si="41">N52*P52</f>
+        <v>0.1</v>
+      </c>
+      <c r="R52" s="96"/>
+    </row>
+    <row r="53" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>44</v>
       </c>
-      <c r="C53" s="90" t="s">
-        <v>289</v>
-      </c>
-      <c r="D53" s="91" t="s">
+      <c r="C53" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D53" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="E53" s="92" t="s">
-        <v>98</v>
-      </c>
-      <c r="F53" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="G53" s="92" t="s">
-        <v>175</v>
-      </c>
-      <c r="H53" s="91" t="s">
-        <v>199</v>
-      </c>
-      <c r="I53" s="92" t="s">
-        <v>251</v>
-      </c>
-      <c r="J53" s="91">
+      <c r="E53" s="108" t="s">
+        <v>106</v>
+      </c>
+      <c r="F53" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G53" s="108" t="s">
+        <v>202</v>
+      </c>
+      <c r="H53" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="I53" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J53" s="107" t="s">
+        <v>388</v>
+      </c>
+      <c r="K53" s="108" t="s">
+        <v>285</v>
+      </c>
+      <c r="L53" s="107">
         <v>1</v>
       </c>
-      <c r="K53" s="93">
+      <c r="M53" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L53" s="93"/>
-    </row>
-    <row r="54" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N53" s="109">
+        <v>100</v>
+      </c>
+      <c r="O53" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P53" s="109">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q53" s="109">
+        <f t="shared" ref="Q53" si="42">P53*N53</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R53" s="109"/>
+    </row>
+    <row r="54" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>45</v>
       </c>
-      <c r="C54" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="D54" s="88" t="s">
+      <c r="C54" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D54" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="E54" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="F54" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="G54" s="89" t="s">
-        <v>176</v>
-      </c>
-      <c r="H54" s="88" t="s">
-        <v>217</v>
-      </c>
-      <c r="I54" s="89" t="s">
-        <v>252</v>
-      </c>
-      <c r="J54" s="88">
+      <c r="E54" s="104" t="s">
+        <v>107</v>
+      </c>
+      <c r="F54" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="H54" s="103" t="s">
+        <v>249</v>
+      </c>
+      <c r="I54" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J54" s="103" t="s">
+        <v>389</v>
+      </c>
+      <c r="K54" s="104" t="s">
+        <v>286</v>
+      </c>
+      <c r="L54" s="103">
         <v>1</v>
       </c>
-      <c r="K54" s="82">
+      <c r="M54" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L54" s="82"/>
-    </row>
-    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N54" s="96">
+        <v>100</v>
+      </c>
+      <c r="O54" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P54" s="96">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q54" s="96">
+        <f t="shared" ref="Q54" si="43">N54*P54</f>
+        <v>0.16</v>
+      </c>
+      <c r="R54" s="96"/>
+    </row>
+    <row r="55" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>46</v>
       </c>
-      <c r="C55" s="90" t="s">
-        <v>289</v>
-      </c>
-      <c r="D55" s="91" t="s">
+      <c r="C55" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D55" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="E55" s="92" t="s">
-        <v>100</v>
-      </c>
-      <c r="F55" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="G55" s="92" t="s">
-        <v>177</v>
-      </c>
-      <c r="H55" s="91" t="s">
-        <v>199</v>
-      </c>
-      <c r="I55" s="92" t="s">
-        <v>253</v>
-      </c>
-      <c r="J55" s="91">
+      <c r="E55" s="108" t="s">
+        <v>108</v>
+      </c>
+      <c r="F55" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" s="108" t="s">
+        <v>204</v>
+      </c>
+      <c r="H55" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="I55" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J55" s="107" t="s">
+        <v>390</v>
+      </c>
+      <c r="K55" s="108" t="s">
+        <v>287</v>
+      </c>
+      <c r="L55" s="107">
         <v>2</v>
       </c>
-      <c r="K55" s="93">
+      <c r="M55" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L55" s="93"/>
-    </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N55" s="109">
+        <v>100</v>
+      </c>
+      <c r="O55" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P55" s="109">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q55" s="109">
+        <f t="shared" ref="Q55" si="44">P55*N55</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R55" s="109"/>
+    </row>
+    <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>47</v>
       </c>
-      <c r="C56" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="D56" s="88" t="s">
+      <c r="C56" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="E56" s="89" t="s">
-        <v>101</v>
-      </c>
-      <c r="F56" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="G56" s="89" t="s">
-        <v>178</v>
-      </c>
-      <c r="H56" s="88" t="s">
-        <v>199</v>
-      </c>
-      <c r="I56" s="89" t="s">
-        <v>254</v>
-      </c>
-      <c r="J56" s="88">
+      <c r="E56" s="104" t="s">
+        <v>109</v>
+      </c>
+      <c r="F56" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G56" s="104" t="s">
+        <v>205</v>
+      </c>
+      <c r="H56" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I56" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J56" s="103" t="s">
+        <v>391</v>
+      </c>
+      <c r="K56" s="104" t="s">
+        <v>288</v>
+      </c>
+      <c r="L56" s="103">
         <v>4</v>
       </c>
-      <c r="K56" s="82">
+      <c r="M56" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L56" s="82"/>
-    </row>
-    <row r="57" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N56" s="96">
+        <v>100</v>
+      </c>
+      <c r="O56" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P56" s="96">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q56" s="96">
+        <f t="shared" ref="Q56" si="45">N56*P56</f>
+        <v>0.13</v>
+      </c>
+      <c r="R56" s="96"/>
+    </row>
+    <row r="57" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>48</v>
       </c>
-      <c r="C57" s="90" t="s">
+      <c r="C57" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D57" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="108" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" s="107" t="s">
+        <v>167</v>
+      </c>
+      <c r="G57" s="108" t="s">
+        <v>329</v>
+      </c>
+      <c r="H57" s="107" t="s">
+        <v>250</v>
+      </c>
+      <c r="I57" s="107" t="s">
+        <v>392</v>
+      </c>
+      <c r="J57" s="107" t="s">
+        <v>393</v>
+      </c>
+      <c r="K57" s="108" t="s">
         <v>289</v>
       </c>
-      <c r="D57" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="E57" s="92" t="s">
-        <v>381</v>
-      </c>
-      <c r="F57" s="91" t="s">
-        <v>148</v>
-      </c>
-      <c r="G57" s="92" t="s">
-        <v>310</v>
-      </c>
-      <c r="H57" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="I57" s="92" t="s">
-        <v>255</v>
-      </c>
-      <c r="J57" s="91">
+      <c r="L57" s="107">
         <v>4</v>
       </c>
-      <c r="K57" s="93">
+      <c r="M57" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L57" s="93"/>
-    </row>
-    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N57" s="109">
+        <v>90</v>
+      </c>
+      <c r="O57" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P57" s="109">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="Q57" s="109">
+        <f t="shared" ref="Q57" si="46">P57*N57</f>
+        <v>5.8049999999999997</v>
+      </c>
+      <c r="R57" s="109"/>
+    </row>
+    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>316</v>
+        <v>423</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>328</v>
+        <v>440</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>318</v>
+        <v>425</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="J58" s="37">
+        <v>314</v>
+      </c>
+      <c r="J58" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="K58" s="37" t="s">
+        <v>427</v>
+      </c>
+      <c r="L58" s="37">
         <v>8</v>
       </c>
-      <c r="K58" s="37">
+      <c r="M58" s="37">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="L58" s="67"/>
-    </row>
-    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N58" s="96">
+        <v>100</v>
+      </c>
+      <c r="O58" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="P58" s="37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q58" s="37">
+        <f t="shared" ref="Q58" si="47">N58*P58</f>
+        <v>0.11</v>
+      </c>
+      <c r="R58" s="76"/>
+    </row>
+    <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>50</v>
       </c>
-      <c r="C59" s="90" t="s">
-        <v>289</v>
-      </c>
-      <c r="D59" s="91" t="s">
+      <c r="C59" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D59" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="92" t="s">
-        <v>103</v>
-      </c>
-      <c r="F59" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="G59" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="H59" s="91" t="s">
-        <v>218</v>
-      </c>
-      <c r="I59" s="92" t="s">
-        <v>257</v>
-      </c>
-      <c r="J59" s="91">
+      <c r="E59" s="108" t="s">
+        <v>112</v>
+      </c>
+      <c r="F59" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G59" s="108" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I59" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K59" s="108" t="s">
+        <v>291</v>
+      </c>
+      <c r="L59" s="107">
         <v>1</v>
       </c>
-      <c r="K59" s="93">
+      <c r="M59" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L59" s="93"/>
-    </row>
-    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N59" s="109">
+        <v>30</v>
+      </c>
+      <c r="O59" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P59" s="109">
+        <v>1.8589999999999999E-2</v>
+      </c>
+      <c r="Q59" s="109">
+        <f t="shared" ref="Q59" si="48">P59*N59</f>
+        <v>0.55769999999999997</v>
+      </c>
+      <c r="R59" s="109"/>
+    </row>
+    <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>51</v>
       </c>
-      <c r="C60" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="D60" s="88" t="s">
+      <c r="C60" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D60" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="F60" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="G60" s="89" t="s">
-        <v>181</v>
-      </c>
-      <c r="H60" s="88" t="s">
-        <v>199</v>
-      </c>
-      <c r="I60" s="89" t="s">
-        <v>258</v>
-      </c>
-      <c r="J60" s="88">
+      <c r="E60" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="F60" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G60" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="H60" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I60" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J60" s="103" t="s">
+        <v>395</v>
+      </c>
+      <c r="K60" s="104" t="s">
+        <v>292</v>
+      </c>
+      <c r="L60" s="103">
         <v>1</v>
       </c>
-      <c r="K60" s="82">
+      <c r="M60" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L60" s="82"/>
-    </row>
-    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N60" s="96">
+        <v>100</v>
+      </c>
+      <c r="O60" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P60" s="96">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q60" s="96">
+        <f t="shared" ref="Q60" si="49">N60*P60</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R60" s="96"/>
+    </row>
+    <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>52</v>
       </c>
-      <c r="C61" s="90" t="s">
-        <v>289</v>
-      </c>
-      <c r="D61" s="91" t="s">
+      <c r="C61" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D61" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="F61" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="G61" s="92" t="s">
-        <v>182</v>
-      </c>
-      <c r="H61" s="91" t="s">
-        <v>218</v>
-      </c>
-      <c r="I61" s="92" t="s">
-        <v>259</v>
-      </c>
-      <c r="J61" s="91">
+      <c r="E61" s="108" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G61" s="108" t="s">
+        <v>209</v>
+      </c>
+      <c r="H61" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I61" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J61" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K61" s="108" t="s">
+        <v>293</v>
+      </c>
+      <c r="L61" s="107">
         <v>1</v>
       </c>
-      <c r="K61" s="93">
+      <c r="M61" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L61" s="93"/>
-    </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N61" s="109">
+        <v>50</v>
+      </c>
+      <c r="O61" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P61" s="109">
+        <v>4.6699999999999997E-3</v>
+      </c>
+      <c r="Q61" s="109">
+        <f t="shared" ref="Q61" si="50">P61*N61</f>
+        <v>0.23349999999999999</v>
+      </c>
+      <c r="R61" s="109"/>
+    </row>
+    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>53</v>
       </c>
-      <c r="C62" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="D62" s="88" t="s">
+      <c r="C62" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D62" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="F62" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="G62" s="89" t="s">
-        <v>183</v>
-      </c>
-      <c r="H62" s="88" t="s">
-        <v>199</v>
-      </c>
-      <c r="I62" s="89" t="s">
-        <v>260</v>
-      </c>
-      <c r="J62" s="88">
+      <c r="E62" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="F62" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G62" s="104" t="s">
+        <v>210</v>
+      </c>
+      <c r="H62" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I62" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="103" t="s">
+        <v>396</v>
+      </c>
+      <c r="K62" s="104" t="s">
+        <v>294</v>
+      </c>
+      <c r="L62" s="103">
         <v>1</v>
       </c>
-      <c r="K62" s="82">
+      <c r="M62" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L62" s="82"/>
-    </row>
-    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N62" s="96">
+        <v>100</v>
+      </c>
+      <c r="O62" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P62" s="96">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q62" s="96">
+        <f t="shared" ref="Q62" si="51">N62*P62</f>
+        <v>0.12</v>
+      </c>
+      <c r="R62" s="96"/>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>54</v>
       </c>
-      <c r="C63" s="90" t="s">
-        <v>289</v>
-      </c>
-      <c r="D63" s="91" t="s">
+      <c r="C63" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D63" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="E63" s="92" t="s">
-        <v>107</v>
-      </c>
-      <c r="F63" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="G63" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="H63" s="91" t="s">
-        <v>218</v>
-      </c>
-      <c r="I63" s="92" t="s">
-        <v>261</v>
-      </c>
-      <c r="J63" s="91">
+      <c r="E63" s="108" t="s">
+        <v>116</v>
+      </c>
+      <c r="F63" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G63" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="H63" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="I63" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K63" s="108" t="s">
+        <v>295</v>
+      </c>
+      <c r="L63" s="107">
         <v>1</v>
       </c>
-      <c r="K63" s="93">
+      <c r="M63" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L63" s="93"/>
-    </row>
-    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N63" s="109">
+        <v>50</v>
+      </c>
+      <c r="O63" s="110" t="s">
+        <v>382</v>
+      </c>
+      <c r="P63" s="109">
+        <v>1.11E-2</v>
+      </c>
+      <c r="Q63" s="109">
+        <f t="shared" ref="Q63" si="52">P63*N63</f>
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="R63" s="109"/>
+    </row>
+    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>55</v>
       </c>
-      <c r="C64" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="D64" s="88" t="s">
+      <c r="C64" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D64" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="E64" s="89" t="s">
-        <v>108</v>
-      </c>
-      <c r="F64" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="G64" s="89" t="s">
-        <v>185</v>
-      </c>
-      <c r="H64" s="88" t="s">
-        <v>199</v>
-      </c>
-      <c r="I64" s="89" t="s">
-        <v>262</v>
-      </c>
-      <c r="J64" s="88">
+      <c r="E64" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="F64" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G64" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="H64" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I64" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J64" s="103" t="s">
+        <v>397</v>
+      </c>
+      <c r="K64" s="104" t="s">
+        <v>296</v>
+      </c>
+      <c r="L64" s="103">
         <v>1</v>
       </c>
-      <c r="K64" s="82">
+      <c r="M64" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L64" s="82"/>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N64" s="96">
+        <v>100</v>
+      </c>
+      <c r="O64" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P64" s="96">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="Q64" s="96">
+        <f t="shared" ref="Q64" si="53">N64*P64</f>
+        <v>0.21</v>
+      </c>
+      <c r="R64" s="96"/>
+    </row>
+    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>56</v>
       </c>
-      <c r="C65" s="90" t="s">
-        <v>289</v>
-      </c>
-      <c r="D65" s="91" t="s">
+      <c r="C65" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D65" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="F65" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="G65" s="92" t="s">
-        <v>186</v>
-      </c>
-      <c r="H65" s="91" t="s">
-        <v>199</v>
-      </c>
-      <c r="I65" s="92" t="s">
-        <v>263</v>
-      </c>
-      <c r="J65" s="91">
+      <c r="E65" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="F65" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G65" s="108" t="s">
+        <v>213</v>
+      </c>
+      <c r="H65" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="I65" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J65" s="107" t="s">
+        <v>398</v>
+      </c>
+      <c r="K65" s="108" t="s">
+        <v>297</v>
+      </c>
+      <c r="L65" s="107">
         <v>1</v>
       </c>
-      <c r="K65" s="93">
+      <c r="M65" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L65" s="93"/>
-    </row>
-    <row r="66" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N65" s="109">
+        <v>100</v>
+      </c>
+      <c r="O65" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P65" s="109">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q65" s="109">
+        <f t="shared" ref="Q65" si="54">P65*N65</f>
+        <v>0.16</v>
+      </c>
+      <c r="R65" s="109"/>
+    </row>
+    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>57</v>
       </c>
-      <c r="C66" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="D66" s="88" t="s">
+      <c r="C66" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D66" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="E66" s="89" t="s">
-        <v>383</v>
-      </c>
-      <c r="F66" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="G66" s="89" t="s">
-        <v>311</v>
-      </c>
-      <c r="H66" s="88" t="s">
-        <v>382</v>
-      </c>
-      <c r="I66" s="89" t="s">
-        <v>264</v>
-      </c>
-      <c r="J66" s="88">
+      <c r="E66" s="104" t="s">
+        <v>119</v>
+      </c>
+      <c r="F66" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="G66" s="104" t="s">
+        <v>214</v>
+      </c>
+      <c r="H66" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="I66" s="103" t="s">
+        <v>399</v>
+      </c>
+      <c r="J66" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="K66" s="104" t="s">
+        <v>298</v>
+      </c>
+      <c r="L66" s="103">
         <v>1</v>
       </c>
-      <c r="K66" s="82">
+      <c r="M66" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L66" s="82"/>
-    </row>
-    <row r="67" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N66" s="96">
+        <v>50</v>
+      </c>
+      <c r="O66" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P66" s="96">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="Q66" s="96">
+        <f t="shared" ref="Q66" si="55">N66*P66</f>
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="R66" s="96"/>
+    </row>
+    <row r="67" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>58</v>
       </c>
-      <c r="C67" s="90" t="s">
-        <v>289</v>
-      </c>
-      <c r="D67" s="91" t="s">
-        <v>350</v>
-      </c>
-      <c r="E67" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="F67" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="G67" s="92" t="s">
-        <v>187</v>
-      </c>
-      <c r="H67" s="91" t="s">
-        <v>199</v>
-      </c>
-      <c r="I67" s="92" t="s">
-        <v>265</v>
-      </c>
-      <c r="J67" s="91">
+      <c r="C67" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D67" s="107" t="s">
+        <v>462</v>
+      </c>
+      <c r="E67" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="F67" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="G67" s="108" t="s">
+        <v>215</v>
+      </c>
+      <c r="H67" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="I67" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J67" s="107" t="s">
+        <v>401</v>
+      </c>
+      <c r="K67" s="108" t="s">
+        <v>299</v>
+      </c>
+      <c r="L67" s="107">
         <v>2</v>
       </c>
-      <c r="K67" s="93">
+      <c r="M67" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L67" s="93"/>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N67" s="109">
+        <v>100</v>
+      </c>
+      <c r="O67" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P67" s="109">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q67" s="109">
+        <f t="shared" ref="Q67" si="56">P67*N67</f>
+        <v>0.11</v>
+      </c>
+      <c r="R67" s="109"/>
+    </row>
+    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D68" s="37" t="s">
         <v>50</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="I68" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="J68" s="37">
+        <v>229</v>
+      </c>
+      <c r="I68" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J68" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="L68" s="37">
         <v>2</v>
       </c>
-      <c r="K68" s="41">
+      <c r="M68" s="41">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L68" s="41"/>
-    </row>
-    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N68" s="41">
+        <v>100</v>
+      </c>
+      <c r="O68" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P68" s="41">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q68" s="41">
+        <f t="shared" ref="Q68" si="57">P68*N68</f>
+        <v>0.15</v>
+      </c>
+      <c r="R68" s="41"/>
+    </row>
+    <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>60</v>
       </c>
       <c r="C69" s="59" t="s">
-        <v>289</v>
-      </c>
-      <c r="D69" s="76" t="s">
-        <v>317</v>
+        <v>324</v>
+      </c>
+      <c r="D69" s="87" t="s">
+        <v>424</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F69" s="39" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G69" s="40" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="H69" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="I69" s="40" t="s">
-        <v>256</v>
-      </c>
-      <c r="J69" s="39">
+        <v>229</v>
+      </c>
+      <c r="I69" s="39"/>
+      <c r="J69" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="L69" s="39">
         <v>1</v>
       </c>
-      <c r="K69" s="42">
-        <f>J69*20</f>
+      <c r="M69" s="42">
+        <f>L69*20</f>
         <v>20</v>
       </c>
-      <c r="L69" s="68"/>
-    </row>
-    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N69" s="42">
+        <v>100</v>
+      </c>
+      <c r="O69" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P69" s="42">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q69" s="42">
+        <f>N69*P69</f>
+        <v>0.15</v>
+      </c>
+      <c r="R69" s="77"/>
+    </row>
+    <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D70" s="37" t="s">
         <v>51</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="I70" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="J70" s="37">
+        <v>229</v>
+      </c>
+      <c r="I70" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J70" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="K70" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="L70" s="37">
         <v>2</v>
       </c>
-      <c r="K70" s="41">
+      <c r="M70" s="41">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L70" s="41"/>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N70" s="41">
+        <v>100</v>
+      </c>
+      <c r="O70" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P70" s="41">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q70" s="41">
+        <f t="shared" ref="Q70" si="58">P70*N70</f>
+        <v>0.15</v>
+      </c>
+      <c r="R70" s="41"/>
+    </row>
+    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>62</v>
       </c>
       <c r="C71" s="59" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D71" s="39" t="s">
         <v>52</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F71" s="39" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G71" s="40" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="H71" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="I71" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="J71" s="39">
+        <v>251</v>
+      </c>
+      <c r="I71" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J71" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K71" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="L71" s="39">
         <v>1</v>
       </c>
-      <c r="K71" s="42">
+      <c r="M71" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L71" s="42"/>
-    </row>
-    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="42">
+        <v>25</v>
+      </c>
+      <c r="O71" s="64" t="s">
+        <v>404</v>
+      </c>
+      <c r="P71" s="42">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="Q71" s="42">
+        <f t="shared" ref="Q71" si="59">N71*P71</f>
+        <v>2.1350000000000002</v>
+      </c>
+      <c r="R71" s="42"/>
+    </row>
+    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D72" s="37" t="s">
         <v>53</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="F72" s="75" t="s">
-        <v>147</v>
+        <v>434</v>
+      </c>
+      <c r="F72" s="86" t="s">
+        <v>166</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>338</v>
+        <v>450</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I72" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="J72" s="37">
+        <v>252</v>
+      </c>
+      <c r="I72" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J72" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="L72" s="37">
         <v>1</v>
       </c>
-      <c r="K72" s="41">
-        <f t="shared" ref="K72:K90" si="3">J72*20</f>
+      <c r="M72" s="41">
+        <f t="shared" ref="M72:M90" si="60">L72*20</f>
         <v>20</v>
       </c>
-      <c r="L72" s="67"/>
-    </row>
-    <row r="73" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N72" s="41">
+        <v>50</v>
+      </c>
+      <c r="O72" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P72" s="41">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q72" s="41">
+        <f t="shared" ref="Q72" si="61">P72*N72</f>
+        <v>0.19</v>
+      </c>
+      <c r="R72" s="76"/>
+    </row>
+    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>64</v>
       </c>
       <c r="C73" s="59" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D73" s="39" t="s">
-        <v>339</v>
+        <v>451</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F73" s="39" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="H73" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="I73" s="40" t="s">
-        <v>272</v>
-      </c>
-      <c r="J73" s="39">
+        <v>229</v>
+      </c>
+      <c r="I73" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J73" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="K73" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="L73" s="39">
         <v>6</v>
       </c>
-      <c r="K73" s="42">
-        <f>J73*20</f>
+      <c r="M73" s="42">
+        <f>L73*20</f>
         <v>120</v>
       </c>
-      <c r="L73" s="68"/>
-    </row>
-    <row r="74" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N73" s="42">
+        <v>200</v>
+      </c>
+      <c r="O73" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P73" s="42">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q73" s="42">
+        <f t="shared" ref="Q73" si="62">N73*P73</f>
+        <v>0.24</v>
+      </c>
+      <c r="R73" s="77"/>
+    </row>
+    <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D74" s="37" t="s">
         <v>54</v>
       </c>
       <c r="E74" s="38" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I74" s="38" t="s">
-        <v>269</v>
-      </c>
-      <c r="J74" s="37">
+        <v>252</v>
+      </c>
+      <c r="I74" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J74" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="L74" s="37">
         <v>1</v>
       </c>
-      <c r="K74" s="41">
-        <f t="shared" si="3"/>
+      <c r="M74" s="41">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L74" s="41"/>
-    </row>
-    <row r="75" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N74" s="41">
+        <v>100</v>
+      </c>
+      <c r="O74" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P74" s="41">
+        <v>1E-3</v>
+      </c>
+      <c r="Q74" s="41">
+        <f t="shared" ref="Q74" si="63">P74*N74</f>
+        <v>0.1</v>
+      </c>
+      <c r="R74" s="41"/>
+    </row>
+    <row r="75" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>66</v>
       </c>
       <c r="C75" s="59" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D75" s="39" t="s">
         <v>55</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F75" s="39" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="H75" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="I75" s="40" t="s">
-        <v>270</v>
-      </c>
-      <c r="J75" s="39">
+        <v>253</v>
+      </c>
+      <c r="I75" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J75" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="K75" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="L75" s="39">
         <v>1</v>
       </c>
-      <c r="K75" s="42">
-        <f t="shared" si="3"/>
+      <c r="M75" s="42">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L75" s="42"/>
-    </row>
-    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N75" s="42">
+        <v>50</v>
+      </c>
+      <c r="O75" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P75" s="42">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q75" s="42">
+        <f t="shared" ref="Q75" si="64">N75*P75</f>
+        <v>0.215</v>
+      </c>
+      <c r="R75" s="42"/>
+    </row>
+    <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>67</v>
       </c>
-      <c r="C76" s="83" t="s">
-        <v>289</v>
-      </c>
-      <c r="D76" s="84" t="s">
+      <c r="C76" s="97" t="s">
+        <v>324</v>
+      </c>
+      <c r="D76" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="E76" s="85" t="s">
-        <v>116</v>
-      </c>
-      <c r="F76" s="84" t="s">
-        <v>149</v>
-      </c>
-      <c r="G76" s="85" t="s">
-        <v>191</v>
-      </c>
-      <c r="H76" s="84" t="s">
-        <v>199</v>
-      </c>
-      <c r="I76" s="85" t="s">
-        <v>271</v>
-      </c>
-      <c r="J76" s="84">
+      <c r="E76" s="99" t="s">
+        <v>126</v>
+      </c>
+      <c r="F76" s="98" t="s">
+        <v>168</v>
+      </c>
+      <c r="G76" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="H76" s="98" t="s">
+        <v>229</v>
+      </c>
+      <c r="I76" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="J76" s="98" t="s">
+        <v>407</v>
+      </c>
+      <c r="K76" s="99" t="s">
+        <v>305</v>
+      </c>
+      <c r="L76" s="98">
         <v>4</v>
       </c>
-      <c r="K76" s="62">
-        <f t="shared" si="3"/>
+      <c r="M76" s="66">
+        <f t="shared" si="60"/>
         <v>80</v>
       </c>
-      <c r="L76" s="62" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N76" s="66">
+        <v>100</v>
+      </c>
+      <c r="O76" s="100" t="s">
+        <v>343</v>
+      </c>
+      <c r="P76" s="66">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q76" s="66">
+        <f t="shared" ref="Q76" si="65">P76*N76</f>
+        <v>0.12</v>
+      </c>
+      <c r="R76" s="66" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>68</v>
       </c>
-      <c r="C77" s="83" t="s">
-        <v>150</v>
-      </c>
-      <c r="D77" s="84" t="s">
-        <v>341</v>
-      </c>
-      <c r="E77" s="85" t="s">
-        <v>118</v>
-      </c>
-      <c r="F77" s="84" t="s">
-        <v>150</v>
-      </c>
-      <c r="G77" s="85" t="s">
-        <v>279</v>
-      </c>
-      <c r="H77" s="84" t="s">
-        <v>279</v>
-      </c>
-      <c r="I77" s="85" t="s">
-        <v>279</v>
-      </c>
-      <c r="J77" s="84">
+      <c r="C77" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="D77" s="98" t="s">
+        <v>453</v>
+      </c>
+      <c r="E77" s="99" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" s="98" t="s">
+        <v>169</v>
+      </c>
+      <c r="G77" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L77" s="98">
         <v>15</v>
       </c>
-      <c r="K77" s="62">
-        <f t="shared" si="3"/>
+      <c r="M77" s="66">
+        <f t="shared" si="60"/>
         <v>300</v>
       </c>
-      <c r="L77" s="62" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N77" s="66">
+        <f t="shared" ref="N77:N78" si="66">M77+(M77*0.1)</f>
+        <v>330</v>
+      </c>
+      <c r="O77" s="66"/>
+      <c r="P77" s="66"/>
+      <c r="Q77" s="66">
+        <f t="shared" ref="Q77" si="67">P77*N77</f>
+        <v>0</v>
+      </c>
+      <c r="R77" s="66" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>69</v>
       </c>
-      <c r="C78" s="87" t="s">
-        <v>291</v>
-      </c>
-      <c r="D78" s="88" t="s">
+      <c r="C78" s="102" t="s">
+        <v>326</v>
+      </c>
+      <c r="D78" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="E78" s="89" t="s">
-        <v>119</v>
-      </c>
-      <c r="F78" s="88" t="s">
-        <v>151</v>
-      </c>
-      <c r="G78" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="H78" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="I78" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J78" s="88">
+      <c r="E78" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="F78" s="103" t="s">
+        <v>170</v>
+      </c>
+      <c r="G78" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="H78" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="I78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L78" s="103">
         <v>1</v>
       </c>
-      <c r="K78" s="82">
-        <f t="shared" si="3"/>
+      <c r="M78" s="96">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L78" s="82"/>
-    </row>
-    <row r="79" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N78" s="96">
+        <f t="shared" si="66"/>
+        <v>22</v>
+      </c>
+      <c r="O78" s="96"/>
+      <c r="P78" s="96"/>
+      <c r="Q78" s="96">
+        <f t="shared" ref="Q78" si="68">N78*P78</f>
+        <v>0</v>
+      </c>
+      <c r="R78" s="96"/>
+    </row>
+    <row r="79" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>70</v>
       </c>
-      <c r="C79" s="90" t="s">
-        <v>292</v>
-      </c>
-      <c r="D79" s="91" t="s">
+      <c r="C79" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="D79" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="E79" s="92" t="s">
-        <v>120</v>
-      </c>
-      <c r="F79" s="91" t="s">
-        <v>274</v>
-      </c>
-      <c r="G79" s="92">
+      <c r="E79" s="108" t="s">
+        <v>130</v>
+      </c>
+      <c r="F79" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="G79" s="108">
         <v>750314597</v>
       </c>
-      <c r="H79" s="91" t="s">
-        <v>222</v>
-      </c>
-      <c r="I79" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J79" s="91">
+      <c r="H79" s="107" t="s">
+        <v>255</v>
+      </c>
+      <c r="I79" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J79" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K79" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L79" s="107">
         <v>1</v>
       </c>
-      <c r="K79" s="93">
-        <f t="shared" si="3"/>
+      <c r="M79" s="109">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L79" s="93"/>
-    </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N79" s="109">
+        <v>21</v>
+      </c>
+      <c r="O79" s="110" t="s">
+        <v>379</v>
+      </c>
+      <c r="P79" s="109">
+        <v>3.81</v>
+      </c>
+      <c r="Q79" s="109">
+        <f t="shared" ref="Q79" si="69">P79*N79</f>
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R79" s="109"/>
+    </row>
+    <row r="80" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>71</v>
       </c>
-      <c r="C80" s="87" t="s">
-        <v>293</v>
-      </c>
-      <c r="D80" s="88" t="s">
+      <c r="C80" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="D80" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="E80" s="89" t="s">
-        <v>121</v>
-      </c>
-      <c r="F80" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G80" s="89" t="s">
-        <v>152</v>
-      </c>
-      <c r="H80" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="I80" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J80" s="88">
+      <c r="E80" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="F80" s="103" t="s">
+        <v>308</v>
+      </c>
+      <c r="G80" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H80" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I80" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J80" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K80" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L80" s="103">
         <v>1</v>
       </c>
-      <c r="K80" s="82">
-        <f t="shared" si="3"/>
+      <c r="M80" s="96">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L80" s="82"/>
-    </row>
-    <row r="81" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N80" s="96">
+        <v>21</v>
+      </c>
+      <c r="O80" s="105" t="s">
+        <v>409</v>
+      </c>
+      <c r="P80" s="96">
+        <v>2.48</v>
+      </c>
+      <c r="Q80" s="96">
+        <f t="shared" ref="Q80" si="70">N80*P80</f>
+        <v>52.08</v>
+      </c>
+      <c r="R80" s="96"/>
+    </row>
+    <row r="81" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>72</v>
       </c>
-      <c r="C81" s="90" t="s">
-        <v>293</v>
-      </c>
-      <c r="D81" s="91" t="s">
+      <c r="C81" s="106" t="s">
+        <v>328</v>
+      </c>
+      <c r="D81" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="E81" s="92" t="s">
-        <v>385</v>
-      </c>
-      <c r="F81" s="91" t="s">
-        <v>384</v>
-      </c>
-      <c r="G81" s="91" t="s">
-        <v>312</v>
-      </c>
-      <c r="H81" s="91" t="s">
-        <v>223</v>
-      </c>
-      <c r="I81" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J81" s="91">
+      <c r="E81" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="F81" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="G81" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="H81" s="107" t="s">
+        <v>257</v>
+      </c>
+      <c r="I81" s="107" t="s">
+        <v>410</v>
+      </c>
+      <c r="J81" s="107" t="s">
+        <v>411</v>
+      </c>
+      <c r="K81" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L81" s="107">
         <v>1</v>
       </c>
-      <c r="K81" s="93">
-        <f t="shared" si="3"/>
+      <c r="M81" s="109">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L81" s="70"/>
-    </row>
-    <row r="82" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N81" s="109">
+        <v>21</v>
+      </c>
+      <c r="O81" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P81" s="109">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="Q81" s="109">
+        <f t="shared" ref="Q81" si="71">P81*N81</f>
+        <v>29.273999999999997</v>
+      </c>
+      <c r="R81" s="79"/>
+    </row>
+    <row r="82" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>73</v>
       </c>
-      <c r="C82" s="87" t="s">
-        <v>293</v>
-      </c>
-      <c r="D82" s="88" t="s">
+      <c r="C82" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="D82" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="E82" s="89" t="s">
-        <v>386</v>
-      </c>
-      <c r="F82" s="88" t="s">
-        <v>154</v>
-      </c>
-      <c r="G82" s="88" t="s">
-        <v>313</v>
-      </c>
-      <c r="H82" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="I82" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J82" s="88">
+      <c r="E82" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="F82" s="103" t="s">
+        <v>173</v>
+      </c>
+      <c r="G82" s="104" t="s">
+        <v>222</v>
+      </c>
+      <c r="H82" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I82" s="103" t="s">
+        <v>412</v>
+      </c>
+      <c r="J82" s="103" t="s">
+        <v>413</v>
+      </c>
+      <c r="K82" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L82" s="103">
         <v>1</v>
       </c>
-      <c r="K82" s="82">
-        <f t="shared" si="3"/>
+      <c r="M82" s="96">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L82" s="69"/>
-    </row>
-    <row r="83" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N82" s="96">
+        <v>21</v>
+      </c>
+      <c r="O82" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P82" s="96">
+        <v>0.69430000000000003</v>
+      </c>
+      <c r="Q82" s="96">
+        <f t="shared" ref="Q82" si="72">N82*P82</f>
+        <v>14.580300000000001</v>
+      </c>
+      <c r="R82" s="78"/>
+    </row>
+    <row r="83" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>74</v>
       </c>
-      <c r="C83" s="90" t="s">
-        <v>293</v>
-      </c>
-      <c r="D83" s="91" t="s">
+      <c r="C83" s="106" t="s">
+        <v>328</v>
+      </c>
+      <c r="D83" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="E83" s="92" t="s">
-        <v>122</v>
-      </c>
-      <c r="F83" s="91" t="s">
-        <v>276</v>
-      </c>
-      <c r="G83" s="92" t="s">
-        <v>153</v>
-      </c>
-      <c r="H83" s="91" t="s">
-        <v>223</v>
-      </c>
-      <c r="I83" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J83" s="91">
+      <c r="E83" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="F83" s="107" t="s">
+        <v>310</v>
+      </c>
+      <c r="G83" s="108" t="s">
+        <v>174</v>
+      </c>
+      <c r="H83" s="107" t="s">
+        <v>256</v>
+      </c>
+      <c r="I83" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J83" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K83" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L83" s="107">
         <v>1</v>
       </c>
-      <c r="K83" s="93">
-        <f t="shared" si="3"/>
+      <c r="M83" s="109">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L83" s="93"/>
-    </row>
-    <row r="84" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N83" s="109">
+        <v>21</v>
+      </c>
+      <c r="O83" s="110" t="s">
+        <v>409</v>
+      </c>
+      <c r="P83" s="109">
+        <v>3.637</v>
+      </c>
+      <c r="Q83" s="109">
+        <f t="shared" ref="Q83" si="73">P83*N83</f>
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R83" s="109"/>
+    </row>
+    <row r="84" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>75</v>
       </c>
-      <c r="C84" s="87" t="s">
-        <v>293</v>
-      </c>
-      <c r="D84" s="88" t="s">
+      <c r="C84" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="D84" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="E84" s="89" t="s">
-        <v>123</v>
-      </c>
-      <c r="F84" s="88" t="s">
-        <v>154</v>
-      </c>
-      <c r="G84" s="89" t="s">
-        <v>193</v>
-      </c>
-      <c r="H84" s="88" t="s">
+      <c r="E84" s="104" t="s">
+        <v>135</v>
+      </c>
+      <c r="F84" s="103" t="s">
+        <v>175</v>
+      </c>
+      <c r="G84" s="104" t="s">
         <v>223</v>
       </c>
-      <c r="I84" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J84" s="88">
+      <c r="H84" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I84" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" s="103" t="s">
+        <v>414</v>
+      </c>
+      <c r="K84" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L84" s="103">
         <v>1</v>
       </c>
-      <c r="K84" s="82">
-        <f t="shared" si="3"/>
+      <c r="M84" s="96">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L84" s="82"/>
-    </row>
-    <row r="85" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N84" s="96">
+        <v>21</v>
+      </c>
+      <c r="O84" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="P84" s="96">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="Q84" s="96">
+        <f t="shared" ref="Q84" si="74">N84*P84</f>
+        <v>9.0888000000000009</v>
+      </c>
+      <c r="R84" s="96"/>
+    </row>
+    <row r="85" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>76</v>
       </c>
-      <c r="C85" s="63" t="s">
-        <v>293</v>
-      </c>
-      <c r="D85" s="64" t="s">
+      <c r="C85" s="71" t="s">
+        <v>328</v>
+      </c>
+      <c r="D85" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="E85" s="65" t="s">
-        <v>124</v>
-      </c>
-      <c r="F85" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="G85" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="H85" s="64" t="s">
+      <c r="E85" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="F85" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="G85" s="73" t="s">
         <v>224</v>
       </c>
-      <c r="I85" s="65" t="s">
-        <v>279</v>
-      </c>
-      <c r="J85" s="64">
+      <c r="H85" s="72" t="s">
+        <v>258</v>
+      </c>
+      <c r="I85" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="J85" s="72" t="s">
+        <v>415</v>
+      </c>
+      <c r="K85" s="73" t="s">
+        <v>314</v>
+      </c>
+      <c r="L85" s="72">
         <v>1</v>
       </c>
-      <c r="K85" s="66">
-        <f t="shared" si="3"/>
+      <c r="M85" s="74">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L85" s="66" t="s">
-        <v>326</v>
-      </c>
-      <c r="O85" s="98"/>
-    </row>
-    <row r="86" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N85" s="74">
+        <v>21</v>
+      </c>
+      <c r="O85" s="75" t="s">
+        <v>343</v>
+      </c>
+      <c r="P85" s="74">
+        <v>7.4638</v>
+      </c>
+      <c r="Q85" s="74">
+        <f t="shared" ref="Q85" si="75">P85*N85</f>
+        <v>156.7398</v>
+      </c>
+      <c r="R85" s="74" t="s">
+        <v>438</v>
+      </c>
+      <c r="U85" s="118"/>
+    </row>
+    <row r="86" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>77</v>
       </c>
-      <c r="C86" s="87" t="s">
-        <v>293</v>
-      </c>
-      <c r="D86" s="88" t="s">
+      <c r="C86" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="D86" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="E86" s="89" t="s">
-        <v>125</v>
-      </c>
-      <c r="F86" s="88" t="s">
-        <v>156</v>
-      </c>
-      <c r="G86" s="89" t="s">
-        <v>195</v>
-      </c>
-      <c r="H86" s="88" t="s">
+      <c r="E86" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="F86" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="G86" s="104" t="s">
         <v>225</v>
       </c>
-      <c r="I86" s="96" t="s">
-        <v>279</v>
-      </c>
-      <c r="J86" s="88">
+      <c r="H86" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="I86" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J86" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K86" s="113" t="s">
+        <v>314</v>
+      </c>
+      <c r="L86" s="103">
         <v>1</v>
       </c>
-      <c r="K86" s="82">
-        <f t="shared" si="3"/>
+      <c r="M86" s="96">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L86" s="82"/>
-    </row>
-    <row r="87" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N86" s="96">
+        <v>21</v>
+      </c>
+      <c r="O86" s="105" t="s">
+        <v>409</v>
+      </c>
+      <c r="P86" s="96">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="Q86" s="96">
+        <f t="shared" ref="Q86" si="76">N86*P86</f>
+        <v>55.565999999999995</v>
+      </c>
+      <c r="R86" s="96"/>
+    </row>
+    <row r="87" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>78</v>
       </c>
-      <c r="C87" s="90" t="s">
-        <v>293</v>
-      </c>
-      <c r="D87" s="91" t="s">
-        <v>342</v>
-      </c>
-      <c r="E87" s="92" t="s">
-        <v>387</v>
-      </c>
-      <c r="F87" s="91" t="s">
-        <v>154</v>
-      </c>
-      <c r="G87" s="91" t="s">
-        <v>314</v>
-      </c>
-      <c r="H87" s="91" t="s">
-        <v>223</v>
-      </c>
-      <c r="I87" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="J87" s="97">
+      <c r="C87" s="106" t="s">
+        <v>328</v>
+      </c>
+      <c r="D87" s="107" t="s">
+        <v>454</v>
+      </c>
+      <c r="E87" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="F87" s="107" t="s">
+        <v>311</v>
+      </c>
+      <c r="G87" s="108" t="s">
+        <v>178</v>
+      </c>
+      <c r="H87" s="107" t="s">
+        <v>256</v>
+      </c>
+      <c r="I87" s="107" t="s">
+        <v>416</v>
+      </c>
+      <c r="J87" s="107" t="s">
+        <v>417</v>
+      </c>
+      <c r="K87" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L87" s="114">
         <v>2</v>
       </c>
-      <c r="K87" s="93">
-        <f t="shared" si="3"/>
+      <c r="M87" s="109">
+        <f t="shared" si="60"/>
         <v>40</v>
       </c>
-      <c r="L87" s="70"/>
-    </row>
-    <row r="88" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N87" s="109">
+        <v>42</v>
+      </c>
+      <c r="O87" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="P87" s="109">
+        <v>2.2974000000000001</v>
+      </c>
+      <c r="Q87" s="109">
+        <f t="shared" ref="Q87" si="77">P87*N87</f>
+        <v>96.490800000000007</v>
+      </c>
+      <c r="R87" s="79"/>
+    </row>
+    <row r="88" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>79</v>
       </c>
       <c r="C88" s="60" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="D88" s="37" t="s">
         <v>66</v>
       </c>
       <c r="E88" s="38" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="I88" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="J88" s="37">
+        <v>256</v>
+      </c>
+      <c r="I88" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="J88" s="62" t="s">
+        <v>420</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L88" s="37">
         <v>1</v>
       </c>
-      <c r="K88" s="41">
-        <f>J88*20</f>
+      <c r="M88" s="41">
+        <f>L88*20</f>
         <v>20</v>
       </c>
-      <c r="L88" s="41"/>
-    </row>
-    <row r="89" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N88" s="41">
+        <v>21</v>
+      </c>
+      <c r="O88" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="P88" s="41">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="Q88" s="41">
+        <f t="shared" ref="Q88" si="78">P88*N88</f>
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R88" s="41"/>
+    </row>
+    <row r="89" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>80</v>
       </c>
       <c r="C89" s="59" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>343</v>
+        <v>455</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>388</v>
+        <v>139</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="G89" s="91" t="s">
-        <v>315</v>
+        <v>312</v>
+      </c>
+      <c r="G89" s="40" t="s">
+        <v>179</v>
       </c>
       <c r="H89" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="I89" s="40" t="s">
-        <v>279</v>
-      </c>
-      <c r="J89" s="39">
+        <v>259</v>
+      </c>
+      <c r="I89" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="J89" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K89" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L89" s="39">
         <v>1</v>
       </c>
-      <c r="K89" s="42">
-        <f t="shared" si="3"/>
+      <c r="M89" s="42">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L89" s="70"/>
-    </row>
-    <row r="90" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N89" s="42">
+        <v>21</v>
+      </c>
+      <c r="O89" s="64" t="s">
+        <v>419</v>
+      </c>
+      <c r="P89" s="42">
+        <v>3.532</v>
+      </c>
+      <c r="Q89" s="42">
+        <f t="shared" ref="Q89:Q90" si="79">N89*P89</f>
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R89" s="79"/>
+    </row>
+    <row r="90" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="35"/>
         <v>81</v>
       </c>
-      <c r="C90" s="87" t="s">
-        <v>358</v>
-      </c>
-      <c r="D90" s="88" t="s">
-        <v>279</v>
-      </c>
-      <c r="E90" s="89" t="s">
-        <v>361</v>
-      </c>
-      <c r="F90" s="88" t="s">
-        <v>274</v>
-      </c>
-      <c r="G90" s="89" t="s">
-        <v>359</v>
-      </c>
-      <c r="H90" s="88" t="s">
-        <v>360</v>
-      </c>
-      <c r="I90" s="89"/>
-      <c r="J90" s="88">
+      <c r="C90" s="59" t="s">
+        <v>470</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="E90" s="40" t="s">
+        <v>473</v>
+      </c>
+      <c r="F90" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="G90" s="40" t="s">
+        <v>471</v>
+      </c>
+      <c r="H90" s="39" t="s">
+        <v>472</v>
+      </c>
+      <c r="I90" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J90" s="39" t="s">
+        <v>471</v>
+      </c>
+      <c r="K90" s="40"/>
+      <c r="L90" s="39">
         <v>1</v>
       </c>
-      <c r="K90" s="82">
-        <f t="shared" si="3"/>
+      <c r="M90" s="42">
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
-      <c r="L90" s="69"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N90" s="42">
+        <v>25</v>
+      </c>
+      <c r="O90" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="P90" s="42">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="Q90" s="42">
+        <f t="shared" si="79"/>
+        <v>2.2250000000000001</v>
+      </c>
+      <c r="R90" s="79"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="32"/>
       <c r="C91" s="51"/>
@@ -5541,12 +7493,23 @@
       <c r="F91" s="35"/>
       <c r="G91" s="36"/>
       <c r="H91" s="35"/>
-      <c r="I91" s="36"/>
-      <c r="J91" s="36"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
       <c r="K91" s="36"/>
-      <c r="L91" s="44"/>
-    </row>
-    <row r="92" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L91" s="36"/>
+      <c r="M91" s="36"/>
+      <c r="N91" s="36"/>
+      <c r="O91" s="69" t="s">
+        <v>421</v>
+      </c>
+      <c r="P91" s="67"/>
+      <c r="Q91" s="67">
+        <f>SUM(Q10:Q90)</f>
+        <v>976.95380000000011</v>
+      </c>
+      <c r="R91" s="44"/>
+    </row>
+    <row r="92" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="24"/>
       <c r="C92" s="52"/>
@@ -5560,15 +7523,105 @@
       <c r="I92" s="9"/>
       <c r="J92" s="9"/>
       <c r="K92" s="9"/>
-      <c r="L92" s="45"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="70" t="s">
+        <v>422</v>
+      </c>
+      <c r="P92" s="68"/>
+      <c r="Q92" s="68">
+        <f>Q91/20</f>
+        <v>48.847690000000007</v>
+      </c>
+      <c r="R92" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="R3:R8"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O15" r:id="rId6"/>
+    <hyperlink ref="O16" r:id="rId7"/>
+    <hyperlink ref="O17" r:id="rId8"/>
+    <hyperlink ref="O18" r:id="rId9"/>
+    <hyperlink ref="O19" r:id="rId10"/>
+    <hyperlink ref="O20" r:id="rId11"/>
+    <hyperlink ref="O21" r:id="rId12"/>
+    <hyperlink ref="O22" r:id="rId13"/>
+    <hyperlink ref="O23" r:id="rId14"/>
+    <hyperlink ref="O24" r:id="rId15"/>
+    <hyperlink ref="O25" r:id="rId16"/>
+    <hyperlink ref="O26" r:id="rId17"/>
+    <hyperlink ref="O27" r:id="rId18"/>
+    <hyperlink ref="O28" r:id="rId19"/>
+    <hyperlink ref="O29" r:id="rId20"/>
+    <hyperlink ref="O30" r:id="rId21"/>
+    <hyperlink ref="O31" r:id="rId22"/>
+    <hyperlink ref="O32" r:id="rId23"/>
+    <hyperlink ref="O33" r:id="rId24"/>
+    <hyperlink ref="O34" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O36" r:id="rId27"/>
+    <hyperlink ref="O37" r:id="rId28"/>
+    <hyperlink ref="O38" r:id="rId29"/>
+    <hyperlink ref="O39" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId31"/>
+    <hyperlink ref="O41" r:id="rId32"/>
+    <hyperlink ref="O43" r:id="rId33"/>
+    <hyperlink ref="O44" r:id="rId34"/>
+    <hyperlink ref="O45" r:id="rId35"/>
+    <hyperlink ref="O46" r:id="rId36"/>
+    <hyperlink ref="O48" r:id="rId37"/>
+    <hyperlink ref="O50" r:id="rId38"/>
+    <hyperlink ref="O51" r:id="rId39"/>
+    <hyperlink ref="O52" r:id="rId40"/>
+    <hyperlink ref="O53" r:id="rId41"/>
+    <hyperlink ref="O54" r:id="rId42"/>
+    <hyperlink ref="O55" r:id="rId43"/>
+    <hyperlink ref="O56" r:id="rId44"/>
+    <hyperlink ref="O57" r:id="rId45"/>
+    <hyperlink ref="O69" r:id="rId46"/>
+    <hyperlink ref="O59" r:id="rId47"/>
+    <hyperlink ref="O60" r:id="rId48"/>
+    <hyperlink ref="O61" r:id="rId49"/>
+    <hyperlink ref="O62" r:id="rId50"/>
+    <hyperlink ref="O63" r:id="rId51"/>
+    <hyperlink ref="O64" r:id="rId52"/>
+    <hyperlink ref="O65" r:id="rId53"/>
+    <hyperlink ref="O66" r:id="rId54"/>
+    <hyperlink ref="O67" r:id="rId55"/>
+    <hyperlink ref="O68" r:id="rId56"/>
+    <hyperlink ref="O70" r:id="rId57"/>
+    <hyperlink ref="O71" r:id="rId58"/>
+    <hyperlink ref="O72" r:id="rId59"/>
+    <hyperlink ref="O75" r:id="rId60"/>
+    <hyperlink ref="O76" r:id="rId61"/>
+    <hyperlink ref="O73" r:id="rId62"/>
+    <hyperlink ref="O79" r:id="rId63"/>
+    <hyperlink ref="O80" r:id="rId64"/>
+    <hyperlink ref="O81" r:id="rId65"/>
+    <hyperlink ref="O82" r:id="rId66"/>
+    <hyperlink ref="O83" r:id="rId67"/>
+    <hyperlink ref="O84" r:id="rId68"/>
+    <hyperlink ref="O85" r:id="rId69"/>
+    <hyperlink ref="O86" r:id="rId70"/>
+    <hyperlink ref="O87" r:id="rId71"/>
+    <hyperlink ref="O89" r:id="rId72"/>
+    <hyperlink ref="O88" r:id="rId73"/>
+    <hyperlink ref="O58" r:id="rId74"/>
+    <hyperlink ref="O47" r:id="rId75"/>
+    <hyperlink ref="O90" r:id="rId76"/>
+    <hyperlink ref="O42" r:id="rId77"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId78"/>
+  <drawing r:id="rId79"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB40EDC2-CBB5-4BE0-A2E3-1495B815E57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="480">
   <si>
     <t>Component list</t>
   </si>
@@ -1055,9 +1056,6 @@
   </si>
   <si>
     <t>Total Cost (20 Boards)</t>
-  </si>
-  <si>
-    <t>C116211</t>
   </si>
   <si>
     <t>LCSC</t>
@@ -1601,15 +1599,21 @@
   <si>
     <t>C780053</t>
   </si>
+  <si>
+    <t>EEEFT1H221AP</t>
+  </si>
+  <si>
+    <t>C178594</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1799,6 +1803,14 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2106,22 +2118,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2131,18 +2143,18 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2157,7 +2169,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2167,8 +2179,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2180,22 +2192,22 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2217,31 +2229,31 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2251,7 +2263,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2269,7 +2281,7 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2285,10 +2297,10 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2426,6 +2438,12 @@
     <xf numFmtId="0" fontId="26" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2435,10 +2453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2485,7 +2500,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2781,7 +2796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:U92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2814,14 +2829,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2869,7 +2884,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="116"/>
+      <c r="R3" s="118"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2893,7 +2908,7 @@
       <c r="O4" s="61"/>
       <c r="P4" s="61"/>
       <c r="Q4" s="61"/>
-      <c r="R4" s="117"/>
+      <c r="R4" s="119"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2915,7 +2930,7 @@
       <c r="O5" s="61"/>
       <c r="P5" s="61"/>
       <c r="Q5" s="61"/>
-      <c r="R5" s="117"/>
+      <c r="R5" s="119"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2935,7 +2950,7 @@
       <c r="O6" s="61"/>
       <c r="P6" s="61"/>
       <c r="Q6" s="61"/>
-      <c r="R6" s="117"/>
+      <c r="R6" s="119"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2955,7 +2970,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="117"/>
+      <c r="R7" s="119"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2975,7 +2990,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="117"/>
+      <c r="R8" s="119"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3049,17 +3064,17 @@
       <c r="F10" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="120" t="s">
         <v>142</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>227</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>314</v>
+        <v>478</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>342</v>
+        <v>479</v>
       </c>
       <c r="K10" s="38" t="s">
         <v>261</v>
@@ -3075,14 +3090,14 @@
         <v>22</v>
       </c>
       <c r="O10" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P10" s="41">
-        <v>0.25869999999999999</v>
+        <v>0.38819999999999999</v>
       </c>
       <c r="Q10" s="41">
         <f>P10*N10</f>
-        <v>5.6913999999999998</v>
+        <v>8.5404</v>
       </c>
       <c r="R10" s="41"/>
     </row>
@@ -3096,7 +3111,7 @@
         <v>316</v>
       </c>
       <c r="D11" s="82" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E11" s="83" t="s">
         <v>69</v>
@@ -3114,7 +3129,7 @@
         <v>314</v>
       </c>
       <c r="J11" s="82" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K11" s="83" t="s">
         <v>262</v>
@@ -3130,7 +3145,7 @@
         <v>300</v>
       </c>
       <c r="O11" s="85" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P11" s="84">
         <v>1.4E-3</v>
@@ -3140,7 +3155,7 @@
         <v>0.42</v>
       </c>
       <c r="R11" s="84" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3153,7 +3168,7 @@
         <v>316</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>70</v>
@@ -3171,7 +3186,7 @@
         <v>314</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K12" s="38" t="s">
         <v>263</v>
@@ -3187,7 +3202,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
@@ -3208,7 +3223,7 @@
         <v>316</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>71</v>
@@ -3226,7 +3241,7 @@
         <v>314</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K13" s="40" t="s">
         <v>264</v>
@@ -3242,7 +3257,7 @@
         <v>40</v>
       </c>
       <c r="O13" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
@@ -3263,7 +3278,7 @@
         <v>316</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>72</v>
@@ -3281,7 +3296,7 @@
         <v>314</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K14" s="38" t="s">
         <v>265</v>
@@ -3297,7 +3312,7 @@
         <v>200</v>
       </c>
       <c r="O14" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
@@ -3318,7 +3333,7 @@
         <v>316</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>73</v>
@@ -3336,7 +3351,7 @@
         <v>314</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K15" s="40" t="s">
         <v>266</v>
@@ -3352,7 +3367,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
@@ -3373,16 +3388,16 @@
         <v>316</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F16" s="37" t="s">
         <v>143</v>
       </c>
       <c r="G16" s="101" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H16" s="86" t="s">
         <v>231</v>
@@ -3391,7 +3406,7 @@
         <v>314</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K16" s="38" t="s">
         <v>267</v>
@@ -3407,7 +3422,7 @@
         <v>130</v>
       </c>
       <c r="O16" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P16" s="41">
         <v>3.32E-2</v>
@@ -3446,7 +3461,7 @@
         <v>314</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K17" s="40" t="s">
         <v>268</v>
@@ -3462,7 +3477,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
@@ -3483,7 +3498,7 @@
         <v>316</v>
       </c>
       <c r="D18" s="103" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E18" s="104" t="s">
         <v>75</v>
@@ -3498,10 +3513,10 @@
         <v>232</v>
       </c>
       <c r="I18" s="103" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J18" s="103" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K18" s="104" t="s">
         <v>269</v>
@@ -3517,7 +3532,7 @@
         <v>180</v>
       </c>
       <c r="O18" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P18" s="96">
         <v>3.09E-2</v>
@@ -3553,10 +3568,10 @@
         <v>233</v>
       </c>
       <c r="I19" s="107" t="s">
+        <v>351</v>
+      </c>
+      <c r="J19" s="107" t="s">
         <v>352</v>
-      </c>
-      <c r="J19" s="107" t="s">
-        <v>353</v>
       </c>
       <c r="K19" s="108" t="s">
         <v>270</v>
@@ -3572,7 +3587,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P19" s="109">
         <v>5.3E-3</v>
@@ -3611,7 +3626,7 @@
         <v>314</v>
       </c>
       <c r="J20" s="103" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K20" s="104" t="s">
         <v>261</v>
@@ -3627,7 +3642,7 @@
         <v>22</v>
       </c>
       <c r="O20" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P20" s="96">
         <v>0.22189999999999999</v>
@@ -3666,7 +3681,7 @@
         <v>314</v>
       </c>
       <c r="J21" s="107" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K21" s="108" t="s">
         <v>271</v>
@@ -3682,7 +3697,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P21" s="109">
         <v>7.7000000000000002E-3</v>
@@ -3721,7 +3736,7 @@
         <v>314</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K22" s="38" t="s">
         <v>264</v>
@@ -3737,7 +3752,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P22" s="41">
         <v>3.49E-2</v>
@@ -3758,7 +3773,7 @@
         <v>316</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>80</v>
@@ -3776,7 +3791,7 @@
         <v>314</v>
       </c>
       <c r="J23" s="39" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K23" s="40" t="s">
         <v>272</v>
@@ -3792,7 +3807,7 @@
         <v>40</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P23" s="42">
         <v>1.9199999999999998E-2</v>
@@ -3828,10 +3843,10 @@
         <v>235</v>
       </c>
       <c r="I24" s="37" t="s">
+        <v>358</v>
+      </c>
+      <c r="J24" s="37" t="s">
         <v>359</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>360</v>
       </c>
       <c r="K24" s="38" t="s">
         <v>273</v>
@@ -3847,7 +3862,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P24" s="41">
         <v>5.1999999999999998E-3</v>
@@ -3886,7 +3901,7 @@
         <v>314</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K25" s="40" t="s">
         <v>274</v>
@@ -3902,7 +3917,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P25" s="42">
         <v>3.2000000000000002E-3</v>
@@ -3926,13 +3941,13 @@
         <v>16</v>
       </c>
       <c r="E26" s="111" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F26" s="103" t="s">
         <v>143</v>
       </c>
       <c r="G26" s="111" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H26" s="112" t="s">
         <v>249</v>
@@ -3941,10 +3956,10 @@
         <v>314</v>
       </c>
       <c r="J26" s="103" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K26" s="111" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L26" s="103">
         <v>1</v>
@@ -3957,7 +3972,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P26" s="96">
         <v>3.3999999999999998E-3</v>
@@ -3978,7 +3993,7 @@
         <v>316</v>
       </c>
       <c r="D27" s="107" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E27" s="108" t="s">
         <v>83</v>
@@ -3996,7 +4011,7 @@
         <v>314</v>
       </c>
       <c r="J27" s="107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K27" s="108" t="s">
         <v>275</v>
@@ -4012,7 +4027,7 @@
         <v>30</v>
       </c>
       <c r="O27" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P27" s="109">
         <v>0.2525</v>
@@ -4051,7 +4066,7 @@
         <v>314</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K28" s="38" t="s">
         <v>276</v>
@@ -4067,7 +4082,7 @@
         <v>22</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P28" s="41">
         <v>0.89629999999999999</v>
@@ -4106,7 +4121,7 @@
         <v>314</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K29" s="40" t="s">
         <v>277</v>
@@ -4122,7 +4137,7 @@
         <v>21</v>
       </c>
       <c r="O29" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P29" s="42">
         <v>0.47249999999999998</v>
@@ -4161,7 +4176,7 @@
         <v>314</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K30" s="38" t="s">
         <v>278</v>
@@ -4177,7 +4192,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P30" s="41">
         <v>3.0999999999999999E-3</v>
@@ -4216,7 +4231,7 @@
         <v>314</v>
       </c>
       <c r="J31" s="107" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K31" s="108" t="s">
         <v>279</v>
@@ -4232,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P31" s="109">
         <v>5.4999999999999997E-3</v>
@@ -4271,7 +4286,7 @@
         <v>314</v>
       </c>
       <c r="J32" s="103" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K32" s="104" t="s">
         <v>314</v>
@@ -4287,7 +4302,7 @@
         <v>30</v>
       </c>
       <c r="O32" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P32" s="96">
         <v>4.87E-2</v>
@@ -4326,7 +4341,7 @@
         <v>314</v>
       </c>
       <c r="J33" s="107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K33" s="108" t="s">
         <v>314</v>
@@ -4342,7 +4357,7 @@
         <v>30</v>
       </c>
       <c r="O33" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P33" s="109">
         <v>7.4300000000000005E-2</v>
@@ -4363,7 +4378,7 @@
         <v>317</v>
       </c>
       <c r="D34" s="103" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E34" s="104" t="s">
         <v>90</v>
@@ -4381,7 +4396,7 @@
         <v>281</v>
       </c>
       <c r="J34" s="103" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K34" s="104" t="s">
         <v>314</v>
@@ -4397,7 +4412,7 @@
         <v>60</v>
       </c>
       <c r="O34" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P34" s="96">
         <v>2.8899999999999999E-2</v>
@@ -4418,7 +4433,7 @@
         <v>317</v>
       </c>
       <c r="D35" s="90" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E35" s="91" t="s">
         <v>91</v>
@@ -4433,10 +4448,10 @@
         <v>239</v>
       </c>
       <c r="I35" s="90" t="s">
+        <v>369</v>
+      </c>
+      <c r="J35" s="90" t="s">
         <v>370</v>
-      </c>
-      <c r="J35" s="90" t="s">
-        <v>371</v>
       </c>
       <c r="K35" s="91" t="s">
         <v>314</v>
@@ -4452,7 +4467,7 @@
         <v>170</v>
       </c>
       <c r="O35" s="95" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P35" s="93">
         <v>0.12590000000000001</v>
@@ -4462,9 +4477,9 @@
         <v>21.403000000000002</v>
       </c>
       <c r="R35" s="84" t="s">
-        <v>445</v>
-      </c>
-      <c r="U35" s="119"/>
+        <v>444</v>
+      </c>
+      <c r="U35" s="116"/>
     </row>
     <row r="36" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -4491,10 +4506,10 @@
         <v>240</v>
       </c>
       <c r="I36" s="103" t="s">
+        <v>371</v>
+      </c>
+      <c r="J36" s="103" t="s">
         <v>372</v>
-      </c>
-      <c r="J36" s="103" t="s">
-        <v>373</v>
       </c>
       <c r="K36" s="104" t="s">
         <v>314</v>
@@ -4510,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="O36" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P36" s="96">
         <v>5.6000000000000001E-2</v>
@@ -4549,7 +4564,7 @@
         <v>314</v>
       </c>
       <c r="J37" s="107" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K37" s="108" t="s">
         <v>314</v>
@@ -4565,7 +4580,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P37" s="109">
         <v>2.9499999999999998E-2</v>
@@ -4601,10 +4616,10 @@
         <v>241</v>
       </c>
       <c r="I38" s="103" t="s">
+        <v>374</v>
+      </c>
+      <c r="J38" s="103" t="s">
         <v>375</v>
-      </c>
-      <c r="J38" s="103" t="s">
-        <v>376</v>
       </c>
       <c r="K38" s="104" t="s">
         <v>314</v>
@@ -4620,7 +4635,7 @@
         <v>21</v>
       </c>
       <c r="O38" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P38" s="96">
         <v>0.53559999999999997</v>
@@ -4656,10 +4671,10 @@
         <v>242</v>
       </c>
       <c r="I39" s="107" t="s">
+        <v>376</v>
+      </c>
+      <c r="J39" s="107" t="s">
         <v>377</v>
-      </c>
-      <c r="J39" s="107" t="s">
-        <v>378</v>
       </c>
       <c r="K39" s="108" t="s">
         <v>314</v>
@@ -4675,7 +4690,7 @@
         <v>42</v>
       </c>
       <c r="O39" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P39" s="109">
         <v>0.65639999999999998</v>
@@ -4730,7 +4745,7 @@
         <v>21</v>
       </c>
       <c r="O40" s="105" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P40" s="96">
         <v>1.2</v>
@@ -4769,7 +4784,7 @@
         <v>314</v>
       </c>
       <c r="J41" s="107" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K41" s="108" t="s">
         <v>314</v>
@@ -4785,7 +4800,7 @@
         <v>25</v>
       </c>
       <c r="O41" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P41" s="109">
         <v>9.2200000000000004E-2</v>
@@ -4803,25 +4818,25 @@
         <v>321</v>
       </c>
       <c r="D42" s="107" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E42" s="108" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F42" s="107" t="s">
         <v>308</v>
       </c>
       <c r="G42" s="108" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H42" s="107" t="s">
+        <v>476</v>
+      </c>
+      <c r="I42" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J42" s="107" t="s">
         <v>477</v>
-      </c>
-      <c r="I42" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J42" s="107" t="s">
-        <v>478</v>
       </c>
       <c r="K42" s="108" t="s">
         <v>314</v>
@@ -4837,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="O42" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P42" s="109">
         <v>0.21210000000000001</v>
@@ -4876,7 +4891,7 @@
         <v>314</v>
       </c>
       <c r="J43" s="103" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K43" s="104" t="s">
         <v>282</v>
@@ -4892,7 +4907,7 @@
         <v>21</v>
       </c>
       <c r="O43" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P43" s="96">
         <v>0.45629999999999998</v>
@@ -4916,25 +4931,25 @@
         <v>30</v>
       </c>
       <c r="E44" s="108" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F44" s="107" t="s">
         <v>308</v>
       </c>
       <c r="G44" s="108" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H44" s="107" t="s">
+        <v>435</v>
+      </c>
+      <c r="I44" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J44" s="107" t="s">
         <v>436</v>
       </c>
-      <c r="I44" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J44" s="107" t="s">
-        <v>437</v>
-      </c>
       <c r="K44" s="108" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L44" s="107">
         <v>1</v>
@@ -4947,7 +4962,7 @@
         <v>25</v>
       </c>
       <c r="O44" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P44" s="109">
         <v>0.1012</v>
@@ -5002,7 +5017,7 @@
         <v>30</v>
       </c>
       <c r="O45" s="105" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P45" s="96">
         <v>0.156</v>
@@ -5057,7 +5072,7 @@
         <v>30</v>
       </c>
       <c r="O46" s="110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P46" s="109">
         <v>0.08</v>
@@ -5075,22 +5090,22 @@
         <v>38</v>
       </c>
       <c r="C47" s="106" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D47" s="107" t="s">
         <v>314</v>
       </c>
       <c r="E47" s="108" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F47" s="107" t="s">
         <v>308</v>
       </c>
       <c r="G47" s="108" t="s">
+        <v>467</v>
+      </c>
+      <c r="H47" s="107" t="s">
         <v>468</v>
-      </c>
-      <c r="H47" s="107" t="s">
-        <v>469</v>
       </c>
       <c r="I47" s="107" t="s">
         <v>314</v>
@@ -5112,7 +5127,7 @@
         <v>20</v>
       </c>
       <c r="O47" s="110" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P47" s="109">
         <v>0.435</v>
@@ -5122,7 +5137,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="R47" s="79" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5169,7 +5184,7 @@
         <v>50</v>
       </c>
       <c r="O48" s="105" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P48" s="96">
         <v>1.5</v>
@@ -5227,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="R49" s="66" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5274,7 +5289,7 @@
         <v>90</v>
       </c>
       <c r="O50" s="105" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P50" s="96">
         <v>0.13</v>
@@ -5295,7 +5310,7 @@
         <v>323</v>
       </c>
       <c r="D51" s="107" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E51" s="108" t="s">
         <v>104</v>
@@ -5310,10 +5325,10 @@
         <v>248</v>
       </c>
       <c r="I51" s="107" t="s">
+        <v>384</v>
+      </c>
+      <c r="J51" s="107" t="s">
         <v>385</v>
-      </c>
-      <c r="J51" s="107" t="s">
-        <v>386</v>
       </c>
       <c r="K51" s="108" t="s">
         <v>314</v>
@@ -5329,7 +5344,7 @@
         <v>85</v>
       </c>
       <c r="O51" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P51" s="109">
         <v>0.21740000000000001</v>
@@ -5368,7 +5383,7 @@
         <v>314</v>
       </c>
       <c r="J52" s="103" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K52" s="104" t="s">
         <v>284</v>
@@ -5384,7 +5399,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P52" s="96">
         <v>1E-3</v>
@@ -5423,7 +5438,7 @@
         <v>314</v>
       </c>
       <c r="J53" s="107" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K53" s="108" t="s">
         <v>285</v>
@@ -5439,7 +5454,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P53" s="109">
         <v>1.4E-3</v>
@@ -5478,7 +5493,7 @@
         <v>314</v>
       </c>
       <c r="J54" s="103" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K54" s="104" t="s">
         <v>286</v>
@@ -5494,7 +5509,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P54" s="96">
         <v>1.6000000000000001E-3</v>
@@ -5533,7 +5548,7 @@
         <v>314</v>
       </c>
       <c r="J55" s="107" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K55" s="108" t="s">
         <v>287</v>
@@ -5549,7 +5564,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P55" s="109">
         <v>1.4E-3</v>
@@ -5588,7 +5603,7 @@
         <v>314</v>
       </c>
       <c r="J56" s="103" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K56" s="104" t="s">
         <v>288</v>
@@ -5604,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P56" s="96">
         <v>1.2999999999999999E-3</v>
@@ -5640,10 +5655,10 @@
         <v>250</v>
       </c>
       <c r="I57" s="107" t="s">
+        <v>391</v>
+      </c>
+      <c r="J57" s="107" t="s">
         <v>392</v>
-      </c>
-      <c r="J57" s="107" t="s">
-        <v>393</v>
       </c>
       <c r="K57" s="108" t="s">
         <v>289</v>
@@ -5659,7 +5674,7 @@
         <v>90</v>
       </c>
       <c r="O57" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P57" s="109">
         <v>6.4500000000000002E-2</v>
@@ -5680,16 +5695,16 @@
         <v>324</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F58" s="37" t="s">
         <v>166</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H58" s="37" t="s">
         <v>252</v>
@@ -5698,10 +5713,10 @@
         <v>314</v>
       </c>
       <c r="J58" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="K58" s="37" t="s">
         <v>426</v>
-      </c>
-      <c r="K58" s="37" t="s">
-        <v>427</v>
       </c>
       <c r="L58" s="37">
         <v>8</v>
@@ -5714,7 +5729,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P58" s="37">
         <v>1.1000000000000001E-3</v>
@@ -5769,7 +5784,7 @@
         <v>30</v>
       </c>
       <c r="O59" s="110" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P59" s="109">
         <v>1.8589999999999999E-2</v>
@@ -5808,7 +5823,7 @@
         <v>314</v>
       </c>
       <c r="J60" s="103" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K60" s="104" t="s">
         <v>292</v>
@@ -5824,7 +5839,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P60" s="96">
         <v>1.4E-3</v>
@@ -5879,7 +5894,7 @@
         <v>50</v>
       </c>
       <c r="O61" s="110" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P61" s="109">
         <v>4.6699999999999997E-3</v>
@@ -5918,7 +5933,7 @@
         <v>314</v>
       </c>
       <c r="J62" s="103" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K62" s="104" t="s">
         <v>294</v>
@@ -5934,7 +5949,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P62" s="96">
         <v>1.1999999999999999E-3</v>
@@ -5989,7 +6004,7 @@
         <v>50</v>
       </c>
       <c r="O63" s="110" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P63" s="109">
         <v>1.11E-2</v>
@@ -6028,7 +6043,7 @@
         <v>314</v>
       </c>
       <c r="J64" s="103" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K64" s="104" t="s">
         <v>296</v>
@@ -6044,7 +6059,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P64" s="96">
         <v>2.0999999999999999E-3</v>
@@ -6083,7 +6098,7 @@
         <v>314</v>
       </c>
       <c r="J65" s="107" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K65" s="108" t="s">
         <v>297</v>
@@ -6099,7 +6114,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P65" s="109">
         <v>1.6000000000000001E-3</v>
@@ -6135,10 +6150,10 @@
         <v>229</v>
       </c>
       <c r="I66" s="103" t="s">
+        <v>398</v>
+      </c>
+      <c r="J66" s="103" t="s">
         <v>399</v>
-      </c>
-      <c r="J66" s="103" t="s">
-        <v>400</v>
       </c>
       <c r="K66" s="104" t="s">
         <v>298</v>
@@ -6154,7 +6169,7 @@
         <v>50</v>
       </c>
       <c r="O66" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P66" s="96">
         <v>6.8999999999999999E-3</v>
@@ -6175,7 +6190,7 @@
         <v>324</v>
       </c>
       <c r="D67" s="107" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E67" s="108" t="s">
         <v>120</v>
@@ -6193,7 +6208,7 @@
         <v>314</v>
       </c>
       <c r="J67" s="107" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K67" s="108" t="s">
         <v>299</v>
@@ -6209,7 +6224,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P67" s="109">
         <v>1.1000000000000001E-3</v>
@@ -6248,7 +6263,7 @@
         <v>314</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K68" s="38" t="s">
         <v>300</v>
@@ -6264,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P68" s="41">
         <v>1.5E-3</v>
@@ -6285,7 +6300,7 @@
         <v>324</v>
       </c>
       <c r="D69" s="87" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E69" s="40" t="s">
         <v>111</v>
@@ -6301,7 +6316,7 @@
       </c>
       <c r="I69" s="39"/>
       <c r="J69" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K69" s="40" t="s">
         <v>290</v>
@@ -6317,7 +6332,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P69" s="42">
         <v>1.5E-3</v>
@@ -6356,7 +6371,7 @@
         <v>314</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K70" s="38" t="s">
         <v>301</v>
@@ -6372,7 +6387,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P70" s="41">
         <v>1.5E-3</v>
@@ -6427,7 +6442,7 @@
         <v>25</v>
       </c>
       <c r="O71" s="64" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P71" s="42">
         <v>8.5400000000000004E-2</v>
@@ -6451,13 +6466,13 @@
         <v>53</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F72" s="86" t="s">
         <v>166</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H72" s="37" t="s">
         <v>252</v>
@@ -6466,10 +6481,10 @@
         <v>314</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L72" s="37">
         <v>1</v>
@@ -6482,7 +6497,7 @@
         <v>50</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P72" s="41">
         <v>3.8E-3</v>
@@ -6503,7 +6518,7 @@
         <v>324</v>
       </c>
       <c r="D73" s="39" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E73" s="40" t="s">
         <v>127</v>
@@ -6521,7 +6536,7 @@
         <v>314</v>
       </c>
       <c r="J73" s="39" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K73" s="40" t="s">
         <v>306</v>
@@ -6537,7 +6552,7 @@
         <v>200</v>
       </c>
       <c r="O73" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P73" s="42">
         <v>1.1999999999999999E-3</v>
@@ -6576,7 +6591,7 @@
         <v>314</v>
       </c>
       <c r="J74" s="37" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K74" s="38" t="s">
         <v>303</v>
@@ -6592,7 +6607,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P74" s="41">
         <v>1E-3</v>
@@ -6631,7 +6646,7 @@
         <v>314</v>
       </c>
       <c r="J75" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K75" s="40" t="s">
         <v>304</v>
@@ -6647,7 +6662,7 @@
         <v>50</v>
       </c>
       <c r="O75" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P75" s="42">
         <v>4.3E-3</v>
@@ -6686,7 +6701,7 @@
         <v>314</v>
       </c>
       <c r="J76" s="98" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K76" s="99" t="s">
         <v>305</v>
@@ -6702,7 +6717,7 @@
         <v>100</v>
       </c>
       <c r="O76" s="100" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P76" s="66">
         <v>1.1999999999999999E-3</v>
@@ -6712,7 +6727,7 @@
         <v>0.12</v>
       </c>
       <c r="R76" s="66" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6725,7 +6740,7 @@
         <v>169</v>
       </c>
       <c r="D77" s="98" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E77" s="99" t="s">
         <v>128</v>
@@ -6766,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="66" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6865,7 +6880,7 @@
         <v>21</v>
       </c>
       <c r="O79" s="110" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P79" s="109">
         <v>3.81</v>
@@ -6920,7 +6935,7 @@
         <v>21</v>
       </c>
       <c r="O80" s="105" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P80" s="96">
         <v>2.48</v>
@@ -6956,10 +6971,10 @@
         <v>257</v>
       </c>
       <c r="I81" s="107" t="s">
+        <v>409</v>
+      </c>
+      <c r="J81" s="107" t="s">
         <v>410</v>
-      </c>
-      <c r="J81" s="107" t="s">
-        <v>411</v>
       </c>
       <c r="K81" s="108" t="s">
         <v>314</v>
@@ -6975,7 +6990,7 @@
         <v>21</v>
       </c>
       <c r="O81" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P81" s="109">
         <v>1.3939999999999999</v>
@@ -7011,10 +7026,10 @@
         <v>256</v>
       </c>
       <c r="I82" s="103" t="s">
+        <v>411</v>
+      </c>
+      <c r="J82" s="103" t="s">
         <v>412</v>
-      </c>
-      <c r="J82" s="103" t="s">
-        <v>413</v>
       </c>
       <c r="K82" s="104" t="s">
         <v>314</v>
@@ -7030,7 +7045,7 @@
         <v>21</v>
       </c>
       <c r="O82" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P82" s="96">
         <v>0.69430000000000003</v>
@@ -7085,7 +7100,7 @@
         <v>21</v>
       </c>
       <c r="O83" s="110" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P83" s="109">
         <v>3.637</v>
@@ -7124,7 +7139,7 @@
         <v>314</v>
       </c>
       <c r="J84" s="103" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K84" s="104" t="s">
         <v>314</v>
@@ -7140,7 +7155,7 @@
         <v>21</v>
       </c>
       <c r="O84" s="105" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P84" s="96">
         <v>0.43280000000000002</v>
@@ -7179,7 +7194,7 @@
         <v>314</v>
       </c>
       <c r="J85" s="72" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K85" s="73" t="s">
         <v>314</v>
@@ -7195,7 +7210,7 @@
         <v>21</v>
       </c>
       <c r="O85" s="75" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P85" s="74">
         <v>7.4638</v>
@@ -7205,9 +7220,9 @@
         <v>156.7398</v>
       </c>
       <c r="R85" s="74" t="s">
-        <v>438</v>
-      </c>
-      <c r="U85" s="118"/>
+        <v>437</v>
+      </c>
+      <c r="U85" s="115"/>
     </row>
     <row r="86" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
@@ -7253,7 +7268,7 @@
         <v>21</v>
       </c>
       <c r="O86" s="105" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P86" s="96">
         <v>2.6459999999999999</v>
@@ -7274,7 +7289,7 @@
         <v>328</v>
       </c>
       <c r="D87" s="107" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E87" s="108" t="s">
         <v>138</v>
@@ -7289,10 +7304,10 @@
         <v>256</v>
       </c>
       <c r="I87" s="107" t="s">
+        <v>415</v>
+      </c>
+      <c r="J87" s="107" t="s">
         <v>416</v>
-      </c>
-      <c r="J87" s="107" t="s">
-        <v>417</v>
       </c>
       <c r="K87" s="108" t="s">
         <v>314</v>
@@ -7308,7 +7323,7 @@
         <v>42</v>
       </c>
       <c r="O87" s="110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P87" s="109">
         <v>2.2974000000000001</v>
@@ -7347,7 +7362,7 @@
         <v>314</v>
       </c>
       <c r="J88" s="62" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K88" s="38" t="s">
         <v>314</v>
@@ -7363,7 +7378,7 @@
         <v>21</v>
       </c>
       <c r="O88" s="63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P88" s="41">
         <v>0.39140000000000003</v>
@@ -7384,7 +7399,7 @@
         <v>328</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E89" s="40" t="s">
         <v>139</v>
@@ -7399,7 +7414,7 @@
         <v>259</v>
       </c>
       <c r="I89" s="39" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J89" s="39" t="s">
         <v>314</v>
@@ -7418,7 +7433,7 @@
         <v>21</v>
       </c>
       <c r="O89" s="64" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P89" s="42">
         <v>3.532</v>
@@ -7436,28 +7451,28 @@
         <v>81</v>
       </c>
       <c r="C90" s="59" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D90" s="39" t="s">
         <v>314</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F90" s="39" t="s">
         <v>308</v>
       </c>
       <c r="G90" s="40" t="s">
+        <v>470</v>
+      </c>
+      <c r="H90" s="39" t="s">
         <v>471</v>
       </c>
-      <c r="H90" s="39" t="s">
-        <v>472</v>
-      </c>
       <c r="I90" s="39" t="s">
         <v>314</v>
       </c>
       <c r="J90" s="39" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K90" s="40"/>
       <c r="L90" s="39">
@@ -7471,7 +7486,7 @@
         <v>25</v>
       </c>
       <c r="O90" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P90" s="42">
         <v>8.8999999999999996E-2</v>
@@ -7500,12 +7515,12 @@
       <c r="M91" s="36"/>
       <c r="N91" s="36"/>
       <c r="O91" s="69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P91" s="67"/>
       <c r="Q91" s="67">
         <f>SUM(Q10:Q90)</f>
-        <v>976.95380000000011</v>
+        <v>979.80280000000005</v>
       </c>
       <c r="R91" s="44"/>
     </row>
@@ -7527,12 +7542,12 @@
       <c r="M92" s="9"/>
       <c r="N92" s="9"/>
       <c r="O92" s="70" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P92" s="68"/>
       <c r="Q92" s="68">
         <f>Q91/20</f>
-        <v>48.847690000000007</v>
+        <v>48.990140000000004</v>
       </c>
       <c r="R92" s="45"/>
     </row>
@@ -7542,83 +7557,83 @@
     <mergeCell ref="R3:R8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
-    <hyperlink ref="O12" r:id="rId3"/>
-    <hyperlink ref="O13" r:id="rId4"/>
-    <hyperlink ref="O14" r:id="rId5"/>
-    <hyperlink ref="O15" r:id="rId6"/>
-    <hyperlink ref="O16" r:id="rId7"/>
-    <hyperlink ref="O17" r:id="rId8"/>
-    <hyperlink ref="O18" r:id="rId9"/>
-    <hyperlink ref="O19" r:id="rId10"/>
-    <hyperlink ref="O20" r:id="rId11"/>
-    <hyperlink ref="O21" r:id="rId12"/>
-    <hyperlink ref="O22" r:id="rId13"/>
-    <hyperlink ref="O23" r:id="rId14"/>
-    <hyperlink ref="O24" r:id="rId15"/>
-    <hyperlink ref="O25" r:id="rId16"/>
-    <hyperlink ref="O26" r:id="rId17"/>
-    <hyperlink ref="O27" r:id="rId18"/>
-    <hyperlink ref="O28" r:id="rId19"/>
-    <hyperlink ref="O29" r:id="rId20"/>
-    <hyperlink ref="O30" r:id="rId21"/>
-    <hyperlink ref="O31" r:id="rId22"/>
-    <hyperlink ref="O32" r:id="rId23"/>
-    <hyperlink ref="O33" r:id="rId24"/>
-    <hyperlink ref="O34" r:id="rId25"/>
-    <hyperlink ref="O35" r:id="rId26"/>
-    <hyperlink ref="O36" r:id="rId27"/>
-    <hyperlink ref="O37" r:id="rId28"/>
-    <hyperlink ref="O38" r:id="rId29"/>
-    <hyperlink ref="O39" r:id="rId30"/>
-    <hyperlink ref="O40" r:id="rId31"/>
-    <hyperlink ref="O41" r:id="rId32"/>
-    <hyperlink ref="O43" r:id="rId33"/>
-    <hyperlink ref="O44" r:id="rId34"/>
-    <hyperlink ref="O45" r:id="rId35"/>
-    <hyperlink ref="O46" r:id="rId36"/>
-    <hyperlink ref="O48" r:id="rId37"/>
-    <hyperlink ref="O50" r:id="rId38"/>
-    <hyperlink ref="O51" r:id="rId39"/>
-    <hyperlink ref="O52" r:id="rId40"/>
-    <hyperlink ref="O53" r:id="rId41"/>
-    <hyperlink ref="O54" r:id="rId42"/>
-    <hyperlink ref="O55" r:id="rId43"/>
-    <hyperlink ref="O56" r:id="rId44"/>
-    <hyperlink ref="O57" r:id="rId45"/>
-    <hyperlink ref="O69" r:id="rId46"/>
-    <hyperlink ref="O59" r:id="rId47"/>
-    <hyperlink ref="O60" r:id="rId48"/>
-    <hyperlink ref="O61" r:id="rId49"/>
-    <hyperlink ref="O62" r:id="rId50"/>
-    <hyperlink ref="O63" r:id="rId51"/>
-    <hyperlink ref="O64" r:id="rId52"/>
-    <hyperlink ref="O65" r:id="rId53"/>
-    <hyperlink ref="O66" r:id="rId54"/>
-    <hyperlink ref="O67" r:id="rId55"/>
-    <hyperlink ref="O68" r:id="rId56"/>
-    <hyperlink ref="O70" r:id="rId57"/>
-    <hyperlink ref="O71" r:id="rId58"/>
-    <hyperlink ref="O72" r:id="rId59"/>
-    <hyperlink ref="O75" r:id="rId60"/>
-    <hyperlink ref="O76" r:id="rId61"/>
-    <hyperlink ref="O73" r:id="rId62"/>
-    <hyperlink ref="O79" r:id="rId63"/>
-    <hyperlink ref="O80" r:id="rId64"/>
-    <hyperlink ref="O81" r:id="rId65"/>
-    <hyperlink ref="O82" r:id="rId66"/>
-    <hyperlink ref="O83" r:id="rId67"/>
-    <hyperlink ref="O84" r:id="rId68"/>
-    <hyperlink ref="O85" r:id="rId69"/>
-    <hyperlink ref="O86" r:id="rId70"/>
-    <hyperlink ref="O87" r:id="rId71"/>
-    <hyperlink ref="O89" r:id="rId72"/>
-    <hyperlink ref="O88" r:id="rId73"/>
-    <hyperlink ref="O58" r:id="rId74"/>
-    <hyperlink ref="O47" r:id="rId75"/>
-    <hyperlink ref="O90" r:id="rId76"/>
-    <hyperlink ref="O42" r:id="rId77"/>
+    <hyperlink ref="O11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="O12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="O13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="O14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="O16" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="O17" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="O24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O25" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O26" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O28" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O29" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O30" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O31" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O32" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O33" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O34" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O35" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O36" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O37" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O39" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O40" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O41" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O43" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O44" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="O45" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O46" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O48" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O50" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O51" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O52" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O53" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O54" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O55" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O56" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O57" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O69" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O59" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O60" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O61" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O62" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O63" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O64" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O65" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O66" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O67" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O68" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O70" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O71" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O72" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O75" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O76" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O73" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O79" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O80" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O81" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="O82" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O83" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O84" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="O85" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O86" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O87" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O89" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O88" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O58" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O47" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O90" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="O42" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="O10" r:id="rId77" xr:uid="{5D88A11D-3624-47E9-BBD7-2366F8BA7980}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId78"/>

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB40EDC2-CBB5-4BE0-A2E3-1495B815E57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836C6BEA-F6BF-4605-9BD0-374D7807DBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1429,9 +1432,6 @@
     <t>DO NOT MOUNT BUT ORDER</t>
   </si>
   <si>
-    <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SBx1, SBx2, SBx3, SBx4</t>
-  </si>
-  <si>
     <t>U8, U9</t>
   </si>
   <si>
@@ -1604,6 +1604,9 @@
   </si>
   <si>
     <t>C178594</t>
+  </si>
+  <si>
+    <t>SB1, SB3, SB4, SB6, SB7, SB9, SB11, SBx1, SBx2, SBx3, SBx4</t>
   </si>
 </sst>
 </file>
@@ -2118,7 +2121,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2291,9 +2294,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2444,6 +2444,9 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2453,7 +2456,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3064,17 +3082,17 @@
       <c r="F10" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="G10" s="120" t="s">
+      <c r="G10" s="116" t="s">
         <v>142</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>227</v>
       </c>
       <c r="I10" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="J10" s="37" t="s">
         <v>478</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>479</v>
       </c>
       <c r="K10" s="38" t="s">
         <v>261</v>
@@ -3104,71 +3122,71 @@
     <row r="11" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B45" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B74" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="80" t="s">
         <v>316</v>
       </c>
-      <c r="D11" s="82" t="s">
-        <v>463</v>
-      </c>
-      <c r="E11" s="83" t="s">
+      <c r="D11" s="81" t="s">
+        <v>462</v>
+      </c>
+      <c r="E11" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="82" t="s">
+      <c r="F11" s="81" t="s">
         <v>143</v>
       </c>
-      <c r="G11" s="83" t="s">
+      <c r="G11" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="H11" s="82" t="s">
+      <c r="H11" s="81" t="s">
         <v>228</v>
       </c>
-      <c r="I11" s="82" t="s">
-        <v>314</v>
-      </c>
-      <c r="J11" s="82" t="s">
+      <c r="I11" s="81" t="s">
+        <v>314</v>
+      </c>
+      <c r="J11" s="81" t="s">
         <v>343</v>
       </c>
-      <c r="K11" s="83" t="s">
+      <c r="K11" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="L11" s="82">
+      <c r="L11" s="81">
         <v>15</v>
       </c>
-      <c r="M11" s="84">
+      <c r="M11" s="83">
         <f>L11*20</f>
         <v>300</v>
       </c>
-      <c r="N11" s="84">
+      <c r="N11" s="83">
         <v>300</v>
       </c>
-      <c r="O11" s="85" t="s">
+      <c r="O11" s="84" t="s">
         <v>342</v>
       </c>
-      <c r="P11" s="84">
+      <c r="P11" s="83">
         <v>1.4E-3</v>
       </c>
-      <c r="Q11" s="84">
+      <c r="Q11" s="83">
         <f>N11*P11</f>
         <v>0.42</v>
       </c>
-      <c r="R11" s="84" t="s">
-        <v>462</v>
+      <c r="R11" s="83" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
-        <f>ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="60" t="s">
         <v>316</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>70</v>
@@ -3191,7 +3209,7 @@
       <c r="K12" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="L12" s="86">
+      <c r="L12" s="85">
         <v>2</v>
       </c>
       <c r="M12" s="41">
@@ -3211,7 +3229,7 @@
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="76"/>
+      <c r="R12" s="75"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -3246,14 +3264,14 @@
       <c r="K13" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="L13" s="87">
+      <c r="L13" s="86">
         <v>1</v>
       </c>
       <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="88">
+      <c r="N13" s="87">
         <v>40</v>
       </c>
       <c r="O13" s="64" t="s">
@@ -3266,12 +3284,12 @@
         <f t="shared" ref="Q13" si="3">N13*P13</f>
         <v>1.4359999999999999</v>
       </c>
-      <c r="R13" s="77"/>
+      <c r="R13" s="76"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
-        <f>ROW(B14) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="60" t="s">
@@ -3321,7 +3339,7 @@
         <f>P14*N14</f>
         <v>8.18</v>
       </c>
-      <c r="R14" s="76"/>
+      <c r="R14" s="75"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
@@ -3333,7 +3351,7 @@
         <v>316</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>73</v>
@@ -3356,14 +3374,14 @@
       <c r="K15" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="L15" s="87">
+      <c r="L15" s="86">
         <v>3</v>
       </c>
       <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N15" s="88">
+      <c r="N15" s="87">
         <v>100</v>
       </c>
       <c r="O15" s="64" t="s">
@@ -3376,30 +3394,30 @@
         <f t="shared" ref="Q15" si="4">N15*P15</f>
         <v>0.59</v>
       </c>
-      <c r="R15" s="77"/>
+      <c r="R15" s="76"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
-        <f>ROW(B16) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="60" t="s">
         <v>316</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F16" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="101" t="s">
+      <c r="G16" s="100" t="s">
         <v>431</v>
       </c>
-      <c r="H16" s="86" t="s">
+      <c r="H16" s="85" t="s">
         <v>231</v>
       </c>
       <c r="I16" s="37" t="s">
@@ -3431,7 +3449,7 @@
         <f t="shared" ref="Q16" si="5">P16*N16</f>
         <v>4.3159999999999998</v>
       </c>
-      <c r="R16" s="76"/>
+      <c r="R16" s="75"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
@@ -3494,109 +3512,109 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="102" t="s">
+      <c r="C18" s="101" t="s">
         <v>316</v>
       </c>
-      <c r="D18" s="103" t="s">
+      <c r="D18" s="102" t="s">
         <v>355</v>
       </c>
-      <c r="E18" s="104" t="s">
+      <c r="E18" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="103" t="s">
+      <c r="F18" s="102" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="104" t="s">
+      <c r="G18" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="H18" s="103" t="s">
+      <c r="H18" s="102" t="s">
         <v>232</v>
       </c>
-      <c r="I18" s="103" t="s">
+      <c r="I18" s="102" t="s">
         <v>350</v>
       </c>
-      <c r="J18" s="103" t="s">
+      <c r="J18" s="102" t="s">
         <v>349</v>
       </c>
-      <c r="K18" s="104" t="s">
+      <c r="K18" s="103" t="s">
         <v>269</v>
       </c>
-      <c r="L18" s="103">
+      <c r="L18" s="102">
         <v>8</v>
       </c>
-      <c r="M18" s="96">
+      <c r="M18" s="95">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N18" s="96">
+      <c r="N18" s="95">
         <v>180</v>
       </c>
-      <c r="O18" s="105" t="s">
+      <c r="O18" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P18" s="96">
+      <c r="P18" s="95">
         <v>3.09E-2</v>
       </c>
-      <c r="Q18" s="96">
+      <c r="Q18" s="95">
         <f t="shared" ref="Q18" si="7">N18*P18</f>
         <v>5.5620000000000003</v>
       </c>
-      <c r="R18" s="96"/>
+      <c r="R18" s="95"/>
     </row>
     <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
-        <f>ROW(B19) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="105" t="s">
         <v>316</v>
       </c>
-      <c r="D19" s="107" t="s">
+      <c r="D19" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="108" t="s">
+      <c r="E19" s="107" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="107" t="s">
+      <c r="F19" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="108" t="s">
+      <c r="G19" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="H19" s="107" t="s">
+      <c r="H19" s="106" t="s">
         <v>233</v>
       </c>
-      <c r="I19" s="107" t="s">
+      <c r="I19" s="106" t="s">
         <v>351</v>
       </c>
-      <c r="J19" s="107" t="s">
+      <c r="J19" s="106" t="s">
         <v>352</v>
       </c>
-      <c r="K19" s="108" t="s">
+      <c r="K19" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="L19" s="107">
+      <c r="L19" s="106">
         <v>1</v>
       </c>
-      <c r="M19" s="109">
+      <c r="M19" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N19" s="109">
+      <c r="N19" s="108">
         <v>50</v>
       </c>
-      <c r="O19" s="110" t="s">
+      <c r="O19" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P19" s="109">
+      <c r="P19" s="108">
         <v>5.3E-3</v>
       </c>
-      <c r="Q19" s="109">
+      <c r="Q19" s="108">
         <f t="shared" ref="Q19" si="8">P19*N19</f>
         <v>0.26500000000000001</v>
       </c>
-      <c r="R19" s="109"/>
+      <c r="R19" s="108"/>
     </row>
     <row r="20" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -3604,114 +3622,114 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="102" t="s">
+      <c r="C20" s="101" t="s">
         <v>316</v>
       </c>
-      <c r="D20" s="103" t="s">
+      <c r="D20" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="104" t="s">
+      <c r="E20" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="103" t="s">
+      <c r="F20" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G20" s="103" t="s">
+      <c r="G20" s="102" t="s">
         <v>146</v>
       </c>
-      <c r="H20" s="103" t="s">
+      <c r="H20" s="102" t="s">
         <v>234</v>
       </c>
-      <c r="I20" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J20" s="103" t="s">
+      <c r="I20" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J20" s="102" t="s">
         <v>353</v>
       </c>
-      <c r="K20" s="104" t="s">
+      <c r="K20" s="103" t="s">
         <v>261</v>
       </c>
-      <c r="L20" s="103">
+      <c r="L20" s="102">
         <v>1</v>
       </c>
-      <c r="M20" s="96">
+      <c r="M20" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N20" s="96">
+      <c r="N20" s="95">
         <v>22</v>
       </c>
-      <c r="O20" s="105" t="s">
+      <c r="O20" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P20" s="96">
+      <c r="P20" s="95">
         <v>0.22189999999999999</v>
       </c>
-      <c r="Q20" s="96">
+      <c r="Q20" s="95">
         <f t="shared" ref="Q20" si="9">N20*P20</f>
         <v>4.8818000000000001</v>
       </c>
-      <c r="R20" s="96"/>
+      <c r="R20" s="95"/>
     </row>
     <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
-        <f>ROW(B21) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="106" t="s">
+      <c r="C21" s="105" t="s">
         <v>316</v>
       </c>
-      <c r="D21" s="107" t="s">
+      <c r="D21" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="108" t="s">
+      <c r="E21" s="107" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="107" t="s">
+      <c r="F21" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="108" t="s">
+      <c r="G21" s="107" t="s">
         <v>190</v>
       </c>
-      <c r="H21" s="107" t="s">
+      <c r="H21" s="106" t="s">
         <v>228</v>
       </c>
-      <c r="I21" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J21" s="107" t="s">
+      <c r="I21" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J21" s="106" t="s">
         <v>354</v>
       </c>
-      <c r="K21" s="108" t="s">
+      <c r="K21" s="107" t="s">
         <v>271</v>
       </c>
-      <c r="L21" s="107">
+      <c r="L21" s="106">
         <v>2</v>
       </c>
-      <c r="M21" s="109">
+      <c r="M21" s="108">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N21" s="109">
+      <c r="N21" s="108">
         <v>50</v>
       </c>
-      <c r="O21" s="110" t="s">
+      <c r="O21" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P21" s="109">
+      <c r="P21" s="108">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="Q21" s="109">
+      <c r="Q21" s="108">
         <f t="shared" ref="Q21" si="10">P21*N21</f>
         <v>0.38500000000000001</v>
       </c>
-      <c r="R21" s="109"/>
+      <c r="R21" s="108"/>
     </row>
     <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="60" t="s">
@@ -3816,12 +3834,12 @@
         <f t="shared" ref="Q23" si="12">N23*P23</f>
         <v>0.7679999999999999</v>
       </c>
-      <c r="R23" s="77"/>
+      <c r="R23" s="76"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
-        <f>ROW(B24) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
@@ -3836,7 +3854,7 @@
       <c r="F24" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="65">
+      <c r="G24" s="123">
         <v>885012205080</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -3934,114 +3952,114 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="102" t="s">
+      <c r="C26" s="101" t="s">
         <v>316</v>
       </c>
-      <c r="D26" s="103" t="s">
+      <c r="D26" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="111" t="s">
+      <c r="E26" s="110" t="s">
         <v>429</v>
       </c>
-      <c r="F26" s="103" t="s">
+      <c r="F26" s="102" t="s">
         <v>143</v>
       </c>
-      <c r="G26" s="111" t="s">
-        <v>455</v>
-      </c>
-      <c r="H26" s="112" t="s">
+      <c r="G26" s="110" t="s">
+        <v>454</v>
+      </c>
+      <c r="H26" s="111" t="s">
         <v>249</v>
       </c>
-      <c r="I26" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J26" s="103" t="s">
+      <c r="I26" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J26" s="102" t="s">
         <v>430</v>
       </c>
-      <c r="K26" s="111" t="s">
+      <c r="K26" s="110" t="s">
         <v>442</v>
       </c>
-      <c r="L26" s="103">
+      <c r="L26" s="102">
         <v>1</v>
       </c>
-      <c r="M26" s="96">
+      <c r="M26" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N26" s="96">
+      <c r="N26" s="95">
         <v>100</v>
       </c>
-      <c r="O26" s="105" t="s">
+      <c r="O26" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P26" s="96">
+      <c r="P26" s="95">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q26" s="96">
+      <c r="Q26" s="95">
         <f t="shared" ref="Q26" si="15">N26*P26</f>
         <v>0.33999999999999997</v>
       </c>
-      <c r="R26" s="76"/>
+      <c r="R26" s="75"/>
     </row>
     <row r="27" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
-        <f>ROW(B27) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="106" t="s">
+      <c r="C27" s="105" t="s">
         <v>316</v>
       </c>
-      <c r="D27" s="107" t="s">
+      <c r="D27" s="106" t="s">
         <v>441</v>
       </c>
-      <c r="E27" s="108" t="s">
+      <c r="E27" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="107" t="s">
+      <c r="F27" s="106" t="s">
         <v>147</v>
       </c>
-      <c r="G27" s="108" t="s">
+      <c r="G27" s="107" t="s">
         <v>194</v>
       </c>
-      <c r="H27" s="107" t="s">
+      <c r="H27" s="106" t="s">
         <v>231</v>
       </c>
-      <c r="I27" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J27" s="107" t="s">
+      <c r="I27" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J27" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K27" s="108" t="s">
+      <c r="K27" s="107" t="s">
         <v>275</v>
       </c>
-      <c r="L27" s="107">
+      <c r="L27" s="106">
         <v>1</v>
       </c>
-      <c r="M27" s="109">
+      <c r="M27" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="109">
+      <c r="N27" s="108">
         <v>30</v>
       </c>
-      <c r="O27" s="110" t="s">
+      <c r="O27" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P27" s="109">
+      <c r="P27" s="108">
         <v>0.2525</v>
       </c>
-      <c r="Q27" s="109">
+      <c r="Q27" s="108">
         <f t="shared" ref="Q27" si="16">P27*N27</f>
         <v>7.5750000000000002</v>
       </c>
-      <c r="R27" s="79"/>
+      <c r="R27" s="78"/>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
@@ -4151,7 +4169,7 @@
     <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="60" t="s">
@@ -4206,57 +4224,57 @@
     <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
-        <f>ROW(B31) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="106" t="s">
+      <c r="C31" s="105" t="s">
         <v>316</v>
       </c>
-      <c r="D31" s="107" t="s">
+      <c r="D31" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="108" t="s">
+      <c r="E31" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="107" t="s">
+      <c r="F31" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="108" t="s">
+      <c r="G31" s="107" t="s">
         <v>197</v>
       </c>
-      <c r="H31" s="107" t="s">
+      <c r="H31" s="106" t="s">
         <v>228</v>
       </c>
-      <c r="I31" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J31" s="107" t="s">
+      <c r="I31" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J31" s="106" t="s">
         <v>365</v>
       </c>
-      <c r="K31" s="108" t="s">
+      <c r="K31" s="107" t="s">
         <v>279</v>
       </c>
-      <c r="L31" s="107">
+      <c r="L31" s="106">
         <v>4</v>
       </c>
-      <c r="M31" s="109">
+      <c r="M31" s="108">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N31" s="109">
+      <c r="N31" s="108">
         <v>100</v>
       </c>
-      <c r="O31" s="110" t="s">
+      <c r="O31" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P31" s="109">
+      <c r="P31" s="108">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q31" s="109">
+      <c r="Q31" s="108">
         <f t="shared" ref="Q31" si="20">P31*N31</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="R31" s="109"/>
+      <c r="R31" s="108"/>
     </row>
     <row r="32" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -4264,109 +4282,109 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="102" t="s">
+      <c r="C32" s="101" t="s">
         <v>317</v>
       </c>
-      <c r="D32" s="103" t="s">
+      <c r="D32" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="104" t="s">
+      <c r="E32" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="103" t="s">
+      <c r="F32" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G32" s="104" t="s">
+      <c r="G32" s="103" t="s">
         <v>150</v>
       </c>
-      <c r="H32" s="103" t="s">
+      <c r="H32" s="102" t="s">
         <v>237</v>
       </c>
-      <c r="I32" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J32" s="103" t="s">
+      <c r="I32" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J32" s="102" t="s">
         <v>366</v>
       </c>
-      <c r="K32" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L32" s="103">
+      <c r="K32" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L32" s="102">
         <v>1</v>
       </c>
-      <c r="M32" s="96">
+      <c r="M32" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N32" s="96">
+      <c r="N32" s="95">
         <v>30</v>
       </c>
-      <c r="O32" s="105" t="s">
+      <c r="O32" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P32" s="96">
+      <c r="P32" s="95">
         <v>4.87E-2</v>
       </c>
-      <c r="Q32" s="96">
+      <c r="Q32" s="95">
         <f t="shared" ref="Q32" si="21">N32*P32</f>
         <v>1.4610000000000001</v>
       </c>
-      <c r="R32" s="96"/>
+      <c r="R32" s="95"/>
     </row>
     <row r="33" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
-        <f>ROW(B33) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="106" t="s">
+      <c r="C33" s="105" t="s">
         <v>317</v>
       </c>
-      <c r="D33" s="107" t="s">
+      <c r="D33" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="108" t="s">
+      <c r="E33" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="107" t="s">
+      <c r="F33" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="G33" s="108" t="s">
+      <c r="G33" s="107" t="s">
         <v>280</v>
       </c>
-      <c r="H33" s="107" t="s">
+      <c r="H33" s="106" t="s">
         <v>238</v>
       </c>
-      <c r="I33" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J33" s="107" t="s">
+      <c r="I33" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J33" s="106" t="s">
         <v>367</v>
       </c>
-      <c r="K33" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L33" s="107">
+      <c r="K33" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L33" s="106">
         <v>1</v>
       </c>
-      <c r="M33" s="109">
+      <c r="M33" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N33" s="109">
+      <c r="N33" s="108">
         <v>30</v>
       </c>
-      <c r="O33" s="110" t="s">
+      <c r="O33" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P33" s="109">
+      <c r="P33" s="108">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="Q33" s="109">
+      <c r="Q33" s="108">
         <f t="shared" ref="Q33" si="22">P33*N33</f>
         <v>2.2290000000000001</v>
       </c>
-      <c r="R33" s="109"/>
+      <c r="R33" s="108"/>
     </row>
     <row r="34" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -4374,112 +4392,112 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="102" t="s">
+      <c r="C34" s="101" t="s">
         <v>317</v>
       </c>
-      <c r="D34" s="103" t="s">
-        <v>460</v>
-      </c>
-      <c r="E34" s="104" t="s">
+      <c r="D34" s="102" t="s">
+        <v>459</v>
+      </c>
+      <c r="E34" s="103" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="103" t="s">
+      <c r="F34" s="102" t="s">
         <v>151</v>
       </c>
-      <c r="G34" s="104" t="s">
+      <c r="G34" s="103" t="s">
         <v>281</v>
       </c>
-      <c r="H34" s="103" t="s">
+      <c r="H34" s="102" t="s">
         <v>238</v>
       </c>
-      <c r="I34" s="103" t="s">
+      <c r="I34" s="102" t="s">
         <v>281</v>
       </c>
-      <c r="J34" s="103" t="s">
+      <c r="J34" s="102" t="s">
         <v>368</v>
       </c>
-      <c r="K34" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L34" s="103">
+      <c r="K34" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L34" s="102">
         <v>2</v>
       </c>
-      <c r="M34" s="96">
+      <c r="M34" s="95">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N34" s="96">
+      <c r="N34" s="95">
         <v>60</v>
       </c>
-      <c r="O34" s="105" t="s">
+      <c r="O34" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P34" s="96">
+      <c r="P34" s="95">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="Q34" s="96">
+      <c r="Q34" s="95">
         <f t="shared" ref="Q34" si="23">N34*P34</f>
         <v>1.734</v>
       </c>
-      <c r="R34" s="78"/>
+      <c r="R34" s="77"/>
     </row>
     <row r="35" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
-        <f>ROW(B35) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="C35" s="88" t="s">
         <v>317</v>
       </c>
-      <c r="D35" s="90" t="s">
+      <c r="D35" s="89" t="s">
         <v>443</v>
       </c>
-      <c r="E35" s="91" t="s">
+      <c r="E35" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="F35" s="90" t="s">
+      <c r="F35" s="89" t="s">
         <v>152</v>
       </c>
-      <c r="G35" s="91" t="s">
+      <c r="G35" s="120" t="s">
         <v>198</v>
       </c>
-      <c r="H35" s="90" t="s">
+      <c r="H35" s="89" t="s">
         <v>239</v>
       </c>
-      <c r="I35" s="90" t="s">
+      <c r="I35" s="89" t="s">
         <v>369</v>
       </c>
-      <c r="J35" s="90" t="s">
+      <c r="J35" s="89" t="s">
         <v>370</v>
       </c>
-      <c r="K35" s="91" t="s">
-        <v>314</v>
-      </c>
-      <c r="L35" s="92">
+      <c r="K35" s="90" t="s">
+        <v>314</v>
+      </c>
+      <c r="L35" s="91">
         <v>8</v>
       </c>
-      <c r="M35" s="93">
+      <c r="M35" s="92">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N35" s="94">
+      <c r="N35" s="93">
         <v>170</v>
       </c>
-      <c r="O35" s="95" t="s">
+      <c r="O35" s="94" t="s">
         <v>342</v>
       </c>
-      <c r="P35" s="93">
+      <c r="P35" s="92">
         <v>0.12590000000000001</v>
       </c>
-      <c r="Q35" s="93">
+      <c r="Q35" s="92">
         <f t="shared" ref="Q35" si="24">P35*N35</f>
         <v>21.403000000000002</v>
       </c>
-      <c r="R35" s="84" t="s">
+      <c r="R35" s="83" t="s">
         <v>444</v>
       </c>
-      <c r="U35" s="116"/>
+      <c r="U35" s="115"/>
     </row>
     <row r="36" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -4487,109 +4505,109 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="102" t="s">
+      <c r="C36" s="101" t="s">
         <v>319</v>
       </c>
-      <c r="D36" s="103" t="s">
+      <c r="D36" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="104" t="s">
+      <c r="E36" s="103" t="s">
         <v>92</v>
       </c>
-      <c r="F36" s="103" t="s">
+      <c r="F36" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G36" s="104" t="s">
+      <c r="G36" s="121" t="s">
         <v>153</v>
       </c>
-      <c r="H36" s="103" t="s">
+      <c r="H36" s="102" t="s">
         <v>240</v>
       </c>
-      <c r="I36" s="103" t="s">
+      <c r="I36" s="102" t="s">
         <v>371</v>
       </c>
-      <c r="J36" s="103" t="s">
+      <c r="J36" s="102" t="s">
         <v>372</v>
       </c>
-      <c r="K36" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L36" s="103">
+      <c r="K36" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L36" s="102">
         <v>1</v>
       </c>
-      <c r="M36" s="96">
+      <c r="M36" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N36" s="96">
+      <c r="N36" s="95">
         <v>30</v>
       </c>
-      <c r="O36" s="105" t="s">
+      <c r="O36" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P36" s="96">
+      <c r="P36" s="95">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="Q36" s="96">
+      <c r="Q36" s="95">
         <f t="shared" ref="Q36" si="25">N36*P36</f>
         <v>1.68</v>
       </c>
-      <c r="R36" s="96"/>
+      <c r="R36" s="95"/>
     </row>
     <row r="37" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
-        <f>ROW(B37) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="106" t="s">
+      <c r="C37" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="D37" s="107" t="s">
+      <c r="D37" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="108" t="s">
+      <c r="E37" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="107" t="s">
+      <c r="F37" s="106" t="s">
         <v>309</v>
       </c>
-      <c r="G37" s="108" t="s">
+      <c r="G37" s="107" t="s">
         <v>154</v>
       </c>
-      <c r="H37" s="107" t="s">
+      <c r="H37" s="106" t="s">
         <v>233</v>
       </c>
-      <c r="I37" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J37" s="107" t="s">
+      <c r="I37" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J37" s="106" t="s">
         <v>373</v>
       </c>
-      <c r="K37" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L37" s="107">
+      <c r="K37" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L37" s="106">
         <v>4</v>
       </c>
-      <c r="M37" s="109">
+      <c r="M37" s="108">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N37" s="109">
+      <c r="N37" s="108">
         <v>100</v>
       </c>
-      <c r="O37" s="110" t="s">
+      <c r="O37" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P37" s="109">
+      <c r="P37" s="108">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="Q37" s="109">
+      <c r="Q37" s="108">
         <f t="shared" ref="Q37" si="26">P37*N37</f>
         <v>2.9499999999999997</v>
       </c>
-      <c r="R37" s="109"/>
+      <c r="R37" s="108"/>
     </row>
     <row r="38" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -4597,109 +4615,109 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="102" t="s">
+      <c r="C38" s="101" t="s">
         <v>320</v>
       </c>
-      <c r="D38" s="103" t="s">
+      <c r="D38" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="104" t="s">
+      <c r="E38" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="103" t="s">
+      <c r="F38" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G38" s="104" t="s">
+      <c r="G38" s="121" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="103" t="s">
+      <c r="H38" s="102" t="s">
         <v>241</v>
       </c>
-      <c r="I38" s="103" t="s">
+      <c r="I38" s="102" t="s">
         <v>374</v>
       </c>
-      <c r="J38" s="103" t="s">
+      <c r="J38" s="102" t="s">
         <v>375</v>
       </c>
-      <c r="K38" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L38" s="103">
+      <c r="K38" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L38" s="102">
         <v>1</v>
       </c>
-      <c r="M38" s="96">
+      <c r="M38" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N38" s="96">
+      <c r="N38" s="95">
         <v>21</v>
       </c>
-      <c r="O38" s="105" t="s">
+      <c r="O38" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P38" s="96">
+      <c r="P38" s="95">
         <v>0.53559999999999997</v>
       </c>
-      <c r="Q38" s="96">
+      <c r="Q38" s="95">
         <f t="shared" ref="Q38" si="27">N38*P38</f>
         <v>11.247599999999998</v>
       </c>
-      <c r="R38" s="78"/>
+      <c r="R38" s="77"/>
     </row>
     <row r="39" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
-        <f>ROW(B39) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="106" t="s">
+      <c r="C39" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="D39" s="107" t="s">
+      <c r="D39" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="108" t="s">
+      <c r="E39" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="107" t="s">
+      <c r="F39" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G39" s="108" t="s">
+      <c r="G39" s="122" t="s">
         <v>156</v>
       </c>
-      <c r="H39" s="107" t="s">
+      <c r="H39" s="106" t="s">
         <v>242</v>
       </c>
-      <c r="I39" s="107" t="s">
+      <c r="I39" s="106" t="s">
         <v>376</v>
       </c>
-      <c r="J39" s="107" t="s">
+      <c r="J39" s="106" t="s">
         <v>377</v>
       </c>
-      <c r="K39" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L39" s="107">
+      <c r="K39" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L39" s="106">
         <v>2</v>
       </c>
-      <c r="M39" s="109">
+      <c r="M39" s="108">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N39" s="109">
+      <c r="N39" s="108">
         <v>42</v>
       </c>
-      <c r="O39" s="110" t="s">
+      <c r="O39" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P39" s="109">
+      <c r="P39" s="108">
         <v>0.65639999999999998</v>
       </c>
-      <c r="Q39" s="109">
+      <c r="Q39" s="108">
         <f t="shared" ref="Q39" si="28">P39*N39</f>
         <v>27.5688</v>
       </c>
-      <c r="R39" s="79"/>
+      <c r="R39" s="78"/>
     </row>
     <row r="40" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
@@ -4707,161 +4725,164 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="102" t="s">
+      <c r="C40" s="101" t="s">
         <v>321</v>
       </c>
-      <c r="D40" s="103" t="s">
+      <c r="D40" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="104" t="s">
+      <c r="E40" s="103" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="103" t="s">
+      <c r="F40" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G40" s="104" t="s">
+      <c r="G40" s="103" t="s">
         <v>157</v>
       </c>
-      <c r="H40" s="103" t="s">
+      <c r="H40" s="102" t="s">
         <v>243</v>
       </c>
-      <c r="I40" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J40" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K40" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L40" s="103">
+      <c r="I40" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J40" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="K40" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L40" s="102">
         <v>1</v>
       </c>
-      <c r="M40" s="96">
+      <c r="M40" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N40" s="96">
+      <c r="N40" s="95">
         <v>21</v>
       </c>
-      <c r="O40" s="105" t="s">
+      <c r="O40" s="104" t="s">
         <v>378</v>
       </c>
-      <c r="P40" s="96">
+      <c r="P40" s="95">
         <v>1.2</v>
       </c>
-      <c r="Q40" s="96">
+      <c r="Q40" s="95">
         <f t="shared" ref="Q40" si="29">N40*P40</f>
         <v>25.2</v>
       </c>
-      <c r="R40" s="96"/>
+      <c r="R40" s="95"/>
     </row>
     <row r="41" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
-        <f>ROW(B41) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="106" t="s">
+      <c r="C41" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="D41" s="107" t="s">
+      <c r="D41" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="108" t="s">
+      <c r="E41" s="107" t="s">
         <v>97</v>
       </c>
-      <c r="F41" s="107" t="s">
+      <c r="F41" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G41" s="108" t="s">
+      <c r="G41" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="H41" s="107" t="s">
+      <c r="H41" s="106" t="s">
         <v>244</v>
       </c>
-      <c r="I41" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J41" s="107" t="s">
+      <c r="I41" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J41" s="106" t="s">
         <v>379</v>
       </c>
-      <c r="K41" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L41" s="107">
+      <c r="K41" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L41" s="106">
         <v>1</v>
       </c>
-      <c r="M41" s="109">
+      <c r="M41" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N41" s="109">
+      <c r="N41" s="108">
         <v>25</v>
       </c>
-      <c r="O41" s="110" t="s">
+      <c r="O41" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P41" s="109">
+      <c r="P41" s="108">
         <v>9.2200000000000004E-2</v>
       </c>
-      <c r="Q41" s="109">
+      <c r="Q41" s="108">
         <f t="shared" ref="Q41" si="30">P41*N41</f>
         <v>2.3050000000000002</v>
       </c>
-      <c r="R41" s="109"/>
+      <c r="R41" s="108"/>
     </row>
     <row r="42" spans="1:21" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="53"/>
-      <c r="C42" s="106" t="s">
+      <c r="B42" s="53">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="D42" s="107" t="s">
+      <c r="D42" s="106" t="s">
+        <v>472</v>
+      </c>
+      <c r="E42" s="107" t="s">
+        <v>474</v>
+      </c>
+      <c r="F42" s="106" t="s">
+        <v>308</v>
+      </c>
+      <c r="G42" s="107" t="s">
         <v>473</v>
       </c>
-      <c r="E42" s="108" t="s">
+      <c r="H42" s="106" t="s">
         <v>475</v>
       </c>
-      <c r="F42" s="107" t="s">
-        <v>308</v>
-      </c>
-      <c r="G42" s="108" t="s">
-        <v>474</v>
-      </c>
-      <c r="H42" s="107" t="s">
+      <c r="I42" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J42" s="106" t="s">
         <v>476</v>
       </c>
-      <c r="I42" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J42" s="107" t="s">
-        <v>477</v>
-      </c>
-      <c r="K42" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L42" s="107">
+      <c r="K42" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L42" s="106">
         <v>1</v>
       </c>
-      <c r="M42" s="109">
+      <c r="M42" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N42" s="109">
+      <c r="N42" s="108">
         <v>25</v>
       </c>
-      <c r="O42" s="110" t="s">
+      <c r="O42" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P42" s="109">
+      <c r="P42" s="108">
         <v>0.21210000000000001</v>
       </c>
-      <c r="Q42" s="109">
+      <c r="Q42" s="108">
         <f>P42*N42</f>
         <v>5.3025000000000002</v>
       </c>
-      <c r="R42" s="109"/>
+      <c r="R42" s="108"/>
     </row>
     <row r="43" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -4869,109 +4890,109 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="102" t="s">
+      <c r="C43" s="101" t="s">
         <v>318</v>
       </c>
-      <c r="D43" s="103" t="s">
+      <c r="D43" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="104" t="s">
+      <c r="E43" s="103" t="s">
         <v>98</v>
       </c>
-      <c r="F43" s="103" t="s">
+      <c r="F43" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G43" s="104" t="s">
+      <c r="G43" s="103" t="s">
         <v>159</v>
       </c>
-      <c r="H43" s="103" t="s">
+      <c r="H43" s="102" t="s">
         <v>233</v>
       </c>
-      <c r="I43" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J43" s="103" t="s">
+      <c r="I43" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J43" s="102" t="s">
         <v>380</v>
       </c>
-      <c r="K43" s="104" t="s">
+      <c r="K43" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="L43" s="103">
+      <c r="L43" s="102">
         <v>1</v>
       </c>
-      <c r="M43" s="96">
+      <c r="M43" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N43" s="96">
+      <c r="N43" s="95">
         <v>21</v>
       </c>
-      <c r="O43" s="105" t="s">
+      <c r="O43" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P43" s="96">
+      <c r="P43" s="95">
         <v>0.45629999999999998</v>
       </c>
-      <c r="Q43" s="96">
+      <c r="Q43" s="95">
         <f t="shared" ref="Q43" si="31">N43*P43</f>
         <v>9.5823</v>
       </c>
-      <c r="R43" s="96"/>
+      <c r="R43" s="95"/>
     </row>
     <row r="44" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
-        <f>ROW(B44) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="106" t="s">
+      <c r="C44" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="D44" s="107" t="s">
+      <c r="D44" s="106" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="108" t="s">
+      <c r="E44" s="107" t="s">
         <v>447</v>
       </c>
-      <c r="F44" s="107" t="s">
+      <c r="F44" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G44" s="108" t="s">
+      <c r="G44" s="107" t="s">
         <v>446</v>
       </c>
-      <c r="H44" s="107" t="s">
+      <c r="H44" s="106" t="s">
         <v>435</v>
       </c>
-      <c r="I44" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J44" s="107" t="s">
+      <c r="I44" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J44" s="106" t="s">
         <v>436</v>
       </c>
-      <c r="K44" s="108" t="s">
+      <c r="K44" s="107" t="s">
         <v>445</v>
       </c>
-      <c r="L44" s="107">
+      <c r="L44" s="106">
         <v>1</v>
       </c>
-      <c r="M44" s="109">
+      <c r="M44" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N44" s="109">
+      <c r="N44" s="108">
         <v>25</v>
       </c>
-      <c r="O44" s="110" t="s">
+      <c r="O44" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P44" s="109">
+      <c r="P44" s="108">
         <v>0.1012</v>
       </c>
-      <c r="Q44" s="109">
+      <c r="Q44" s="108">
         <f t="shared" ref="Q44" si="32">P44*N44</f>
         <v>2.5299999999999998</v>
       </c>
-      <c r="R44" s="77"/>
+      <c r="R44" s="76"/>
     </row>
     <row r="45" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
@@ -4979,716 +5000,716 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="102" t="s">
+      <c r="C45" s="101" t="s">
         <v>322</v>
       </c>
-      <c r="D45" s="103" t="s">
+      <c r="D45" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="104" t="s">
+      <c r="E45" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="F45" s="103" t="s">
+      <c r="F45" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G45" s="104" t="s">
+      <c r="G45" s="103" t="s">
         <v>160</v>
       </c>
-      <c r="H45" s="103" t="s">
+      <c r="H45" s="102" t="s">
         <v>245</v>
       </c>
-      <c r="I45" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J45" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K45" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L45" s="103">
+      <c r="I45" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J45" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="K45" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L45" s="102">
         <v>1</v>
       </c>
-      <c r="M45" s="96">
+      <c r="M45" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N45" s="96">
+      <c r="N45" s="95">
         <v>30</v>
       </c>
-      <c r="O45" s="105" t="s">
+      <c r="O45" s="104" t="s">
         <v>381</v>
       </c>
-      <c r="P45" s="96">
+      <c r="P45" s="95">
         <v>0.156</v>
       </c>
-      <c r="Q45" s="96">
+      <c r="Q45" s="95">
         <f t="shared" ref="Q45" si="33">N45*P45</f>
         <v>4.68</v>
       </c>
-      <c r="R45" s="96"/>
+      <c r="R45" s="95"/>
     </row>
     <row r="46" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
-        <f>ROW(B46) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="106" t="s">
+      <c r="C46" s="105" t="s">
         <v>322</v>
       </c>
-      <c r="D46" s="107" t="s">
+      <c r="D46" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="E46" s="108" t="s">
+      <c r="E46" s="107" t="s">
         <v>100</v>
       </c>
-      <c r="F46" s="107" t="s">
+      <c r="F46" s="106" t="s">
         <v>161</v>
       </c>
-      <c r="G46" s="108" t="s">
+      <c r="G46" s="107" t="s">
         <v>199</v>
       </c>
-      <c r="H46" s="107" t="s">
+      <c r="H46" s="106" t="s">
         <v>246</v>
       </c>
-      <c r="I46" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J46" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K46" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L46" s="107">
+      <c r="I46" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J46" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K46" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L46" s="106">
         <v>1</v>
       </c>
-      <c r="M46" s="109">
+      <c r="M46" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N46" s="109">
+      <c r="N46" s="108">
         <v>30</v>
       </c>
-      <c r="O46" s="110" t="s">
+      <c r="O46" s="109" t="s">
         <v>382</v>
       </c>
-      <c r="P46" s="109">
+      <c r="P46" s="108">
         <v>0.08</v>
       </c>
-      <c r="Q46" s="109">
+      <c r="Q46" s="108">
         <f t="shared" ref="Q46:Q47" si="34">P46*N46</f>
         <v>2.4</v>
       </c>
-      <c r="R46" s="109"/>
+      <c r="R46" s="108"/>
     </row>
     <row r="47" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
-        <f t="shared" ref="B47:B90" si="35">ROW(B47) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="106" t="s">
-        <v>464</v>
-      </c>
-      <c r="D47" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="E47" s="108" t="s">
+      <c r="C47" s="105" t="s">
+        <v>463</v>
+      </c>
+      <c r="D47" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="E47" s="107" t="s">
+        <v>465</v>
+      </c>
+      <c r="F47" s="106" t="s">
+        <v>308</v>
+      </c>
+      <c r="G47" s="107" t="s">
         <v>466</v>
       </c>
-      <c r="F47" s="107" t="s">
-        <v>308</v>
-      </c>
-      <c r="G47" s="108" t="s">
+      <c r="H47" s="106" t="s">
         <v>467</v>
       </c>
-      <c r="H47" s="107" t="s">
-        <v>468</v>
-      </c>
-      <c r="I47" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J47" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K47" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L47" s="107">
+      <c r="I47" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J47" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K47" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L47" s="106">
         <v>1</v>
       </c>
-      <c r="M47" s="109">
+      <c r="M47" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N47" s="109">
+      <c r="N47" s="108">
         <v>20</v>
       </c>
-      <c r="O47" s="110" t="s">
+      <c r="O47" s="109" t="s">
         <v>418</v>
       </c>
-      <c r="P47" s="109">
+      <c r="P47" s="108">
         <v>0.435</v>
       </c>
-      <c r="Q47" s="109">
+      <c r="Q47" s="108">
         <f t="shared" si="34"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="R47" s="79" t="s">
-        <v>465</v>
+      <c r="R47" s="78" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="102" t="s">
+      <c r="C48" s="101" t="s">
         <v>320</v>
       </c>
-      <c r="D48" s="103" t="s">
+      <c r="D48" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="E48" s="104" t="s">
+      <c r="E48" s="103" t="s">
         <v>101</v>
       </c>
-      <c r="F48" s="103" t="s">
+      <c r="F48" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G48" s="104" t="s">
+      <c r="G48" s="103" t="s">
         <v>162</v>
       </c>
-      <c r="H48" s="103" t="s">
+      <c r="H48" s="102" t="s">
         <v>247</v>
       </c>
-      <c r="I48" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J48" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K48" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L48" s="103">
+      <c r="I48" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J48" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="K48" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L48" s="102">
         <v>2</v>
       </c>
-      <c r="M48" s="96">
+      <c r="M48" s="95">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N48" s="96">
+      <c r="N48" s="95">
         <v>50</v>
       </c>
-      <c r="O48" s="105" t="s">
+      <c r="O48" s="104" t="s">
         <v>378</v>
       </c>
-      <c r="P48" s="96">
+      <c r="P48" s="95">
         <v>1.5</v>
       </c>
-      <c r="Q48" s="96">
-        <f t="shared" ref="Q48" si="36">N48*P48</f>
+      <c r="Q48" s="95">
+        <f t="shared" ref="Q48" si="35">N48*P48</f>
         <v>75</v>
       </c>
-      <c r="R48" s="96"/>
+      <c r="R48" s="95"/>
     </row>
     <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="97" t="s">
+      <c r="C49" s="96" t="s">
         <v>283</v>
       </c>
-      <c r="D49" s="98" t="s">
+      <c r="D49" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="E49" s="99" t="s">
+      <c r="E49" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="98" t="s">
+      <c r="F49" s="97" t="s">
         <v>163</v>
       </c>
-      <c r="G49" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="H49" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="I49" s="98"/>
-      <c r="J49" s="98"/>
-      <c r="K49" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="L49" s="98">
+      <c r="G49" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="H49" s="97" t="s">
+        <v>314</v>
+      </c>
+      <c r="I49" s="97"/>
+      <c r="J49" s="97"/>
+      <c r="K49" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="L49" s="97">
         <v>4</v>
       </c>
-      <c r="M49" s="66">
+      <c r="M49" s="65">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N49" s="66">
-        <f t="shared" ref="N49" si="37">M49+(M49*0.1)</f>
+      <c r="N49" s="65">
+        <f t="shared" ref="N49" si="36">M49+(M49*0.1)</f>
         <v>88</v>
       </c>
-      <c r="O49" s="66"/>
-      <c r="P49" s="66"/>
-      <c r="Q49" s="66">
-        <f t="shared" ref="Q49" si="38">P49*N49</f>
+      <c r="O49" s="65"/>
+      <c r="P49" s="65"/>
+      <c r="Q49" s="65">
+        <f t="shared" ref="Q49" si="37">P49*N49</f>
         <v>0</v>
       </c>
-      <c r="R49" s="66" t="s">
+      <c r="R49" s="65" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="102" t="s">
+      <c r="C50" s="101" t="s">
         <v>321</v>
       </c>
-      <c r="D50" s="103" t="s">
+      <c r="D50" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="104" t="s">
+      <c r="E50" s="103" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="103" t="s">
+      <c r="F50" s="102" t="s">
         <v>164</v>
       </c>
-      <c r="G50" s="104">
+      <c r="G50" s="103">
         <v>61300211121</v>
       </c>
-      <c r="H50" s="103" t="s">
+      <c r="H50" s="102" t="s">
         <v>235</v>
       </c>
-      <c r="I50" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J50" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K50" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L50" s="103">
+      <c r="I50" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J50" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="K50" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L50" s="102">
         <v>4</v>
       </c>
-      <c r="M50" s="96">
+      <c r="M50" s="95">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N50" s="96">
+      <c r="N50" s="95">
         <v>90</v>
       </c>
-      <c r="O50" s="105" t="s">
+      <c r="O50" s="104" t="s">
         <v>378</v>
       </c>
-      <c r="P50" s="96">
+      <c r="P50" s="95">
         <v>0.13</v>
       </c>
-      <c r="Q50" s="96">
-        <f t="shared" ref="Q50" si="39">N50*P50</f>
+      <c r="Q50" s="95">
+        <f t="shared" ref="Q50" si="38">N50*P50</f>
         <v>11.700000000000001</v>
       </c>
-      <c r="R50" s="96"/>
+      <c r="R50" s="95"/>
     </row>
     <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="106" t="s">
+      <c r="C51" s="105" t="s">
         <v>323</v>
       </c>
-      <c r="D51" s="107" t="s">
+      <c r="D51" s="106" t="s">
         <v>438</v>
       </c>
-      <c r="E51" s="108" t="s">
+      <c r="E51" s="107" t="s">
         <v>104</v>
       </c>
-      <c r="F51" s="107" t="s">
+      <c r="F51" s="106" t="s">
         <v>165</v>
       </c>
-      <c r="G51" s="108" t="s">
+      <c r="G51" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H51" s="107" t="s">
+      <c r="H51" s="106" t="s">
         <v>248</v>
       </c>
-      <c r="I51" s="107" t="s">
+      <c r="I51" s="106" t="s">
         <v>384</v>
       </c>
-      <c r="J51" s="107" t="s">
+      <c r="J51" s="106" t="s">
         <v>385</v>
       </c>
-      <c r="K51" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L51" s="107">
+      <c r="K51" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L51" s="106">
         <v>4</v>
       </c>
-      <c r="M51" s="109">
+      <c r="M51" s="108">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N51" s="109">
+      <c r="N51" s="108">
         <v>85</v>
       </c>
-      <c r="O51" s="110" t="s">
+      <c r="O51" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P51" s="109">
+      <c r="P51" s="108">
         <v>0.21740000000000001</v>
       </c>
-      <c r="Q51" s="109">
-        <f t="shared" ref="Q51" si="40">P51*N51</f>
+      <c r="Q51" s="108">
+        <f t="shared" ref="Q51" si="39">P51*N51</f>
         <v>18.478999999999999</v>
       </c>
-      <c r="R51" s="109"/>
+      <c r="R51" s="108"/>
     </row>
     <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="102" t="s">
+      <c r="C52" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="D52" s="103" t="s">
+      <c r="D52" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="E52" s="104" t="s">
+      <c r="E52" s="103" t="s">
         <v>105</v>
       </c>
-      <c r="F52" s="103" t="s">
+      <c r="F52" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="104" t="s">
+      <c r="G52" s="103" t="s">
         <v>201</v>
       </c>
-      <c r="H52" s="103" t="s">
+      <c r="H52" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="I52" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J52" s="103" t="s">
+      <c r="I52" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J52" s="102" t="s">
         <v>386</v>
       </c>
-      <c r="K52" s="104" t="s">
+      <c r="K52" s="103" t="s">
         <v>284</v>
       </c>
-      <c r="L52" s="103">
+      <c r="L52" s="102">
         <v>2</v>
       </c>
-      <c r="M52" s="96">
+      <c r="M52" s="95">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N52" s="96">
+      <c r="N52" s="95">
         <v>100</v>
       </c>
-      <c r="O52" s="105" t="s">
+      <c r="O52" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P52" s="96">
+      <c r="P52" s="95">
         <v>1E-3</v>
       </c>
-      <c r="Q52" s="96">
-        <f t="shared" ref="Q52" si="41">N52*P52</f>
+      <c r="Q52" s="95">
+        <f t="shared" ref="Q52" si="40">N52*P52</f>
         <v>0.1</v>
       </c>
-      <c r="R52" s="96"/>
+      <c r="R52" s="95"/>
     </row>
     <row r="53" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="106" t="s">
+      <c r="C53" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D53" s="107" t="s">
+      <c r="D53" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="E53" s="108" t="s">
+      <c r="E53" s="107" t="s">
         <v>106</v>
       </c>
-      <c r="F53" s="107" t="s">
+      <c r="F53" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="108" t="s">
+      <c r="G53" s="107" t="s">
         <v>202</v>
       </c>
-      <c r="H53" s="107" t="s">
+      <c r="H53" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I53" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J53" s="107" t="s">
+      <c r="I53" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J53" s="106" t="s">
         <v>387</v>
       </c>
-      <c r="K53" s="108" t="s">
+      <c r="K53" s="107" t="s">
         <v>285</v>
       </c>
-      <c r="L53" s="107">
+      <c r="L53" s="106">
         <v>1</v>
       </c>
-      <c r="M53" s="109">
+      <c r="M53" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N53" s="109">
+      <c r="N53" s="108">
         <v>100</v>
       </c>
-      <c r="O53" s="110" t="s">
+      <c r="O53" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P53" s="109">
+      <c r="P53" s="108">
         <v>1.4E-3</v>
       </c>
-      <c r="Q53" s="109">
-        <f t="shared" ref="Q53" si="42">P53*N53</f>
+      <c r="Q53" s="108">
+        <f t="shared" ref="Q53" si="41">P53*N53</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R53" s="109"/>
+      <c r="R53" s="108"/>
     </row>
     <row r="54" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="102" t="s">
+      <c r="C54" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="D54" s="103" t="s">
+      <c r="D54" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="E54" s="104" t="s">
+      <c r="E54" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="104" t="s">
+      <c r="G54" s="103" t="s">
         <v>203</v>
       </c>
-      <c r="H54" s="103" t="s">
+      <c r="H54" s="102" t="s">
         <v>249</v>
       </c>
-      <c r="I54" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J54" s="103" t="s">
+      <c r="I54" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J54" s="102" t="s">
         <v>388</v>
       </c>
-      <c r="K54" s="104" t="s">
+      <c r="K54" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="L54" s="103">
+      <c r="L54" s="102">
         <v>1</v>
       </c>
-      <c r="M54" s="96">
+      <c r="M54" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N54" s="96">
+      <c r="N54" s="95">
         <v>100</v>
       </c>
-      <c r="O54" s="105" t="s">
+      <c r="O54" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P54" s="96">
+      <c r="P54" s="95">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q54" s="96">
-        <f t="shared" ref="Q54" si="43">N54*P54</f>
+      <c r="Q54" s="95">
+        <f t="shared" ref="Q54" si="42">N54*P54</f>
         <v>0.16</v>
       </c>
-      <c r="R54" s="96"/>
+      <c r="R54" s="95"/>
     </row>
     <row r="55" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="106" t="s">
+      <c r="C55" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D55" s="107" t="s">
+      <c r="D55" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E55" s="108" t="s">
+      <c r="E55" s="107" t="s">
         <v>108</v>
       </c>
-      <c r="F55" s="107" t="s">
+      <c r="F55" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G55" s="108" t="s">
+      <c r="G55" s="107" t="s">
         <v>204</v>
       </c>
-      <c r="H55" s="107" t="s">
+      <c r="H55" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I55" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J55" s="107" t="s">
+      <c r="I55" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J55" s="106" t="s">
         <v>389</v>
       </c>
-      <c r="K55" s="108" t="s">
+      <c r="K55" s="107" t="s">
         <v>287</v>
       </c>
-      <c r="L55" s="107">
+      <c r="L55" s="106">
         <v>2</v>
       </c>
-      <c r="M55" s="109">
+      <c r="M55" s="108">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N55" s="109">
+      <c r="N55" s="108">
         <v>100</v>
       </c>
-      <c r="O55" s="110" t="s">
+      <c r="O55" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P55" s="109">
+      <c r="P55" s="108">
         <v>1.4E-3</v>
       </c>
-      <c r="Q55" s="109">
-        <f t="shared" ref="Q55" si="44">P55*N55</f>
+      <c r="Q55" s="108">
+        <f t="shared" ref="Q55" si="43">P55*N55</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R55" s="109"/>
+      <c r="R55" s="108"/>
     </row>
     <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="102" t="s">
+      <c r="C56" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="D56" s="103" t="s">
+      <c r="D56" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="E56" s="104" t="s">
+      <c r="E56" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G56" s="104" t="s">
+      <c r="G56" s="103" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="103" t="s">
+      <c r="H56" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="I56" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J56" s="103" t="s">
+      <c r="I56" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J56" s="102" t="s">
         <v>390</v>
       </c>
-      <c r="K56" s="104" t="s">
+      <c r="K56" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="L56" s="103">
+      <c r="L56" s="102">
         <v>4</v>
       </c>
-      <c r="M56" s="96">
+      <c r="M56" s="95">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N56" s="96">
+      <c r="N56" s="95">
         <v>100</v>
       </c>
-      <c r="O56" s="105" t="s">
+      <c r="O56" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P56" s="96">
+      <c r="P56" s="95">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q56" s="96">
-        <f t="shared" ref="Q56" si="45">N56*P56</f>
+      <c r="Q56" s="95">
+        <f t="shared" ref="Q56" si="44">N56*P56</f>
         <v>0.13</v>
       </c>
-      <c r="R56" s="96"/>
+      <c r="R56" s="95"/>
     </row>
     <row r="57" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="106" t="s">
+      <c r="C57" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D57" s="107" t="s">
+      <c r="D57" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="E57" s="108" t="s">
+      <c r="E57" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="107" t="s">
+      <c r="F57" s="106" t="s">
         <v>167</v>
       </c>
-      <c r="G57" s="108" t="s">
+      <c r="G57" s="107" t="s">
         <v>329</v>
       </c>
-      <c r="H57" s="107" t="s">
+      <c r="H57" s="106" t="s">
         <v>250</v>
       </c>
-      <c r="I57" s="107" t="s">
+      <c r="I57" s="106" t="s">
         <v>391</v>
       </c>
-      <c r="J57" s="107" t="s">
+      <c r="J57" s="106" t="s">
         <v>392</v>
       </c>
-      <c r="K57" s="108" t="s">
+      <c r="K57" s="107" t="s">
         <v>289</v>
       </c>
-      <c r="L57" s="107">
+      <c r="L57" s="106">
         <v>4</v>
       </c>
-      <c r="M57" s="109">
+      <c r="M57" s="108">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N57" s="109">
+      <c r="N57" s="108">
         <v>90</v>
       </c>
-      <c r="O57" s="110" t="s">
+      <c r="O57" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P57" s="109">
+      <c r="P57" s="108">
         <v>6.4500000000000002E-2</v>
       </c>
-      <c r="Q57" s="109">
-        <f t="shared" ref="Q57" si="46">P57*N57</f>
+      <c r="Q57" s="108">
+        <f t="shared" ref="Q57" si="45">P57*N57</f>
         <v>5.8049999999999997</v>
       </c>
-      <c r="R57" s="109"/>
+      <c r="R57" s="108"/>
     </row>
     <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
@@ -5725,520 +5746,520 @@
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N58" s="96">
+      <c r="N58" s="95">
         <v>100</v>
       </c>
-      <c r="O58" s="80" t="s">
+      <c r="O58" s="79" t="s">
         <v>342</v>
       </c>
       <c r="P58" s="37">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q58" s="37">
-        <f t="shared" ref="Q58" si="47">N58*P58</f>
+        <f t="shared" ref="Q58" si="46">N58*P58</f>
         <v>0.11</v>
       </c>
-      <c r="R58" s="76"/>
+      <c r="R58" s="75"/>
     </row>
     <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="106" t="s">
+      <c r="C59" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D59" s="107" t="s">
+      <c r="D59" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="108" t="s">
+      <c r="E59" s="107" t="s">
         <v>112</v>
       </c>
-      <c r="F59" s="107" t="s">
+      <c r="F59" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G59" s="108" t="s">
+      <c r="G59" s="107" t="s">
         <v>207</v>
       </c>
-      <c r="H59" s="107" t="s">
+      <c r="H59" s="106" t="s">
         <v>251</v>
       </c>
-      <c r="I59" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J59" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K59" s="108" t="s">
+      <c r="I59" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K59" s="107" t="s">
         <v>291</v>
       </c>
-      <c r="L59" s="107">
+      <c r="L59" s="106">
         <v>1</v>
       </c>
-      <c r="M59" s="109">
+      <c r="M59" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N59" s="109">
+      <c r="N59" s="108">
         <v>30</v>
       </c>
-      <c r="O59" s="110" t="s">
+      <c r="O59" s="109" t="s">
         <v>381</v>
       </c>
-      <c r="P59" s="109">
+      <c r="P59" s="108">
         <v>1.8589999999999999E-2</v>
       </c>
-      <c r="Q59" s="109">
-        <f t="shared" ref="Q59" si="48">P59*N59</f>
+      <c r="Q59" s="108">
+        <f t="shared" ref="Q59" si="47">P59*N59</f>
         <v>0.55769999999999997</v>
       </c>
-      <c r="R59" s="109"/>
+      <c r="R59" s="108"/>
     </row>
     <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="D60" s="103" t="s">
+      <c r="D60" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="104" t="s">
+      <c r="E60" s="103" t="s">
         <v>113</v>
       </c>
-      <c r="F60" s="103" t="s">
+      <c r="F60" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G60" s="104" t="s">
+      <c r="G60" s="103" t="s">
         <v>208</v>
       </c>
-      <c r="H60" s="103" t="s">
+      <c r="H60" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="I60" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J60" s="103" t="s">
+      <c r="I60" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J60" s="102" t="s">
         <v>394</v>
       </c>
-      <c r="K60" s="104" t="s">
+      <c r="K60" s="103" t="s">
         <v>292</v>
       </c>
-      <c r="L60" s="103">
+      <c r="L60" s="102">
         <v>1</v>
       </c>
-      <c r="M60" s="96">
+      <c r="M60" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="96">
+      <c r="N60" s="95">
         <v>100</v>
       </c>
-      <c r="O60" s="105" t="s">
+      <c r="O60" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P60" s="96">
+      <c r="P60" s="95">
         <v>1.4E-3</v>
       </c>
-      <c r="Q60" s="96">
-        <f t="shared" ref="Q60" si="49">N60*P60</f>
+      <c r="Q60" s="95">
+        <f t="shared" ref="Q60" si="48">N60*P60</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R60" s="96"/>
+      <c r="R60" s="95"/>
     </row>
     <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="106" t="s">
+      <c r="C61" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D61" s="107" t="s">
+      <c r="D61" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="108" t="s">
+      <c r="E61" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="F61" s="107" t="s">
+      <c r="F61" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G61" s="108" t="s">
+      <c r="G61" s="107" t="s">
         <v>209</v>
       </c>
-      <c r="H61" s="107" t="s">
+      <c r="H61" s="106" t="s">
         <v>251</v>
       </c>
-      <c r="I61" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J61" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K61" s="108" t="s">
+      <c r="I61" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J61" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K61" s="107" t="s">
         <v>293</v>
       </c>
-      <c r="L61" s="107">
+      <c r="L61" s="106">
         <v>1</v>
       </c>
-      <c r="M61" s="109">
+      <c r="M61" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="109">
+      <c r="N61" s="108">
         <v>50</v>
       </c>
-      <c r="O61" s="110" t="s">
+      <c r="O61" s="109" t="s">
         <v>381</v>
       </c>
-      <c r="P61" s="109">
+      <c r="P61" s="108">
         <v>4.6699999999999997E-3</v>
       </c>
-      <c r="Q61" s="109">
-        <f t="shared" ref="Q61" si="50">P61*N61</f>
+      <c r="Q61" s="108">
+        <f t="shared" ref="Q61" si="49">P61*N61</f>
         <v>0.23349999999999999</v>
       </c>
-      <c r="R61" s="109"/>
+      <c r="R61" s="108"/>
     </row>
     <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="102" t="s">
+      <c r="C62" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="D62" s="103" t="s">
+      <c r="D62" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="104" t="s">
+      <c r="E62" s="103" t="s">
         <v>115</v>
       </c>
-      <c r="F62" s="103" t="s">
+      <c r="F62" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G62" s="104" t="s">
+      <c r="G62" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="H62" s="103" t="s">
+      <c r="H62" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="I62" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="103" t="s">
+      <c r="I62" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="102" t="s">
         <v>395</v>
       </c>
-      <c r="K62" s="104" t="s">
+      <c r="K62" s="103" t="s">
         <v>294</v>
       </c>
-      <c r="L62" s="103">
+      <c r="L62" s="102">
         <v>1</v>
       </c>
-      <c r="M62" s="96">
+      <c r="M62" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N62" s="96">
+      <c r="N62" s="95">
         <v>100</v>
       </c>
-      <c r="O62" s="105" t="s">
+      <c r="O62" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P62" s="96">
+      <c r="P62" s="95">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q62" s="96">
-        <f t="shared" ref="Q62" si="51">N62*P62</f>
+      <c r="Q62" s="95">
+        <f t="shared" ref="Q62" si="50">N62*P62</f>
         <v>0.12</v>
       </c>
-      <c r="R62" s="96"/>
+      <c r="R62" s="95"/>
     </row>
     <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="106" t="s">
+      <c r="C63" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D63" s="107" t="s">
+      <c r="D63" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="E63" s="108" t="s">
+      <c r="E63" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="F63" s="107" t="s">
+      <c r="F63" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G63" s="108" t="s">
+      <c r="G63" s="107" t="s">
         <v>211</v>
       </c>
-      <c r="H63" s="107" t="s">
+      <c r="H63" s="106" t="s">
         <v>251</v>
       </c>
-      <c r="I63" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J63" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K63" s="108" t="s">
+      <c r="I63" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K63" s="107" t="s">
         <v>295</v>
       </c>
-      <c r="L63" s="107">
+      <c r="L63" s="106">
         <v>1</v>
       </c>
-      <c r="M63" s="109">
+      <c r="M63" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N63" s="109">
+      <c r="N63" s="108">
         <v>50</v>
       </c>
-      <c r="O63" s="110" t="s">
+      <c r="O63" s="109" t="s">
         <v>381</v>
       </c>
-      <c r="P63" s="109">
+      <c r="P63" s="108">
         <v>1.11E-2</v>
       </c>
-      <c r="Q63" s="109">
-        <f t="shared" ref="Q63" si="52">P63*N63</f>
+      <c r="Q63" s="108">
+        <f t="shared" ref="Q63" si="51">P63*N63</f>
         <v>0.55500000000000005</v>
       </c>
-      <c r="R63" s="109"/>
+      <c r="R63" s="108"/>
     </row>
     <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="102" t="s">
+      <c r="C64" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="D64" s="103" t="s">
+      <c r="D64" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="E64" s="104" t="s">
+      <c r="E64" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="F64" s="103" t="s">
+      <c r="F64" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G64" s="104" t="s">
+      <c r="G64" s="103" t="s">
         <v>212</v>
       </c>
-      <c r="H64" s="103" t="s">
+      <c r="H64" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="I64" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J64" s="103" t="s">
+      <c r="I64" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J64" s="102" t="s">
         <v>396</v>
       </c>
-      <c r="K64" s="104" t="s">
+      <c r="K64" s="103" t="s">
         <v>296</v>
       </c>
-      <c r="L64" s="103">
+      <c r="L64" s="102">
         <v>1</v>
       </c>
-      <c r="M64" s="96">
+      <c r="M64" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N64" s="96">
+      <c r="N64" s="95">
         <v>100</v>
       </c>
-      <c r="O64" s="105" t="s">
+      <c r="O64" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P64" s="96">
+      <c r="P64" s="95">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q64" s="96">
-        <f t="shared" ref="Q64" si="53">N64*P64</f>
+      <c r="Q64" s="95">
+        <f t="shared" ref="Q64" si="52">N64*P64</f>
         <v>0.21</v>
       </c>
-      <c r="R64" s="96"/>
+      <c r="R64" s="95"/>
     </row>
     <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="106" t="s">
+      <c r="C65" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D65" s="107" t="s">
+      <c r="D65" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="108" t="s">
+      <c r="E65" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="F65" s="107" t="s">
+      <c r="F65" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G65" s="108" t="s">
+      <c r="G65" s="107" t="s">
         <v>213</v>
       </c>
-      <c r="H65" s="107" t="s">
+      <c r="H65" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I65" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J65" s="107" t="s">
+      <c r="I65" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J65" s="106" t="s">
         <v>397</v>
       </c>
-      <c r="K65" s="108" t="s">
+      <c r="K65" s="107" t="s">
         <v>297</v>
       </c>
-      <c r="L65" s="107">
+      <c r="L65" s="106">
         <v>1</v>
       </c>
-      <c r="M65" s="109">
+      <c r="M65" s="108">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N65" s="109">
+      <c r="N65" s="108">
         <v>100</v>
       </c>
-      <c r="O65" s="110" t="s">
+      <c r="O65" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P65" s="109">
+      <c r="P65" s="108">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q65" s="109">
-        <f t="shared" ref="Q65" si="54">P65*N65</f>
+      <c r="Q65" s="108">
+        <f t="shared" ref="Q65" si="53">P65*N65</f>
         <v>0.16</v>
       </c>
-      <c r="R65" s="109"/>
+      <c r="R65" s="108"/>
     </row>
     <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="102" t="s">
+      <c r="C66" s="101" t="s">
         <v>324</v>
       </c>
-      <c r="D66" s="103" t="s">
+      <c r="D66" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="E66" s="104" t="s">
+      <c r="E66" s="103" t="s">
         <v>119</v>
       </c>
-      <c r="F66" s="103" t="s">
+      <c r="F66" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G66" s="104" t="s">
+      <c r="G66" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="H66" s="103" t="s">
+      <c r="H66" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="I66" s="103" t="s">
+      <c r="I66" s="102" t="s">
         <v>398</v>
       </c>
-      <c r="J66" s="103" t="s">
+      <c r="J66" s="102" t="s">
         <v>399</v>
       </c>
-      <c r="K66" s="104" t="s">
+      <c r="K66" s="103" t="s">
         <v>298</v>
       </c>
-      <c r="L66" s="103">
+      <c r="L66" s="102">
         <v>1</v>
       </c>
-      <c r="M66" s="96">
+      <c r="M66" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N66" s="96">
+      <c r="N66" s="95">
         <v>50</v>
       </c>
-      <c r="O66" s="105" t="s">
+      <c r="O66" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P66" s="96">
+      <c r="P66" s="95">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q66" s="96">
-        <f t="shared" ref="Q66" si="55">N66*P66</f>
+      <c r="Q66" s="95">
+        <f t="shared" ref="Q66" si="54">N66*P66</f>
         <v>0.34499999999999997</v>
       </c>
-      <c r="R66" s="96"/>
+      <c r="R66" s="95"/>
     </row>
     <row r="67" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="106" t="s">
+      <c r="C67" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D67" s="107" t="s">
-        <v>461</v>
-      </c>
-      <c r="E67" s="108" t="s">
+      <c r="D67" s="106" t="s">
+        <v>460</v>
+      </c>
+      <c r="E67" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="F67" s="107" t="s">
+      <c r="F67" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G67" s="108" t="s">
+      <c r="G67" s="107" t="s">
         <v>215</v>
       </c>
-      <c r="H67" s="107" t="s">
+      <c r="H67" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I67" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J67" s="107" t="s">
+      <c r="I67" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J67" s="106" t="s">
         <v>400</v>
       </c>
-      <c r="K67" s="108" t="s">
+      <c r="K67" s="107" t="s">
         <v>299</v>
       </c>
-      <c r="L67" s="107">
+      <c r="L67" s="106">
         <v>2</v>
       </c>
-      <c r="M67" s="109">
+      <c r="M67" s="108">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N67" s="109">
+      <c r="N67" s="108">
         <v>100</v>
       </c>
-      <c r="O67" s="110" t="s">
+      <c r="O67" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P67" s="109">
+      <c r="P67" s="108">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q67" s="109">
-        <f t="shared" ref="Q67" si="56">P67*N67</f>
+      <c r="Q67" s="108">
+        <f t="shared" ref="Q67" si="55">P67*N67</f>
         <v>0.11</v>
       </c>
-      <c r="R67" s="109"/>
+      <c r="R67" s="108"/>
     </row>
     <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
@@ -6285,7 +6306,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="Q68" s="41">
-        <f t="shared" ref="Q68" si="57">P68*N68</f>
+        <f t="shared" ref="Q68" si="56">P68*N68</f>
         <v>0.15</v>
       </c>
       <c r="R68" s="41"/>
@@ -6293,13 +6314,13 @@
     <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="C69" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="D69" s="87" t="s">
+      <c r="D69" s="86" t="s">
         <v>423</v>
       </c>
       <c r="E69" s="40" t="s">
@@ -6341,12 +6362,12 @@
         <f>N69*P69</f>
         <v>0.15</v>
       </c>
-      <c r="R69" s="77"/>
+      <c r="R69" s="76"/>
     </row>
     <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
@@ -6393,7 +6414,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="Q70" s="41">
-        <f t="shared" ref="Q70" si="58">P70*N70</f>
+        <f t="shared" ref="Q70" si="57">P70*N70</f>
         <v>0.15</v>
       </c>
       <c r="R70" s="41"/>
@@ -6401,7 +6422,7 @@
     <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="C71" s="59" t="s">
@@ -6448,7 +6469,7 @@
         <v>8.5400000000000004E-2</v>
       </c>
       <c r="Q71" s="42">
-        <f t="shared" ref="Q71" si="59">N71*P71</f>
+        <f t="shared" ref="Q71" si="58">N71*P71</f>
         <v>2.1350000000000002</v>
       </c>
       <c r="R71" s="42"/>
@@ -6456,7 +6477,7 @@
     <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
@@ -6468,7 +6489,7 @@
       <c r="E72" s="38" t="s">
         <v>433</v>
       </c>
-      <c r="F72" s="86" t="s">
+      <c r="F72" s="85" t="s">
         <v>166</v>
       </c>
       <c r="G72" s="38" t="s">
@@ -6490,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="41">
-        <f t="shared" ref="M72:M90" si="60">L72*20</f>
+        <f t="shared" ref="M72:M90" si="59">L72*20</f>
         <v>20</v>
       </c>
       <c r="N72" s="41">
@@ -6503,15 +6524,15 @@
         <v>3.8E-3</v>
       </c>
       <c r="Q72" s="41">
-        <f t="shared" ref="Q72" si="61">P72*N72</f>
+        <f t="shared" ref="Q72" si="60">P72*N72</f>
         <v>0.19</v>
       </c>
-      <c r="R72" s="76"/>
+      <c r="R72" s="75"/>
     </row>
     <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C73" s="59" t="s">
@@ -6558,15 +6579,15 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q73" s="42">
-        <f t="shared" ref="Q73" si="62">N73*P73</f>
+        <f t="shared" ref="Q73" si="61">N73*P73</f>
         <v>0.24</v>
       </c>
-      <c r="R73" s="77"/>
+      <c r="R73" s="76"/>
     </row>
     <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
@@ -6600,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="41">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
       <c r="N74" s="41">
@@ -6613,7 +6634,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q74" s="41">
-        <f t="shared" ref="Q74" si="63">P74*N74</f>
+        <f t="shared" ref="Q74" si="62">P74*N74</f>
         <v>0.1</v>
       </c>
       <c r="R74" s="41"/>
@@ -6621,7 +6642,7 @@
     <row r="75" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="B75:B90" si="63">ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
       <c r="C75" s="59" t="s">
@@ -6655,7 +6676,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="42">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
       <c r="N75" s="42">
@@ -6676,668 +6697,668 @@
     <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>67</v>
       </c>
-      <c r="C76" s="97" t="s">
+      <c r="C76" s="96" t="s">
         <v>324</v>
       </c>
-      <c r="D76" s="98" t="s">
+      <c r="D76" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="E76" s="99" t="s">
+      <c r="E76" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="F76" s="98" t="s">
+      <c r="F76" s="97" t="s">
         <v>168</v>
       </c>
-      <c r="G76" s="99" t="s">
+      <c r="G76" s="98" t="s">
         <v>219</v>
       </c>
-      <c r="H76" s="98" t="s">
+      <c r="H76" s="97" t="s">
         <v>229</v>
       </c>
-      <c r="I76" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="J76" s="98" t="s">
+      <c r="I76" s="97" t="s">
+        <v>314</v>
+      </c>
+      <c r="J76" s="97" t="s">
         <v>406</v>
       </c>
-      <c r="K76" s="99" t="s">
+      <c r="K76" s="98" t="s">
         <v>305</v>
       </c>
-      <c r="L76" s="98">
+      <c r="L76" s="97">
         <v>4</v>
       </c>
-      <c r="M76" s="66">
-        <f t="shared" si="60"/>
+      <c r="M76" s="65">
+        <f t="shared" si="59"/>
         <v>80</v>
       </c>
-      <c r="N76" s="66">
+      <c r="N76" s="65">
         <v>100</v>
       </c>
-      <c r="O76" s="100" t="s">
+      <c r="O76" s="99" t="s">
         <v>342</v>
       </c>
-      <c r="P76" s="66">
+      <c r="P76" s="65">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q76" s="66">
+      <c r="Q76" s="65">
         <f t="shared" ref="Q76" si="65">P76*N76</f>
         <v>0.12</v>
       </c>
-      <c r="R76" s="66" t="s">
+      <c r="R76" s="65" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>68</v>
       </c>
-      <c r="C77" s="97" t="s">
+      <c r="C77" s="96" t="s">
         <v>169</v>
       </c>
-      <c r="D77" s="98" t="s">
-        <v>452</v>
-      </c>
-      <c r="E77" s="99" t="s">
+      <c r="D77" s="125" t="s">
+        <v>479</v>
+      </c>
+      <c r="E77" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="F77" s="98" t="s">
+      <c r="F77" s="97" t="s">
         <v>169</v>
       </c>
-      <c r="G77" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="H77" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="I77" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="J77" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="K77" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="L77" s="98">
-        <v>15</v>
-      </c>
-      <c r="M77" s="66">
-        <f t="shared" si="60"/>
-        <v>300</v>
-      </c>
-      <c r="N77" s="66">
+      <c r="G77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="H77" s="97" t="s">
+        <v>314</v>
+      </c>
+      <c r="I77" s="97" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="97" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="L77" s="97">
+        <v>11</v>
+      </c>
+      <c r="M77" s="65">
+        <f t="shared" si="59"/>
+        <v>220</v>
+      </c>
+      <c r="N77" s="65">
         <f t="shared" ref="N77:N78" si="66">M77+(M77*0.1)</f>
-        <v>330</v>
-      </c>
-      <c r="O77" s="66"/>
-      <c r="P77" s="66"/>
-      <c r="Q77" s="66">
+        <v>242</v>
+      </c>
+      <c r="O77" s="65"/>
+      <c r="P77" s="65"/>
+      <c r="Q77" s="65">
         <f t="shared" ref="Q77" si="67">P77*N77</f>
         <v>0</v>
       </c>
-      <c r="R77" s="66" t="s">
+      <c r="R77" s="65" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>69</v>
       </c>
-      <c r="C78" s="102" t="s">
+      <c r="C78" s="101" t="s">
         <v>326</v>
       </c>
-      <c r="D78" s="103" t="s">
+      <c r="D78" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="E78" s="104" t="s">
+      <c r="E78" s="103" t="s">
         <v>129</v>
       </c>
-      <c r="F78" s="103" t="s">
+      <c r="F78" s="102" t="s">
         <v>170</v>
       </c>
-      <c r="G78" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="H78" s="103" t="s">
+      <c r="G78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="H78" s="102" t="s">
         <v>254</v>
       </c>
-      <c r="I78" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J78" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K78" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L78" s="103">
+      <c r="I78" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L78" s="102">
         <v>1</v>
       </c>
-      <c r="M78" s="96">
-        <f t="shared" si="60"/>
+      <c r="M78" s="95">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N78" s="96">
+      <c r="N78" s="95">
         <f t="shared" si="66"/>
         <v>22</v>
       </c>
-      <c r="O78" s="96"/>
-      <c r="P78" s="96"/>
-      <c r="Q78" s="96">
+      <c r="O78" s="95"/>
+      <c r="P78" s="95"/>
+      <c r="Q78" s="95">
         <f t="shared" ref="Q78" si="68">N78*P78</f>
         <v>0</v>
       </c>
-      <c r="R78" s="96"/>
+      <c r="R78" s="95"/>
     </row>
     <row r="79" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>70</v>
       </c>
-      <c r="C79" s="106" t="s">
+      <c r="C79" s="105" t="s">
         <v>327</v>
       </c>
-      <c r="D79" s="107" t="s">
+      <c r="D79" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="E79" s="108" t="s">
+      <c r="E79" s="107" t="s">
         <v>130</v>
       </c>
-      <c r="F79" s="107" t="s">
+      <c r="F79" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G79" s="108">
+      <c r="G79" s="107">
         <v>750314597</v>
       </c>
-      <c r="H79" s="107" t="s">
+      <c r="H79" s="106" t="s">
         <v>255</v>
       </c>
-      <c r="I79" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J79" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K79" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L79" s="107">
+      <c r="I79" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J79" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K79" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L79" s="106">
         <v>1</v>
       </c>
-      <c r="M79" s="109">
-        <f t="shared" si="60"/>
+      <c r="M79" s="108">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N79" s="109">
+      <c r="N79" s="108">
         <v>21</v>
       </c>
-      <c r="O79" s="110" t="s">
+      <c r="O79" s="109" t="s">
         <v>378</v>
       </c>
-      <c r="P79" s="109">
+      <c r="P79" s="108">
         <v>3.81</v>
       </c>
-      <c r="Q79" s="109">
+      <c r="Q79" s="108">
         <f t="shared" ref="Q79" si="69">P79*N79</f>
         <v>80.010000000000005</v>
       </c>
-      <c r="R79" s="109"/>
+      <c r="R79" s="108"/>
     </row>
     <row r="80" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>71</v>
       </c>
-      <c r="C80" s="102" t="s">
+      <c r="C80" s="101" t="s">
         <v>328</v>
       </c>
-      <c r="D80" s="103" t="s">
+      <c r="D80" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="E80" s="104" t="s">
+      <c r="E80" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="F80" s="103" t="s">
+      <c r="F80" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G80" s="104" t="s">
+      <c r="G80" s="103" t="s">
         <v>171</v>
       </c>
-      <c r="H80" s="103" t="s">
+      <c r="H80" s="102" t="s">
         <v>256</v>
       </c>
-      <c r="I80" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J80" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K80" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L80" s="103">
+      <c r="I80" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J80" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="K80" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L80" s="102">
         <v>1</v>
       </c>
-      <c r="M80" s="96">
-        <f t="shared" si="60"/>
+      <c r="M80" s="95">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N80" s="96">
+      <c r="N80" s="95">
         <v>21</v>
       </c>
-      <c r="O80" s="105" t="s">
+      <c r="O80" s="104" t="s">
         <v>408</v>
       </c>
-      <c r="P80" s="96">
+      <c r="P80" s="95">
         <v>2.48</v>
       </c>
-      <c r="Q80" s="96">
+      <c r="Q80" s="95">
         <f t="shared" ref="Q80" si="70">N80*P80</f>
         <v>52.08</v>
       </c>
-      <c r="R80" s="96"/>
+      <c r="R80" s="95"/>
     </row>
     <row r="81" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>72</v>
       </c>
-      <c r="C81" s="106" t="s">
+      <c r="C81" s="105" t="s">
         <v>328</v>
       </c>
-      <c r="D81" s="107" t="s">
+      <c r="D81" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="E81" s="108" t="s">
+      <c r="E81" s="107" t="s">
         <v>132</v>
       </c>
-      <c r="F81" s="107" t="s">
+      <c r="F81" s="106" t="s">
         <v>172</v>
       </c>
-      <c r="G81" s="108" t="s">
+      <c r="G81" s="122" t="s">
         <v>221</v>
       </c>
-      <c r="H81" s="107" t="s">
+      <c r="H81" s="106" t="s">
         <v>257</v>
       </c>
-      <c r="I81" s="107" t="s">
+      <c r="I81" s="106" t="s">
         <v>409</v>
       </c>
-      <c r="J81" s="107" t="s">
+      <c r="J81" s="106" t="s">
         <v>410</v>
       </c>
-      <c r="K81" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L81" s="107">
+      <c r="K81" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L81" s="106">
         <v>1</v>
       </c>
-      <c r="M81" s="109">
-        <f t="shared" si="60"/>
+      <c r="M81" s="108">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N81" s="109">
+      <c r="N81" s="108">
         <v>21</v>
       </c>
-      <c r="O81" s="110" t="s">
+      <c r="O81" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P81" s="109">
+      <c r="P81" s="108">
         <v>1.3939999999999999</v>
       </c>
-      <c r="Q81" s="109">
+      <c r="Q81" s="108">
         <f t="shared" ref="Q81" si="71">P81*N81</f>
         <v>29.273999999999997</v>
       </c>
-      <c r="R81" s="79"/>
+      <c r="R81" s="78"/>
     </row>
     <row r="82" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>73</v>
       </c>
-      <c r="C82" s="102" t="s">
+      <c r="C82" s="101" t="s">
         <v>328</v>
       </c>
-      <c r="D82" s="103" t="s">
+      <c r="D82" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="E82" s="104" t="s">
+      <c r="E82" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="F82" s="103" t="s">
+      <c r="F82" s="102" t="s">
         <v>173</v>
       </c>
-      <c r="G82" s="104" t="s">
+      <c r="G82" s="121" t="s">
         <v>222</v>
       </c>
-      <c r="H82" s="103" t="s">
+      <c r="H82" s="102" t="s">
         <v>256</v>
       </c>
-      <c r="I82" s="103" t="s">
+      <c r="I82" s="102" t="s">
         <v>411</v>
       </c>
-      <c r="J82" s="103" t="s">
+      <c r="J82" s="102" t="s">
         <v>412</v>
       </c>
-      <c r="K82" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L82" s="103">
+      <c r="K82" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L82" s="102">
         <v>1</v>
       </c>
-      <c r="M82" s="96">
-        <f t="shared" si="60"/>
+      <c r="M82" s="95">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N82" s="96">
+      <c r="N82" s="95">
         <v>21</v>
       </c>
-      <c r="O82" s="105" t="s">
+      <c r="O82" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P82" s="96">
+      <c r="P82" s="95">
         <v>0.69430000000000003</v>
       </c>
-      <c r="Q82" s="96">
+      <c r="Q82" s="95">
         <f t="shared" ref="Q82" si="72">N82*P82</f>
         <v>14.580300000000001</v>
       </c>
-      <c r="R82" s="78"/>
+      <c r="R82" s="77"/>
     </row>
     <row r="83" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>74</v>
       </c>
-      <c r="C83" s="106" t="s">
+      <c r="C83" s="105" t="s">
         <v>328</v>
       </c>
-      <c r="D83" s="107" t="s">
+      <c r="D83" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="E83" s="108" t="s">
+      <c r="E83" s="107" t="s">
         <v>134</v>
       </c>
-      <c r="F83" s="107" t="s">
+      <c r="F83" s="106" t="s">
         <v>310</v>
       </c>
-      <c r="G83" s="108" t="s">
+      <c r="G83" s="107" t="s">
         <v>174</v>
       </c>
-      <c r="H83" s="107" t="s">
+      <c r="H83" s="106" t="s">
         <v>256</v>
       </c>
-      <c r="I83" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="J83" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="K83" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L83" s="107">
+      <c r="I83" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J83" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K83" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L83" s="106">
         <v>1</v>
       </c>
-      <c r="M83" s="109">
-        <f t="shared" si="60"/>
+      <c r="M83" s="108">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N83" s="109">
+      <c r="N83" s="108">
         <v>21</v>
       </c>
-      <c r="O83" s="110" t="s">
+      <c r="O83" s="109" t="s">
         <v>408</v>
       </c>
-      <c r="P83" s="109">
+      <c r="P83" s="108">
         <v>3.637</v>
       </c>
-      <c r="Q83" s="109">
+      <c r="Q83" s="108">
         <f t="shared" ref="Q83" si="73">P83*N83</f>
         <v>76.376999999999995</v>
       </c>
-      <c r="R83" s="109"/>
+      <c r="R83" s="108"/>
     </row>
     <row r="84" spans="1:21" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>75</v>
       </c>
-      <c r="C84" s="102" t="s">
+      <c r="C84" s="101" t="s">
         <v>328</v>
       </c>
-      <c r="D84" s="103" t="s">
+      <c r="D84" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="E84" s="104" t="s">
+      <c r="E84" s="103" t="s">
         <v>135</v>
       </c>
-      <c r="F84" s="103" t="s">
+      <c r="F84" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="G84" s="104" t="s">
+      <c r="G84" s="103" t="s">
         <v>223</v>
       </c>
-      <c r="H84" s="103" t="s">
+      <c r="H84" s="102" t="s">
         <v>256</v>
       </c>
-      <c r="I84" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J84" s="103" t="s">
+      <c r="I84" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" s="102" t="s">
         <v>413</v>
       </c>
-      <c r="K84" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="L84" s="103">
+      <c r="K84" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="L84" s="102">
         <v>1</v>
       </c>
-      <c r="M84" s="96">
-        <f t="shared" si="60"/>
+      <c r="M84" s="95">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N84" s="96">
+      <c r="N84" s="95">
         <v>21</v>
       </c>
-      <c r="O84" s="105" t="s">
+      <c r="O84" s="104" t="s">
         <v>342</v>
       </c>
-      <c r="P84" s="96">
+      <c r="P84" s="95">
         <v>0.43280000000000002</v>
       </c>
-      <c r="Q84" s="96">
+      <c r="Q84" s="95">
         <f t="shared" ref="Q84" si="74">N84*P84</f>
         <v>9.0888000000000009</v>
       </c>
-      <c r="R84" s="96"/>
+      <c r="R84" s="95"/>
     </row>
     <row r="85" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>76</v>
       </c>
-      <c r="C85" s="71" t="s">
+      <c r="C85" s="70" t="s">
         <v>328</v>
       </c>
-      <c r="D85" s="72" t="s">
+      <c r="D85" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="E85" s="73" t="s">
+      <c r="E85" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="F85" s="72" t="s">
+      <c r="F85" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="G85" s="73" t="s">
+      <c r="G85" s="72" t="s">
         <v>224</v>
       </c>
-      <c r="H85" s="72" t="s">
+      <c r="H85" s="71" t="s">
         <v>258</v>
       </c>
-      <c r="I85" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="J85" s="72" t="s">
+      <c r="I85" s="71" t="s">
+        <v>314</v>
+      </c>
+      <c r="J85" s="71" t="s">
         <v>414</v>
       </c>
-      <c r="K85" s="73" t="s">
-        <v>314</v>
-      </c>
-      <c r="L85" s="72">
+      <c r="K85" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="L85" s="71">
         <v>1</v>
       </c>
-      <c r="M85" s="74">
-        <f t="shared" si="60"/>
+      <c r="M85" s="73">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N85" s="74">
+      <c r="N85" s="73">
         <v>21</v>
       </c>
-      <c r="O85" s="75" t="s">
+      <c r="O85" s="74" t="s">
         <v>342</v>
       </c>
-      <c r="P85" s="74">
+      <c r="P85" s="73">
         <v>7.4638</v>
       </c>
-      <c r="Q85" s="74">
+      <c r="Q85" s="73">
         <f t="shared" ref="Q85" si="75">P85*N85</f>
         <v>156.7398</v>
       </c>
-      <c r="R85" s="74" t="s">
+      <c r="R85" s="73" t="s">
         <v>437</v>
       </c>
-      <c r="U85" s="115"/>
+      <c r="U85" s="114"/>
     </row>
     <row r="86" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>77</v>
       </c>
-      <c r="C86" s="102" t="s">
+      <c r="C86" s="101" t="s">
         <v>328</v>
       </c>
-      <c r="D86" s="103" t="s">
+      <c r="D86" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="E86" s="104" t="s">
+      <c r="E86" s="103" t="s">
         <v>137</v>
       </c>
-      <c r="F86" s="103" t="s">
+      <c r="F86" s="102" t="s">
         <v>177</v>
       </c>
-      <c r="G86" s="104" t="s">
+      <c r="G86" s="103" t="s">
         <v>225</v>
       </c>
-      <c r="H86" s="103" t="s">
+      <c r="H86" s="102" t="s">
         <v>259</v>
       </c>
-      <c r="I86" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="J86" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="K86" s="113" t="s">
-        <v>314</v>
-      </c>
-      <c r="L86" s="103">
+      <c r="I86" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="J86" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="K86" s="112" t="s">
+        <v>314</v>
+      </c>
+      <c r="L86" s="102">
         <v>1</v>
       </c>
-      <c r="M86" s="96">
-        <f t="shared" si="60"/>
+      <c r="M86" s="95">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N86" s="96">
+      <c r="N86" s="95">
         <v>21</v>
       </c>
-      <c r="O86" s="105" t="s">
+      <c r="O86" s="104" t="s">
         <v>408</v>
       </c>
-      <c r="P86" s="96">
+      <c r="P86" s="95">
         <v>2.6459999999999999</v>
       </c>
-      <c r="Q86" s="96">
+      <c r="Q86" s="95">
         <f t="shared" ref="Q86" si="76">N86*P86</f>
         <v>55.565999999999995</v>
       </c>
-      <c r="R86" s="96"/>
+      <c r="R86" s="95"/>
     </row>
     <row r="87" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>78</v>
       </c>
-      <c r="C87" s="106" t="s">
+      <c r="C87" s="105" t="s">
         <v>328</v>
       </c>
-      <c r="D87" s="107" t="s">
-        <v>453</v>
-      </c>
-      <c r="E87" s="108" t="s">
+      <c r="D87" s="106" t="s">
+        <v>452</v>
+      </c>
+      <c r="E87" s="107" t="s">
         <v>138</v>
       </c>
-      <c r="F87" s="107" t="s">
+      <c r="F87" s="106" t="s">
         <v>311</v>
       </c>
-      <c r="G87" s="108" t="s">
+      <c r="G87" s="122" t="s">
         <v>178</v>
       </c>
-      <c r="H87" s="107" t="s">
+      <c r="H87" s="106" t="s">
         <v>256</v>
       </c>
-      <c r="I87" s="107" t="s">
+      <c r="I87" s="106" t="s">
         <v>415</v>
       </c>
-      <c r="J87" s="107" t="s">
+      <c r="J87" s="106" t="s">
         <v>416</v>
       </c>
-      <c r="K87" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="L87" s="114">
+      <c r="K87" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L87" s="113">
         <v>2</v>
       </c>
-      <c r="M87" s="109">
-        <f t="shared" si="60"/>
+      <c r="M87" s="108">
+        <f t="shared" si="59"/>
         <v>40</v>
       </c>
-      <c r="N87" s="109">
+      <c r="N87" s="108">
         <v>42</v>
       </c>
-      <c r="O87" s="110" t="s">
+      <c r="O87" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="P87" s="109">
+      <c r="P87" s="108">
         <v>2.2974000000000001</v>
       </c>
-      <c r="Q87" s="109">
+      <c r="Q87" s="108">
         <f t="shared" ref="Q87" si="77">P87*N87</f>
         <v>96.490800000000007</v>
       </c>
-      <c r="R87" s="79"/>
+      <c r="R87" s="78"/>
     </row>
     <row r="88" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>79</v>
       </c>
       <c r="C88" s="60" t="s">
@@ -7392,14 +7413,14 @@
     <row r="89" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>80</v>
       </c>
       <c r="C89" s="59" t="s">
         <v>328</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E89" s="40" t="s">
         <v>139</v>
@@ -7407,7 +7428,7 @@
       <c r="F89" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G89" s="40" t="s">
+      <c r="G89" s="124" t="s">
         <v>179</v>
       </c>
       <c r="H89" s="39" t="s">
@@ -7426,7 +7447,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="42">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
       <c r="N89" s="42">
@@ -7442,44 +7463,44 @@
         <f t="shared" ref="Q89:Q90" si="79">N89*P89</f>
         <v>74.171999999999997</v>
       </c>
-      <c r="R89" s="79"/>
+      <c r="R89" s="78"/>
     </row>
     <row r="90" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="63"/>
         <v>81</v>
       </c>
       <c r="C90" s="59" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D90" s="39" t="s">
         <v>314</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F90" s="39" t="s">
         <v>308</v>
       </c>
       <c r="G90" s="40" t="s">
+        <v>469</v>
+      </c>
+      <c r="H90" s="39" t="s">
         <v>470</v>
       </c>
-      <c r="H90" s="39" t="s">
-        <v>471</v>
-      </c>
       <c r="I90" s="39" t="s">
         <v>314</v>
       </c>
       <c r="J90" s="39" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K90" s="40"/>
       <c r="L90" s="39">
         <v>1</v>
       </c>
       <c r="M90" s="42">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
       <c r="N90" s="42">
@@ -7495,7 +7516,7 @@
         <f t="shared" si="79"/>
         <v>2.2250000000000001</v>
       </c>
-      <c r="R90" s="79"/>
+      <c r="R90" s="78"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
@@ -7514,11 +7535,11 @@
       <c r="L91" s="36"/>
       <c r="M91" s="36"/>
       <c r="N91" s="36"/>
-      <c r="O91" s="69" t="s">
+      <c r="O91" s="68" t="s">
         <v>420</v>
       </c>
-      <c r="P91" s="67"/>
-      <c r="Q91" s="67">
+      <c r="P91" s="66"/>
+      <c r="Q91" s="66">
         <f>SUM(Q10:Q90)</f>
         <v>979.80280000000005</v>
       </c>
@@ -7541,11 +7562,11 @@
       <c r="L92" s="9"/>
       <c r="M92" s="9"/>
       <c r="N92" s="9"/>
-      <c r="O92" s="70" t="s">
+      <c r="O92" s="69" t="s">
         <v>421</v>
       </c>
-      <c r="P92" s="68"/>
-      <c r="Q92" s="68">
+      <c r="P92" s="67"/>
+      <c r="Q92" s="67">
         <f>Q91/20</f>
         <v>48.990140000000004</v>
       </c>

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836C6BEA-F6BF-4605-9BD0-374D7807DBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0715989E-5DE6-4099-AA1E-1C8381B57125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="482">
   <si>
     <t>Component list</t>
   </si>
@@ -1608,6 +1608,12 @@
   <si>
     <t>SB1, SB3, SB4, SB6, SB7, SB9, SB11, SBx1, SBx2, SBx3, SBx4</t>
   </si>
+  <si>
+    <t>C492401</t>
+  </si>
+  <si>
+    <t>PZ254V-11-02P</t>
+  </si>
 </sst>
 </file>
 
@@ -1628,6 +1634,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2447,6 +2454,24 @@
     <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2455,24 +2480,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2847,14 +2854,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2902,7 +2909,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="118"/>
+      <c r="R3" s="124"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2926,7 +2933,7 @@
       <c r="O4" s="61"/>
       <c r="P4" s="61"/>
       <c r="Q4" s="61"/>
-      <c r="R4" s="119"/>
+      <c r="R4" s="125"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2948,7 +2955,7 @@
       <c r="O5" s="61"/>
       <c r="P5" s="61"/>
       <c r="Q5" s="61"/>
-      <c r="R5" s="119"/>
+      <c r="R5" s="125"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2968,7 +2975,7 @@
       <c r="O6" s="61"/>
       <c r="P6" s="61"/>
       <c r="Q6" s="61"/>
-      <c r="R6" s="119"/>
+      <c r="R6" s="125"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2988,7 +2995,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="119"/>
+      <c r="R7" s="125"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3008,7 +3015,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="119"/>
+      <c r="R8" s="125"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3524,7 +3531,7 @@
       <c r="F18" s="102" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="121" t="s">
+      <c r="G18" s="118" t="s">
         <v>188</v>
       </c>
       <c r="H18" s="102" t="s">
@@ -3579,7 +3586,7 @@
       <c r="F19" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="122" t="s">
+      <c r="G19" s="119" t="s">
         <v>189</v>
       </c>
       <c r="H19" s="106" t="s">
@@ -3854,7 +3861,7 @@
       <c r="F24" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="123">
+      <c r="G24" s="120">
         <v>885012205080</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -4459,7 +4466,7 @@
       <c r="F35" s="89" t="s">
         <v>152</v>
       </c>
-      <c r="G35" s="120" t="s">
+      <c r="G35" s="117" t="s">
         <v>198</v>
       </c>
       <c r="H35" s="89" t="s">
@@ -4517,7 +4524,7 @@
       <c r="F36" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G36" s="121" t="s">
+      <c r="G36" s="118" t="s">
         <v>153</v>
       </c>
       <c r="H36" s="102" t="s">
@@ -4627,7 +4634,7 @@
       <c r="F38" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="G38" s="121" t="s">
+      <c r="G38" s="118" t="s">
         <v>155</v>
       </c>
       <c r="H38" s="102" t="s">
@@ -4682,7 +4689,7 @@
       <c r="F39" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G39" s="122" t="s">
+      <c r="G39" s="119" t="s">
         <v>156</v>
       </c>
       <c r="H39" s="106" t="s">
@@ -5284,17 +5291,17 @@
       <c r="F50" s="102" t="s">
         <v>164</v>
       </c>
-      <c r="G50" s="103">
+      <c r="G50" s="118">
         <v>61300211121</v>
       </c>
       <c r="H50" s="102" t="s">
         <v>235</v>
       </c>
       <c r="I50" s="102" t="s">
-        <v>314</v>
+        <v>481</v>
       </c>
       <c r="J50" s="102" t="s">
-        <v>314</v>
+        <v>480</v>
       </c>
       <c r="K50" s="103" t="s">
         <v>314</v>
@@ -5307,17 +5314,17 @@
         <v>80</v>
       </c>
       <c r="N50" s="95">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O50" s="104" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="P50" s="95">
-        <v>0.13</v>
+        <v>1.47E-2</v>
       </c>
       <c r="Q50" s="95">
         <f t="shared" ref="Q50" si="38">N50*P50</f>
-        <v>11.700000000000001</v>
+        <v>1.47</v>
       </c>
       <c r="R50" s="95"/>
     </row>
@@ -5339,7 +5346,7 @@
       <c r="F51" s="106" t="s">
         <v>165</v>
       </c>
-      <c r="G51" s="107" t="s">
+      <c r="G51" s="119" t="s">
         <v>200</v>
       </c>
       <c r="H51" s="106" t="s">
@@ -5669,7 +5676,7 @@
       <c r="F57" s="106" t="s">
         <v>167</v>
       </c>
-      <c r="G57" s="107" t="s">
+      <c r="G57" s="119" t="s">
         <v>329</v>
       </c>
       <c r="H57" s="106" t="s">
@@ -6164,7 +6171,7 @@
       <c r="F66" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="G66" s="103" t="s">
+      <c r="G66" s="118" t="s">
         <v>214</v>
       </c>
       <c r="H66" s="102" t="s">
@@ -6760,7 +6767,7 @@
       <c r="C77" s="96" t="s">
         <v>169</v>
       </c>
-      <c r="D77" s="125" t="s">
+      <c r="D77" s="122" t="s">
         <v>479</v>
       </c>
       <c r="E77" s="98" t="s">
@@ -6985,7 +6992,7 @@
       <c r="F81" s="106" t="s">
         <v>172</v>
       </c>
-      <c r="G81" s="122" t="s">
+      <c r="G81" s="119" t="s">
         <v>221</v>
       </c>
       <c r="H81" s="106" t="s">
@@ -7040,7 +7047,7 @@
       <c r="F82" s="102" t="s">
         <v>173</v>
       </c>
-      <c r="G82" s="121" t="s">
+      <c r="G82" s="118" t="s">
         <v>222</v>
       </c>
       <c r="H82" s="102" t="s">
@@ -7318,7 +7325,7 @@
       <c r="F87" s="106" t="s">
         <v>311</v>
       </c>
-      <c r="G87" s="122" t="s">
+      <c r="G87" s="119" t="s">
         <v>178</v>
       </c>
       <c r="H87" s="106" t="s">
@@ -7428,7 +7435,7 @@
       <c r="F89" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G89" s="124" t="s">
+      <c r="G89" s="121" t="s">
         <v>179</v>
       </c>
       <c r="H89" s="39" t="s">
@@ -7541,7 +7548,7 @@
       <c r="P91" s="66"/>
       <c r="Q91" s="66">
         <f>SUM(Q10:Q90)</f>
-        <v>979.80280000000005</v>
+        <v>969.57280000000003</v>
       </c>
       <c r="R91" s="44"/>
     </row>
@@ -7568,7 +7575,7 @@
       <c r="P92" s="67"/>
       <c r="Q92" s="67">
         <f>Q91/20</f>
-        <v>48.990140000000004</v>
+        <v>48.478639999999999</v>
       </c>
       <c r="R92" s="45"/>
     </row>
@@ -7614,47 +7621,47 @@
     <hyperlink ref="O45" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
     <hyperlink ref="O46" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
     <hyperlink ref="O48" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="O50" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="O51" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="O52" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="O53" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="O54" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="O55" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="O56" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="O57" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="O69" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="O59" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="O60" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="O61" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="O62" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="O63" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="O64" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="O65" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="O66" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="O67" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="O68" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="O70" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="O71" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="O72" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="O75" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="O76" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="O73" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="O79" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="O80" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="O81" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="O82" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="O83" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="O84" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="O85" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="O86" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="O87" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="O89" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="O88" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="O58" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="O47" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="O90" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="O42" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="O10" r:id="rId77" xr:uid="{5D88A11D-3624-47E9-BBD7-2366F8BA7980}"/>
+    <hyperlink ref="O51" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O52" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O53" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O54" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O55" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O56" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O57" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O69" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O59" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O60" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O61" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O62" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O63" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O64" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O65" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O66" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O67" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O68" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O70" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O71" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O72" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O75" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O76" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O73" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O79" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O80" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O81" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="O82" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O83" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O84" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="O85" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O86" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O87" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O89" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O88" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O58" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O47" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O90" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="O42" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="O10" r:id="rId76" xr:uid="{5D88A11D-3624-47E9-BBD7-2366F8BA7980}"/>
+    <hyperlink ref="O50" r:id="rId77" xr:uid="{3AF3C69B-110E-4BD5-B2CB-21B12CDADF8A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId78"/>

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0715989E-5DE6-4099-AA1E-1C8381B57125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD49FCC0-8CB8-4350-BC87-798A3C4365C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="483">
   <si>
     <t>Component list</t>
   </si>
@@ -1613,6 +1613,9 @@
   </si>
   <si>
     <t>PZ254V-11-02P</t>
+  </si>
+  <si>
+    <t>Ali-E</t>
   </si>
 </sst>
 </file>
@@ -6856,11 +6859,14 @@
         <f t="shared" si="66"/>
         <v>22</v>
       </c>
-      <c r="O78" s="95"/>
-      <c r="P78" s="95"/>
+      <c r="O78" s="104" t="s">
+        <v>482</v>
+      </c>
+      <c r="P78" s="95">
+        <v>1.42</v>
+      </c>
       <c r="Q78" s="95">
-        <f t="shared" ref="Q78" si="68">N78*P78</f>
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R78" s="95"/>
     </row>
@@ -6914,7 +6920,7 @@
         <v>3.81</v>
       </c>
       <c r="Q79" s="108">
-        <f t="shared" ref="Q79" si="69">P79*N79</f>
+        <f t="shared" ref="Q79" si="68">P79*N79</f>
         <v>80.010000000000005</v>
       </c>
       <c r="R79" s="108"/>
@@ -6969,7 +6975,7 @@
         <v>2.48</v>
       </c>
       <c r="Q80" s="95">
-        <f t="shared" ref="Q80" si="70">N80*P80</f>
+        <f t="shared" ref="Q80" si="69">N80*P80</f>
         <v>52.08</v>
       </c>
       <c r="R80" s="95"/>
@@ -7024,7 +7030,7 @@
         <v>1.3939999999999999</v>
       </c>
       <c r="Q81" s="108">
-        <f t="shared" ref="Q81" si="71">P81*N81</f>
+        <f t="shared" ref="Q81" si="70">P81*N81</f>
         <v>29.273999999999997</v>
       </c>
       <c r="R81" s="78"/>
@@ -7079,7 +7085,7 @@
         <v>0.69430000000000003</v>
       </c>
       <c r="Q82" s="95">
-        <f t="shared" ref="Q82" si="72">N82*P82</f>
+        <f t="shared" ref="Q82" si="71">N82*P82</f>
         <v>14.580300000000001</v>
       </c>
       <c r="R82" s="77"/>
@@ -7134,7 +7140,7 @@
         <v>3.637</v>
       </c>
       <c r="Q83" s="108">
-        <f t="shared" ref="Q83" si="73">P83*N83</f>
+        <f t="shared" ref="Q83" si="72">P83*N83</f>
         <v>76.376999999999995</v>
       </c>
       <c r="R83" s="108"/>
@@ -7189,7 +7195,7 @@
         <v>0.43280000000000002</v>
       </c>
       <c r="Q84" s="95">
-        <f t="shared" ref="Q84" si="74">N84*P84</f>
+        <f t="shared" ref="Q84" si="73">N84*P84</f>
         <v>9.0888000000000009</v>
       </c>
       <c r="R84" s="95"/>
@@ -7244,7 +7250,7 @@
         <v>7.4638</v>
       </c>
       <c r="Q85" s="73">
-        <f t="shared" ref="Q85" si="75">P85*N85</f>
+        <f t="shared" ref="Q85" si="74">P85*N85</f>
         <v>156.7398</v>
       </c>
       <c r="R85" s="73" t="s">
@@ -7302,7 +7308,7 @@
         <v>2.6459999999999999</v>
       </c>
       <c r="Q86" s="95">
-        <f t="shared" ref="Q86" si="76">N86*P86</f>
+        <f t="shared" ref="Q86" si="75">N86*P86</f>
         <v>55.565999999999995</v>
       </c>
       <c r="R86" s="95"/>
@@ -7357,7 +7363,7 @@
         <v>2.2974000000000001</v>
       </c>
       <c r="Q87" s="108">
-        <f t="shared" ref="Q87" si="77">P87*N87</f>
+        <f t="shared" ref="Q87" si="76">P87*N87</f>
         <v>96.490800000000007</v>
       </c>
       <c r="R87" s="78"/>
@@ -7412,7 +7418,7 @@
         <v>0.39140000000000003</v>
       </c>
       <c r="Q88" s="41">
-        <f t="shared" ref="Q88" si="78">P88*N88</f>
+        <f t="shared" ref="Q88" si="77">P88*N88</f>
         <v>8.2194000000000003</v>
       </c>
       <c r="R88" s="41"/>
@@ -7467,7 +7473,7 @@
         <v>3.532</v>
       </c>
       <c r="Q89" s="42">
-        <f t="shared" ref="Q89:Q90" si="79">N89*P89</f>
+        <f t="shared" ref="Q89:Q90" si="78">N89*P89</f>
         <v>74.171999999999997</v>
       </c>
       <c r="R89" s="78"/>
@@ -7520,7 +7526,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="Q90" s="42">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>2.2250000000000001</v>
       </c>
       <c r="R90" s="78"/>
@@ -7548,7 +7554,7 @@
       <c r="P91" s="66"/>
       <c r="Q91" s="66">
         <f>SUM(Q10:Q90)</f>
-        <v>969.57280000000003</v>
+        <v>970.9928000000001</v>
       </c>
       <c r="R91" s="44"/>
     </row>
@@ -7575,7 +7581,7 @@
       <c r="P92" s="67"/>
       <c r="Q92" s="67">
         <f>Q91/20</f>
-        <v>48.478639999999999</v>
+        <v>48.549640000000004</v>
       </c>
       <c r="R92" s="45"/>
     </row>
@@ -7662,9 +7668,10 @@
     <hyperlink ref="O42" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
     <hyperlink ref="O10" r:id="rId76" xr:uid="{5D88A11D-3624-47E9-BBD7-2366F8BA7980}"/>
     <hyperlink ref="O50" r:id="rId77" xr:uid="{3AF3C69B-110E-4BD5-B2CB-21B12CDADF8A}"/>
+    <hyperlink ref="O78" r:id="rId78" xr:uid="{D0B601F1-C091-44E0-B215-033F4B4B50D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId78"/>
-  <drawing r:id="rId79"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId79"/>
+  <drawing r:id="rId80"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD49FCC0-8CB8-4350-BC87-798A3C4365C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="482">
   <si>
     <t>Component list</t>
   </si>
@@ -80,9 +79,6 @@
     <t>C36</t>
   </si>
   <si>
-    <t>C37</t>
-  </si>
-  <si>
     <t>C42</t>
   </si>
   <si>
@@ -158,9 +154,6 @@
     <t>R6, R7, R8, R9</t>
   </si>
   <si>
-    <t>R10, R11, R12, R13</t>
-  </si>
-  <si>
     <t>R21</t>
   </si>
   <si>
@@ -365,9 +358,6 @@
     <t>RES SMD 47OHM 0.1W 0603</t>
   </si>
   <si>
-    <t>0.033Ω ±1% 2W ±1800ppm/°C 2512 Low Resistors &amp; Current Sense Resistors - Surface Mount RoHS</t>
-  </si>
-  <si>
     <t>RES SMD 150OHM 1/10W 0603</t>
   </si>
   <si>
@@ -902,9 +892,6 @@
     <t>47R</t>
   </si>
   <si>
-    <t>33m</t>
-  </si>
-  <si>
     <t>150R</t>
   </si>
   <si>
@@ -1022,9 +1009,6 @@
     <t>IC</t>
   </si>
   <si>
-    <t>CRH2512FR033E04Z</t>
-  </si>
-  <si>
     <t>0603WAF1201T5E</t>
   </si>
   <si>
@@ -1208,12 +1192,6 @@
     <t>C114623</t>
   </si>
   <si>
-    <t>LR2512-22R033F4</t>
-  </si>
-  <si>
-    <t>C2681032</t>
-  </si>
-  <si>
     <t>C114608</t>
   </si>
   <si>
@@ -1353,9 +1331,6 @@
   </si>
   <si>
     <t>RES SMD 22HM 1/10W 0603</t>
-  </si>
-  <si>
-    <t>C5, C6, C14, C23, C24, C29, C34, C35</t>
   </si>
   <si>
     <t>C43</t>
@@ -1617,11 +1592,32 @@
   <si>
     <t>Ali-E</t>
   </si>
+  <si>
+    <t>C23, C24, C37</t>
+  </si>
+  <si>
+    <t>C5, C6, C14, C29, C34, C35</t>
+  </si>
+  <si>
+    <t>R12, R13</t>
+  </si>
+  <si>
+    <t>2W 50mΩ ±1% 2512 Current Sense Resistors/Shunt Resistors ROHS</t>
+  </si>
+  <si>
+    <t>CRH2512FR050E04Z</t>
+  </si>
+  <si>
+    <t>C176035</t>
+  </si>
+  <si>
+    <t>50mR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -2824,7 +2820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:U92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2875,7 +2871,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2899,7 +2895,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -2923,7 +2919,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -3026,52 +3022,52 @@
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I9" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="M9" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="O9" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="P9" s="31" t="s">
         <v>335</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="Q9" s="31" t="s">
         <v>336</v>
       </c>
-      <c r="K9" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="M9" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="N9" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="O9" s="31" t="s">
-        <v>339</v>
-      </c>
-      <c r="P9" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q9" s="31" t="s">
-        <v>341</v>
-      </c>
       <c r="R9" s="31" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3081,31 +3077,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G10" s="116" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -3118,7 +3114,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P10" s="41">
         <v>0.38819999999999999</v>
@@ -3136,31 +3132,31 @@
         <v>2</v>
       </c>
       <c r="C11" s="80" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D11" s="81" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="E11" s="82" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F11" s="81" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G11" s="82" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H11" s="81" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I11" s="81" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J11" s="81" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L11" s="81">
         <v>15</v>
@@ -3173,7 +3169,7 @@
         <v>300</v>
       </c>
       <c r="O11" s="84" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P11" s="83">
         <v>1.4E-3</v>
@@ -3183,7 +3179,7 @@
         <v>0.42</v>
       </c>
       <c r="R11" s="83" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3193,31 +3189,31 @@
         <v>3</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="L12" s="85">
         <v>2</v>
@@ -3230,7 +3226,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
@@ -3248,31 +3244,31 @@
         <v>4</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L13" s="86">
         <v>1</v>
@@ -3285,7 +3281,7 @@
         <v>40</v>
       </c>
       <c r="O13" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
@@ -3303,44 +3299,44 @@
         <v>5</v>
       </c>
       <c r="C14" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L14" s="37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M14" s="41">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="N14" s="41">
         <v>200</v>
       </c>
       <c r="O14" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
@@ -3358,31 +3354,31 @@
         <v>6</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="L15" s="86">
         <v>3</v>
@@ -3395,7 +3391,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
@@ -3413,31 +3409,31 @@
         <v>7</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G16" s="100" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="H16" s="85" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="L16" s="37">
         <v>6</v>
@@ -3450,7 +3446,7 @@
         <v>130</v>
       </c>
       <c r="O16" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P16" s="41">
         <v>3.32E-2</v>
@@ -3468,31 +3464,31 @@
         <v>8</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="K17" s="40" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="L17" s="39">
         <v>1</v>
@@ -3505,7 +3501,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
@@ -3523,31 +3519,31 @@
         <v>9</v>
       </c>
       <c r="C18" s="101" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D18" s="102" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E18" s="103" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F18" s="102" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G18" s="118" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H18" s="102" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I18" s="102" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="J18" s="102" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K18" s="103" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L18" s="102">
         <v>8</v>
@@ -3560,7 +3556,7 @@
         <v>180</v>
       </c>
       <c r="O18" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P18" s="95">
         <v>3.09E-2</v>
@@ -3578,31 +3574,31 @@
         <v>10</v>
       </c>
       <c r="C19" s="105" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D19" s="106" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="107" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F19" s="106" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G19" s="119" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H19" s="106" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I19" s="106" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="J19" s="106" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="K19" s="107" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L19" s="106">
         <v>1</v>
@@ -3615,7 +3611,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P19" s="108">
         <v>5.3E-3</v>
@@ -3633,31 +3629,31 @@
         <v>11</v>
       </c>
       <c r="C20" s="101" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D20" s="102" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="103" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F20" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G20" s="102" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H20" s="102" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I20" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J20" s="102" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="K20" s="103" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L20" s="102">
         <v>1</v>
@@ -3670,7 +3666,7 @@
         <v>22</v>
       </c>
       <c r="O20" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P20" s="95">
         <v>0.22189999999999999</v>
@@ -3688,31 +3684,31 @@
         <v>12</v>
       </c>
       <c r="C21" s="105" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D21" s="106" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="107" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F21" s="106" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G21" s="107" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H21" s="106" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I21" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J21" s="106" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="K21" s="107" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L21" s="106">
         <v>2</v>
@@ -3725,7 +3721,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P21" s="108">
         <v>7.7000000000000002E-3</v>
@@ -3743,31 +3739,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -3780,7 +3776,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P22" s="41">
         <v>3.49E-2</v>
@@ -3798,31 +3794,31 @@
         <v>14</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J23" s="39" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L23" s="39">
         <v>1</v>
@@ -3835,7 +3831,7 @@
         <v>40</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P23" s="42">
         <v>1.9199999999999998E-2</v>
@@ -3853,31 +3849,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D24" s="37" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G24" s="120">
         <v>885012205080</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -3890,7 +3886,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P24" s="41">
         <v>5.1999999999999998E-3</v>
@@ -3908,44 +3904,44 @@
         <v>16</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>15</v>
+        <v>475</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H25" s="39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="K25" s="40" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="L25" s="39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" s="42">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="N25" s="42">
         <v>100</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P25" s="42">
         <v>3.2000000000000002E-3</v>
@@ -3963,31 +3959,31 @@
         <v>17</v>
       </c>
       <c r="C26" s="101" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D26" s="102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" s="110" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="F26" s="102" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G26" s="110" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="H26" s="111" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I26" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J26" s="102" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K26" s="110" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="L26" s="102">
         <v>1</v>
@@ -4000,7 +3996,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P26" s="95">
         <v>3.3999999999999998E-3</v>
@@ -4018,31 +4014,31 @@
         <v>18</v>
       </c>
       <c r="C27" s="105" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D27" s="106" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E27" s="107" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F27" s="106" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G27" s="107" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H27" s="106" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I27" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J27" s="106" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="K27" s="107" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="L27" s="106">
         <v>1</v>
@@ -4055,7 +4051,7 @@
         <v>30</v>
       </c>
       <c r="O27" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P27" s="108">
         <v>0.2525</v>
@@ -4073,31 +4069,31 @@
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -4110,7 +4106,7 @@
         <v>22</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P28" s="41">
         <v>0.89629999999999999</v>
@@ -4128,31 +4124,31 @@
         <v>20</v>
       </c>
       <c r="C29" s="59" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G29" s="39" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H29" s="39" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I29" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="K29" s="40" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L29" s="39">
         <v>1</v>
@@ -4165,7 +4161,7 @@
         <v>21</v>
       </c>
       <c r="O29" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P29" s="42">
         <v>0.47249999999999998</v>
@@ -4183,31 +4179,31 @@
         <v>21</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -4220,7 +4216,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P30" s="41">
         <v>3.0999999999999999E-3</v>
@@ -4238,31 +4234,31 @@
         <v>22</v>
       </c>
       <c r="C31" s="105" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D31" s="106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" s="107" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F31" s="106" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G31" s="107" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H31" s="106" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I31" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J31" s="106" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="K31" s="107" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L31" s="106">
         <v>4</v>
@@ -4275,7 +4271,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P31" s="108">
         <v>5.4999999999999997E-3</v>
@@ -4293,31 +4289,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="101" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D32" s="102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E32" s="103" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F32" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G32" s="103" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H32" s="102" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I32" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J32" s="102" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="K32" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L32" s="102">
         <v>1</v>
@@ -4330,7 +4326,7 @@
         <v>30</v>
       </c>
       <c r="O32" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P32" s="95">
         <v>4.87E-2</v>
@@ -4348,31 +4344,31 @@
         <v>24</v>
       </c>
       <c r="C33" s="105" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D33" s="106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33" s="107" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F33" s="106" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G33" s="107" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H33" s="106" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I33" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J33" s="106" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="K33" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L33" s="106">
         <v>1</v>
@@ -4385,7 +4381,7 @@
         <v>30</v>
       </c>
       <c r="O33" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P33" s="108">
         <v>7.4300000000000005E-2</v>
@@ -4403,31 +4399,31 @@
         <v>25</v>
       </c>
       <c r="C34" s="101" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D34" s="102" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="E34" s="103" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F34" s="102" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G34" s="103" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H34" s="102" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I34" s="102" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J34" s="102" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="K34" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L34" s="102">
         <v>2</v>
@@ -4440,7 +4436,7 @@
         <v>60</v>
       </c>
       <c r="O34" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P34" s="95">
         <v>2.8899999999999999E-2</v>
@@ -4458,31 +4454,31 @@
         <v>26</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D35" s="89" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="E35" s="90" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F35" s="89" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G35" s="117" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H35" s="89" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I35" s="89" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="J35" s="89" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="K35" s="90" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L35" s="91">
         <v>8</v>
@@ -4495,7 +4491,7 @@
         <v>170</v>
       </c>
       <c r="O35" s="94" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P35" s="92">
         <v>0.12590000000000001</v>
@@ -4505,7 +4501,7 @@
         <v>21.403000000000002</v>
       </c>
       <c r="R35" s="83" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="U35" s="115"/>
     </row>
@@ -4516,31 +4512,31 @@
         <v>27</v>
       </c>
       <c r="C36" s="101" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D36" s="102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" s="103" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F36" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G36" s="118" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H36" s="102" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I36" s="102" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J36" s="102" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="K36" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L36" s="102">
         <v>1</v>
@@ -4553,7 +4549,7 @@
         <v>30</v>
       </c>
       <c r="O36" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P36" s="95">
         <v>5.6000000000000001E-2</v>
@@ -4571,31 +4567,31 @@
         <v>28</v>
       </c>
       <c r="C37" s="105" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D37" s="106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="107" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F37" s="106" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G37" s="107" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H37" s="106" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I37" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J37" s="106" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="K37" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L37" s="106">
         <v>4</v>
@@ -4608,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P37" s="108">
         <v>2.9499999999999998E-2</v>
@@ -4626,31 +4622,31 @@
         <v>29</v>
       </c>
       <c r="C38" s="101" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D38" s="102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" s="103" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F38" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G38" s="118" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H38" s="102" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I38" s="102" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J38" s="102" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K38" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L38" s="102">
         <v>1</v>
@@ -4663,7 +4659,7 @@
         <v>21</v>
       </c>
       <c r="O38" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P38" s="95">
         <v>0.53559999999999997</v>
@@ -4681,31 +4677,31 @@
         <v>30</v>
       </c>
       <c r="C39" s="105" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D39" s="106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="107" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F39" s="106" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G39" s="119" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H39" s="106" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I39" s="106" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="J39" s="106" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="K39" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L39" s="106">
         <v>2</v>
@@ -4718,7 +4714,7 @@
         <v>42</v>
       </c>
       <c r="O39" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P39" s="108">
         <v>0.65639999999999998</v>
@@ -4736,31 +4732,31 @@
         <v>31</v>
       </c>
       <c r="C40" s="101" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D40" s="102" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40" s="103" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F40" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G40" s="103" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H40" s="102" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I40" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J40" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K40" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L40" s="102">
         <v>1</v>
@@ -4773,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="O40" s="104" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="P40" s="95">
         <v>1.2</v>
@@ -4791,31 +4787,31 @@
         <v>32</v>
       </c>
       <c r="C41" s="105" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D41" s="106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E41" s="107" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F41" s="106" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G41" s="107" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H41" s="106" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I41" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J41" s="106" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="K41" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L41" s="106">
         <v>1</v>
@@ -4828,7 +4824,7 @@
         <v>25</v>
       </c>
       <c r="O41" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P41" s="108">
         <v>9.2200000000000004E-2</v>
@@ -4846,31 +4842,31 @@
         <v>33</v>
       </c>
       <c r="C42" s="105" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D42" s="106" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="E42" s="107" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F42" s="106" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G42" s="107" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="H42" s="106" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="I42" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J42" s="106" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="K42" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L42" s="106">
         <v>1</v>
@@ -4883,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="O42" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P42" s="108">
         <v>0.21210000000000001</v>
@@ -4901,31 +4897,31 @@
         <v>34</v>
       </c>
       <c r="C43" s="101" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D43" s="102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E43" s="103" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F43" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G43" s="103" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H43" s="102" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I43" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J43" s="102" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="K43" s="103" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L43" s="102">
         <v>1</v>
@@ -4938,7 +4934,7 @@
         <v>21</v>
       </c>
       <c r="O43" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P43" s="95">
         <v>0.45629999999999998</v>
@@ -4956,31 +4952,31 @@
         <v>35</v>
       </c>
       <c r="C44" s="105" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D44" s="106" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E44" s="107" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="F44" s="106" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G44" s="107" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="H44" s="106" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="I44" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J44" s="106" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="K44" s="107" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="L44" s="106">
         <v>1</v>
@@ -4993,7 +4989,7 @@
         <v>25</v>
       </c>
       <c r="O44" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P44" s="108">
         <v>0.1012</v>
@@ -5011,31 +5007,31 @@
         <v>36</v>
       </c>
       <c r="C45" s="101" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D45" s="102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E45" s="103" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F45" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G45" s="103" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H45" s="102" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I45" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J45" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K45" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L45" s="102">
         <v>1</v>
@@ -5048,7 +5044,7 @@
         <v>30</v>
       </c>
       <c r="O45" s="104" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="P45" s="95">
         <v>0.156</v>
@@ -5066,31 +5062,31 @@
         <v>37</v>
       </c>
       <c r="C46" s="105" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D46" s="106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46" s="107" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F46" s="106" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G46" s="107" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H46" s="106" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I46" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J46" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K46" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L46" s="106">
         <v>1</v>
@@ -5103,7 +5099,7 @@
         <v>30</v>
       </c>
       <c r="O46" s="109" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="P46" s="108">
         <v>0.08</v>
@@ -5121,31 +5117,31 @@
         <v>38</v>
       </c>
       <c r="C47" s="105" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="D47" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E47" s="107" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="F47" s="106" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G47" s="107" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="H47" s="106" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="I47" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J47" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K47" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L47" s="106">
         <v>1</v>
@@ -5158,7 +5154,7 @@
         <v>20</v>
       </c>
       <c r="O47" s="109" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="P47" s="108">
         <v>0.435</v>
@@ -5168,7 +5164,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="R47" s="78" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5178,31 +5174,31 @@
         <v>39</v>
       </c>
       <c r="C48" s="101" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D48" s="102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E48" s="103" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F48" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G48" s="103" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H48" s="102" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I48" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J48" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K48" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L48" s="102">
         <v>2</v>
@@ -5215,7 +5211,7 @@
         <v>50</v>
       </c>
       <c r="O48" s="104" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="P48" s="95">
         <v>1.5</v>
@@ -5233,27 +5229,27 @@
         <v>40</v>
       </c>
       <c r="C49" s="96" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D49" s="97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E49" s="98" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F49" s="97" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G49" s="98" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H49" s="97" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I49" s="97"/>
       <c r="J49" s="97"/>
       <c r="K49" s="98" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L49" s="97">
         <v>4</v>
@@ -5273,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="R49" s="65" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5283,31 +5279,31 @@
         <v>41</v>
       </c>
       <c r="C50" s="101" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D50" s="102" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E50" s="103" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F50" s="102" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G50" s="118">
         <v>61300211121</v>
       </c>
       <c r="H50" s="102" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I50" s="102" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J50" s="102" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="K50" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L50" s="102">
         <v>4</v>
@@ -5320,7 +5316,7 @@
         <v>100</v>
       </c>
       <c r="O50" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P50" s="95">
         <v>1.47E-2</v>
@@ -5338,31 +5334,31 @@
         <v>42</v>
       </c>
       <c r="C51" s="105" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D51" s="106" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="E51" s="107" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F51" s="106" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G51" s="119" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H51" s="106" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I51" s="106" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J51" s="106" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="K51" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L51" s="106">
         <v>4</v>
@@ -5375,7 +5371,7 @@
         <v>85</v>
       </c>
       <c r="O51" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P51" s="108">
         <v>0.21740000000000001</v>
@@ -5393,31 +5389,31 @@
         <v>43</v>
       </c>
       <c r="C52" s="101" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D52" s="102" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" s="103" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F52" s="102" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G52" s="103" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H52" s="102" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I52" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J52" s="102" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="K52" s="103" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="L52" s="102">
         <v>2</v>
@@ -5430,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P52" s="95">
         <v>1E-3</v>
@@ -5448,31 +5444,31 @@
         <v>44</v>
       </c>
       <c r="C53" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D53" s="106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E53" s="107" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F53" s="106" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G53" s="107" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H53" s="106" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I53" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J53" s="106" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K53" s="107" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="L53" s="106">
         <v>1</v>
@@ -5485,7 +5481,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P53" s="108">
         <v>1.4E-3</v>
@@ -5503,31 +5499,31 @@
         <v>45</v>
       </c>
       <c r="C54" s="101" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D54" s="102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E54" s="103" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F54" s="102" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G54" s="103" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H54" s="102" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I54" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J54" s="102" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="K54" s="103" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="L54" s="102">
         <v>1</v>
@@ -5540,7 +5536,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P54" s="95">
         <v>1.6000000000000001E-3</v>
@@ -5558,31 +5554,31 @@
         <v>46</v>
       </c>
       <c r="C55" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D55" s="106" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E55" s="107" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F55" s="106" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G55" s="107" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H55" s="106" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I55" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J55" s="106" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="K55" s="107" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="L55" s="106">
         <v>2</v>
@@ -5595,7 +5591,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P55" s="108">
         <v>1.4E-3</v>
@@ -5613,31 +5609,31 @@
         <v>47</v>
       </c>
       <c r="C56" s="101" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D56" s="102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E56" s="103" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F56" s="102" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G56" s="103" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H56" s="102" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I56" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J56" s="102" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="K56" s="103" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="L56" s="102">
         <v>4</v>
@@ -5650,7 +5646,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P56" s="95">
         <v>1.2999999999999999E-3</v>
@@ -5661,58 +5657,58 @@
       </c>
       <c r="R56" s="95"/>
     </row>
-    <row r="57" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="C57" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D57" s="106" t="s">
-        <v>41</v>
-      </c>
-      <c r="E57" s="107" t="s">
-        <v>110</v>
+        <v>477</v>
+      </c>
+      <c r="E57" s="39" t="s">
+        <v>478</v>
       </c>
       <c r="F57" s="106" t="s">
-        <v>167</v>
-      </c>
-      <c r="G57" s="119" t="s">
-        <v>329</v>
+        <v>164</v>
+      </c>
+      <c r="G57" s="106" t="s">
+        <v>479</v>
       </c>
       <c r="H57" s="106" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I57" s="106" t="s">
-        <v>391</v>
+        <v>310</v>
       </c>
       <c r="J57" s="106" t="s">
-        <v>392</v>
+        <v>480</v>
       </c>
       <c r="K57" s="107" t="s">
-        <v>289</v>
+        <v>481</v>
       </c>
       <c r="L57" s="106">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M57" s="108">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N57" s="108">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="O57" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P57" s="108">
-        <v>6.4500000000000002E-2</v>
+        <v>2.9100000000000001E-2</v>
       </c>
       <c r="Q57" s="108">
         <f t="shared" ref="Q57" si="45">P57*N57</f>
-        <v>5.8049999999999997</v>
+        <v>1.3095000000000001</v>
       </c>
       <c r="R57" s="108"/>
     </row>
@@ -5723,31 +5719,31 @@
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="L58" s="37">
         <v>8</v>
@@ -5760,7 +5756,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="79" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P58" s="37">
         <v>1.1000000000000001E-3</v>
@@ -5778,31 +5774,31 @@
         <v>50</v>
       </c>
       <c r="C59" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D59" s="106" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E59" s="107" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F59" s="106" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G59" s="107" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H59" s="106" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I59" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J59" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K59" s="107" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="L59" s="106">
         <v>1</v>
@@ -5815,7 +5811,7 @@
         <v>30</v>
       </c>
       <c r="O59" s="109" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="P59" s="108">
         <v>1.8589999999999999E-2</v>
@@ -5833,31 +5829,31 @@
         <v>51</v>
       </c>
       <c r="C60" s="101" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D60" s="102" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F60" s="102" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G60" s="103" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H60" s="102" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I60" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J60" s="102" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K60" s="103" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="L60" s="102">
         <v>1</v>
@@ -5870,7 +5866,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P60" s="95">
         <v>1.4E-3</v>
@@ -5888,31 +5884,31 @@
         <v>52</v>
       </c>
       <c r="C61" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D61" s="106" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E61" s="107" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F61" s="106" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G61" s="107" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H61" s="106" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I61" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J61" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K61" s="107" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="L61" s="106">
         <v>1</v>
@@ -5925,7 +5921,7 @@
         <v>50</v>
       </c>
       <c r="O61" s="109" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="P61" s="108">
         <v>4.6699999999999997E-3</v>
@@ -5943,31 +5939,31 @@
         <v>53</v>
       </c>
       <c r="C62" s="101" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D62" s="102" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E62" s="103" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F62" s="102" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G62" s="103" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H62" s="102" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I62" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J62" s="102" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="K62" s="103" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="L62" s="102">
         <v>1</v>
@@ -5980,7 +5976,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P62" s="95">
         <v>1.1999999999999999E-3</v>
@@ -5998,31 +5994,31 @@
         <v>54</v>
       </c>
       <c r="C63" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D63" s="106" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E63" s="107" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F63" s="106" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G63" s="107" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H63" s="106" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I63" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J63" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K63" s="107" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="L63" s="106">
         <v>1</v>
@@ -6035,7 +6031,7 @@
         <v>50</v>
       </c>
       <c r="O63" s="109" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="P63" s="108">
         <v>1.11E-2</v>
@@ -6053,31 +6049,31 @@
         <v>55</v>
       </c>
       <c r="C64" s="101" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D64" s="102" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E64" s="103" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F64" s="102" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G64" s="103" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H64" s="102" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I64" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J64" s="102" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="K64" s="103" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="L64" s="102">
         <v>1</v>
@@ -6090,7 +6086,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P64" s="95">
         <v>2.0999999999999999E-3</v>
@@ -6108,31 +6104,31 @@
         <v>56</v>
       </c>
       <c r="C65" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D65" s="106" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E65" s="107" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F65" s="106" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G65" s="107" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H65" s="106" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I65" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J65" s="106" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="K65" s="107" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="L65" s="106">
         <v>1</v>
@@ -6145,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P65" s="108">
         <v>1.6000000000000001E-3</v>
@@ -6163,31 +6159,31 @@
         <v>57</v>
       </c>
       <c r="C66" s="101" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D66" s="102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E66" s="103" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F66" s="102" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G66" s="118" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H66" s="102" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I66" s="102" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="J66" s="102" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="K66" s="103" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="L66" s="102">
         <v>1</v>
@@ -6200,7 +6196,7 @@
         <v>50</v>
       </c>
       <c r="O66" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P66" s="95">
         <v>6.8999999999999999E-3</v>
@@ -6218,31 +6214,31 @@
         <v>58</v>
       </c>
       <c r="C67" s="105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D67" s="106" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="E67" s="107" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F67" s="106" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G67" s="107" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H67" s="106" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I67" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J67" s="106" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="K67" s="107" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="L67" s="106">
         <v>2</v>
@@ -6255,7 +6251,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P67" s="108">
         <v>1.1000000000000001E-3</v>
@@ -6273,31 +6269,31 @@
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L68" s="37">
         <v>2</v>
@@ -6310,7 +6306,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P68" s="41">
         <v>1.5E-3</v>
@@ -6328,29 +6324,29 @@
         <v>60</v>
       </c>
       <c r="C69" s="59" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D69" s="86" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F69" s="39" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G69" s="40" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H69" s="39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I69" s="39"/>
       <c r="J69" s="39" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="L69" s="39">
         <v>1</v>
@@ -6363,7 +6359,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P69" s="42">
         <v>1.5E-3</v>
@@ -6381,31 +6377,31 @@
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="L70" s="37">
         <v>2</v>
@@ -6418,7 +6414,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P70" s="41">
         <v>1.5E-3</v>
@@ -6436,31 +6432,31 @@
         <v>62</v>
       </c>
       <c r="C71" s="59" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F71" s="39" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G71" s="40" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H71" s="39" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I71" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J71" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K71" s="40" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="L71" s="39">
         <v>1</v>
@@ -6473,7 +6469,7 @@
         <v>25</v>
       </c>
       <c r="O71" s="64" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="P71" s="42">
         <v>8.5400000000000004E-2</v>
@@ -6491,31 +6487,31 @@
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F72" s="85" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="L72" s="37">
         <v>1</v>
@@ -6528,7 +6524,7 @@
         <v>50</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P72" s="41">
         <v>3.8E-3</v>
@@ -6546,31 +6542,31 @@
         <v>64</v>
       </c>
       <c r="C73" s="59" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D73" s="39" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F73" s="39" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H73" s="39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I73" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J73" s="39" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="K73" s="40" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="L73" s="39">
         <v>6</v>
@@ -6583,7 +6579,7 @@
         <v>200</v>
       </c>
       <c r="O73" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P73" s="42">
         <v>1.1999999999999999E-3</v>
@@ -6601,31 +6597,31 @@
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E74" s="38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J74" s="37" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="L74" s="37">
         <v>1</v>
@@ -6638,7 +6634,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P74" s="41">
         <v>1E-3</v>
@@ -6656,31 +6652,31 @@
         <v>66</v>
       </c>
       <c r="C75" s="59" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D75" s="39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F75" s="39" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H75" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I75" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J75" s="39" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="K75" s="40" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L75" s="39">
         <v>1</v>
@@ -6693,7 +6689,7 @@
         <v>50</v>
       </c>
       <c r="O75" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P75" s="42">
         <v>4.3E-3</v>
@@ -6711,31 +6707,31 @@
         <v>67</v>
       </c>
       <c r="C76" s="96" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D76" s="97" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E76" s="98" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F76" s="97" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G76" s="98" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H76" s="97" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I76" s="97" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J76" s="97" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="K76" s="98" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="L76" s="97">
         <v>4</v>
@@ -6748,7 +6744,7 @@
         <v>100</v>
       </c>
       <c r="O76" s="99" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P76" s="65">
         <v>1.1999999999999999E-3</v>
@@ -6758,7 +6754,7 @@
         <v>0.12</v>
       </c>
       <c r="R76" s="65" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6768,31 +6764,31 @@
         <v>68</v>
       </c>
       <c r="C77" s="96" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D77" s="122" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E77" s="98" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F77" s="97" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G77" s="98" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H77" s="97" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I77" s="97" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J77" s="97" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K77" s="98" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L77" s="97">
         <v>11</v>
@@ -6812,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="65" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6822,31 +6818,31 @@
         <v>69</v>
       </c>
       <c r="C78" s="101" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D78" s="102" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E78" s="103" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F78" s="102" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G78" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H78" s="102" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I78" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J78" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K78" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L78" s="102">
         <v>1</v>
@@ -6860,7 +6856,7 @@
         <v>22</v>
       </c>
       <c r="O78" s="104" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="P78" s="95">
         <v>1.42</v>
@@ -6877,31 +6873,31 @@
         <v>70</v>
       </c>
       <c r="C79" s="105" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D79" s="106" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E79" s="107" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F79" s="106" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G79" s="107">
         <v>750314597</v>
       </c>
       <c r="H79" s="106" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I79" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J79" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K79" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L79" s="106">
         <v>1</v>
@@ -6914,7 +6910,7 @@
         <v>21</v>
       </c>
       <c r="O79" s="109" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="P79" s="108">
         <v>3.81</v>
@@ -6932,31 +6928,31 @@
         <v>71</v>
       </c>
       <c r="C80" s="101" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D80" s="102" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E80" s="103" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F80" s="102" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G80" s="103" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H80" s="102" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I80" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J80" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K80" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L80" s="102">
         <v>1</v>
@@ -6969,7 +6965,7 @@
         <v>21</v>
       </c>
       <c r="O80" s="104" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="P80" s="95">
         <v>2.48</v>
@@ -6987,31 +6983,31 @@
         <v>72</v>
       </c>
       <c r="C81" s="105" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D81" s="106" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E81" s="107" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F81" s="106" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G81" s="119" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H81" s="106" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I81" s="106" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="J81" s="106" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="K81" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L81" s="106">
         <v>1</v>
@@ -7024,7 +7020,7 @@
         <v>21</v>
       </c>
       <c r="O81" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P81" s="108">
         <v>1.3939999999999999</v>
@@ -7042,31 +7038,31 @@
         <v>73</v>
       </c>
       <c r="C82" s="101" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D82" s="102" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E82" s="103" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F82" s="102" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G82" s="118" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H82" s="102" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I82" s="102" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="J82" s="102" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="K82" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L82" s="102">
         <v>1</v>
@@ -7079,7 +7075,7 @@
         <v>21</v>
       </c>
       <c r="O82" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P82" s="95">
         <v>0.69430000000000003</v>
@@ -7097,31 +7093,31 @@
         <v>74</v>
       </c>
       <c r="C83" s="105" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D83" s="106" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E83" s="107" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F83" s="106" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G83" s="107" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H83" s="106" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I83" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J83" s="106" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K83" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L83" s="106">
         <v>1</v>
@@ -7134,7 +7130,7 @@
         <v>21</v>
       </c>
       <c r="O83" s="109" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="P83" s="108">
         <v>3.637</v>
@@ -7152,31 +7148,31 @@
         <v>75</v>
       </c>
       <c r="C84" s="101" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D84" s="102" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E84" s="103" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F84" s="102" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G84" s="103" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H84" s="102" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I84" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J84" s="102" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="K84" s="103" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L84" s="102">
         <v>1</v>
@@ -7189,7 +7185,7 @@
         <v>21</v>
       </c>
       <c r="O84" s="104" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P84" s="95">
         <v>0.43280000000000002</v>
@@ -7207,31 +7203,31 @@
         <v>76</v>
       </c>
       <c r="C85" s="70" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D85" s="71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E85" s="72" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F85" s="71" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G85" s="72" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H85" s="71" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I85" s="71" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J85" s="71" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="K85" s="72" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L85" s="71">
         <v>1</v>
@@ -7244,7 +7240,7 @@
         <v>21</v>
       </c>
       <c r="O85" s="74" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P85" s="73">
         <v>7.4638</v>
@@ -7254,7 +7250,7 @@
         <v>156.7398</v>
       </c>
       <c r="R85" s="73" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="U85" s="114"/>
     </row>
@@ -7265,31 +7261,31 @@
         <v>77</v>
       </c>
       <c r="C86" s="101" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D86" s="102" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E86" s="103" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F86" s="102" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G86" s="103" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H86" s="102" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I86" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J86" s="102" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K86" s="112" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L86" s="102">
         <v>1</v>
@@ -7302,7 +7298,7 @@
         <v>21</v>
       </c>
       <c r="O86" s="104" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="P86" s="95">
         <v>2.6459999999999999</v>
@@ -7320,31 +7316,31 @@
         <v>78</v>
       </c>
       <c r="C87" s="105" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D87" s="106" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="E87" s="107" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F87" s="106" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G87" s="119" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H87" s="106" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I87" s="106" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="J87" s="106" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="K87" s="107" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L87" s="113">
         <v>2</v>
@@ -7357,7 +7353,7 @@
         <v>42</v>
       </c>
       <c r="O87" s="109" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P87" s="108">
         <v>2.2974000000000001</v>
@@ -7375,31 +7371,31 @@
         <v>79</v>
       </c>
       <c r="C88" s="60" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E88" s="38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I88" s="62" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J88" s="62" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="K88" s="38" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L88" s="37">
         <v>1</v>
@@ -7412,7 +7408,7 @@
         <v>21</v>
       </c>
       <c r="O88" s="63" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P88" s="41">
         <v>0.39140000000000003</v>
@@ -7430,31 +7426,31 @@
         <v>80</v>
       </c>
       <c r="C89" s="59" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G89" s="121" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H89" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I89" s="39" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="J89" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K89" s="40" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L89" s="39">
         <v>1</v>
@@ -7467,7 +7463,7 @@
         <v>21</v>
       </c>
       <c r="O89" s="64" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="P89" s="42">
         <v>3.532</v>
@@ -7485,28 +7481,28 @@
         <v>81</v>
       </c>
       <c r="C90" s="59" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G90" s="40" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="H90" s="39" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="I90" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J90" s="39" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="K90" s="40"/>
       <c r="L90" s="39">
@@ -7520,7 +7516,7 @@
         <v>25</v>
       </c>
       <c r="O90" s="64" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="P90" s="42">
         <v>8.8999999999999996E-2</v>
@@ -7549,12 +7545,12 @@
       <c r="M91" s="36"/>
       <c r="N91" s="36"/>
       <c r="O91" s="68" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="P91" s="66"/>
       <c r="Q91" s="66">
         <f>SUM(Q10:Q90)</f>
-        <v>970.9928000000001</v>
+        <v>966.49730000000011</v>
       </c>
       <c r="R91" s="44"/>
     </row>
@@ -7576,12 +7572,12 @@
       <c r="M92" s="9"/>
       <c r="N92" s="9"/>
       <c r="O92" s="69" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="P92" s="67"/>
       <c r="Q92" s="67">
         <f>Q91/20</f>
-        <v>48.549640000000004</v>
+        <v>48.324865000000003</v>
       </c>
       <c r="R92" s="45"/>
     </row>
@@ -7591,84 +7587,84 @@
     <mergeCell ref="R3:R8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="O12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="O13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="O14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="O16" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="O18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="O20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="O21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="O22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="O24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="O25" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="O26" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="O27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="O28" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="O29" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="O30" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="O31" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="O32" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="O33" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="O34" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="O35" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="O36" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="O37" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="O38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="O39" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="O40" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="O41" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="O43" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="O44" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="O45" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="O46" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="O48" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="O51" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="O52" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="O53" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="O54" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="O55" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="O56" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="O57" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="O69" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="O59" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="O60" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="O61" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="O62" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="O63" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="O64" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="O65" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="O66" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="O67" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="O68" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="O70" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="O71" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="O72" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="O75" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="O76" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="O73" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="O79" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="O80" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="O81" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="O82" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="O83" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="O84" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="O85" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="O86" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="O87" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="O89" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="O88" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="O58" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="O47" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="O90" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="O42" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="O10" r:id="rId76" xr:uid="{5D88A11D-3624-47E9-BBD7-2366F8BA7980}"/>
-    <hyperlink ref="O50" r:id="rId77" xr:uid="{3AF3C69B-110E-4BD5-B2CB-21B12CDADF8A}"/>
-    <hyperlink ref="O78" r:id="rId78" xr:uid="{D0B601F1-C091-44E0-B215-033F4B4B50D1}"/>
+    <hyperlink ref="O11" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O17" r:id="rId7"/>
+    <hyperlink ref="O18" r:id="rId8"/>
+    <hyperlink ref="O19" r:id="rId9"/>
+    <hyperlink ref="O20" r:id="rId10"/>
+    <hyperlink ref="O21" r:id="rId11"/>
+    <hyperlink ref="O22" r:id="rId12"/>
+    <hyperlink ref="O23" r:id="rId13"/>
+    <hyperlink ref="O24" r:id="rId14"/>
+    <hyperlink ref="O25" r:id="rId15"/>
+    <hyperlink ref="O26" r:id="rId16"/>
+    <hyperlink ref="O27" r:id="rId17"/>
+    <hyperlink ref="O28" r:id="rId18"/>
+    <hyperlink ref="O29" r:id="rId19"/>
+    <hyperlink ref="O30" r:id="rId20"/>
+    <hyperlink ref="O31" r:id="rId21"/>
+    <hyperlink ref="O32" r:id="rId22"/>
+    <hyperlink ref="O33" r:id="rId23"/>
+    <hyperlink ref="O34" r:id="rId24"/>
+    <hyperlink ref="O35" r:id="rId25"/>
+    <hyperlink ref="O36" r:id="rId26"/>
+    <hyperlink ref="O37" r:id="rId27"/>
+    <hyperlink ref="O38" r:id="rId28"/>
+    <hyperlink ref="O39" r:id="rId29"/>
+    <hyperlink ref="O40" r:id="rId30"/>
+    <hyperlink ref="O41" r:id="rId31"/>
+    <hyperlink ref="O43" r:id="rId32"/>
+    <hyperlink ref="O44" r:id="rId33"/>
+    <hyperlink ref="O45" r:id="rId34"/>
+    <hyperlink ref="O46" r:id="rId35"/>
+    <hyperlink ref="O48" r:id="rId36"/>
+    <hyperlink ref="O51" r:id="rId37"/>
+    <hyperlink ref="O52" r:id="rId38"/>
+    <hyperlink ref="O53" r:id="rId39"/>
+    <hyperlink ref="O54" r:id="rId40"/>
+    <hyperlink ref="O55" r:id="rId41"/>
+    <hyperlink ref="O56" r:id="rId42"/>
+    <hyperlink ref="O69" r:id="rId43"/>
+    <hyperlink ref="O59" r:id="rId44"/>
+    <hyperlink ref="O60" r:id="rId45"/>
+    <hyperlink ref="O61" r:id="rId46"/>
+    <hyperlink ref="O62" r:id="rId47"/>
+    <hyperlink ref="O63" r:id="rId48"/>
+    <hyperlink ref="O64" r:id="rId49"/>
+    <hyperlink ref="O65" r:id="rId50"/>
+    <hyperlink ref="O66" r:id="rId51"/>
+    <hyperlink ref="O67" r:id="rId52"/>
+    <hyperlink ref="O68" r:id="rId53"/>
+    <hyperlink ref="O70" r:id="rId54"/>
+    <hyperlink ref="O71" r:id="rId55"/>
+    <hyperlink ref="O72" r:id="rId56"/>
+    <hyperlink ref="O75" r:id="rId57"/>
+    <hyperlink ref="O76" r:id="rId58"/>
+    <hyperlink ref="O73" r:id="rId59"/>
+    <hyperlink ref="O79" r:id="rId60"/>
+    <hyperlink ref="O80" r:id="rId61"/>
+    <hyperlink ref="O81" r:id="rId62"/>
+    <hyperlink ref="O82" r:id="rId63"/>
+    <hyperlink ref="O83" r:id="rId64"/>
+    <hyperlink ref="O84" r:id="rId65"/>
+    <hyperlink ref="O85" r:id="rId66"/>
+    <hyperlink ref="O86" r:id="rId67"/>
+    <hyperlink ref="O87" r:id="rId68"/>
+    <hyperlink ref="O89" r:id="rId69"/>
+    <hyperlink ref="O88" r:id="rId70"/>
+    <hyperlink ref="O58" r:id="rId71"/>
+    <hyperlink ref="O47" r:id="rId72"/>
+    <hyperlink ref="O90" r:id="rId73"/>
+    <hyperlink ref="O42" r:id="rId74"/>
+    <hyperlink ref="O10" r:id="rId75"/>
+    <hyperlink ref="O50" r:id="rId76"/>
+    <hyperlink ref="O78" r:id="rId77"/>
+    <hyperlink ref="O57" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId79"/>
